--- a/succession.xlsx
+++ b/succession.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF871B80-3997-4DF4-A055-9DFCE31C65E4}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2237006A-4AFC-4CB6-A038-9920F142ADA1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="กรอกข้อมูล" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$73</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="275">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -782,15 +782,6 @@
   </si>
   <si>
     <t>28/11/1980</t>
-  </si>
-  <si>
-    <t>สุวิกา บุตรศรี</t>
-  </si>
-  <si>
-    <t>Support Manager - Finance and Account</t>
-  </si>
-  <si>
-    <t>29/11/1994</t>
   </si>
   <si>
     <t>อารีรัตน์ เดชสุขมนัส</t>
@@ -1205,43 +1196,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1252,6 +1219,30 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1336,6 +1327,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1527,727 +1522,693 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="30" t="s">
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="30"/>
+      <c r="G26" s="33"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="30" t="s">
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="30"/>
+      <c r="G27" s="33"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="30" t="s">
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="30"/>
+      <c r="G28" s="33"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="29" t="s">
+      <c r="B29" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="30" t="s">
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="30"/>
+      <c r="G29" s="33"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="30" t="s">
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="30"/>
+      <c r="G30" s="33"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="27" t="s">
+      <c r="C33" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="27" t="s">
+      <c r="C35" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="27" t="s">
+      <c r="C38" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="27" t="s">
+      <c r="C39" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="27" t="s">
+      <c r="C40" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="27" t="s">
+      <c r="C41" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="27" t="s">
+      <c r="C42" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="27" t="s">
+      <c r="C45" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="27" t="s">
+      <c r="C46" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="27" t="s">
+      <c r="C47" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="27" t="s">
+      <c r="C48" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="27"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="27"/>
-      <c r="G48" s="27"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="27" t="s">
+      <c r="C49" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="25"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="24" t="s">
+      <c r="B51" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="24"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="23"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="31" t="s">
+      <c r="B52" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="31"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="32" t="s">
+      <c r="B53" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
-      <c r="E53" s="32"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="24" t="s">
+      <c r="B55" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="24"/>
-      <c r="D55" s="24"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="23"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="33" t="s">
+      <c r="B56" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="33"/>
-      <c r="D56" s="33"/>
-      <c r="E56" s="27" t="s">
+      <c r="C56" s="24"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="27"/>
-      <c r="G56" s="27"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="34" t="s">
+      <c r="B57" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="34"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="27" t="s">
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="35" t="s">
+      <c r="B58" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="35"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="27" t="s">
+      <c r="C58" s="27"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="36" t="s">
+      <c r="B59" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="36"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="27" t="s">
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
+      <c r="F59" s="25"/>
+      <c r="G59" s="25"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="24" t="s">
+      <c r="B62" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="24"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
+      <c r="C62" s="23"/>
+      <c r="D62" s="23"/>
+      <c r="E62" s="23"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="23"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="25" t="s">
+      <c r="B63" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="25"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="21"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="21" t="s">
+      <c r="B64" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="21" t="s">
+      <c r="B65" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="21" t="s">
+      <c r="B66" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="21" t="s">
+      <c r="B67" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-      <c r="G67" s="21"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="24" t="s">
+      <c r="B69" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="24"/>
-      <c r="D69" s="24"/>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="23"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="23"/>
+      <c r="G69" s="23"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="25" t="s">
+      <c r="B70" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="25"/>
-      <c r="D70" s="25"/>
-      <c r="E70" s="25"/>
-      <c r="F70" s="25"/>
-      <c r="G70" s="25"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="25" t="s">
+      <c r="B71" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="25"/>
-      <c r="D71" s="25"/>
-      <c r="E71" s="25"/>
-      <c r="F71" s="25"/>
-      <c r="G71" s="25"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="25" t="s">
+      <c r="B72" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="25"/>
-      <c r="D72" s="25"/>
-      <c r="E72" s="25"/>
-      <c r="F72" s="25"/>
-      <c r="G72" s="25"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="25" t="s">
+      <c r="B73" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="25"/>
-      <c r="D73" s="25"/>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="25" t="s">
+      <c r="B74" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="25"/>
-      <c r="D74" s="25"/>
-      <c r="E74" s="25"/>
-      <c r="F74" s="25"/>
-      <c r="G74" s="25"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="25" t="s">
+      <c r="B75" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="25"/>
-      <c r="D75" s="25"/>
-      <c r="E75" s="25"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="25"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="21"/>
+      <c r="G75" s="21"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="25"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="25"/>
-      <c r="E76" s="25"/>
-      <c r="F76" s="25"/>
-      <c r="G76" s="25"/>
+      <c r="B76" s="21"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="21"/>
+      <c r="G76" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B15:G15"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="B17:G17"/>
@@ -2261,18 +2222,52 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2281,7 +2276,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S74"/>
+  <dimension ref="A1:S73"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -4644,7 +4639,7 @@
       </c>
       <c r="F46" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G46" s="11">
         <f t="shared" ca="1" si="0"/>
@@ -4869,11 +4864,11 @@
         <v>5</v>
       </c>
       <c r="L50" s="13">
-        <f t="shared" ref="L50:L73" si="6">IF(OR(I50="",J50="",K50="",G50=""),"",ROUND(G50*0.2+I50*0.3+J50*0.3+K50*0.2,2))</f>
+        <f t="shared" ref="L50:L72" si="6">IF(OR(I50="",J50="",K50="",G50=""),"",ROUND(G50*0.2+I50*0.3+J50*0.3+K50*0.2,2))</f>
         <v>4.0999999999999996</v>
       </c>
       <c r="M50" s="13" t="str">
-        <f t="shared" ref="M50:M73" si="7">IF(OR(H50="",L50=""),"",IF(AND(H50&gt;=4,L50&gt;=3.5),"High Impact + High Risk",IF(AND(H50&gt;=4,L50&lt;3.5),"High Impact + Low Risk",IF(AND(H50&lt;4,L50&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+        <f t="shared" ref="M50:M72" si="7">IF(OR(H50="",L50=""),"",IF(AND(H50&gt;=4,L50&gt;=3.5),"High Impact + High Risk",IF(AND(H50&gt;=4,L50&lt;3.5),"High Impact + Low Risk",IF(AND(H50&lt;4,L50&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
         <v>High Impact + High Risk</v>
       </c>
       <c r="N50" s="9"/>
@@ -4881,7 +4876,7 @@
       <c r="P50" s="9"/>
       <c r="Q50" s="9"/>
       <c r="S50" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="51" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -4931,7 +4926,7 @@
       <c r="P51" s="15"/>
       <c r="Q51" s="15"/>
       <c r="S51" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="52" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -4981,7 +4976,7 @@
       <c r="P52" s="9"/>
       <c r="Q52" s="9"/>
       <c r="S52" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="53" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5031,7 +5026,7 @@
       <c r="P53" s="15"/>
       <c r="Q53" s="15"/>
       <c r="S53" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="54" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5081,7 +5076,7 @@
       <c r="P54" s="9"/>
       <c r="Q54" s="9"/>
       <c r="S54" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="55" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5131,7 +5126,7 @@
       <c r="P55" s="15"/>
       <c r="Q55" s="15"/>
       <c r="S55" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="56" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5181,7 +5176,7 @@
       <c r="P56" s="9"/>
       <c r="Q56" s="9"/>
       <c r="S56" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="57" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5231,7 +5226,7 @@
       <c r="P57" s="15"/>
       <c r="Q57" s="15"/>
       <c r="S57" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="58" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5281,7 +5276,7 @@
       <c r="P58" s="9"/>
       <c r="Q58" s="9"/>
       <c r="S58" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="59" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5331,7 +5326,7 @@
       <c r="P59" s="15"/>
       <c r="Q59" s="15"/>
       <c r="S59" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="60" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5381,7 +5376,7 @@
       <c r="P60" s="9"/>
       <c r="Q60" s="9"/>
       <c r="S60" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="61" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5431,7 +5426,7 @@
       <c r="P61" s="15"/>
       <c r="Q61" s="15"/>
       <c r="S61" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="62" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5481,7 +5476,7 @@
       <c r="P62" s="9"/>
       <c r="Q62" s="9"/>
       <c r="S62" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="63" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5531,7 +5526,7 @@
       <c r="P63" s="15"/>
       <c r="Q63" s="15"/>
       <c r="S63" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="64" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5581,7 +5576,7 @@
       <c r="P64" s="9"/>
       <c r="Q64" s="9"/>
       <c r="S64" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="65" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5631,483 +5626,433 @@
       <c r="P65" s="15"/>
       <c r="Q65" s="15"/>
       <c r="S65" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="66" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="7">
-        <v>168029</v>
-      </c>
-      <c r="B66" s="9" t="s">
+      <c r="A66" s="8">
+        <v>337004</v>
+      </c>
+      <c r="B66" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C66" s="9" t="s">
+      <c r="C66" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="D66" s="9" t="s">
+      <c r="D66" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E66" s="10" t="s">
+      <c r="E66" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="F66" s="11">
-        <v>32</v>
-      </c>
-      <c r="G66" s="11">
-        <v>1</v>
+      <c r="F66" s="17">
+        <v>55</v>
+      </c>
+      <c r="G66" s="17">
+        <v>3</v>
       </c>
       <c r="H66" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I66" s="12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J66" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K66" s="12">
         <v>4</v>
       </c>
-      <c r="L66" s="13">
+      <c r="L66" s="18">
+        <f t="shared" si="6"/>
+        <v>2.6</v>
+      </c>
+      <c r="M66" s="18" t="str">
+        <f t="shared" si="7"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N66" s="15"/>
+      <c r="O66" s="15"/>
+      <c r="P66" s="15"/>
+      <c r="Q66" s="15"/>
+      <c r="S66" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="7">
+        <v>267085</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F67" s="11">
+        <v>30</v>
+      </c>
+      <c r="G67" s="11">
+        <v>1</v>
+      </c>
+      <c r="H67" s="12">
+        <v>3</v>
+      </c>
+      <c r="I67" s="12">
+        <v>4</v>
+      </c>
+      <c r="J67" s="12">
+        <v>3</v>
+      </c>
+      <c r="K67" s="12">
+        <v>3</v>
+      </c>
+      <c r="L67" s="13">
+        <f t="shared" si="6"/>
+        <v>2.9</v>
+      </c>
+      <c r="M67" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N67" s="9"/>
+      <c r="O67" s="9"/>
+      <c r="P67" s="9"/>
+      <c r="Q67" s="9"/>
+      <c r="S67" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="8">
+        <v>268044</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="F68" s="17">
+        <v>28</v>
+      </c>
+      <c r="G68" s="17">
+        <v>1</v>
+      </c>
+      <c r="H68" s="12">
+        <v>3</v>
+      </c>
+      <c r="I68" s="12">
+        <v>4</v>
+      </c>
+      <c r="J68" s="12">
+        <v>3</v>
+      </c>
+      <c r="K68" s="12">
+        <v>3</v>
+      </c>
+      <c r="L68" s="18">
+        <f t="shared" si="6"/>
+        <v>2.9</v>
+      </c>
+      <c r="M68" s="18" t="str">
+        <f t="shared" si="7"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N68" s="15"/>
+      <c r="O68" s="15"/>
+      <c r="P68" s="15"/>
+      <c r="Q68" s="15"/>
+      <c r="S68" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="7">
+        <v>368004</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="F69" s="11">
+        <v>59</v>
+      </c>
+      <c r="G69" s="11">
+        <v>4</v>
+      </c>
+      <c r="H69" s="12">
+        <v>4</v>
+      </c>
+      <c r="I69" s="12">
+        <v>3</v>
+      </c>
+      <c r="J69" s="12">
+        <v>4</v>
+      </c>
+      <c r="K69" s="12">
+        <v>4</v>
+      </c>
+      <c r="L69" s="13">
         <f t="shared" si="6"/>
         <v>3.7</v>
       </c>
-      <c r="M66" s="13" t="str">
+      <c r="M69" s="13" t="str">
         <f t="shared" si="7"/>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N66" s="9"/>
-      <c r="O66" s="9"/>
-      <c r="P66" s="9"/>
-      <c r="Q66" s="9"/>
-      <c r="S66" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="8">
-        <v>337004</v>
-      </c>
-      <c r="B67" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="C67" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="D67" s="15" t="s">
+      <c r="N69" s="9"/>
+      <c r="O69" s="9"/>
+      <c r="P69" s="9"/>
+      <c r="Q69" s="9"/>
+      <c r="S69" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="8">
+        <v>269040</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="D70" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E67" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="F67" s="17">
-        <v>55</v>
-      </c>
-      <c r="G67" s="17">
-        <v>3</v>
-      </c>
-      <c r="H67" s="12">
-        <v>3</v>
-      </c>
-      <c r="I67" s="12">
-        <v>1</v>
-      </c>
-      <c r="J67" s="12">
-        <v>3</v>
-      </c>
-      <c r="K67" s="12">
-        <v>4</v>
-      </c>
-      <c r="L67" s="18">
-        <f t="shared" si="6"/>
-        <v>2.6</v>
-      </c>
-      <c r="M67" s="18" t="str">
-        <f t="shared" si="7"/>
-        <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N67" s="15"/>
-      <c r="O67" s="15"/>
-      <c r="P67" s="15"/>
-      <c r="Q67" s="15"/>
-      <c r="S67" s="8" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="7">
-        <v>267085</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="F68" s="11">
-        <v>30</v>
-      </c>
-      <c r="G68" s="11">
-        <v>1</v>
-      </c>
-      <c r="H68" s="12">
-        <v>3</v>
-      </c>
-      <c r="I68" s="12">
-        <v>4</v>
-      </c>
-      <c r="J68" s="12">
-        <v>3</v>
-      </c>
-      <c r="K68" s="12">
-        <v>3</v>
-      </c>
-      <c r="L68" s="13">
+      <c r="E70" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="F70" s="17">
+        <v>45</v>
+      </c>
+      <c r="G70" s="17">
+        <v>1</v>
+      </c>
+      <c r="H70" s="12">
+        <v>4</v>
+      </c>
+      <c r="I70" s="12">
+        <v>3</v>
+      </c>
+      <c r="J70" s="12">
+        <v>4</v>
+      </c>
+      <c r="K70" s="12">
+        <v>3</v>
+      </c>
+      <c r="L70" s="18">
         <f t="shared" si="6"/>
         <v>2.9</v>
       </c>
-      <c r="M68" s="13" t="str">
+      <c r="M70" s="18" t="str">
         <f t="shared" si="7"/>
-        <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N68" s="9"/>
-      <c r="O68" s="9"/>
-      <c r="P68" s="9"/>
-      <c r="Q68" s="9"/>
-      <c r="S68" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="8">
-        <v>268044</v>
-      </c>
-      <c r="B69" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="C69" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="D69" s="15" t="s">
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N70" s="15"/>
+      <c r="O70" s="15"/>
+      <c r="P70" s="15"/>
+      <c r="Q70" s="15"/>
+      <c r="S70" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="D71" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E69" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="F69" s="17">
-        <v>28</v>
-      </c>
-      <c r="G69" s="17">
-        <v>1</v>
-      </c>
-      <c r="H69" s="12">
-        <v>3</v>
-      </c>
-      <c r="I69" s="12">
-        <v>4</v>
-      </c>
-      <c r="J69" s="12">
-        <v>3</v>
-      </c>
-      <c r="K69" s="12">
-        <v>3</v>
-      </c>
-      <c r="L69" s="18">
+      <c r="E71" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="F71" s="11">
+        <v>55</v>
+      </c>
+      <c r="G71" s="11">
+        <v>3</v>
+      </c>
+      <c r="H71" s="12">
+        <v>4</v>
+      </c>
+      <c r="I71" s="12">
+        <v>4</v>
+      </c>
+      <c r="J71" s="12">
+        <v>4</v>
+      </c>
+      <c r="K71" s="12">
+        <v>4</v>
+      </c>
+      <c r="L71" s="13">
         <f t="shared" si="6"/>
-        <v>2.9</v>
-      </c>
-      <c r="M69" s="18" t="str">
-        <f t="shared" si="7"/>
-        <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N69" s="15"/>
-      <c r="O69" s="15"/>
-      <c r="P69" s="15"/>
-      <c r="Q69" s="15"/>
-      <c r="S69" s="8" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="7">
-        <v>368004</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="F70" s="11">
-        <v>59</v>
-      </c>
-      <c r="G70" s="11">
-        <v>4</v>
-      </c>
-      <c r="H70" s="12">
-        <v>4</v>
-      </c>
-      <c r="I70" s="12">
-        <v>3</v>
-      </c>
-      <c r="J70" s="12">
-        <v>4</v>
-      </c>
-      <c r="K70" s="12">
-        <v>4</v>
-      </c>
-      <c r="L70" s="13">
-        <f t="shared" si="6"/>
-        <v>3.7</v>
-      </c>
-      <c r="M70" s="13" t="str">
+        <v>3.8</v>
+      </c>
+      <c r="M71" s="13" t="str">
         <f t="shared" si="7"/>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N70" s="9"/>
-      <c r="O70" s="9"/>
-      <c r="P70" s="9"/>
-      <c r="Q70" s="9"/>
-      <c r="S70" s="7" t="s">
+      <c r="N71" s="9"/>
+      <c r="O71" s="9"/>
+      <c r="P71" s="9"/>
+      <c r="Q71" s="9"/>
+      <c r="S71" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="7">
+        <v>168016</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="C72" s="9" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="71" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="8">
-        <v>269040</v>
-      </c>
-      <c r="B71" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="C71" s="15" t="s">
-        <v>263</v>
-      </c>
-      <c r="D71" s="15" t="s">
+      <c r="D72" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E71" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="F71" s="17">
-        <v>45</v>
-      </c>
-      <c r="G71" s="17">
-        <v>1</v>
-      </c>
-      <c r="H71" s="12">
-        <v>4</v>
-      </c>
-      <c r="I71" s="12">
-        <v>3</v>
-      </c>
-      <c r="J71" s="12">
-        <v>4</v>
-      </c>
-      <c r="K71" s="12">
-        <v>3</v>
-      </c>
-      <c r="L71" s="18">
+      <c r="E72" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F72" s="11">
+        <v>35</v>
+      </c>
+      <c r="G72" s="11">
+        <v>1</v>
+      </c>
+      <c r="H72" s="12">
+        <v>4</v>
+      </c>
+      <c r="I72" s="12">
+        <v>3</v>
+      </c>
+      <c r="J72" s="12">
+        <v>4</v>
+      </c>
+      <c r="K72" s="12">
+        <v>1</v>
+      </c>
+      <c r="L72" s="13">
         <f t="shared" si="6"/>
-        <v>2.9</v>
-      </c>
-      <c r="M71" s="18" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="M72" s="13" t="str">
         <f t="shared" si="7"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N71" s="15"/>
-      <c r="O71" s="15"/>
-      <c r="P71" s="15"/>
-      <c r="Q71" s="15"/>
-      <c r="S71" s="8" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="7" t="s">
+      <c r="N72" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="B72" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="D72" s="9" t="s">
+      <c r="O72" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="P72" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q72" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="R72" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="S72" s="7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="8">
+        <v>258026</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="D73" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E72" s="10" t="s">
+      <c r="E73" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="F73" s="17">
+        <v>42</v>
+      </c>
+      <c r="G73" s="17">
+        <v>1</v>
+      </c>
+      <c r="H73" s="12">
+        <v>4</v>
+      </c>
+      <c r="I73" s="12">
+        <v>3</v>
+      </c>
+      <c r="J73" s="12">
+        <v>4</v>
+      </c>
+      <c r="K73" s="12">
+        <v>3</v>
+      </c>
+      <c r="L73" s="18">
+        <f t="shared" ref="L73" si="8">IF(OR(I73="",J73="",K73="",G73=""),"",ROUND(G73*0.2+I73*0.3+J73*0.3+K73*0.2,2))</f>
+        <v>2.9</v>
+      </c>
+      <c r="M73" s="18" t="str">
+        <f t="shared" ref="M73" si="9">IF(OR(H73="",L73=""),"",IF(AND(H73&gt;=4,L73&gt;=3.5),"High Impact + High Risk",IF(AND(H73&gt;=4,L73&lt;3.5),"High Impact + Low Risk",IF(AND(H73&lt;4,L73&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N73" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="O73" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="P73" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q73" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="F72" s="11">
-        <v>55</v>
-      </c>
-      <c r="G72" s="11">
-        <v>3</v>
-      </c>
-      <c r="H72" s="12">
-        <v>4</v>
-      </c>
-      <c r="I72" s="12">
-        <v>4</v>
-      </c>
-      <c r="J72" s="12">
-        <v>4</v>
-      </c>
-      <c r="K72" s="12">
-        <v>4</v>
-      </c>
-      <c r="L72" s="13">
-        <f t="shared" si="6"/>
-        <v>3.8</v>
-      </c>
-      <c r="M72" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>High Impact + High Risk</v>
-      </c>
-      <c r="N72" s="9"/>
-      <c r="O72" s="9"/>
-      <c r="P72" s="9"/>
-      <c r="Q72" s="9"/>
-      <c r="S72" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="7">
-        <v>168016</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="F73" s="11">
-        <v>35</v>
-      </c>
-      <c r="G73" s="11">
-        <v>1</v>
-      </c>
-      <c r="H73" s="12">
-        <v>4</v>
-      </c>
-      <c r="I73" s="12">
-        <v>3</v>
-      </c>
-      <c r="J73" s="12">
-        <v>4</v>
-      </c>
-      <c r="K73" s="12">
-        <v>1</v>
-      </c>
-      <c r="L73" s="13">
-        <f t="shared" si="6"/>
-        <v>2.5</v>
-      </c>
-      <c r="M73" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N73" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="O73" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q73" s="9" t="s">
-        <v>270</v>
-      </c>
       <c r="R73" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="S73" s="7" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="8">
-        <v>258026</v>
-      </c>
-      <c r="B74" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C74" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="D74" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E74" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="F74" s="17">
-        <v>42</v>
-      </c>
-      <c r="G74" s="17">
-        <v>1</v>
-      </c>
-      <c r="H74" s="12">
-        <v>4</v>
-      </c>
-      <c r="I74" s="12">
-        <v>3</v>
-      </c>
-      <c r="J74" s="12">
-        <v>4</v>
-      </c>
-      <c r="K74" s="12">
-        <v>3</v>
-      </c>
-      <c r="L74" s="18">
-        <f t="shared" ref="L74" si="8">IF(OR(I74="",J74="",K74="",G74=""),"",ROUND(G74*0.2+I74*0.3+J74*0.3+K74*0.2,2))</f>
-        <v>2.9</v>
-      </c>
-      <c r="M74" s="18" t="str">
-        <f t="shared" ref="M74" si="9">IF(OR(H74="",L74=""),"",IF(AND(H74&gt;=4,L74&gt;=3.5),"High Impact + High Risk",IF(AND(H74&gt;=4,L74&lt;3.5),"High Impact + Low Risk",IF(AND(H74&lt;4,L74&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N74" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="O74" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="P74" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q74" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="R74" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="S74" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="S73" s="8" t="s">
         <v>93</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S74" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:S73" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2237006A-4AFC-4CB6-A038-9920F142ADA1}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15F68C52-17BF-46B6-AFE0-FDA4E35D8434}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="กรอกข้อมูล" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$72</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="264">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -601,21 +601,6 @@
     <t>Director - Marketing</t>
   </si>
   <si>
-    <t>ยังไม่มีคนใน</t>
-  </si>
-  <si>
-    <t>No Successor</t>
-  </si>
-  <si>
-    <t>Speacial of knowledge + managerial skill</t>
-  </si>
-  <si>
-    <t>หาคนนอก+educate production knowledge</t>
-  </si>
-  <si>
-    <t>ผู้สืบทอดภายในอาจจะพร้อม 3+years</t>
-  </si>
-  <si>
     <t>รักดี ภักดีชุมพล</t>
   </si>
   <si>
@@ -634,12 +619,6 @@
     <t>06/08/1960</t>
   </si>
   <si>
-    <t>สิรภพ</t>
-  </si>
-  <si>
-    <t>Ready in 3 Years</t>
-  </si>
-  <si>
     <t>ไชยยันต์ กิจมีรัศมีโยธิน</t>
   </si>
   <si>
@@ -739,15 +718,6 @@
     <t>17/06/1980</t>
   </si>
   <si>
-    <t>ณัฐฐา สมานทรัพย์</t>
-  </si>
-  <si>
-    <t>Supervisor - Accounting Receivable</t>
-  </si>
-  <si>
-    <t>09/08/1977</t>
-  </si>
-  <si>
     <t>ภัทรานิษฐ์ เกิดสุข</t>
   </si>
   <si>
@@ -839,9 +809,6 @@
   </si>
   <si>
     <t>FAIP</t>
-  </si>
-  <si>
-    <t>ยังไม่ได้กรอกคะแนน</t>
   </si>
   <si>
     <t>เวทัส ศฤงฆารสกล</t>
@@ -1196,19 +1163,43 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1219,30 +1210,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1522,693 +1489,727 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="33"/>
+      <c r="G26" s="30"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="32" t="s">
+      <c r="B27" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="33" t="s">
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="33"/>
+      <c r="G27" s="30"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="33" t="s">
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="33"/>
+      <c r="G28" s="30"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="33" t="s">
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="33"/>
+      <c r="G29" s="30"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="33" t="s">
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="30"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="29" t="s">
+      <c r="B32" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C34" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C35" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="C38" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="25" t="s">
+      <c r="C39" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="25" t="s">
+      <c r="C40" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C42" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="29" t="s">
+      <c r="B44" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="25" t="s">
+      <c r="C45" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="27"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C46" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="C47" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="25" t="s">
+      <c r="C48" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="25"/>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="25" t="s">
+      <c r="C49" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="25"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="30" t="s">
+      <c r="B52" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="31" t="s">
+      <c r="B53" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="23" t="s">
+      <c r="B55" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="24" t="s">
+      <c r="B56" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="25" t="s">
+      <c r="C56" s="33"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="26" t="s">
+      <c r="B57" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="25" t="s">
+      <c r="C57" s="34"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="25" t="s">
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="25"/>
-      <c r="G58" s="25"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="28" t="s">
+      <c r="B59" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="28"/>
-      <c r="D59" s="28"/>
-      <c r="E59" s="25" t="s">
+      <c r="C59" s="36"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="25"/>
-      <c r="G59" s="25"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="23" t="s">
+      <c r="B62" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="23"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="21" t="s">
+      <c r="B63" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="25"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="22" t="s">
+      <c r="B64" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="22" t="s">
+      <c r="B65" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="21"/>
+      <c r="G65" s="21"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="22" t="s">
+      <c r="B66" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="22"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="21"/>
+      <c r="G66" s="21"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="22" t="s">
+      <c r="B67" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="23" t="s">
+      <c r="B69" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="23"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="23"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="21" t="s">
+      <c r="B70" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="25"/>
+      <c r="E70" s="25"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="25"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="21" t="s">
+      <c r="B71" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="25"/>
+      <c r="E71" s="25"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="25"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="21" t="s">
+      <c r="B72" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="25"/>
+      <c r="F72" s="25"/>
+      <c r="G72" s="25"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="21" t="s">
+      <c r="B73" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
+      <c r="C73" s="25"/>
+      <c r="D73" s="25"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="21" t="s">
+      <c r="B74" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="21" t="s">
+      <c r="B75" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="25"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="21"/>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
+      <c r="B76" s="25"/>
+      <c r="C76" s="25"/>
+      <c r="D76" s="25"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="B17:G17"/>
@@ -2222,52 +2223,18 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B15:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2276,7 +2243,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S73"/>
+  <dimension ref="A1:S72"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2902,16 +2869,16 @@
         <v>466004</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F13" s="17">
         <v>66</v>
@@ -2952,16 +2919,16 @@
         <v>159029</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F14" s="11">
         <v>52</v>
@@ -2989,15 +2956,13 @@
         <f t="shared" ref="M14" si="5">IF(OR(H14="",L14=""),"",IF(AND(H14&gt;=4,L14&gt;=3.5),"High Impact + High Risk",IF(AND(H14&gt;=4,L14&lt;3.5),"High Impact + Low Risk",IF(AND(H14&lt;4,L14&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N14" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>199</v>
-      </c>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="9"/>
-      <c r="S14" s="7"/>
+      <c r="S14" s="7" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="15" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
@@ -3069,11 +3034,11 @@
       </c>
       <c r="F16" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G16" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="12">
         <v>4</v>
@@ -3089,7 +3054,7 @@
       </c>
       <c r="L16" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="M16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3685,7 +3650,7 @@
       </c>
       <c r="F28" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G28" s="17">
         <f t="shared" ca="1" si="0"/>
@@ -3893,7 +3858,7 @@
       </c>
       <c r="F32" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G32" s="17">
         <f t="shared" ca="1" si="0"/>
@@ -4153,7 +4118,7 @@
       </c>
       <c r="F37" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G37" s="11">
         <f t="shared" ca="1" si="0"/>
@@ -4491,16 +4456,10 @@
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N43" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="O43" s="9" t="s">
-        <v>188</v>
-      </c>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
       <c r="P43" s="9"/>
-      <c r="Q43" s="9" t="s">
-        <v>189</v>
-      </c>
+      <c r="Q43" s="9"/>
       <c r="S43" s="7" t="s">
         <v>182</v>
       </c>
@@ -4549,16 +4508,10 @@
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N44" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="O44" s="15" t="s">
-        <v>188</v>
-      </c>
+      <c r="N44" s="15"/>
+      <c r="O44" s="15"/>
       <c r="P44" s="15"/>
-      <c r="Q44" s="15" t="s">
-        <v>190</v>
-      </c>
+      <c r="Q44" s="15"/>
       <c r="S44" s="8" t="s">
         <v>182</v>
       </c>
@@ -4607,16 +4560,10 @@
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N45" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="O45" s="9" t="s">
-        <v>188</v>
-      </c>
+      <c r="N45" s="9"/>
+      <c r="O45" s="9"/>
       <c r="P45" s="9"/>
-      <c r="Q45" s="9" t="s">
-        <v>191</v>
-      </c>
+      <c r="Q45" s="9"/>
       <c r="S45" s="7" t="s">
         <v>182</v>
       </c>
@@ -4795,7 +4742,7 @@
       </c>
       <c r="F49" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G49" s="17">
         <f t="shared" ca="1" si="0"/>
@@ -4834,16 +4781,16 @@
         <v>146037</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="F50" s="11">
         <v>60</v>
@@ -4864,11 +4811,11 @@
         <v>5</v>
       </c>
       <c r="L50" s="13">
-        <f t="shared" ref="L50:L72" si="6">IF(OR(I50="",J50="",K50="",G50=""),"",ROUND(G50*0.2+I50*0.3+J50*0.3+K50*0.2,2))</f>
+        <f t="shared" ref="L50:L71" si="6">IF(OR(I50="",J50="",K50="",G50=""),"",ROUND(G50*0.2+I50*0.3+J50*0.3+K50*0.2,2))</f>
         <v>4.0999999999999996</v>
       </c>
       <c r="M50" s="13" t="str">
-        <f t="shared" ref="M50:M72" si="7">IF(OR(H50="",L50=""),"",IF(AND(H50&gt;=4,L50&gt;=3.5),"High Impact + High Risk",IF(AND(H50&gt;=4,L50&lt;3.5),"High Impact + Low Risk",IF(AND(H50&lt;4,L50&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+        <f t="shared" ref="M50:M71" si="7">IF(OR(H50="",L50=""),"",IF(AND(H50&gt;=4,L50&gt;=3.5),"High Impact + High Risk",IF(AND(H50&gt;=4,L50&lt;3.5),"High Impact + Low Risk",IF(AND(H50&lt;4,L50&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
         <v>High Impact + High Risk</v>
       </c>
       <c r="N50" s="9"/>
@@ -4876,7 +4823,7 @@
       <c r="P50" s="9"/>
       <c r="Q50" s="9"/>
       <c r="S50" s="7" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="51" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -4884,16 +4831,16 @@
         <v>139013</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D51" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F51" s="17">
         <v>58</v>
@@ -4926,7 +4873,7 @@
       <c r="P51" s="15"/>
       <c r="Q51" s="15"/>
       <c r="S51" s="8" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="52" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -4934,16 +4881,16 @@
         <v>145015</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="F52" s="11">
         <v>50</v>
@@ -4976,7 +4923,7 @@
       <c r="P52" s="9"/>
       <c r="Q52" s="9"/>
       <c r="S52" s="7" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="53" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -4984,16 +4931,16 @@
         <v>161005</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D53" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F53" s="17">
         <v>45</v>
@@ -5026,7 +4973,7 @@
       <c r="P53" s="15"/>
       <c r="Q53" s="15"/>
       <c r="S53" s="8" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="54" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5034,16 +4981,16 @@
         <v>163003</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="F54" s="11">
         <v>34</v>
@@ -5076,7 +5023,7 @@
       <c r="P54" s="9"/>
       <c r="Q54" s="9"/>
       <c r="S54" s="7" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="55" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5084,16 +5031,16 @@
         <v>166024</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D55" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F55" s="17">
         <v>27</v>
@@ -5126,7 +5073,7 @@
       <c r="P55" s="15"/>
       <c r="Q55" s="15"/>
       <c r="S55" s="8" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="56" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5134,16 +5081,16 @@
         <v>167001</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F56" s="11">
         <v>37</v>
@@ -5176,7 +5123,7 @@
       <c r="P56" s="9"/>
       <c r="Q56" s="9"/>
       <c r="S56" s="7" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="57" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5184,16 +5131,16 @@
         <v>167012</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D57" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F57" s="17">
         <v>31</v>
@@ -5226,7 +5173,7 @@
       <c r="P57" s="15"/>
       <c r="Q57" s="15"/>
       <c r="S57" s="8" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="58" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5234,16 +5181,16 @@
         <v>260001</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F58" s="11">
         <v>35</v>
@@ -5276,7 +5223,7 @@
       <c r="P58" s="9"/>
       <c r="Q58" s="9"/>
       <c r="S58" s="7" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="59" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5284,16 +5231,16 @@
         <v>267001</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D59" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F59" s="17">
         <v>31</v>
@@ -5326,7 +5273,7 @@
       <c r="P59" s="15"/>
       <c r="Q59" s="15"/>
       <c r="S59" s="8" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="60" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5334,16 +5281,16 @@
         <v>160001</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="F60" s="11">
         <v>46</v>
@@ -5376,33 +5323,33 @@
       <c r="P60" s="9"/>
       <c r="Q60" s="9"/>
       <c r="S60" s="7" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="61" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="8">
-        <v>165004</v>
-      </c>
-      <c r="B61" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="C61" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="D61" s="15" t="s">
+      <c r="A61" s="7">
+        <v>167020</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D61" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E61" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="F61" s="17">
-        <v>49</v>
-      </c>
-      <c r="G61" s="17">
-        <v>1</v>
+      <c r="E61" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F61" s="11">
+        <v>51</v>
+      </c>
+      <c r="G61" s="11">
+        <v>2</v>
       </c>
       <c r="H61" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I61" s="12">
         <v>3</v>
@@ -5413,292 +5360,292 @@
       <c r="K61" s="12">
         <v>4</v>
       </c>
-      <c r="L61" s="18">
+      <c r="L61" s="13">
         <f t="shared" si="6"/>
-        <v>2.8</v>
-      </c>
-      <c r="M61" s="18" t="str">
+        <v>3</v>
+      </c>
+      <c r="M61" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N61" s="9"/>
+      <c r="O61" s="9"/>
+      <c r="P61" s="9"/>
+      <c r="Q61" s="9"/>
+      <c r="S61" s="7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="8">
+        <v>167029</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E62" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="F62" s="17">
+        <v>35</v>
+      </c>
+      <c r="G62" s="17">
+        <v>1</v>
+      </c>
+      <c r="H62" s="12">
+        <v>5</v>
+      </c>
+      <c r="I62" s="12">
+        <v>3</v>
+      </c>
+      <c r="J62" s="12">
+        <v>4</v>
+      </c>
+      <c r="K62" s="12">
+        <v>5</v>
+      </c>
+      <c r="L62" s="18">
+        <f t="shared" si="6"/>
+        <v>3.3</v>
+      </c>
+      <c r="M62" s="18" t="str">
         <f t="shared" si="7"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N61" s="15"/>
-      <c r="O61" s="15"/>
-      <c r="P61" s="15"/>
-      <c r="Q61" s="15"/>
-      <c r="S61" s="8" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="7">
-        <v>167020</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="D62" s="9" t="s">
+      <c r="N62" s="15"/>
+      <c r="O62" s="15"/>
+      <c r="P62" s="15"/>
+      <c r="Q62" s="15"/>
+      <c r="S62" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="7">
+        <v>167032</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D63" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E62" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="F62" s="11">
-        <v>51</v>
-      </c>
-      <c r="G62" s="11">
-        <v>2</v>
-      </c>
-      <c r="H62" s="12">
-        <v>3</v>
-      </c>
-      <c r="I62" s="12">
-        <v>3</v>
-      </c>
-      <c r="J62" s="12">
-        <v>3</v>
-      </c>
-      <c r="K62" s="12">
-        <v>4</v>
-      </c>
-      <c r="L62" s="13">
+      <c r="E63" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="F63" s="11">
+        <v>29</v>
+      </c>
+      <c r="G63" s="11">
+        <v>1</v>
+      </c>
+      <c r="H63" s="12">
+        <v>3</v>
+      </c>
+      <c r="I63" s="12">
+        <v>5</v>
+      </c>
+      <c r="J63" s="12">
+        <v>3</v>
+      </c>
+      <c r="K63" s="12">
+        <v>3</v>
+      </c>
+      <c r="L63" s="13">
         <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="M62" s="13" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="M63" s="13" t="str">
         <f t="shared" si="7"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N62" s="9"/>
-      <c r="O62" s="9"/>
-      <c r="P62" s="9"/>
-      <c r="Q62" s="9"/>
-      <c r="S62" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="8">
-        <v>167029</v>
-      </c>
-      <c r="B63" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="C63" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="D63" s="15" t="s">
+      <c r="N63" s="9"/>
+      <c r="O63" s="9"/>
+      <c r="P63" s="9"/>
+      <c r="Q63" s="9"/>
+      <c r="S63" s="7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="8">
+        <v>168024</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="D64" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E63" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="F63" s="17">
-        <v>35</v>
-      </c>
-      <c r="G63" s="17">
-        <v>1</v>
-      </c>
-      <c r="H63" s="12">
+      <c r="E64" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="F64" s="17">
+        <v>46</v>
+      </c>
+      <c r="G64" s="17">
+        <v>1</v>
+      </c>
+      <c r="H64" s="12">
         <v>5</v>
       </c>
-      <c r="I63" s="12">
-        <v>3</v>
-      </c>
-      <c r="J63" s="12">
-        <v>4</v>
-      </c>
-      <c r="K63" s="12">
+      <c r="I64" s="12">
+        <v>3</v>
+      </c>
+      <c r="J64" s="12">
+        <v>4</v>
+      </c>
+      <c r="K64" s="12">
         <v>5</v>
       </c>
-      <c r="L63" s="18">
+      <c r="L64" s="18">
         <f t="shared" si="6"/>
         <v>3.3</v>
       </c>
-      <c r="M63" s="18" t="str">
+      <c r="M64" s="18" t="str">
         <f t="shared" si="7"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N63" s="15"/>
-      <c r="O63" s="15"/>
-      <c r="P63" s="15"/>
-      <c r="Q63" s="15"/>
-      <c r="S63" s="8" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="7">
-        <v>167032</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="D64" s="9" t="s">
+      <c r="N64" s="15"/>
+      <c r="O64" s="15"/>
+      <c r="P64" s="15"/>
+      <c r="Q64" s="15"/>
+      <c r="S64" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="8">
+        <v>337004</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D65" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E64" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="F64" s="11">
-        <v>29</v>
-      </c>
-      <c r="G64" s="11">
-        <v>1</v>
-      </c>
-      <c r="H64" s="12">
-        <v>3</v>
-      </c>
-      <c r="I64" s="12">
-        <v>5</v>
-      </c>
-      <c r="J64" s="12">
-        <v>3</v>
-      </c>
-      <c r="K64" s="12">
-        <v>3</v>
-      </c>
-      <c r="L64" s="13">
+      <c r="E65" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="F65" s="17">
+        <v>55</v>
+      </c>
+      <c r="G65" s="17">
+        <v>3</v>
+      </c>
+      <c r="H65" s="12">
+        <v>3</v>
+      </c>
+      <c r="I65" s="12">
+        <v>1</v>
+      </c>
+      <c r="J65" s="12">
+        <v>3</v>
+      </c>
+      <c r="K65" s="12">
+        <v>4</v>
+      </c>
+      <c r="L65" s="18">
         <f t="shared" si="6"/>
-        <v>3.2</v>
-      </c>
-      <c r="M64" s="13" t="str">
+        <v>2.6</v>
+      </c>
+      <c r="M65" s="18" t="str">
         <f t="shared" si="7"/>
         <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N64" s="9"/>
-      <c r="O64" s="9"/>
-      <c r="P64" s="9"/>
-      <c r="Q64" s="9"/>
-      <c r="S64" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="8">
-        <v>168024</v>
-      </c>
-      <c r="B65" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="C65" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="D65" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E65" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="F65" s="17">
-        <v>46</v>
-      </c>
-      <c r="G65" s="17">
-        <v>1</v>
-      </c>
-      <c r="H65" s="12">
-        <v>5</v>
-      </c>
-      <c r="I65" s="12">
-        <v>3</v>
-      </c>
-      <c r="J65" s="12">
-        <v>4</v>
-      </c>
-      <c r="K65" s="12">
-        <v>5</v>
-      </c>
-      <c r="L65" s="18">
-        <f t="shared" si="6"/>
-        <v>3.3</v>
-      </c>
-      <c r="M65" s="18" t="str">
-        <f t="shared" si="7"/>
-        <v>High Impact + Low Risk</v>
       </c>
       <c r="N65" s="15"/>
       <c r="O65" s="15"/>
       <c r="P65" s="15"/>
       <c r="Q65" s="15"/>
       <c r="S65" s="8" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="66" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="8">
-        <v>337004</v>
-      </c>
-      <c r="B66" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="C66" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="D66" s="15" t="s">
+      <c r="A66" s="7">
+        <v>267085</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D66" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E66" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="F66" s="17">
-        <v>55</v>
-      </c>
-      <c r="G66" s="17">
-        <v>3</v>
+      <c r="E66" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F66" s="11">
+        <v>30</v>
+      </c>
+      <c r="G66" s="11">
+        <v>1</v>
       </c>
       <c r="H66" s="12">
         <v>3</v>
       </c>
       <c r="I66" s="12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J66" s="12">
         <v>3</v>
       </c>
       <c r="K66" s="12">
-        <v>4</v>
-      </c>
-      <c r="L66" s="18">
+        <v>3</v>
+      </c>
+      <c r="L66" s="13">
         <f t="shared" si="6"/>
-        <v>2.6</v>
-      </c>
-      <c r="M66" s="18" t="str">
+        <v>2.9</v>
+      </c>
+      <c r="M66" s="13" t="str">
         <f t="shared" si="7"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N66" s="15"/>
-      <c r="O66" s="15"/>
-      <c r="P66" s="15"/>
-      <c r="Q66" s="15"/>
-      <c r="S66" s="8" t="s">
-        <v>266</v>
+      <c r="N66" s="9"/>
+      <c r="O66" s="9"/>
+      <c r="P66" s="9"/>
+      <c r="Q66" s="9"/>
+      <c r="S66" s="7" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="67" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="7">
-        <v>267085</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="D67" s="9" t="s">
+      <c r="A67" s="8">
+        <v>268044</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="D67" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E67" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="F67" s="11">
-        <v>30</v>
-      </c>
-      <c r="G67" s="11">
+      <c r="E67" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="F67" s="17">
+        <v>28</v>
+      </c>
+      <c r="G67" s="17">
         <v>1</v>
       </c>
       <c r="H67" s="12">
@@ -5713,242 +5660,251 @@
       <c r="K67" s="12">
         <v>3</v>
       </c>
-      <c r="L67" s="13">
+      <c r="L67" s="18">
         <f t="shared" si="6"/>
         <v>2.9</v>
       </c>
-      <c r="M67" s="13" t="str">
+      <c r="M67" s="18" t="str">
         <f t="shared" si="7"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N67" s="9"/>
-      <c r="O67" s="9"/>
-      <c r="P67" s="9"/>
-      <c r="Q67" s="9"/>
-      <c r="S67" s="7" t="s">
-        <v>266</v>
+      <c r="N67" s="15"/>
+      <c r="O67" s="15"/>
+      <c r="P67" s="15"/>
+      <c r="Q67" s="15"/>
+      <c r="S67" s="8" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="68" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="8">
-        <v>268044</v>
-      </c>
-      <c r="B68" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="C68" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="D68" s="15" t="s">
+      <c r="A68" s="7">
+        <v>368004</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="D68" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E68" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="F68" s="17">
-        <v>28</v>
-      </c>
-      <c r="G68" s="17">
-        <v>1</v>
+      <c r="E68" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="F68" s="11">
+        <v>59</v>
+      </c>
+      <c r="G68" s="11">
+        <v>4</v>
       </c>
       <c r="H68" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I68" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J68" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K68" s="12">
-        <v>3</v>
-      </c>
-      <c r="L68" s="18">
+        <v>4</v>
+      </c>
+      <c r="L68" s="13">
+        <f t="shared" si="6"/>
+        <v>3.7</v>
+      </c>
+      <c r="M68" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N68" s="9"/>
+      <c r="O68" s="9"/>
+      <c r="P68" s="9"/>
+      <c r="Q68" s="9"/>
+      <c r="S68" s="7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="8">
+        <v>269040</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E69" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F69" s="17">
+        <v>45</v>
+      </c>
+      <c r="G69" s="17">
+        <v>1</v>
+      </c>
+      <c r="H69" s="12">
+        <v>4</v>
+      </c>
+      <c r="I69" s="12">
+        <v>3</v>
+      </c>
+      <c r="J69" s="12">
+        <v>4</v>
+      </c>
+      <c r="K69" s="12">
+        <v>3</v>
+      </c>
+      <c r="L69" s="18">
         <f t="shared" si="6"/>
         <v>2.9</v>
       </c>
-      <c r="M68" s="18" t="str">
+      <c r="M69" s="18" t="str">
         <f t="shared" si="7"/>
-        <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N68" s="15"/>
-      <c r="O68" s="15"/>
-      <c r="P68" s="15"/>
-      <c r="Q68" s="15"/>
-      <c r="S68" s="8" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="7">
-        <v>368004</v>
-      </c>
-      <c r="B69" s="9" t="s">
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N69" s="15"/>
+      <c r="O69" s="15"/>
+      <c r="P69" s="15"/>
+      <c r="Q69" s="15"/>
+      <c r="S69" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="C69" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="D69" s="9" t="s">
+    </row>
+    <row r="70" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D70" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E69" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="F69" s="11">
-        <v>59</v>
-      </c>
-      <c r="G69" s="11">
-        <v>4</v>
-      </c>
-      <c r="H69" s="12">
-        <v>4</v>
-      </c>
-      <c r="I69" s="12">
-        <v>3</v>
-      </c>
-      <c r="J69" s="12">
-        <v>4</v>
-      </c>
-      <c r="K69" s="12">
-        <v>4</v>
-      </c>
-      <c r="L69" s="13">
+      <c r="E70" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="F70" s="11">
+        <v>55</v>
+      </c>
+      <c r="G70" s="11">
+        <v>3</v>
+      </c>
+      <c r="H70" s="12">
+        <v>4</v>
+      </c>
+      <c r="I70" s="12">
+        <v>4</v>
+      </c>
+      <c r="J70" s="12">
+        <v>4</v>
+      </c>
+      <c r="K70" s="12">
+        <v>4</v>
+      </c>
+      <c r="L70" s="13">
         <f t="shared" si="6"/>
-        <v>3.7</v>
-      </c>
-      <c r="M69" s="13" t="str">
+        <v>3.8</v>
+      </c>
+      <c r="M70" s="13" t="str">
         <f t="shared" si="7"/>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N69" s="9"/>
-      <c r="O69" s="9"/>
-      <c r="P69" s="9"/>
-      <c r="Q69" s="9"/>
-      <c r="S69" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="8">
-        <v>269040</v>
-      </c>
-      <c r="B70" s="15" t="s">
+      <c r="N70" s="9"/>
+      <c r="O70" s="9"/>
+      <c r="P70" s="9"/>
+      <c r="Q70" s="9"/>
+      <c r="S70" s="7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="7">
+        <v>168016</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E71" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="C70" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="D70" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E70" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="F70" s="17">
-        <v>45</v>
-      </c>
-      <c r="G70" s="17">
-        <v>1</v>
-      </c>
-      <c r="H70" s="12">
-        <v>4</v>
-      </c>
-      <c r="I70" s="12">
-        <v>3</v>
-      </c>
-      <c r="J70" s="12">
-        <v>4</v>
-      </c>
-      <c r="K70" s="12">
-        <v>3</v>
-      </c>
-      <c r="L70" s="18">
+      <c r="F71" s="11">
+        <v>35</v>
+      </c>
+      <c r="G71" s="11">
+        <v>1</v>
+      </c>
+      <c r="H71" s="12">
+        <v>4</v>
+      </c>
+      <c r="I71" s="12">
+        <v>3</v>
+      </c>
+      <c r="J71" s="12">
+        <v>4</v>
+      </c>
+      <c r="K71" s="12">
+        <v>1</v>
+      </c>
+      <c r="L71" s="13">
         <f t="shared" si="6"/>
-        <v>2.9</v>
-      </c>
-      <c r="M70" s="18" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="M71" s="13" t="str">
         <f t="shared" si="7"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N70" s="15"/>
-      <c r="O70" s="15"/>
-      <c r="P70" s="15"/>
-      <c r="Q70" s="15"/>
-      <c r="S70" s="8" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="7" t="s">
+      <c r="N71" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="O71" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="P71" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q71" s="9"/>
+      <c r="R71" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="S71" s="7" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="8">
+        <v>258026</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="C72" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="B71" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C71" s="9" t="s">
+      <c r="D72" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E72" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="D71" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="F71" s="11">
-        <v>55</v>
-      </c>
-      <c r="G71" s="11">
-        <v>3</v>
-      </c>
-      <c r="H71" s="12">
-        <v>4</v>
-      </c>
-      <c r="I71" s="12">
-        <v>4</v>
-      </c>
-      <c r="J71" s="12">
-        <v>4</v>
-      </c>
-      <c r="K71" s="12">
-        <v>4</v>
-      </c>
-      <c r="L71" s="13">
-        <f t="shared" si="6"/>
-        <v>3.8</v>
-      </c>
-      <c r="M71" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>High Impact + High Risk</v>
-      </c>
-      <c r="N71" s="9"/>
-      <c r="O71" s="9"/>
-      <c r="P71" s="9"/>
-      <c r="Q71" s="9"/>
-      <c r="S71" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="7">
-        <v>168016</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="F72" s="11">
-        <v>35</v>
-      </c>
-      <c r="G72" s="11">
+      <c r="F72" s="17">
+        <v>42</v>
+      </c>
+      <c r="G72" s="17">
         <v>1</v>
       </c>
       <c r="H72" s="12">
@@ -5961,98 +5917,35 @@
         <v>4</v>
       </c>
       <c r="K72" s="12">
-        <v>1</v>
-      </c>
-      <c r="L72" s="13">
-        <f t="shared" si="6"/>
-        <v>2.5</v>
-      </c>
-      <c r="M72" s="13" t="str">
-        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="L72" s="18">
+        <f t="shared" ref="L72" si="8">IF(OR(I72="",J72="",K72="",G72=""),"",ROUND(G72*0.2+I72*0.3+J72*0.3+K72*0.2,2))</f>
+        <v>2.9</v>
+      </c>
+      <c r="M72" s="18" t="str">
+        <f t="shared" ref="M72" si="9">IF(OR(H72="",L72=""),"",IF(AND(H72&gt;=4,L72&gt;=3.5),"High Impact + High Risk",IF(AND(H72&gt;=4,L72&lt;3.5),"High Impact + Low Risk",IF(AND(H72&lt;4,L72&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N72" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="O72" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="P72" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q72" s="9" t="s">
-        <v>267</v>
-      </c>
+      <c r="N72" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="O72" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="P72" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q72" s="15"/>
       <c r="R72" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="S72" s="7" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="8">
-        <v>258026</v>
-      </c>
-      <c r="B73" s="15" t="s">
-        <v>272</v>
-      </c>
-      <c r="C73" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="D73" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E73" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="F73" s="17">
-        <v>42</v>
-      </c>
-      <c r="G73" s="17">
-        <v>1</v>
-      </c>
-      <c r="H73" s="12">
-        <v>4</v>
-      </c>
-      <c r="I73" s="12">
-        <v>3</v>
-      </c>
-      <c r="J73" s="12">
-        <v>4</v>
-      </c>
-      <c r="K73" s="12">
-        <v>3</v>
-      </c>
-      <c r="L73" s="18">
-        <f t="shared" ref="L73" si="8">IF(OR(I73="",J73="",K73="",G73=""),"",ROUND(G73*0.2+I73*0.3+J73*0.3+K73*0.2,2))</f>
-        <v>2.9</v>
-      </c>
-      <c r="M73" s="18" t="str">
-        <f t="shared" ref="M73" si="9">IF(OR(H73="",L73=""),"",IF(AND(H73&gt;=4,L73&gt;=3.5),"High Impact + High Risk",IF(AND(H73&gt;=4,L73&lt;3.5),"High Impact + Low Risk",IF(AND(H73&lt;4,L73&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N73" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="O73" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="P73" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q73" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="R73" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="S73" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="S72" s="8" t="s">
         <v>93</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S73" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:S72" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB39A34C-4EB8-47D0-83A2-C47AD46EC616}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C6C0AD5-B5F6-427D-88FC-D1D2CDA588D6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="กรอกข้อมูล" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$69</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="257">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -434,15 +434,6 @@
   </si>
   <si>
     <t>Department Manager - Supply Planning</t>
-  </si>
-  <si>
-    <t>268029 A</t>
-  </si>
-  <si>
-    <t>วุฒิชัย แสงสมชัยพิพัฒน์</t>
-  </si>
-  <si>
-    <t>Acting Department Manager - Production Support &amp; Finished Products</t>
   </si>
   <si>
     <t>เกรียงไกร อำนวยพล</t>
@@ -1151,19 +1142,43 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1174,30 +1189,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1477,693 +1468,727 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="33"/>
+      <c r="G26" s="30"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="32" t="s">
+      <c r="B27" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="33" t="s">
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="33"/>
+      <c r="G27" s="30"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="33" t="s">
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="33"/>
+      <c r="G28" s="30"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="33" t="s">
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="33"/>
+      <c r="G29" s="30"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="33" t="s">
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="30"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="29" t="s">
+      <c r="B32" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C34" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C35" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="C38" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="25" t="s">
+      <c r="C39" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="25" t="s">
+      <c r="C40" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C42" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="29" t="s">
+      <c r="B44" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="25" t="s">
+      <c r="C45" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="27"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C46" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="C47" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="25" t="s">
+      <c r="C48" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="25"/>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="25" t="s">
+      <c r="C49" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="25"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="30" t="s">
+      <c r="B52" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="31" t="s">
+      <c r="B53" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="23" t="s">
+      <c r="B55" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="24" t="s">
+      <c r="B56" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="25" t="s">
+      <c r="C56" s="33"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="26" t="s">
+      <c r="B57" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="25" t="s">
+      <c r="C57" s="34"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="25" t="s">
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="25"/>
-      <c r="G58" s="25"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="28" t="s">
+      <c r="B59" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="28"/>
-      <c r="D59" s="28"/>
-      <c r="E59" s="25" t="s">
+      <c r="C59" s="36"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="25"/>
-      <c r="G59" s="25"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="23" t="s">
+      <c r="B62" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="23"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="21" t="s">
+      <c r="B63" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="25"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="22" t="s">
+      <c r="B64" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="22" t="s">
+      <c r="B65" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="21"/>
+      <c r="G65" s="21"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="22" t="s">
+      <c r="B66" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="22"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="21"/>
+      <c r="G66" s="21"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="22" t="s">
+      <c r="B67" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="23" t="s">
+      <c r="B69" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="23"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="23"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="21" t="s">
+      <c r="B70" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="25"/>
+      <c r="E70" s="25"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="25"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="21" t="s">
+      <c r="B71" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="25"/>
+      <c r="E71" s="25"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="25"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="21" t="s">
+      <c r="B72" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="25"/>
+      <c r="F72" s="25"/>
+      <c r="G72" s="25"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="21" t="s">
+      <c r="B73" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
+      <c r="C73" s="25"/>
+      <c r="D73" s="25"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="21" t="s">
+      <c r="B74" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="21" t="s">
+      <c r="B75" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="25"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="21"/>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
+      <c r="B76" s="25"/>
+      <c r="C76" s="25"/>
+      <c r="D76" s="25"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="B17:G17"/>
@@ -2177,52 +2202,18 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B15:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2231,8 +2222,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:S70"/>
+  <dimension ref="A1:S69"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2333,7 +2323,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>168028</v>
       </c>
@@ -2354,7 +2344,7 @@
         <v>41</v>
       </c>
       <c r="G3" s="11">
-        <f t="shared" ref="G3:G48" ca="1" si="0">IF(F3="","",IF(F3&lt;50,1,IF(F3&lt;55,2,IF(F3&lt;58,3,IF(F3&lt;60,4,5)))))</f>
+        <f t="shared" ref="G3:G47" ca="1" si="0">IF(F3="","",IF(F3&lt;50,1,IF(F3&lt;55,2,IF(F3&lt;58,3,IF(F3&lt;60,4,5)))))</f>
         <v>1</v>
       </c>
       <c r="H3" s="12">
@@ -2370,11 +2360,11 @@
         <v>3</v>
       </c>
       <c r="L3" s="13">
-        <f t="shared" ref="L3:L48" ca="1" si="1">IF(OR(I3="",J3="",K3="",G3=""),"",ROUND(G3*0.2+I3*0.3+J3*0.3+K3*0.2,2))</f>
+        <f t="shared" ref="L3:L47" ca="1" si="1">IF(OR(I3="",J3="",K3="",G3=""),"",ROUND(G3*0.2+I3*0.3+J3*0.3+K3*0.2,2))</f>
         <v>2.2999999999999998</v>
       </c>
       <c r="M3" s="13" t="str">
-        <f t="shared" ref="M3:M48" ca="1" si="2">IF(OR(H3="",L3=""),"",IF(AND(H3&gt;=4,L3&gt;=3.5),"High Impact + High Risk",IF(AND(H3&gt;=4,L3&lt;3.5),"High Impact + Low Risk",IF(AND(H3&lt;4,L3&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+        <f t="shared" ref="M3:M47" ca="1" si="2">IF(OR(H3="",L3=""),"",IF(AND(H3&gt;=4,L3&gt;=3.5),"High Impact + High Risk",IF(AND(H3&gt;=4,L3&lt;3.5),"High Impact + Low Risk",IF(AND(H3&lt;4,L3&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
         <v>Low Impact + Low Risk</v>
       </c>
       <c r="N3" s="9"/>
@@ -2402,7 +2392,7 @@
         <v>29304</v>
       </c>
       <c r="F4" s="17">
-        <f t="shared" ref="F4:F48" ca="1" si="3">DATEDIF(E4,TODAY(),"Y")</f>
+        <f t="shared" ref="F4:F47" ca="1" si="3">DATEDIF(E4,TODAY(),"Y")</f>
         <v>46</v>
       </c>
       <c r="G4" s="17">
@@ -2541,7 +2531,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>161027</v>
       </c>
@@ -2645,7 +2635,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>656008</v>
       </c>
@@ -2697,7 +2687,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>168017</v>
       </c>
@@ -2801,7 +2791,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>166027</v>
       </c>
@@ -2858,16 +2848,16 @@
         <v>466004</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F13" s="17">
         <v>66</v>
@@ -2908,16 +2898,16 @@
         <v>159029</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F14" s="11">
         <v>52</v>
@@ -3057,7 +3047,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>242032</v>
       </c>
@@ -3065,7 +3055,7 @@
         <v>129</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>106</v>
@@ -3109,7 +3099,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>149024</v>
       </c>
@@ -3161,1337 +3151,1345 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+    <row r="19" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="7">
+        <v>232027</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="C19" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="D19" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="10">
+        <v>24838</v>
+      </c>
+      <c r="F19" s="11">
+        <f t="shared" ca="1" si="3"/>
+        <v>58</v>
+      </c>
+      <c r="G19" s="11">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H19" s="12">
+        <v>3</v>
+      </c>
+      <c r="I19" s="12">
+        <v>1</v>
+      </c>
+      <c r="J19" s="12">
+        <v>4</v>
+      </c>
+      <c r="K19" s="12">
+        <v>4</v>
+      </c>
+      <c r="L19" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.1</v>
+      </c>
+      <c r="M19" s="13" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="S19" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>256029</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="C20" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D20" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E19" s="16">
-        <v>27122</v>
-      </c>
-      <c r="F19" s="17">
+      <c r="E20" s="16">
+        <v>31119</v>
+      </c>
+      <c r="F20" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>52</v>
-      </c>
-      <c r="G19" s="17">
+        <v>41</v>
+      </c>
+      <c r="G20" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H20" s="12">
+        <v>3</v>
+      </c>
+      <c r="I20" s="12">
+        <v>1</v>
+      </c>
+      <c r="J20" s="12">
+        <v>3</v>
+      </c>
+      <c r="K20" s="12">
+        <v>3</v>
+      </c>
+      <c r="L20" s="18">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="M20" s="18" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15"/>
+      <c r="S20" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="7">
+        <v>236012</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="10">
+        <v>26421</v>
+      </c>
+      <c r="F21" s="11">
+        <f t="shared" ca="1" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="G21" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="18" t="str">
+      <c r="H21" s="12">
+        <v>3</v>
+      </c>
+      <c r="I21" s="12">
+        <v>1</v>
+      </c>
+      <c r="J21" s="12">
+        <v>3</v>
+      </c>
+      <c r="K21" s="12">
+        <v>3</v>
+      </c>
+      <c r="L21" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="M19" s="18" t="str">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
-      <c r="S19" s="8" t="s">
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="S21" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="7">
-        <v>232027</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="D20" s="9" t="s">
+    <row r="22" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="8">
+        <v>250042</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="16">
+        <v>26738</v>
+      </c>
+      <c r="F22" s="17">
+        <f t="shared" ca="1" si="3"/>
+        <v>53</v>
+      </c>
+      <c r="G22" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H22" s="12">
+        <v>4</v>
+      </c>
+      <c r="I22" s="12">
+        <v>1</v>
+      </c>
+      <c r="J22" s="12">
+        <v>4</v>
+      </c>
+      <c r="K22" s="12">
+        <v>4</v>
+      </c>
+      <c r="L22" s="18">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.7</v>
+      </c>
+      <c r="M22" s="18" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15"/>
+      <c r="S22" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="7">
+        <v>233034</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="10">
-        <v>24838</v>
-      </c>
-      <c r="F20" s="11">
+      <c r="E23" s="10">
+        <v>25245</v>
+      </c>
+      <c r="F23" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>58</v>
-      </c>
-      <c r="G20" s="11">
+        <v>57</v>
+      </c>
+      <c r="G23" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="H20" s="12">
-        <v>3</v>
-      </c>
-      <c r="I20" s="12">
-        <v>1</v>
-      </c>
-      <c r="J20" s="12">
-        <v>4</v>
-      </c>
-      <c r="K20" s="12">
-        <v>4</v>
-      </c>
-      <c r="L20" s="13">
+        <v>3</v>
+      </c>
+      <c r="H23" s="12">
+        <v>3</v>
+      </c>
+      <c r="I23" s="12">
+        <v>1</v>
+      </c>
+      <c r="J23" s="12">
+        <v>3</v>
+      </c>
+      <c r="K23" s="12">
+        <v>4</v>
+      </c>
+      <c r="L23" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.6</v>
+      </c>
+      <c r="M23" s="13" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="S23" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8">
+        <v>268013</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" s="16">
+        <v>29244</v>
+      </c>
+      <c r="F24" s="17">
+        <f t="shared" ca="1" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="G24" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H24" s="12">
+        <v>3</v>
+      </c>
+      <c r="I24" s="12">
+        <v>3</v>
+      </c>
+      <c r="J24" s="12">
+        <v>3</v>
+      </c>
+      <c r="K24" s="12">
+        <v>4</v>
+      </c>
+      <c r="L24" s="18">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.8</v>
+      </c>
+      <c r="M24" s="18" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15"/>
+      <c r="S24" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="7">
+        <v>249010</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="10">
+        <v>27467</v>
+      </c>
+      <c r="F25" s="11">
+        <f t="shared" ca="1" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="G25" s="11">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H25" s="12">
+        <v>3</v>
+      </c>
+      <c r="I25" s="12">
+        <v>1</v>
+      </c>
+      <c r="J25" s="12">
+        <v>4</v>
+      </c>
+      <c r="K25" s="12">
+        <v>4</v>
+      </c>
+      <c r="L25" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.7</v>
+      </c>
+      <c r="M25" s="13" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="S25" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>268012</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" s="16">
+        <v>31704</v>
+      </c>
+      <c r="F26" s="17">
+        <f t="shared" ca="1" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="G26" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H26" s="12">
+        <v>3</v>
+      </c>
+      <c r="I26" s="12">
+        <v>5</v>
+      </c>
+      <c r="J26" s="12">
+        <v>4</v>
+      </c>
+      <c r="K26" s="12">
+        <v>4</v>
+      </c>
+      <c r="L26" s="18">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.7</v>
+      </c>
+      <c r="M26" s="18" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Low Impact + High Risk</v>
+      </c>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15"/>
+      <c r="S26" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="7">
+        <v>238030</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E27" s="10">
+        <v>27404</v>
+      </c>
+      <c r="F27" s="11">
+        <f t="shared" ca="1" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="G27" s="11">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H27" s="12">
+        <v>3</v>
+      </c>
+      <c r="I27" s="12">
+        <v>1</v>
+      </c>
+      <c r="J27" s="12">
+        <v>3</v>
+      </c>
+      <c r="K27" s="12">
+        <v>4</v>
+      </c>
+      <c r="L27" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.4</v>
+      </c>
+      <c r="M27" s="13" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="S27" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>256014</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" s="16">
+        <v>32349</v>
+      </c>
+      <c r="F28" s="17">
+        <f t="shared" ca="1" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="G28" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H28" s="12">
+        <v>4</v>
+      </c>
+      <c r="I28" s="12">
+        <v>1</v>
+      </c>
+      <c r="J28" s="12">
+        <v>4</v>
+      </c>
+      <c r="K28" s="12">
+        <v>4</v>
+      </c>
+      <c r="L28" s="18">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="M28" s="18" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15"/>
+      <c r="S28" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="7">
+        <v>443003</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E29" s="10">
+        <v>28572</v>
+      </c>
+      <c r="F29" s="11">
+        <f t="shared" ca="1" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="G29" s="11">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H29" s="12">
+        <v>4</v>
+      </c>
+      <c r="I29" s="12">
+        <v>1</v>
+      </c>
+      <c r="J29" s="12">
+        <v>4</v>
+      </c>
+      <c r="K29" s="12">
+        <v>5</v>
+      </c>
+      <c r="L29" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.7</v>
+      </c>
+      <c r="M29" s="13" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="S29" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
+        <v>254057</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" s="16">
+        <v>32420</v>
+      </c>
+      <c r="F30" s="17">
+        <f t="shared" ca="1" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="G30" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H30" s="12">
+        <v>4</v>
+      </c>
+      <c r="I30" s="12">
+        <v>1</v>
+      </c>
+      <c r="J30" s="12">
+        <v>4</v>
+      </c>
+      <c r="K30" s="12">
+        <v>4</v>
+      </c>
+      <c r="L30" s="18">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="M30" s="18" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
+      <c r="S30" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="7">
+        <v>237011</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E31" s="10">
+        <v>25410</v>
+      </c>
+      <c r="F31" s="11">
+        <f t="shared" ca="1" si="3"/>
+        <v>57</v>
+      </c>
+      <c r="G31" s="11">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H31" s="12">
+        <v>4</v>
+      </c>
+      <c r="I31" s="12">
+        <v>1</v>
+      </c>
+      <c r="J31" s="12">
+        <v>4</v>
+      </c>
+      <c r="K31" s="12">
+        <v>5</v>
+      </c>
+      <c r="L31" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>3.1</v>
       </c>
-      <c r="M20" s="13" t="str">
+      <c r="M31" s="13" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="S31" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="8">
+        <v>267096</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" s="16">
+        <v>32140</v>
+      </c>
+      <c r="F32" s="17">
+        <f t="shared" ca="1" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="G32" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H32" s="12">
+        <v>4</v>
+      </c>
+      <c r="I32" s="12">
+        <v>3</v>
+      </c>
+      <c r="J32" s="12">
+        <v>4</v>
+      </c>
+      <c r="K32" s="12">
+        <v>4</v>
+      </c>
+      <c r="L32" s="18">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.1</v>
+      </c>
+      <c r="M32" s="18" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
+      <c r="S32" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="7">
+        <v>249048</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" s="10">
+        <v>29299</v>
+      </c>
+      <c r="F33" s="11">
+        <f t="shared" ca="1" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="G33" s="11">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H33" s="12">
+        <v>4</v>
+      </c>
+      <c r="I33" s="12">
+        <v>1</v>
+      </c>
+      <c r="J33" s="12">
+        <v>4</v>
+      </c>
+      <c r="K33" s="12">
+        <v>5</v>
+      </c>
+      <c r="L33" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.7</v>
+      </c>
+      <c r="M33" s="13" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="S33" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="8">
+        <v>269022</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E34" s="16">
+        <v>30852</v>
+      </c>
+      <c r="F34" s="17">
+        <f t="shared" ca="1" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="G34" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H34" s="12">
+        <v>4</v>
+      </c>
+      <c r="I34" s="12">
+        <v>3</v>
+      </c>
+      <c r="J34" s="12">
+        <v>4</v>
+      </c>
+      <c r="K34" s="12">
+        <v>4</v>
+      </c>
+      <c r="L34" s="18">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.1</v>
+      </c>
+      <c r="M34" s="18" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15"/>
+      <c r="S34" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="7">
+        <v>253014</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E35" s="10">
+        <v>30611</v>
+      </c>
+      <c r="F35" s="11">
+        <f t="shared" ca="1" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="G35" s="11">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H35" s="12">
+        <v>3</v>
+      </c>
+      <c r="I35" s="12">
+        <v>1</v>
+      </c>
+      <c r="J35" s="12">
+        <v>3</v>
+      </c>
+      <c r="K35" s="12">
+        <v>4</v>
+      </c>
+      <c r="L35" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="S20" s="7" t="s">
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
+      <c r="S35" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="8">
-        <v>256029</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="D21" s="15" t="s">
+    <row r="36" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="8">
+        <v>248031</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D36" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E21" s="16">
-        <v>31119</v>
-      </c>
-      <c r="F21" s="17">
+      <c r="E36" s="16">
+        <v>29617</v>
+      </c>
+      <c r="F36" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>41</v>
-      </c>
-      <c r="G21" s="17">
+        <v>45</v>
+      </c>
+      <c r="G36" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H21" s="12">
-        <v>3</v>
-      </c>
-      <c r="I21" s="12">
-        <v>1</v>
-      </c>
-      <c r="J21" s="12">
-        <v>3</v>
-      </c>
-      <c r="K21" s="12">
-        <v>3</v>
-      </c>
-      <c r="L21" s="18">
+      <c r="H36" s="12">
+        <v>3</v>
+      </c>
+      <c r="I36" s="12">
+        <v>1</v>
+      </c>
+      <c r="J36" s="12">
+        <v>4</v>
+      </c>
+      <c r="K36" s="12">
+        <v>4</v>
+      </c>
+      <c r="L36" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="M21" s="18" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="M36" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
-      <c r="S21" s="8" t="s">
+      <c r="N36" s="15"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="S36" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="7">
-        <v>236012</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="D22" s="9" t="s">
+    <row r="37" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="7">
+        <v>251007</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="D37" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="10">
-        <v>26421</v>
-      </c>
-      <c r="F22" s="11">
+      <c r="E37" s="10">
+        <v>30522</v>
+      </c>
+      <c r="F37" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>54</v>
-      </c>
-      <c r="G22" s="11">
+        <v>43</v>
+      </c>
+      <c r="G37" s="11">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H37" s="12">
+        <v>4</v>
+      </c>
+      <c r="I37" s="12">
+        <v>1</v>
+      </c>
+      <c r="J37" s="12">
+        <v>3</v>
+      </c>
+      <c r="K37" s="12">
+        <v>4</v>
+      </c>
+      <c r="L37" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M37" s="13" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="S37" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="8">
+        <v>242012</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E38" s="16">
+        <v>28064</v>
+      </c>
+      <c r="F38" s="17">
+        <f t="shared" ca="1" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="G38" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H38" s="12">
+        <v>3</v>
+      </c>
+      <c r="I38" s="12">
+        <v>1</v>
+      </c>
+      <c r="J38" s="12">
+        <v>4</v>
+      </c>
+      <c r="K38" s="12">
+        <v>5</v>
+      </c>
+      <c r="L38" s="18">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.7</v>
+      </c>
+      <c r="M38" s="18" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N38" s="15"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="S38" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="7">
+        <v>257039</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E39" s="10">
+        <v>32578</v>
+      </c>
+      <c r="F39" s="11">
+        <f t="shared" ca="1" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="G39" s="11">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H39" s="12">
+        <v>4</v>
+      </c>
+      <c r="I39" s="12">
+        <v>3</v>
+      </c>
+      <c r="J39" s="12">
+        <v>4</v>
+      </c>
+      <c r="K39" s="12">
+        <v>4</v>
+      </c>
+      <c r="L39" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.1</v>
+      </c>
+      <c r="M39" s="13" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
+      <c r="S39" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="8">
+        <v>244023</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40" s="16">
+        <v>27775</v>
+      </c>
+      <c r="F40" s="17">
+        <f t="shared" ca="1" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="G40" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H22" s="12">
-        <v>3</v>
-      </c>
-      <c r="I22" s="12">
-        <v>1</v>
-      </c>
-      <c r="J22" s="12">
-        <v>3</v>
-      </c>
-      <c r="K22" s="12">
-        <v>3</v>
-      </c>
-      <c r="L22" s="13">
+      <c r="H40" s="12">
+        <v>3</v>
+      </c>
+      <c r="I40" s="12">
+        <v>1</v>
+      </c>
+      <c r="J40" s="12">
+        <v>3</v>
+      </c>
+      <c r="K40" s="12">
+        <v>4</v>
+      </c>
+      <c r="L40" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="M22" s="13" t="str">
+        <v>2.4</v>
+      </c>
+      <c r="M40" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="9"/>
-      <c r="S22" s="7" t="s">
+      <c r="N40" s="15"/>
+      <c r="O40" s="15"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15"/>
+      <c r="S40" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="23" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="8">
-        <v>250042</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23" s="16">
-        <v>26738</v>
-      </c>
-      <c r="F23" s="17">
+    <row r="41" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="7">
+        <v>241009</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E41" s="10">
+        <v>28315</v>
+      </c>
+      <c r="F41" s="11">
         <f t="shared" ca="1" si="3"/>
-        <v>53</v>
-      </c>
-      <c r="G23" s="17">
+        <v>49</v>
+      </c>
+      <c r="G41" s="11">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H41" s="12">
+        <v>4</v>
+      </c>
+      <c r="I41" s="12">
+        <v>3</v>
+      </c>
+      <c r="J41" s="12">
+        <v>4</v>
+      </c>
+      <c r="K41" s="12">
+        <v>5</v>
+      </c>
+      <c r="L41" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.3</v>
+      </c>
+      <c r="M41" s="13" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
+      <c r="S41" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="8">
+        <v>368001</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" s="16">
+        <v>30299</v>
+      </c>
+      <c r="F42" s="17">
+        <f t="shared" ca="1" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="G42" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H42" s="12">
+        <v>4</v>
+      </c>
+      <c r="I42" s="12">
+        <v>5</v>
+      </c>
+      <c r="J42" s="12">
+        <v>4</v>
+      </c>
+      <c r="K42" s="12">
+        <v>3</v>
+      </c>
+      <c r="L42" s="18">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.5</v>
+      </c>
+      <c r="M42" s="18" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N42" s="15"/>
+      <c r="O42" s="15"/>
+      <c r="P42" s="15"/>
+      <c r="Q42" s="15"/>
+      <c r="S42" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="7">
+        <v>148005</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="10">
+        <v>27329</v>
+      </c>
+      <c r="F43" s="11">
+        <f t="shared" ca="1" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="G43" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H23" s="12">
-        <v>4</v>
-      </c>
-      <c r="I23" s="12">
-        <v>1</v>
-      </c>
-      <c r="J23" s="12">
-        <v>4</v>
-      </c>
-      <c r="K23" s="12">
-        <v>4</v>
-      </c>
-      <c r="L23" s="18">
+      <c r="H43" s="12">
+        <v>4</v>
+      </c>
+      <c r="I43" s="12">
+        <v>1</v>
+      </c>
+      <c r="J43" s="12">
+        <v>4</v>
+      </c>
+      <c r="K43" s="12">
+        <v>4</v>
+      </c>
+      <c r="L43" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M23" s="18" t="str">
+      <c r="M43" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-      <c r="S23" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="7">
-        <v>233034</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E24" s="10">
-        <v>25245</v>
-      </c>
-      <c r="F24" s="11">
-        <f t="shared" ca="1" si="3"/>
-        <v>57</v>
-      </c>
-      <c r="G24" s="11">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H24" s="12">
-        <v>3</v>
-      </c>
-      <c r="I24" s="12">
-        <v>1</v>
-      </c>
-      <c r="J24" s="12">
-        <v>3</v>
-      </c>
-      <c r="K24" s="12">
-        <v>4</v>
-      </c>
-      <c r="L24" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.6</v>
-      </c>
-      <c r="M24" s="13" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="9"/>
-      <c r="S24" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="8">
-        <v>268013</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E25" s="16">
-        <v>29244</v>
-      </c>
-      <c r="F25" s="17">
-        <f t="shared" ca="1" si="3"/>
-        <v>46</v>
-      </c>
-      <c r="G25" s="17">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H25" s="12">
-        <v>3</v>
-      </c>
-      <c r="I25" s="12">
-        <v>3</v>
-      </c>
-      <c r="J25" s="12">
-        <v>3</v>
-      </c>
-      <c r="K25" s="12">
-        <v>4</v>
-      </c>
-      <c r="L25" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.8</v>
-      </c>
-      <c r="M25" s="18" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-      <c r="S25" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="7">
-        <v>249010</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E26" s="10">
-        <v>27467</v>
-      </c>
-      <c r="F26" s="11">
-        <f t="shared" ca="1" si="3"/>
-        <v>51</v>
-      </c>
-      <c r="G26" s="11">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H26" s="12">
-        <v>3</v>
-      </c>
-      <c r="I26" s="12">
-        <v>1</v>
-      </c>
-      <c r="J26" s="12">
-        <v>4</v>
-      </c>
-      <c r="K26" s="12">
-        <v>4</v>
-      </c>
-      <c r="L26" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.7</v>
-      </c>
-      <c r="M26" s="13" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="9"/>
-      <c r="Q26" s="9"/>
-      <c r="S26" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="8">
-        <v>268012</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E27" s="16">
-        <v>31704</v>
-      </c>
-      <c r="F27" s="17">
-        <f t="shared" ca="1" si="3"/>
-        <v>40</v>
-      </c>
-      <c r="G27" s="17">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H27" s="12">
-        <v>3</v>
-      </c>
-      <c r="I27" s="12">
-        <v>5</v>
-      </c>
-      <c r="J27" s="12">
-        <v>4</v>
-      </c>
-      <c r="K27" s="12">
-        <v>4</v>
-      </c>
-      <c r="L27" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>3.7</v>
-      </c>
-      <c r="M27" s="18" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>Low Impact + High Risk</v>
-      </c>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
-      <c r="S27" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="7">
-        <v>238030</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" s="10">
-        <v>27404</v>
-      </c>
-      <c r="F28" s="11">
-        <f t="shared" ca="1" si="3"/>
-        <v>51</v>
-      </c>
-      <c r="G28" s="11">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H28" s="12">
-        <v>3</v>
-      </c>
-      <c r="I28" s="12">
-        <v>1</v>
-      </c>
-      <c r="J28" s="12">
-        <v>3</v>
-      </c>
-      <c r="K28" s="12">
-        <v>4</v>
-      </c>
-      <c r="L28" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.4</v>
-      </c>
-      <c r="M28" s="13" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
-      <c r="S28" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="8">
-        <v>256014</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E29" s="16">
-        <v>32349</v>
-      </c>
-      <c r="F29" s="17">
-        <f t="shared" ca="1" si="3"/>
-        <v>38</v>
-      </c>
-      <c r="G29" s="17">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H29" s="12">
-        <v>4</v>
-      </c>
-      <c r="I29" s="12">
-        <v>1</v>
-      </c>
-      <c r="J29" s="12">
-        <v>4</v>
-      </c>
-      <c r="K29" s="12">
-        <v>4</v>
-      </c>
-      <c r="L29" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.5</v>
-      </c>
-      <c r="M29" s="18" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="15"/>
-      <c r="S29" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="7">
-        <v>443003</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" s="10">
-        <v>28572</v>
-      </c>
-      <c r="F30" s="11">
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="9"/>
+      <c r="S43" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="7">
+        <v>267071</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" s="10">
+        <v>28726</v>
+      </c>
+      <c r="F44" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>48</v>
       </c>
-      <c r="G30" s="11">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H30" s="12">
-        <v>4</v>
-      </c>
-      <c r="I30" s="12">
-        <v>1</v>
-      </c>
-      <c r="J30" s="12">
-        <v>4</v>
-      </c>
-      <c r="K30" s="12">
-        <v>5</v>
-      </c>
-      <c r="L30" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.7</v>
-      </c>
-      <c r="M30" s="13" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="9"/>
-      <c r="S30" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="8">
-        <v>254057</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E31" s="16">
-        <v>32420</v>
-      </c>
-      <c r="F31" s="17">
-        <f t="shared" ca="1" si="3"/>
-        <v>38</v>
-      </c>
-      <c r="G31" s="17">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H31" s="12">
-        <v>4</v>
-      </c>
-      <c r="I31" s="12">
-        <v>1</v>
-      </c>
-      <c r="J31" s="12">
-        <v>4</v>
-      </c>
-      <c r="K31" s="12">
-        <v>4</v>
-      </c>
-      <c r="L31" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.5</v>
-      </c>
-      <c r="M31" s="18" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="15"/>
-      <c r="S31" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="7">
-        <v>237011</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="10">
-        <v>25410</v>
-      </c>
-      <c r="F32" s="11">
-        <f t="shared" ca="1" si="3"/>
-        <v>57</v>
-      </c>
-      <c r="G32" s="11">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H32" s="12">
-        <v>4</v>
-      </c>
-      <c r="I32" s="12">
-        <v>1</v>
-      </c>
-      <c r="J32" s="12">
-        <v>4</v>
-      </c>
-      <c r="K32" s="12">
-        <v>5</v>
-      </c>
-      <c r="L32" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>3.1</v>
-      </c>
-      <c r="M32" s="13" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="9"/>
-      <c r="S32" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="8">
-        <v>267096</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E33" s="16">
-        <v>32140</v>
-      </c>
-      <c r="F33" s="17">
-        <f t="shared" ca="1" si="3"/>
-        <v>38</v>
-      </c>
-      <c r="G33" s="17">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H33" s="12">
-        <v>4</v>
-      </c>
-      <c r="I33" s="12">
-        <v>3</v>
-      </c>
-      <c r="J33" s="12">
-        <v>4</v>
-      </c>
-      <c r="K33" s="12">
-        <v>4</v>
-      </c>
-      <c r="L33" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>3.1</v>
-      </c>
-      <c r="M33" s="18" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="15"/>
-      <c r="S33" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="7">
-        <v>249048</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E34" s="10">
-        <v>29299</v>
-      </c>
-      <c r="F34" s="11">
-        <f t="shared" ca="1" si="3"/>
-        <v>46</v>
-      </c>
-      <c r="G34" s="11">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H34" s="12">
-        <v>4</v>
-      </c>
-      <c r="I34" s="12">
-        <v>1</v>
-      </c>
-      <c r="J34" s="12">
-        <v>4</v>
-      </c>
-      <c r="K34" s="12">
-        <v>5</v>
-      </c>
-      <c r="L34" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.7</v>
-      </c>
-      <c r="M34" s="13" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="9"/>
-      <c r="S34" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="8">
-        <v>269022</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E35" s="16">
-        <v>30852</v>
-      </c>
-      <c r="F35" s="17">
-        <f t="shared" ca="1" si="3"/>
-        <v>42</v>
-      </c>
-      <c r="G35" s="17">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H35" s="12">
-        <v>4</v>
-      </c>
-      <c r="I35" s="12">
-        <v>3</v>
-      </c>
-      <c r="J35" s="12">
-        <v>4</v>
-      </c>
-      <c r="K35" s="12">
-        <v>4</v>
-      </c>
-      <c r="L35" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>3.1</v>
-      </c>
-      <c r="M35" s="18" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N35" s="15"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="15"/>
-      <c r="S35" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="7">
-        <v>253014</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E36" s="10">
-        <v>30611</v>
-      </c>
-      <c r="F36" s="11">
-        <f t="shared" ca="1" si="3"/>
-        <v>43</v>
-      </c>
-      <c r="G36" s="11">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H36" s="12">
-        <v>3</v>
-      </c>
-      <c r="I36" s="12">
-        <v>1</v>
-      </c>
-      <c r="J36" s="12">
-        <v>3</v>
-      </c>
-      <c r="K36" s="12">
-        <v>4</v>
-      </c>
-      <c r="L36" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="M36" s="13" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="9"/>
-      <c r="S36" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="8">
-        <v>248031</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E37" s="16">
-        <v>29617</v>
-      </c>
-      <c r="F37" s="17">
-        <f t="shared" ca="1" si="3"/>
-        <v>45</v>
-      </c>
-      <c r="G37" s="17">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H37" s="12">
-        <v>3</v>
-      </c>
-      <c r="I37" s="12">
-        <v>1</v>
-      </c>
-      <c r="J37" s="12">
-        <v>4</v>
-      </c>
-      <c r="K37" s="12">
-        <v>4</v>
-      </c>
-      <c r="L37" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.5</v>
-      </c>
-      <c r="M37" s="18" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N37" s="15"/>
-      <c r="O37" s="15"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="15"/>
-      <c r="S37" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="7">
-        <v>251007</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E38" s="10">
-        <v>30522</v>
-      </c>
-      <c r="F38" s="11">
-        <f t="shared" ca="1" si="3"/>
-        <v>43</v>
-      </c>
-      <c r="G38" s="11">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H38" s="12">
-        <v>4</v>
-      </c>
-      <c r="I38" s="12">
-        <v>1</v>
-      </c>
-      <c r="J38" s="12">
-        <v>3</v>
-      </c>
-      <c r="K38" s="12">
-        <v>4</v>
-      </c>
-      <c r="L38" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="M38" s="13" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="9"/>
-      <c r="S38" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="8">
-        <v>242012</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E39" s="16">
-        <v>28064</v>
-      </c>
-      <c r="F39" s="17">
-        <f t="shared" ca="1" si="3"/>
-        <v>49</v>
-      </c>
-      <c r="G39" s="17">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H39" s="12">
-        <v>3</v>
-      </c>
-      <c r="I39" s="12">
-        <v>1</v>
-      </c>
-      <c r="J39" s="12">
-        <v>4</v>
-      </c>
-      <c r="K39" s="12">
-        <v>5</v>
-      </c>
-      <c r="L39" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.7</v>
-      </c>
-      <c r="M39" s="18" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N39" s="15"/>
-      <c r="O39" s="15"/>
-      <c r="P39" s="15"/>
-      <c r="Q39" s="15"/>
-      <c r="S39" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="7">
-        <v>257039</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E40" s="10">
-        <v>32578</v>
-      </c>
-      <c r="F40" s="11">
-        <f t="shared" ca="1" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="G40" s="11">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H40" s="12">
-        <v>4</v>
-      </c>
-      <c r="I40" s="12">
-        <v>3</v>
-      </c>
-      <c r="J40" s="12">
-        <v>4</v>
-      </c>
-      <c r="K40" s="12">
-        <v>4</v>
-      </c>
-      <c r="L40" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>3.1</v>
-      </c>
-      <c r="M40" s="13" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
-      <c r="P40" s="9"/>
-      <c r="Q40" s="9"/>
-      <c r="S40" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="8">
-        <v>244023</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E41" s="16">
-        <v>27775</v>
-      </c>
-      <c r="F41" s="17">
-        <f t="shared" ca="1" si="3"/>
-        <v>50</v>
-      </c>
-      <c r="G41" s="17">
-        <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H41" s="12">
-        <v>3</v>
-      </c>
-      <c r="I41" s="12">
-        <v>1</v>
-      </c>
-      <c r="J41" s="12">
-        <v>3</v>
-      </c>
-      <c r="K41" s="12">
-        <v>4</v>
-      </c>
-      <c r="L41" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.4</v>
-      </c>
-      <c r="M41" s="18" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N41" s="15"/>
-      <c r="O41" s="15"/>
-      <c r="P41" s="15"/>
-      <c r="Q41" s="15"/>
-      <c r="S41" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="7">
-        <v>241009</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E42" s="10">
-        <v>28315</v>
-      </c>
-      <c r="F42" s="11">
-        <f t="shared" ca="1" si="3"/>
-        <v>49</v>
-      </c>
-      <c r="G42" s="11">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H42" s="12">
-        <v>4</v>
-      </c>
-      <c r="I42" s="12">
-        <v>3</v>
-      </c>
-      <c r="J42" s="12">
-        <v>4</v>
-      </c>
-      <c r="K42" s="12">
-        <v>5</v>
-      </c>
-      <c r="L42" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>3.3</v>
-      </c>
-      <c r="M42" s="13" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N42" s="9"/>
-      <c r="O42" s="9"/>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="9"/>
-      <c r="S42" s="7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="8">
-        <v>368001</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E43" s="16">
-        <v>30299</v>
-      </c>
-      <c r="F43" s="17">
-        <f t="shared" ca="1" si="3"/>
-        <v>43</v>
-      </c>
-      <c r="G43" s="17">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H43" s="12">
-        <v>4</v>
-      </c>
-      <c r="I43" s="12">
-        <v>5</v>
-      </c>
-      <c r="J43" s="12">
-        <v>4</v>
-      </c>
-      <c r="K43" s="12">
-        <v>3</v>
-      </c>
-      <c r="L43" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>3.5</v>
-      </c>
-      <c r="M43" s="18" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>High Impact + High Risk</v>
-      </c>
-      <c r="N43" s="15"/>
-      <c r="O43" s="15"/>
-      <c r="P43" s="15"/>
-      <c r="Q43" s="15"/>
-      <c r="S43" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="7">
-        <v>148005</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E44" s="10">
-        <v>27329</v>
-      </c>
-      <c r="F44" s="11">
-        <f t="shared" ca="1" si="3"/>
-        <v>51</v>
-      </c>
       <c r="G44" s="11">
         <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H44" s="12">
+        <v>4</v>
+      </c>
+      <c r="I44" s="12">
+        <v>1</v>
+      </c>
+      <c r="J44" s="12">
         <v>2</v>
       </c>
-      <c r="H44" s="12">
-        <v>4</v>
-      </c>
-      <c r="I44" s="12">
-        <v>1</v>
-      </c>
-      <c r="J44" s="12">
-        <v>4</v>
-      </c>
       <c r="K44" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L44" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="M44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4502,30 +4500,30 @@
       <c r="P44" s="9"/>
       <c r="Q44" s="9"/>
       <c r="S44" s="7" t="s">
-        <v>178</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="7">
-        <v>267071</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D45" s="9" t="s">
+      <c r="A45" s="8">
+        <v>268051</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D45" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E45" s="10">
-        <v>28726</v>
-      </c>
-      <c r="F45" s="11">
+      <c r="E45" s="16">
+        <v>37469</v>
+      </c>
+      <c r="F45" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>48</v>
-      </c>
-      <c r="G45" s="11">
+        <v>24</v>
+      </c>
+      <c r="G45" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
@@ -4533,7 +4531,7 @@
         <v>4</v>
       </c>
       <c r="I45" s="12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J45" s="12">
         <v>2</v>
@@ -4541,199 +4539,197 @@
       <c r="K45" s="12">
         <v>2</v>
       </c>
-      <c r="L45" s="13">
+      <c r="L45" s="18">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.7</v>
+      </c>
+      <c r="M45" s="18" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N45" s="15"/>
+      <c r="O45" s="15"/>
+      <c r="P45" s="15"/>
+      <c r="Q45" s="15"/>
+      <c r="S45" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="7">
+        <v>269032</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E46" s="10">
+        <v>30484</v>
+      </c>
+      <c r="F46" s="11">
+        <f t="shared" ca="1" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="G46" s="11">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H46" s="12">
+        <v>4</v>
+      </c>
+      <c r="I46" s="12">
+        <v>3</v>
+      </c>
+      <c r="J46" s="12">
+        <v>2</v>
+      </c>
+      <c r="K46" s="12">
+        <v>2</v>
+      </c>
+      <c r="L46" s="13">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.1</v>
+      </c>
+      <c r="M46" s="13" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N46" s="9"/>
+      <c r="O46" s="9"/>
+      <c r="P46" s="9"/>
+      <c r="Q46" s="9"/>
+      <c r="S46" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="8">
+        <v>250051</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" s="16">
+        <v>29866</v>
+      </c>
+      <c r="F47" s="17">
+        <f t="shared" ca="1" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="G47" s="17">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H47" s="12">
+        <v>4</v>
+      </c>
+      <c r="I47" s="12">
+        <v>1</v>
+      </c>
+      <c r="J47" s="12">
+        <v>2</v>
+      </c>
+      <c r="K47" s="12">
+        <v>2</v>
+      </c>
+      <c r="L47" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="M45" s="13" t="str">
+      <c r="M47" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N45" s="9"/>
-      <c r="O45" s="9"/>
-      <c r="P45" s="9"/>
-      <c r="Q45" s="9"/>
-      <c r="S45" s="7" t="s">
+      <c r="N47" s="15"/>
+      <c r="O47" s="15"/>
+      <c r="P47" s="15"/>
+      <c r="Q47" s="15"/>
+      <c r="S47" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="46" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="8">
-        <v>268051</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D46" s="15" t="s">
+    <row r="48" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="7">
+        <v>146037</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D48" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E46" s="16">
-        <v>37469</v>
-      </c>
-      <c r="F46" s="17">
-        <f t="shared" ca="1" si="3"/>
-        <v>24</v>
-      </c>
-      <c r="G46" s="17">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H46" s="12">
-        <v>4</v>
-      </c>
-      <c r="I46" s="12">
+      <c r="E48" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F48" s="11">
+        <v>60</v>
+      </c>
+      <c r="G48" s="11">
         <v>5</v>
       </c>
-      <c r="J46" s="12">
-        <v>2</v>
-      </c>
-      <c r="K46" s="12">
-        <v>2</v>
-      </c>
-      <c r="L46" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.7</v>
-      </c>
-      <c r="M46" s="18" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N46" s="15"/>
-      <c r="O46" s="15"/>
-      <c r="P46" s="15"/>
-      <c r="Q46" s="15"/>
-      <c r="S46" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="7">
-        <v>269032</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D47" s="9" t="s">
+      <c r="H48" s="12">
+        <v>5</v>
+      </c>
+      <c r="I48" s="12">
+        <v>3</v>
+      </c>
+      <c r="J48" s="12">
+        <v>4</v>
+      </c>
+      <c r="K48" s="12">
+        <v>5</v>
+      </c>
+      <c r="L48" s="13">
+        <f t="shared" ref="L48:L68" si="6">IF(OR(I48="",J48="",K48="",G48=""),"",ROUND(G48*0.2+I48*0.3+J48*0.3+K48*0.2,2))</f>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="M48" s="13" t="str">
+        <f t="shared" ref="M48:M68" si="7">IF(OR(H48="",L48=""),"",IF(AND(H48&gt;=4,L48&gt;=3.5),"High Impact + High Risk",IF(AND(H48&gt;=4,L48&lt;3.5),"High Impact + Low Risk",IF(AND(H48&lt;4,L48&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N48" s="9"/>
+      <c r="O48" s="9"/>
+      <c r="P48" s="9"/>
+      <c r="Q48" s="9"/>
+      <c r="S48" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="8">
+        <v>139013</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="D49" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E47" s="10">
-        <v>30484</v>
-      </c>
-      <c r="F47" s="11">
-        <f t="shared" ca="1" si="3"/>
-        <v>43</v>
-      </c>
-      <c r="G47" s="11">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H47" s="12">
-        <v>4</v>
-      </c>
-      <c r="I47" s="12">
-        <v>3</v>
-      </c>
-      <c r="J47" s="12">
-        <v>2</v>
-      </c>
-      <c r="K47" s="12">
-        <v>2</v>
-      </c>
-      <c r="L47" s="13">
-        <f t="shared" ca="1" si="1"/>
-        <v>2.1</v>
-      </c>
-      <c r="M47" s="13" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N47" s="9"/>
-      <c r="O47" s="9"/>
-      <c r="P47" s="9"/>
-      <c r="Q47" s="9"/>
-      <c r="S47" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="8">
-        <v>250051</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E48" s="16">
-        <v>29866</v>
-      </c>
-      <c r="F48" s="17">
-        <f t="shared" ca="1" si="3"/>
-        <v>45</v>
-      </c>
-      <c r="G48" s="17">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H48" s="12">
-        <v>4</v>
-      </c>
-      <c r="I48" s="12">
-        <v>1</v>
-      </c>
-      <c r="J48" s="12">
-        <v>2</v>
-      </c>
-      <c r="K48" s="12">
-        <v>2</v>
-      </c>
-      <c r="L48" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="M48" s="18" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N48" s="15"/>
-      <c r="O48" s="15"/>
-      <c r="P48" s="15"/>
-      <c r="Q48" s="15"/>
-      <c r="S48" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="7">
-        <v>146037</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E49" s="10" t="s">
+      <c r="E49" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="F49" s="11">
-        <v>60</v>
-      </c>
-      <c r="G49" s="11">
-        <v>5</v>
+      <c r="F49" s="17">
+        <v>58</v>
+      </c>
+      <c r="G49" s="17">
+        <v>4</v>
       </c>
       <c r="H49" s="12">
         <v>5</v>
@@ -4747,196 +4743,196 @@
       <c r="K49" s="12">
         <v>5</v>
       </c>
-      <c r="L49" s="13">
-        <f t="shared" ref="L49:L69" si="6">IF(OR(I49="",J49="",K49="",G49=""),"",ROUND(G49*0.2+I49*0.3+J49*0.3+K49*0.2,2))</f>
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="M49" s="13" t="str">
-        <f t="shared" ref="M49:M69" si="7">IF(OR(H49="",L49=""),"",IF(AND(H49&gt;=4,L49&gt;=3.5),"High Impact + High Risk",IF(AND(H49&gt;=4,L49&lt;3.5),"High Impact + Low Risk",IF(AND(H49&lt;4,L49&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
-        <v>High Impact + High Risk</v>
-      </c>
-      <c r="N49" s="9"/>
-      <c r="O49" s="9"/>
-      <c r="P49" s="9"/>
-      <c r="Q49" s="9"/>
-      <c r="S49" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="8">
-        <v>139013</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E50" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="F50" s="17">
-        <v>58</v>
-      </c>
-      <c r="G50" s="17">
-        <v>4</v>
-      </c>
-      <c r="H50" s="12">
-        <v>5</v>
-      </c>
-      <c r="I50" s="12">
-        <v>3</v>
-      </c>
-      <c r="J50" s="12">
-        <v>4</v>
-      </c>
-      <c r="K50" s="12">
-        <v>5</v>
-      </c>
-      <c r="L50" s="18">
+      <c r="L49" s="18">
         <f t="shared" si="6"/>
         <v>3.9</v>
       </c>
-      <c r="M50" s="18" t="str">
+      <c r="M49" s="18" t="str">
         <f t="shared" si="7"/>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N50" s="15"/>
-      <c r="O50" s="15"/>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="15"/>
-      <c r="S50" s="8" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="7">
+      <c r="N49" s="15"/>
+      <c r="O49" s="15"/>
+      <c r="P49" s="15"/>
+      <c r="Q49" s="15"/>
+      <c r="S49" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="7">
         <v>145015</v>
       </c>
-      <c r="B51" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="D51" s="9" t="s">
+      <c r="B50" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E51" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="F51" s="11">
+      <c r="E50" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F50" s="11">
         <v>50</v>
       </c>
-      <c r="G51" s="11">
+      <c r="G50" s="11">
         <v>2</v>
       </c>
-      <c r="H51" s="12">
-        <v>4</v>
-      </c>
-      <c r="I51" s="12">
-        <v>3</v>
-      </c>
-      <c r="J51" s="12">
-        <v>4</v>
-      </c>
-      <c r="K51" s="12">
-        <v>4</v>
-      </c>
-      <c r="L51" s="13">
+      <c r="H50" s="12">
+        <v>4</v>
+      </c>
+      <c r="I50" s="12">
+        <v>3</v>
+      </c>
+      <c r="J50" s="12">
+        <v>4</v>
+      </c>
+      <c r="K50" s="12">
+        <v>4</v>
+      </c>
+      <c r="L50" s="13">
         <f t="shared" si="6"/>
         <v>3.3</v>
       </c>
-      <c r="M51" s="13" t="str">
+      <c r="M50" s="13" t="str">
         <f t="shared" si="7"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N51" s="9"/>
-      <c r="O51" s="9"/>
-      <c r="P51" s="9"/>
-      <c r="Q51" s="9"/>
-      <c r="S51" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="8">
+      <c r="N50" s="9"/>
+      <c r="O50" s="9"/>
+      <c r="P50" s="9"/>
+      <c r="Q50" s="9"/>
+      <c r="S50" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="8">
         <v>161005</v>
       </c>
-      <c r="B52" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="D52" s="15" t="s">
+      <c r="B51" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="D51" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E52" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="F52" s="17">
+      <c r="E51" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="F51" s="17">
         <v>45</v>
       </c>
-      <c r="G52" s="17">
-        <v>1</v>
-      </c>
-      <c r="H52" s="12">
+      <c r="G51" s="17">
+        <v>1</v>
+      </c>
+      <c r="H51" s="12">
         <v>2</v>
       </c>
-      <c r="I52" s="12">
-        <v>1</v>
-      </c>
-      <c r="J52" s="12">
-        <v>3</v>
-      </c>
-      <c r="K52" s="12">
-        <v>3</v>
-      </c>
-      <c r="L52" s="18">
+      <c r="I51" s="12">
+        <v>1</v>
+      </c>
+      <c r="J51" s="12">
+        <v>3</v>
+      </c>
+      <c r="K51" s="12">
+        <v>3</v>
+      </c>
+      <c r="L51" s="18">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="M52" s="18" t="str">
+      <c r="M51" s="18" t="str">
         <f t="shared" si="7"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N52" s="15"/>
-      <c r="O52" s="15"/>
-      <c r="P52" s="15"/>
-      <c r="Q52" s="15"/>
-      <c r="S52" s="8" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="7">
+      <c r="N51" s="15"/>
+      <c r="O51" s="15"/>
+      <c r="P51" s="15"/>
+      <c r="Q51" s="15"/>
+      <c r="S51" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="7">
         <v>163003</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B52" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F52" s="11">
+        <v>34</v>
+      </c>
+      <c r="G52" s="11">
+        <v>1</v>
+      </c>
+      <c r="H52" s="12">
+        <v>3</v>
+      </c>
+      <c r="I52" s="12">
+        <v>3</v>
+      </c>
+      <c r="J52" s="12">
+        <v>2</v>
+      </c>
+      <c r="K52" s="12">
+        <v>3</v>
+      </c>
+      <c r="L52" s="13">
+        <f t="shared" si="6"/>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M52" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N52" s="9"/>
+      <c r="O52" s="9"/>
+      <c r="P52" s="9"/>
+      <c r="Q52" s="9"/>
+      <c r="S52" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="8">
+        <v>166024</v>
+      </c>
+      <c r="B53" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="C53" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="D53" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="F53" s="11">
-        <v>34</v>
-      </c>
-      <c r="G53" s="11">
+      <c r="F53" s="17">
+        <v>27</v>
+      </c>
+      <c r="G53" s="17">
         <v>1</v>
       </c>
       <c r="H53" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I53" s="12">
         <v>3</v>
@@ -4947,99 +4943,99 @@
       <c r="K53" s="12">
         <v>3</v>
       </c>
-      <c r="L53" s="13">
+      <c r="L53" s="18">
         <f t="shared" si="6"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="M53" s="13" t="str">
+      <c r="M53" s="18" t="str">
         <f t="shared" si="7"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N53" s="9"/>
-      <c r="O53" s="9"/>
-      <c r="P53" s="9"/>
-      <c r="Q53" s="9"/>
-      <c r="S53" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="8">
-        <v>166024</v>
-      </c>
-      <c r="B54" s="15" t="s">
+      <c r="N53" s="15"/>
+      <c r="O53" s="15"/>
+      <c r="P53" s="15"/>
+      <c r="Q53" s="15"/>
+      <c r="S53" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="7">
+        <v>167001</v>
+      </c>
+      <c r="B54" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="D54" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E54" s="16" t="s">
+      <c r="E54" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="F54" s="17">
-        <v>27</v>
-      </c>
-      <c r="G54" s="17">
+      <c r="F54" s="11">
+        <v>37</v>
+      </c>
+      <c r="G54" s="11">
         <v>1</v>
       </c>
       <c r="H54" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I54" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J54" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K54" s="12">
         <v>3</v>
       </c>
-      <c r="L54" s="18">
+      <c r="L54" s="13">
         <f t="shared" si="6"/>
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="M54" s="18" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="M54" s="13" t="str">
         <f t="shared" si="7"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N54" s="15"/>
-      <c r="O54" s="15"/>
-      <c r="P54" s="15"/>
-      <c r="Q54" s="15"/>
-      <c r="S54" s="8" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="7">
-        <v>167001</v>
-      </c>
-      <c r="B55" s="9" t="s">
+      <c r="N54" s="9"/>
+      <c r="O54" s="9"/>
+      <c r="P54" s="9"/>
+      <c r="Q54" s="9"/>
+      <c r="S54" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="8">
+        <v>167012</v>
+      </c>
+      <c r="B55" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C55" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="D55" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="F55" s="11">
-        <v>37</v>
-      </c>
-      <c r="G55" s="11">
+      <c r="F55" s="17">
+        <v>31</v>
+      </c>
+      <c r="G55" s="17">
         <v>1</v>
       </c>
       <c r="H55" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I55" s="12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J55" s="12">
         <v>3</v>
@@ -5047,431 +5043,431 @@
       <c r="K55" s="12">
         <v>3</v>
       </c>
-      <c r="L55" s="13">
+      <c r="L55" s="18">
         <f t="shared" si="6"/>
-        <v>3.2</v>
-      </c>
-      <c r="M55" s="13" t="str">
+        <v>2.6</v>
+      </c>
+      <c r="M55" s="18" t="str">
         <f t="shared" si="7"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N55" s="9"/>
-      <c r="O55" s="9"/>
-      <c r="P55" s="9"/>
-      <c r="Q55" s="9"/>
-      <c r="S55" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="8">
-        <v>167012</v>
-      </c>
-      <c r="B56" s="15" t="s">
+      <c r="N55" s="15"/>
+      <c r="O55" s="15"/>
+      <c r="P55" s="15"/>
+      <c r="Q55" s="15"/>
+      <c r="S55" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="7">
+        <v>260001</v>
+      </c>
+      <c r="B56" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="D56" s="15" t="s">
+      <c r="D56" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E56" s="16" t="s">
+      <c r="E56" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="F56" s="17">
+      <c r="F56" s="11">
+        <v>35</v>
+      </c>
+      <c r="G56" s="11">
+        <v>1</v>
+      </c>
+      <c r="H56" s="12">
+        <v>5</v>
+      </c>
+      <c r="I56" s="12">
+        <v>4</v>
+      </c>
+      <c r="J56" s="12">
+        <v>4</v>
+      </c>
+      <c r="K56" s="12">
+        <v>5</v>
+      </c>
+      <c r="L56" s="13">
+        <f t="shared" si="6"/>
+        <v>3.6</v>
+      </c>
+      <c r="M56" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N56" s="9"/>
+      <c r="O56" s="9"/>
+      <c r="P56" s="9"/>
+      <c r="Q56" s="9"/>
+      <c r="S56" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="8">
+        <v>267001</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="F57" s="17">
         <v>31</v>
       </c>
-      <c r="G56" s="17">
-        <v>1</v>
-      </c>
-      <c r="H56" s="12">
-        <v>2</v>
-      </c>
-      <c r="I56" s="12">
-        <v>3</v>
-      </c>
-      <c r="J56" s="12">
-        <v>3</v>
-      </c>
-      <c r="K56" s="12">
-        <v>3</v>
-      </c>
-      <c r="L56" s="18">
+      <c r="G57" s="17">
+        <v>1</v>
+      </c>
+      <c r="H57" s="12">
+        <v>3</v>
+      </c>
+      <c r="I57" s="12">
+        <v>4</v>
+      </c>
+      <c r="J57" s="12">
+        <v>3</v>
+      </c>
+      <c r="K57" s="12">
+        <v>3</v>
+      </c>
+      <c r="L57" s="18">
         <f t="shared" si="6"/>
-        <v>2.6</v>
-      </c>
-      <c r="M56" s="18" t="str">
+        <v>2.9</v>
+      </c>
+      <c r="M57" s="18" t="str">
         <f t="shared" si="7"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N56" s="15"/>
-      <c r="O56" s="15"/>
-      <c r="P56" s="15"/>
-      <c r="Q56" s="15"/>
-      <c r="S56" s="8" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="7">
-        <v>260001</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="D57" s="9" t="s">
+      <c r="N57" s="15"/>
+      <c r="O57" s="15"/>
+      <c r="P57" s="15"/>
+      <c r="Q57" s="15"/>
+      <c r="S57" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="7">
+        <v>160001</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D58" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E57" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="F57" s="11">
-        <v>35</v>
-      </c>
-      <c r="G57" s="11">
-        <v>1</v>
-      </c>
-      <c r="H57" s="12">
-        <v>5</v>
-      </c>
-      <c r="I57" s="12">
-        <v>4</v>
-      </c>
-      <c r="J57" s="12">
-        <v>4</v>
-      </c>
-      <c r="K57" s="12">
-        <v>5</v>
-      </c>
-      <c r="L57" s="13">
+      <c r="E58" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="F58" s="11">
+        <v>46</v>
+      </c>
+      <c r="G58" s="11">
+        <v>1</v>
+      </c>
+      <c r="H58" s="12">
+        <v>4</v>
+      </c>
+      <c r="I58" s="12">
+        <v>3</v>
+      </c>
+      <c r="J58" s="12">
+        <v>4</v>
+      </c>
+      <c r="K58" s="12">
+        <v>4</v>
+      </c>
+      <c r="L58" s="13">
         <f t="shared" si="6"/>
-        <v>3.6</v>
-      </c>
-      <c r="M57" s="13" t="str">
+        <v>3.1</v>
+      </c>
+      <c r="M58" s="13" t="str">
         <f t="shared" si="7"/>
-        <v>High Impact + High Risk</v>
-      </c>
-      <c r="N57" s="9"/>
-      <c r="O57" s="9"/>
-      <c r="P57" s="9"/>
-      <c r="Q57" s="9"/>
-      <c r="S57" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="8">
-        <v>267001</v>
-      </c>
-      <c r="B58" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="D58" s="15" t="s">
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N58" s="9"/>
+      <c r="O58" s="9"/>
+      <c r="P58" s="9"/>
+      <c r="Q58" s="9"/>
+      <c r="S58" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="7">
+        <v>167020</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="D59" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E58" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="F58" s="17">
-        <v>31</v>
-      </c>
-      <c r="G58" s="17">
-        <v>1</v>
-      </c>
-      <c r="H58" s="12">
-        <v>3</v>
-      </c>
-      <c r="I58" s="12">
-        <v>4</v>
-      </c>
-      <c r="J58" s="12">
-        <v>3</v>
-      </c>
-      <c r="K58" s="12">
-        <v>3</v>
-      </c>
-      <c r="L58" s="18">
+      <c r="E59" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="F59" s="11">
+        <v>51</v>
+      </c>
+      <c r="G59" s="11">
+        <v>2</v>
+      </c>
+      <c r="H59" s="12">
+        <v>3</v>
+      </c>
+      <c r="I59" s="12">
+        <v>3</v>
+      </c>
+      <c r="J59" s="12">
+        <v>3</v>
+      </c>
+      <c r="K59" s="12">
+        <v>4</v>
+      </c>
+      <c r="L59" s="13">
         <f t="shared" si="6"/>
-        <v>2.9</v>
-      </c>
-      <c r="M58" s="18" t="str">
+        <v>3</v>
+      </c>
+      <c r="M59" s="13" t="str">
         <f t="shared" si="7"/>
         <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N58" s="15"/>
-      <c r="O58" s="15"/>
-      <c r="P58" s="15"/>
-      <c r="Q58" s="15"/>
-      <c r="S58" s="8" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="7">
-        <v>160001</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="F59" s="11">
-        <v>46</v>
-      </c>
-      <c r="G59" s="11">
-        <v>1</v>
-      </c>
-      <c r="H59" s="12">
-        <v>4</v>
-      </c>
-      <c r="I59" s="12">
-        <v>3</v>
-      </c>
-      <c r="J59" s="12">
-        <v>4</v>
-      </c>
-      <c r="K59" s="12">
-        <v>4</v>
-      </c>
-      <c r="L59" s="13">
-        <f t="shared" si="6"/>
-        <v>3.1</v>
-      </c>
-      <c r="M59" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>High Impact + Low Risk</v>
       </c>
       <c r="N59" s="9"/>
       <c r="O59" s="9"/>
       <c r="P59" s="9"/>
       <c r="Q59" s="9"/>
       <c r="S59" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="7">
-        <v>167020</v>
-      </c>
-      <c r="B60" s="9" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="8">
+        <v>167029</v>
+      </c>
+      <c r="B60" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C60" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="D60" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="E60" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="F60" s="11">
-        <v>51</v>
-      </c>
-      <c r="G60" s="11">
-        <v>2</v>
+      <c r="F60" s="17">
+        <v>35</v>
+      </c>
+      <c r="G60" s="17">
+        <v>1</v>
       </c>
       <c r="H60" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I60" s="12">
         <v>3</v>
       </c>
       <c r="J60" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K60" s="12">
-        <v>4</v>
-      </c>
-      <c r="L60" s="13">
+        <v>5</v>
+      </c>
+      <c r="L60" s="18">
         <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="M60" s="13" t="str">
+        <v>3.3</v>
+      </c>
+      <c r="M60" s="18" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N60" s="15"/>
+      <c r="O60" s="15"/>
+      <c r="P60" s="15"/>
+      <c r="Q60" s="15"/>
+      <c r="S60" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="7">
+        <v>167032</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F61" s="11">
+        <v>29</v>
+      </c>
+      <c r="G61" s="11">
+        <v>1</v>
+      </c>
+      <c r="H61" s="12">
+        <v>3</v>
+      </c>
+      <c r="I61" s="12">
+        <v>5</v>
+      </c>
+      <c r="J61" s="12">
+        <v>3</v>
+      </c>
+      <c r="K61" s="12">
+        <v>3</v>
+      </c>
+      <c r="L61" s="13">
+        <f t="shared" si="6"/>
+        <v>3.2</v>
+      </c>
+      <c r="M61" s="13" t="str">
         <f t="shared" si="7"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N60" s="9"/>
-      <c r="O60" s="9"/>
-      <c r="P60" s="9"/>
-      <c r="Q60" s="9"/>
-      <c r="S60" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="8">
-        <v>167029</v>
-      </c>
-      <c r="B61" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="C61" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="D61" s="15" t="s">
+      <c r="N61" s="9"/>
+      <c r="O61" s="9"/>
+      <c r="P61" s="9"/>
+      <c r="Q61" s="9"/>
+      <c r="S61" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="8">
+        <v>168024</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="D62" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E61" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="F61" s="17">
-        <v>35</v>
-      </c>
-      <c r="G61" s="17">
-        <v>1</v>
-      </c>
-      <c r="H61" s="12">
+      <c r="E62" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="F62" s="17">
+        <v>46</v>
+      </c>
+      <c r="G62" s="17">
+        <v>1</v>
+      </c>
+      <c r="H62" s="12">
         <v>5</v>
       </c>
-      <c r="I61" s="12">
-        <v>3</v>
-      </c>
-      <c r="J61" s="12">
-        <v>4</v>
-      </c>
-      <c r="K61" s="12">
+      <c r="I62" s="12">
+        <v>3</v>
+      </c>
+      <c r="J62" s="12">
+        <v>4</v>
+      </c>
+      <c r="K62" s="12">
         <v>5</v>
       </c>
-      <c r="L61" s="18">
+      <c r="L62" s="18">
         <f t="shared" si="6"/>
         <v>3.3</v>
       </c>
-      <c r="M61" s="18" t="str">
+      <c r="M62" s="18" t="str">
         <f t="shared" si="7"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N61" s="15"/>
-      <c r="O61" s="15"/>
-      <c r="P61" s="15"/>
-      <c r="Q61" s="15"/>
-      <c r="S61" s="8" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="7">
-        <v>167032</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="D62" s="9" t="s">
+      <c r="N62" s="15"/>
+      <c r="O62" s="15"/>
+      <c r="P62" s="15"/>
+      <c r="Q62" s="15"/>
+      <c r="S62" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="8">
+        <v>337004</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="D63" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E62" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="F62" s="11">
-        <v>29</v>
-      </c>
-      <c r="G62" s="11">
-        <v>1</v>
-      </c>
-      <c r="H62" s="12">
-        <v>3</v>
-      </c>
-      <c r="I62" s="12">
-        <v>5</v>
-      </c>
-      <c r="J62" s="12">
-        <v>3</v>
-      </c>
-      <c r="K62" s="12">
-        <v>3</v>
-      </c>
-      <c r="L62" s="13">
+      <c r="E63" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="F63" s="17">
+        <v>55</v>
+      </c>
+      <c r="G63" s="17">
+        <v>3</v>
+      </c>
+      <c r="H63" s="12">
+        <v>3</v>
+      </c>
+      <c r="I63" s="12">
+        <v>1</v>
+      </c>
+      <c r="J63" s="12">
+        <v>3</v>
+      </c>
+      <c r="K63" s="12">
+        <v>4</v>
+      </c>
+      <c r="L63" s="18">
         <f t="shared" si="6"/>
-        <v>3.2</v>
-      </c>
-      <c r="M62" s="13" t="str">
+        <v>2.6</v>
+      </c>
+      <c r="M63" s="18" t="str">
         <f t="shared" si="7"/>
         <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N62" s="9"/>
-      <c r="O62" s="9"/>
-      <c r="P62" s="9"/>
-      <c r="Q62" s="9"/>
-      <c r="S62" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="8">
-        <v>168024</v>
-      </c>
-      <c r="B63" s="15" t="s">
-        <v>231</v>
-      </c>
-      <c r="C63" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="D63" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E63" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="F63" s="17">
-        <v>46</v>
-      </c>
-      <c r="G63" s="17">
-        <v>1</v>
-      </c>
-      <c r="H63" s="12">
-        <v>5</v>
-      </c>
-      <c r="I63" s="12">
-        <v>3</v>
-      </c>
-      <c r="J63" s="12">
-        <v>4</v>
-      </c>
-      <c r="K63" s="12">
-        <v>5</v>
-      </c>
-      <c r="L63" s="18">
-        <f t="shared" si="6"/>
-        <v>3.3</v>
-      </c>
-      <c r="M63" s="18" t="str">
-        <f t="shared" si="7"/>
-        <v>High Impact + Low Risk</v>
       </c>
       <c r="N63" s="15"/>
       <c r="O63" s="15"/>
       <c r="P63" s="15"/>
       <c r="Q63" s="15"/>
       <c r="S63" s="8" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="8">
-        <v>337004</v>
+        <v>268044</v>
       </c>
       <c r="B64" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C64" s="15" t="s">
         <v>234</v>
-      </c>
-      <c r="C64" s="15" t="s">
-        <v>235</v>
       </c>
       <c r="D64" s="15" t="s">
         <v>90</v>
@@ -5480,26 +5476,26 @@
         <v>236</v>
       </c>
       <c r="F64" s="17">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="G64" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H64" s="12">
         <v>3</v>
       </c>
       <c r="I64" s="12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J64" s="12">
         <v>3</v>
       </c>
       <c r="K64" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L64" s="18">
         <f t="shared" si="6"/>
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="M64" s="18" t="str">
         <f t="shared" si="7"/>
@@ -5510,229 +5506,238 @@
       <c r="P64" s="15"/>
       <c r="Q64" s="15"/>
       <c r="S64" s="8" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="8">
-        <v>268044</v>
-      </c>
-      <c r="B65" s="15" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="7">
+        <v>368004</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C65" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="C65" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="D65" s="15" t="s">
+      <c r="D65" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E65" s="16" t="s">
+      <c r="E65" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="F65" s="17">
-        <v>28</v>
-      </c>
-      <c r="G65" s="17">
-        <v>1</v>
+      <c r="F65" s="11">
+        <v>59</v>
+      </c>
+      <c r="G65" s="11">
+        <v>4</v>
       </c>
       <c r="H65" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I65" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J65" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K65" s="12">
-        <v>3</v>
-      </c>
-      <c r="L65" s="18">
+        <v>4</v>
+      </c>
+      <c r="L65" s="13">
+        <f t="shared" si="6"/>
+        <v>3.7</v>
+      </c>
+      <c r="M65" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N65" s="9"/>
+      <c r="O65" s="9"/>
+      <c r="P65" s="9"/>
+      <c r="Q65" s="9"/>
+      <c r="S65" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="8">
+        <v>269040</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="F66" s="17">
+        <v>45</v>
+      </c>
+      <c r="G66" s="17">
+        <v>1</v>
+      </c>
+      <c r="H66" s="12">
+        <v>4</v>
+      </c>
+      <c r="I66" s="12">
+        <v>3</v>
+      </c>
+      <c r="J66" s="12">
+        <v>4</v>
+      </c>
+      <c r="K66" s="12">
+        <v>3</v>
+      </c>
+      <c r="L66" s="18">
         <f t="shared" si="6"/>
         <v>2.9</v>
       </c>
-      <c r="M65" s="18" t="str">
+      <c r="M66" s="18" t="str">
         <f t="shared" si="7"/>
-        <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N65" s="15"/>
-      <c r="O65" s="15"/>
-      <c r="P65" s="15"/>
-      <c r="Q65" s="15"/>
-      <c r="S65" s="8" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="7">
-        <v>368004</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="D66" s="9" t="s">
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N66" s="15"/>
+      <c r="O66" s="15"/>
+      <c r="P66" s="15"/>
+      <c r="Q66" s="15"/>
+      <c r="S66" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D67" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E66" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="F66" s="11">
-        <v>59</v>
-      </c>
-      <c r="G66" s="11">
-        <v>4</v>
-      </c>
-      <c r="H66" s="12">
-        <v>4</v>
-      </c>
-      <c r="I66" s="12">
-        <v>3</v>
-      </c>
-      <c r="J66" s="12">
-        <v>4</v>
-      </c>
-      <c r="K66" s="12">
-        <v>4</v>
-      </c>
-      <c r="L66" s="13">
+      <c r="E67" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="F67" s="11">
+        <v>55</v>
+      </c>
+      <c r="G67" s="11">
+        <v>3</v>
+      </c>
+      <c r="H67" s="12">
+        <v>4</v>
+      </c>
+      <c r="I67" s="12">
+        <v>4</v>
+      </c>
+      <c r="J67" s="12">
+        <v>4</v>
+      </c>
+      <c r="K67" s="12">
+        <v>4</v>
+      </c>
+      <c r="L67" s="13">
         <f t="shared" si="6"/>
-        <v>3.7</v>
-      </c>
-      <c r="M66" s="13" t="str">
+        <v>3.8</v>
+      </c>
+      <c r="M67" s="13" t="str">
         <f t="shared" si="7"/>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N66" s="9"/>
-      <c r="O66" s="9"/>
-      <c r="P66" s="9"/>
-      <c r="Q66" s="9"/>
-      <c r="S66" s="7" t="s">
+      <c r="N67" s="9"/>
+      <c r="O67" s="9"/>
+      <c r="P67" s="9"/>
+      <c r="Q67" s="9"/>
+      <c r="S67" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="7">
+        <v>168016</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E68" s="10" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="67" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="8">
-        <v>269040</v>
-      </c>
-      <c r="B67" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="C67" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E67" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="F67" s="17">
-        <v>45</v>
-      </c>
-      <c r="G67" s="17">
-        <v>1</v>
-      </c>
-      <c r="H67" s="12">
-        <v>4</v>
-      </c>
-      <c r="I67" s="12">
-        <v>3</v>
-      </c>
-      <c r="J67" s="12">
-        <v>4</v>
-      </c>
-      <c r="K67" s="12">
-        <v>3</v>
-      </c>
-      <c r="L67" s="18">
+      <c r="F68" s="11">
+        <v>35</v>
+      </c>
+      <c r="G68" s="11">
+        <v>1</v>
+      </c>
+      <c r="H68" s="12">
+        <v>4</v>
+      </c>
+      <c r="I68" s="12">
+        <v>3</v>
+      </c>
+      <c r="J68" s="12">
+        <v>4</v>
+      </c>
+      <c r="K68" s="12">
+        <v>1</v>
+      </c>
+      <c r="L68" s="13">
         <f t="shared" si="6"/>
-        <v>2.9</v>
-      </c>
-      <c r="M67" s="18" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="M68" s="13" t="str">
         <f t="shared" si="7"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N67" s="15"/>
-      <c r="O67" s="15"/>
-      <c r="P67" s="15"/>
-      <c r="Q67" s="15"/>
-      <c r="S67" s="8" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="7" t="s">
+      <c r="N68" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="B68" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="D68" s="9" t="s">
+      <c r="O68" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="P68" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q68" s="9"/>
+      <c r="R68" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="S68" s="7" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="8">
+        <v>258026</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="D69" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E68" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="F68" s="11">
-        <v>55</v>
-      </c>
-      <c r="G68" s="11">
-        <v>3</v>
-      </c>
-      <c r="H68" s="12">
-        <v>4</v>
-      </c>
-      <c r="I68" s="12">
-        <v>4</v>
-      </c>
-      <c r="J68" s="12">
-        <v>4</v>
-      </c>
-      <c r="K68" s="12">
-        <v>4</v>
-      </c>
-      <c r="L68" s="13">
-        <f t="shared" si="6"/>
-        <v>3.8</v>
-      </c>
-      <c r="M68" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>High Impact + High Risk</v>
-      </c>
-      <c r="N68" s="9"/>
-      <c r="O68" s="9"/>
-      <c r="P68" s="9"/>
-      <c r="Q68" s="9"/>
-      <c r="S68" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="7">
-        <v>168016</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="F69" s="11">
-        <v>35</v>
-      </c>
-      <c r="G69" s="11">
+      <c r="E69" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="F69" s="17">
+        <v>42</v>
+      </c>
+      <c r="G69" s="17">
         <v>1</v>
       </c>
       <c r="H69" s="12">
@@ -5745,114 +5750,48 @@
         <v>4</v>
       </c>
       <c r="K69" s="12">
-        <v>1</v>
-      </c>
-      <c r="L69" s="13">
-        <f t="shared" si="6"/>
-        <v>2.5</v>
-      </c>
-      <c r="M69" s="13" t="str">
-        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="L69" s="18">
+        <f t="shared" ref="L69" si="8">IF(OR(I69="",J69="",K69="",G69=""),"",ROUND(G69*0.2+I69*0.3+J69*0.3+K69*0.2,2))</f>
+        <v>2.9</v>
+      </c>
+      <c r="M69" s="18" t="str">
+        <f t="shared" ref="M69" si="9">IF(OR(H69="",L69=""),"",IF(AND(H69&gt;=4,L69&gt;=3.5),"High Impact + High Risk",IF(AND(H69&gt;=4,L69&lt;3.5),"High Impact + Low Risk",IF(AND(H69&lt;4,L69&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N69" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="O69" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="P69" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q69" s="9"/>
+      <c r="N69" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="O69" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="P69" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q69" s="15"/>
       <c r="R69" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="S69" s="7" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="8">
-        <v>258026</v>
-      </c>
-      <c r="B70" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="C70" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="D70" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E70" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="F70" s="17">
-        <v>42</v>
-      </c>
-      <c r="G70" s="17">
-        <v>1</v>
-      </c>
-      <c r="H70" s="12">
-        <v>4</v>
-      </c>
-      <c r="I70" s="12">
-        <v>3</v>
-      </c>
-      <c r="J70" s="12">
-        <v>4</v>
-      </c>
-      <c r="K70" s="12">
-        <v>3</v>
-      </c>
-      <c r="L70" s="18">
-        <f t="shared" ref="L70" si="8">IF(OR(I70="",J70="",K70="",G70=""),"",ROUND(G70*0.2+I70*0.3+J70*0.3+K70*0.2,2))</f>
-        <v>2.9</v>
-      </c>
-      <c r="M70" s="18" t="str">
-        <f t="shared" ref="M70" si="9">IF(OR(H70="",L70=""),"",IF(AND(H70&gt;=4,L70&gt;=3.5),"High Impact + High Risk",IF(AND(H70&gt;=4,L70&lt;3.5),"High Impact + Low Risk",IF(AND(H70&lt;4,L70&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N70" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="O70" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="P70" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q70" s="15"/>
-      <c r="R70" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="S70" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="S69" s="8" t="s">
         <v>93</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S70" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="12">
-      <filters>
-        <filter val="High Impact + High Risk"/>
-        <filter val="High Impact + Low Risk"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:S69" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="H3:H49 J3:K49" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J3:K48 H3:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"1,2,3,4,5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I3:I49" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I3:I48" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1,3,5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="O3:O48" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="O3:O47" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Ready Now,Ready in 1 Year,Ready in 3 Years,No Successor"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C6C0AD5-B5F6-427D-88FC-D1D2CDA588D6}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEC35E70-7A08-496A-8233-158948C34C43}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="261">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -809,6 +809,18 @@
   </si>
   <si>
     <t>Section Manager - Batch and Furnace</t>
+  </si>
+  <si>
+    <t>3-5 ปี</t>
+  </si>
+  <si>
+    <t>ศรัณย์ กิจเจริญวิศาล</t>
+  </si>
+  <si>
+    <t>ชรัณ แสงจันทร์</t>
+  </si>
+  <si>
+    <t>พร้อมทันที</t>
   </si>
 </sst>
 </file>
@@ -1142,43 +1154,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1189,6 +1177,30 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1468,727 +1480,693 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="30" t="s">
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="30"/>
+      <c r="G26" s="33"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="30" t="s">
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="30"/>
+      <c r="G27" s="33"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="30" t="s">
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="30"/>
+      <c r="G28" s="33"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="29" t="s">
+      <c r="B29" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="30" t="s">
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="30"/>
+      <c r="G29" s="33"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="30" t="s">
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="30"/>
+      <c r="G30" s="33"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="27" t="s">
+      <c r="C33" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="27" t="s">
+      <c r="C35" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="27" t="s">
+      <c r="C38" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="27" t="s">
+      <c r="C39" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="27" t="s">
+      <c r="C40" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="27" t="s">
+      <c r="C41" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="27" t="s">
+      <c r="C42" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="27" t="s">
+      <c r="C45" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="27" t="s">
+      <c r="C46" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="27" t="s">
+      <c r="C47" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="27" t="s">
+      <c r="C48" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="27"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="27"/>
-      <c r="G48" s="27"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="27" t="s">
+      <c r="C49" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="25"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="24" t="s">
+      <c r="B51" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="24"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="23"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="31" t="s">
+      <c r="B52" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="31"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="32" t="s">
+      <c r="B53" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
-      <c r="E53" s="32"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="24" t="s">
+      <c r="B55" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="24"/>
-      <c r="D55" s="24"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="23"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="33" t="s">
+      <c r="B56" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="33"/>
-      <c r="D56" s="33"/>
-      <c r="E56" s="27" t="s">
+      <c r="C56" s="24"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="27"/>
-      <c r="G56" s="27"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="34" t="s">
+      <c r="B57" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="34"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="27" t="s">
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="35" t="s">
+      <c r="B58" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="35"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="27" t="s">
+      <c r="C58" s="27"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="36" t="s">
+      <c r="B59" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="36"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="27" t="s">
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
+      <c r="F59" s="25"/>
+      <c r="G59" s="25"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="24" t="s">
+      <c r="B62" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="24"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
+      <c r="C62" s="23"/>
+      <c r="D62" s="23"/>
+      <c r="E62" s="23"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="23"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="25" t="s">
+      <c r="B63" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="25"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="21"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="21" t="s">
+      <c r="B64" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="21" t="s">
+      <c r="B65" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="21" t="s">
+      <c r="B66" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="21" t="s">
+      <c r="B67" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-      <c r="G67" s="21"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="24" t="s">
+      <c r="B69" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="24"/>
-      <c r="D69" s="24"/>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="23"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="23"/>
+      <c r="G69" s="23"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="25" t="s">
+      <c r="B70" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="25"/>
-      <c r="D70" s="25"/>
-      <c r="E70" s="25"/>
-      <c r="F70" s="25"/>
-      <c r="G70" s="25"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="25" t="s">
+      <c r="B71" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="25"/>
-      <c r="D71" s="25"/>
-      <c r="E71" s="25"/>
-      <c r="F71" s="25"/>
-      <c r="G71" s="25"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="25" t="s">
+      <c r="B72" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="25"/>
-      <c r="D72" s="25"/>
-      <c r="E72" s="25"/>
-      <c r="F72" s="25"/>
-      <c r="G72" s="25"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="25" t="s">
+      <c r="B73" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="25"/>
-      <c r="D73" s="25"/>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="25" t="s">
+      <c r="B74" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="25"/>
-      <c r="D74" s="25"/>
-      <c r="E74" s="25"/>
-      <c r="F74" s="25"/>
-      <c r="G74" s="25"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="25" t="s">
+      <c r="B75" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="25"/>
-      <c r="D75" s="25"/>
-      <c r="E75" s="25"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="25"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="21"/>
+      <c r="G75" s="21"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="25"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="25"/>
-      <c r="E76" s="25"/>
-      <c r="F76" s="25"/>
-      <c r="G76" s="25"/>
+      <c r="B76" s="21"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="21"/>
+      <c r="G76" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B15:G15"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="B17:G17"/>
@@ -2202,18 +2180,52 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2222,6 +2234,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:S69"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2323,7 +2336,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>168028</v>
       </c>
@@ -2531,7 +2544,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>161027</v>
       </c>
@@ -2635,7 +2648,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>656008</v>
       </c>
@@ -2687,7 +2700,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>168017</v>
       </c>
@@ -2791,7 +2804,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>166027</v>
       </c>
@@ -3047,7 +3060,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>242032</v>
       </c>
@@ -3099,7 +3112,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>149024</v>
       </c>
@@ -3151,7 +3164,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>232027</v>
       </c>
@@ -3203,7 +3216,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>256029</v>
       </c>
@@ -3255,7 +3268,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>236012</v>
       </c>
@@ -3359,7 +3372,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="23" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>233034</v>
       </c>
@@ -3411,7 +3424,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>268013</v>
       </c>
@@ -3463,7 +3476,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="25" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>249010</v>
       </c>
@@ -3515,7 +3528,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>268012</v>
       </c>
@@ -3567,7 +3580,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>238030</v>
       </c>
@@ -3983,7 +3996,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="35" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>253014</v>
       </c>
@@ -4035,7 +4048,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="36" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>248031</v>
       </c>
@@ -4139,7 +4152,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="8">
         <v>242012</v>
       </c>
@@ -4243,7 +4256,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>244023</v>
       </c>
@@ -4339,8 +4352,12 @@
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9"/>
+      <c r="N41" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="O41" s="9" t="s">
+        <v>62</v>
+      </c>
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
       <c r="S41" s="7" t="s">
@@ -4651,8 +4668,12 @@
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N47" s="15"/>
-      <c r="O47" s="15"/>
+      <c r="N47" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="O47" s="15" t="s">
+        <v>260</v>
+      </c>
       <c r="P47" s="15"/>
       <c r="Q47" s="15"/>
       <c r="S47" s="8" t="s">
@@ -4751,8 +4772,12 @@
         <f t="shared" si="7"/>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N49" s="15"/>
-      <c r="O49" s="15"/>
+      <c r="N49" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="O49" s="15" t="s">
+        <v>257</v>
+      </c>
       <c r="P49" s="15"/>
       <c r="Q49" s="15"/>
       <c r="S49" s="8" t="s">
@@ -4809,7 +4834,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="51" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>161005</v>
       </c>
@@ -4859,7 +4884,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="7">
         <v>163003</v>
       </c>
@@ -4909,7 +4934,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="53" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <v>166024</v>
       </c>
@@ -4959,7 +4984,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="54" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>167001</v>
       </c>
@@ -5009,7 +5034,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="55" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>167012</v>
       </c>
@@ -5109,7 +5134,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="57" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
         <v>267001</v>
       </c>
@@ -5209,7 +5234,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="59" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
         <v>167020</v>
       </c>
@@ -5309,7 +5334,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="61" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>167032</v>
       </c>
@@ -5409,7 +5434,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="63" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="8">
         <v>337004</v>
       </c>
@@ -5459,7 +5484,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="64" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="8">
         <v>268044</v>
       </c>
@@ -5761,10 +5786,10 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N69" s="15" t="s">
-        <v>246</v>
+        <v>96</v>
       </c>
       <c r="O69" s="15" t="s">
-        <v>246</v>
+        <v>62</v>
       </c>
       <c r="P69" s="15" t="s">
         <v>246</v>
@@ -5778,7 +5803,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S69" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:S69" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="12">
+      <filters>
+        <filter val="High Impact + High Risk"/>
+        <filter val="High Impact + Low Risk"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEC35E70-7A08-496A-8233-158948C34C43}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DC00677-643A-4F77-835F-AA33945B6F8F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="289">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -821,6 +821,90 @@
   </si>
   <si>
     <t>พร้อมทันที</t>
+  </si>
+  <si>
+    <t>466004_Manager_IndustrialRelations.docx</t>
+  </si>
+  <si>
+    <t>159029_CorporateSecretary_DirectorCorporateAffairs.docx</t>
+  </si>
+  <si>
+    <t>239006_DeptManager_Engineering.docx</t>
+  </si>
+  <si>
+    <t>246004_DeptManager_Forming.docx</t>
+  </si>
+  <si>
+    <t>250042_SectionManager_FurnaceSupportMaintenance.docx</t>
+  </si>
+  <si>
+    <t>256014_SupportManager_Forming1.docx</t>
+  </si>
+  <si>
+    <t>443003_237011_249048_Supervisor_Forming.docx</t>
+  </si>
+  <si>
+    <t>254057_SupportManager_Forming2.docx</t>
+  </si>
+  <si>
+    <t>267096_SupportManager_Forming3.docx</t>
+  </si>
+  <si>
+    <t>269022_SupportManager_MoldMaintenanceJobChange.docx</t>
+  </si>
+  <si>
+    <t>251007_SupportManager_PrintingDecorating.docx</t>
+  </si>
+  <si>
+    <t>257039_SectionManager_ProductionPlanning.docx</t>
+  </si>
+  <si>
+    <t>241009_SectionManager_DesignCreative.docx</t>
+  </si>
+  <si>
+    <t>368001_SeniorProductDesigner.docx</t>
+  </si>
+  <si>
+    <t>148005_Director_Marketing.docx</t>
+  </si>
+  <si>
+    <t>267071_SectionManager_InspectionPacking.docx</t>
+  </si>
+  <si>
+    <t>268051_Engineer_InspectionPacking.docx</t>
+  </si>
+  <si>
+    <t>269032_SupportManager_LabQualitySystem.docx</t>
+  </si>
+  <si>
+    <t>250051_SectionManager_QualityControl.docx</t>
+  </si>
+  <si>
+    <t>146037_DeptManager_CorporateIT.docx</t>
+  </si>
+  <si>
+    <t>139013_SectionManager_ITApplication.docx</t>
+  </si>
+  <si>
+    <t>145015_SectionManager_CorporateIT.docx</t>
+  </si>
+  <si>
+    <t>260001_SupportManager_IT.docx</t>
+  </si>
+  <si>
+    <t>160001_FinancialController.docx</t>
+  </si>
+  <si>
+    <t>167029_SectionManager_Costing.docx</t>
+  </si>
+  <si>
+    <t>168024_SectionManager_BusinessControlTreasury.docx</t>
+  </si>
+  <si>
+    <t>168016_SectionManager_StrategicPlanning.docx</t>
+  </si>
+  <si>
+    <t>258026_DeptManager_QualityManagement.docx</t>
   </si>
 </sst>
 </file>
@@ -1154,19 +1238,43 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1177,30 +1285,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1480,693 +1564,727 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="33"/>
+      <c r="G26" s="30"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="32" t="s">
+      <c r="B27" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="33" t="s">
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="33"/>
+      <c r="G27" s="30"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="33" t="s">
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="33"/>
+      <c r="G28" s="30"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="33" t="s">
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="33"/>
+      <c r="G29" s="30"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="33" t="s">
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="30"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="29" t="s">
+      <c r="B32" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C34" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C35" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="C38" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="25" t="s">
+      <c r="C39" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="25" t="s">
+      <c r="C40" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C42" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="29" t="s">
+      <c r="B44" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="25" t="s">
+      <c r="C45" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="27"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C46" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="C47" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="25" t="s">
+      <c r="C48" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="25"/>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="25" t="s">
+      <c r="C49" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="25"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="30" t="s">
+      <c r="B52" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="31" t="s">
+      <c r="B53" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="23" t="s">
+      <c r="B55" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="24" t="s">
+      <c r="B56" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="25" t="s">
+      <c r="C56" s="33"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="26" t="s">
+      <c r="B57" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="25" t="s">
+      <c r="C57" s="34"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="25" t="s">
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="25"/>
-      <c r="G58" s="25"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="28" t="s">
+      <c r="B59" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="28"/>
-      <c r="D59" s="28"/>
-      <c r="E59" s="25" t="s">
+      <c r="C59" s="36"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="25"/>
-      <c r="G59" s="25"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="23" t="s">
+      <c r="B62" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="23"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="21" t="s">
+      <c r="B63" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="25"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="22" t="s">
+      <c r="B64" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="22" t="s">
+      <c r="B65" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="21"/>
+      <c r="G65" s="21"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="22" t="s">
+      <c r="B66" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="22"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="21"/>
+      <c r="G66" s="21"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="22" t="s">
+      <c r="B67" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="23" t="s">
+      <c r="B69" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="23"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="23"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="21" t="s">
+      <c r="B70" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="25"/>
+      <c r="E70" s="25"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="25"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="21" t="s">
+      <c r="B71" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="25"/>
+      <c r="E71" s="25"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="25"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="21" t="s">
+      <c r="B72" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="25"/>
+      <c r="F72" s="25"/>
+      <c r="G72" s="25"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="21" t="s">
+      <c r="B73" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
+      <c r="C73" s="25"/>
+      <c r="D73" s="25"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="21" t="s">
+      <c r="B74" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="21" t="s">
+      <c r="B75" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="25"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="21"/>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
+      <c r="B76" s="25"/>
+      <c r="C76" s="25"/>
+      <c r="D76" s="25"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="B17:G17"/>
@@ -2180,52 +2298,18 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B15:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2234,7 +2318,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:S69"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2336,7 +2419,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>168028</v>
       </c>
@@ -2544,7 +2627,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>161027</v>
       </c>
@@ -2648,7 +2731,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>656008</v>
       </c>
@@ -2700,7 +2783,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>168017</v>
       </c>
@@ -2804,7 +2887,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>166027</v>
       </c>
@@ -2900,7 +2983,9 @@
       </c>
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
+      <c r="P13" s="15" t="s">
+        <v>261</v>
+      </c>
       <c r="Q13" s="15"/>
       <c r="S13" s="8" t="s">
         <v>119</v>
@@ -2950,7 +3035,9 @@
       </c>
       <c r="N14" s="9"/>
       <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
+      <c r="P14" s="9" t="s">
+        <v>262</v>
+      </c>
       <c r="Q14" s="9"/>
       <c r="S14" s="7" t="s">
         <v>119</v>
@@ -3002,7 +3089,9 @@
       </c>
       <c r="N15" s="9"/>
       <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
+      <c r="P15" s="9" t="s">
+        <v>263</v>
+      </c>
       <c r="Q15" s="9"/>
       <c r="S15" s="7" t="s">
         <v>124</v>
@@ -3054,13 +3143,15 @@
       </c>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
+      <c r="P16" s="15" t="s">
+        <v>264</v>
+      </c>
       <c r="Q16" s="15"/>
       <c r="S16" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>242032</v>
       </c>
@@ -3112,7 +3203,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>149024</v>
       </c>
@@ -3164,7 +3255,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>232027</v>
       </c>
@@ -3216,7 +3307,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>256029</v>
       </c>
@@ -3268,7 +3359,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>236012</v>
       </c>
@@ -3366,13 +3457,15 @@
       </c>
       <c r="N22" s="15"/>
       <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
+      <c r="P22" s="15" t="s">
+        <v>265</v>
+      </c>
       <c r="Q22" s="15"/>
       <c r="S22" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="23" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>233034</v>
       </c>
@@ -3424,7 +3517,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>268013</v>
       </c>
@@ -3476,7 +3569,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="25" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>249010</v>
       </c>
@@ -3528,7 +3621,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>268012</v>
       </c>
@@ -3580,7 +3673,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>238030</v>
       </c>
@@ -3678,7 +3771,9 @@
       </c>
       <c r="N28" s="15"/>
       <c r="O28" s="15"/>
-      <c r="P28" s="15"/>
+      <c r="P28" s="15" t="s">
+        <v>266</v>
+      </c>
       <c r="Q28" s="15"/>
       <c r="S28" s="8" t="s">
         <v>124</v>
@@ -3730,7 +3825,9 @@
       </c>
       <c r="N29" s="9"/>
       <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
+      <c r="P29" s="9" t="s">
+        <v>267</v>
+      </c>
       <c r="Q29" s="9"/>
       <c r="S29" s="7" t="s">
         <v>124</v>
@@ -3782,7 +3879,9 @@
       </c>
       <c r="N30" s="15"/>
       <c r="O30" s="15"/>
-      <c r="P30" s="15"/>
+      <c r="P30" s="15" t="s">
+        <v>268</v>
+      </c>
       <c r="Q30" s="15"/>
       <c r="S30" s="8" t="s">
         <v>124</v>
@@ -3834,7 +3933,9 @@
       </c>
       <c r="N31" s="9"/>
       <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
+      <c r="P31" s="9" t="s">
+        <v>267</v>
+      </c>
       <c r="Q31" s="9"/>
       <c r="S31" s="7" t="s">
         <v>124</v>
@@ -3886,7 +3987,9 @@
       </c>
       <c r="N32" s="15"/>
       <c r="O32" s="15"/>
-      <c r="P32" s="15"/>
+      <c r="P32" s="15" t="s">
+        <v>269</v>
+      </c>
       <c r="Q32" s="15"/>
       <c r="S32" s="8" t="s">
         <v>124</v>
@@ -3938,7 +4041,9 @@
       </c>
       <c r="N33" s="9"/>
       <c r="O33" s="9"/>
-      <c r="P33" s="9"/>
+      <c r="P33" s="9" t="s">
+        <v>267</v>
+      </c>
       <c r="Q33" s="9"/>
       <c r="S33" s="7" t="s">
         <v>124</v>
@@ -3990,13 +4095,15 @@
       </c>
       <c r="N34" s="15"/>
       <c r="O34" s="15"/>
-      <c r="P34" s="15"/>
+      <c r="P34" s="15" t="s">
+        <v>270</v>
+      </c>
       <c r="Q34" s="15"/>
       <c r="S34" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="35" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>253014</v>
       </c>
@@ -4048,7 +4155,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="36" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>248031</v>
       </c>
@@ -4146,13 +4253,15 @@
       </c>
       <c r="N37" s="9"/>
       <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
+      <c r="P37" s="9" t="s">
+        <v>271</v>
+      </c>
       <c r="Q37" s="9"/>
       <c r="S37" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="8">
         <v>242012</v>
       </c>
@@ -4250,13 +4359,15 @@
       </c>
       <c r="N39" s="9"/>
       <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
+      <c r="P39" s="9" t="s">
+        <v>272</v>
+      </c>
       <c r="Q39" s="9"/>
       <c r="S39" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>244023</v>
       </c>
@@ -4358,7 +4469,9 @@
       <c r="O41" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="P41" s="9"/>
+      <c r="P41" s="9" t="s">
+        <v>273</v>
+      </c>
       <c r="Q41" s="9"/>
       <c r="S41" s="7" t="s">
         <v>175</v>
@@ -4410,7 +4523,9 @@
       </c>
       <c r="N42" s="15"/>
       <c r="O42" s="15"/>
-      <c r="P42" s="15"/>
+      <c r="P42" s="15" t="s">
+        <v>274</v>
+      </c>
       <c r="Q42" s="15"/>
       <c r="S42" s="8" t="s">
         <v>175</v>
@@ -4462,7 +4577,9 @@
       </c>
       <c r="N43" s="9"/>
       <c r="O43" s="9"/>
-      <c r="P43" s="9"/>
+      <c r="P43" s="9" t="s">
+        <v>275</v>
+      </c>
       <c r="Q43" s="9"/>
       <c r="S43" s="7" t="s">
         <v>175</v>
@@ -4514,7 +4631,9 @@
       </c>
       <c r="N44" s="9"/>
       <c r="O44" s="9"/>
-      <c r="P44" s="9"/>
+      <c r="P44" s="9" t="s">
+        <v>276</v>
+      </c>
       <c r="Q44" s="9"/>
       <c r="S44" s="7" t="s">
         <v>93</v>
@@ -4566,7 +4685,9 @@
       </c>
       <c r="N45" s="15"/>
       <c r="O45" s="15"/>
-      <c r="P45" s="15"/>
+      <c r="P45" s="15" t="s">
+        <v>277</v>
+      </c>
       <c r="Q45" s="15"/>
       <c r="S45" s="8" t="s">
         <v>93</v>
@@ -4618,7 +4739,9 @@
       </c>
       <c r="N46" s="9"/>
       <c r="O46" s="9"/>
-      <c r="P46" s="9"/>
+      <c r="P46" s="9" t="s">
+        <v>278</v>
+      </c>
       <c r="Q46" s="9"/>
       <c r="S46" s="7" t="s">
         <v>93</v>
@@ -4674,7 +4797,9 @@
       <c r="O47" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="P47" s="15"/>
+      <c r="P47" s="15" t="s">
+        <v>279</v>
+      </c>
       <c r="Q47" s="15"/>
       <c r="S47" s="8" t="s">
         <v>93</v>
@@ -4724,7 +4849,9 @@
       </c>
       <c r="N48" s="9"/>
       <c r="O48" s="9"/>
-      <c r="P48" s="9"/>
+      <c r="P48" s="9" t="s">
+        <v>280</v>
+      </c>
       <c r="Q48" s="9"/>
       <c r="S48" s="7" t="s">
         <v>247</v>
@@ -4778,7 +4905,9 @@
       <c r="O49" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="P49" s="15"/>
+      <c r="P49" s="15" t="s">
+        <v>281</v>
+      </c>
       <c r="Q49" s="15"/>
       <c r="S49" s="8" t="s">
         <v>247</v>
@@ -4828,13 +4957,15 @@
       </c>
       <c r="N50" s="9"/>
       <c r="O50" s="9"/>
-      <c r="P50" s="9"/>
+      <c r="P50" s="9" t="s">
+        <v>282</v>
+      </c>
       <c r="Q50" s="9"/>
       <c r="S50" s="7" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="51" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>161005</v>
       </c>
@@ -4884,7 +5015,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="7">
         <v>163003</v>
       </c>
@@ -4934,7 +5065,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="53" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <v>166024</v>
       </c>
@@ -4984,7 +5115,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="54" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>167001</v>
       </c>
@@ -5034,7 +5165,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="55" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>167012</v>
       </c>
@@ -5128,13 +5259,15 @@
       </c>
       <c r="N56" s="9"/>
       <c r="O56" s="9"/>
-      <c r="P56" s="9"/>
+      <c r="P56" s="9" t="s">
+        <v>283</v>
+      </c>
       <c r="Q56" s="9"/>
       <c r="S56" s="7" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="57" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
         <v>267001</v>
       </c>
@@ -5228,13 +5361,15 @@
       </c>
       <c r="N58" s="9"/>
       <c r="O58" s="9"/>
-      <c r="P58" s="9"/>
+      <c r="P58" s="9" t="s">
+        <v>284</v>
+      </c>
       <c r="Q58" s="9"/>
       <c r="S58" s="7" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="59" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
         <v>167020</v>
       </c>
@@ -5328,13 +5463,15 @@
       </c>
       <c r="N60" s="15"/>
       <c r="O60" s="15"/>
-      <c r="P60" s="15"/>
+      <c r="P60" s="15" t="s">
+        <v>285</v>
+      </c>
       <c r="Q60" s="15"/>
       <c r="S60" s="8" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="61" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>167032</v>
       </c>
@@ -5428,13 +5565,15 @@
       </c>
       <c r="N62" s="15"/>
       <c r="O62" s="15"/>
-      <c r="P62" s="15"/>
+      <c r="P62" s="15" t="s">
+        <v>286</v>
+      </c>
       <c r="Q62" s="15"/>
       <c r="S62" s="8" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="63" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="8">
         <v>337004</v>
       </c>
@@ -5484,7 +5623,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="64" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="8">
         <v>268044</v>
       </c>
@@ -5733,7 +5872,7 @@
         <v>246</v>
       </c>
       <c r="P68" s="9" t="s">
-        <v>246</v>
+        <v>287</v>
       </c>
       <c r="Q68" s="9"/>
       <c r="R68" s="14" t="s">
@@ -5792,7 +5931,7 @@
         <v>62</v>
       </c>
       <c r="P69" s="15" t="s">
-        <v>246</v>
+        <v>288</v>
       </c>
       <c r="Q69" s="15"/>
       <c r="R69" s="14" t="s">
@@ -5803,14 +5942,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S69" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="12">
-      <filters>
-        <filter val="High Impact + High Risk"/>
-        <filter val="High Impact + Low Risk"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:S69" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DC00677-643A-4F77-835F-AA33945B6F8F}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5BDEB43-5B14-4A4A-8C2B-3FC265E443E0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="คำอธิบาย" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="292">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -905,6 +905,15 @@
   </si>
   <si>
     <t>258026_DeptManager_QualityManagement.docx</t>
+  </si>
+  <si>
+    <t>266049_Department Manager Human Resources</t>
+  </si>
+  <si>
+    <t>368004_Contract-Procurement</t>
+  </si>
+  <si>
+    <t>149024 A_Acting Procurement Manager</t>
   </si>
 </sst>
 </file>
@@ -2881,7 +2890,9 @@
       </c>
       <c r="N11" s="15"/>
       <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
+      <c r="P11" s="15" t="s">
+        <v>289</v>
+      </c>
       <c r="Q11" s="15"/>
       <c r="S11" s="8" t="s">
         <v>119</v>
@@ -5717,7 +5728,9 @@
       </c>
       <c r="N65" s="9"/>
       <c r="O65" s="9"/>
-      <c r="P65" s="9"/>
+      <c r="P65" s="9" t="s">
+        <v>290</v>
+      </c>
       <c r="Q65" s="9"/>
       <c r="S65" s="7" t="s">
         <v>247</v>
@@ -5817,7 +5830,9 @@
       </c>
       <c r="N67" s="9"/>
       <c r="O67" s="9"/>
-      <c r="P67" s="9"/>
+      <c r="P67" s="9" t="s">
+        <v>291</v>
+      </c>
       <c r="Q67" s="9"/>
       <c r="S67" s="7" t="s">
         <v>247</v>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5BDEB43-5B14-4A4A-8C2B-3FC265E443E0}"/>
+  <xr:revisionPtr revIDLastSave="129" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5D63C34-AFD1-460B-A1AA-ACD88AD9EFC2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="กรอกข้อมูล" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$68</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="292">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -760,15 +760,6 @@
     <t>14/06/1967</t>
   </si>
   <si>
-    <t>อรุณี อุปนันท์</t>
-  </si>
-  <si>
-    <t>Support Manager - Procurement</t>
-  </si>
-  <si>
-    <t>15/03/1981</t>
-  </si>
-  <si>
     <t>149024 A</t>
   </si>
   <si>
@@ -914,13 +905,22 @@
   </si>
   <si>
     <t>149024 A_Acting Procurement Manager</t>
+  </si>
+  <si>
+    <t>สรรหาจากภายนอก</t>
+  </si>
+  <si>
+    <t>พุฒิพงศ์ สีธิสุข</t>
+  </si>
+  <si>
+    <t xml:space="preserve">รอพี่วุฒิแจ้ง </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1050,6 +1050,60 @@
       <color rgb="FF1A1A1A"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9.5"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.5"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FFFFC000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9.5"/>
+      <color rgb="FFFFC000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.5"/>
+      <color rgb="FFFFC000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="14">
@@ -1187,7 +1241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1242,6 +1296,74 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1573,678 +1695,678 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="55"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="30" t="s">
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="30"/>
+      <c r="G26" s="54"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="30" t="s">
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="30"/>
+      <c r="G27" s="54"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="30" t="s">
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="30"/>
+      <c r="G28" s="54"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="29" t="s">
+      <c r="B29" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="30" t="s">
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="30"/>
+      <c r="G29" s="54"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="30" t="s">
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="30"/>
+      <c r="G30" s="54"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="27" t="s">
+      <c r="C33" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="27" t="s">
+      <c r="C35" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="52"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="27" t="s">
+      <c r="C38" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="51"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="27" t="s">
+      <c r="C39" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
+      <c r="G39" s="51"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="27" t="s">
+      <c r="C40" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
+      <c r="G40" s="51"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="27" t="s">
+      <c r="C41" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="27" t="s">
+      <c r="C42" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="51"/>
+      <c r="G42" s="51"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="52"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="27" t="s">
+      <c r="C45" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="51"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="27" t="s">
+      <c r="C46" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
+      <c r="D46" s="51"/>
+      <c r="E46" s="51"/>
+      <c r="F46" s="51"/>
+      <c r="G46" s="51"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="27" t="s">
+      <c r="C47" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
+      <c r="D47" s="51"/>
+      <c r="E47" s="51"/>
+      <c r="F47" s="51"/>
+      <c r="G47" s="51"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="27" t="s">
+      <c r="C48" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="27"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="27"/>
-      <c r="G48" s="27"/>
+      <c r="D48" s="51"/>
+      <c r="E48" s="51"/>
+      <c r="F48" s="51"/>
+      <c r="G48" s="51"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="27" t="s">
+      <c r="C49" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
+      <c r="D49" s="51"/>
+      <c r="E49" s="51"/>
+      <c r="F49" s="51"/>
+      <c r="G49" s="51"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="24" t="s">
+      <c r="B51" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="24"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="31" t="s">
+      <c r="B52" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="31"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="55"/>
+      <c r="G52" s="55"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="32" t="s">
+      <c r="B53" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
-      <c r="E53" s="32"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="56"/>
+      <c r="G53" s="56"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="24" t="s">
+      <c r="B55" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="24"/>
-      <c r="D55" s="24"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
+      <c r="C55" s="48"/>
+      <c r="D55" s="48"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="48"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="33" t="s">
+      <c r="B56" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="33"/>
-      <c r="D56" s="33"/>
-      <c r="E56" s="27" t="s">
+      <c r="C56" s="57"/>
+      <c r="D56" s="57"/>
+      <c r="E56" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="27"/>
-      <c r="G56" s="27"/>
+      <c r="F56" s="51"/>
+      <c r="G56" s="51"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="34" t="s">
+      <c r="B57" s="58" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="34"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="27" t="s">
+      <c r="C57" s="58"/>
+      <c r="D57" s="58"/>
+      <c r="E57" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
+      <c r="F57" s="51"/>
+      <c r="G57" s="51"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="35" t="s">
+      <c r="B58" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="35"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="27" t="s">
+      <c r="C58" s="59"/>
+      <c r="D58" s="59"/>
+      <c r="E58" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
+      <c r="F58" s="51"/>
+      <c r="G58" s="51"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="36" t="s">
+      <c r="B59" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="36"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="27" t="s">
+      <c r="C59" s="60"/>
+      <c r="D59" s="60"/>
+      <c r="E59" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
+      <c r="F59" s="51"/>
+      <c r="G59" s="51"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="24" t="s">
+      <c r="B62" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="24"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="25" t="s">
+      <c r="B63" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="25"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
+      <c r="C63" s="49"/>
+      <c r="D63" s="49"/>
+      <c r="E63" s="49"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="49"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="21" t="s">
+      <c r="B64" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
+      <c r="C64" s="45"/>
+      <c r="D64" s="45"/>
+      <c r="E64" s="45"/>
+      <c r="F64" s="45"/>
+      <c r="G64" s="45"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="21" t="s">
+      <c r="B65" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
+      <c r="C65" s="45"/>
+      <c r="D65" s="45"/>
+      <c r="E65" s="45"/>
+      <c r="F65" s="45"/>
+      <c r="G65" s="45"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="21" t="s">
+      <c r="B66" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
+      <c r="C66" s="45"/>
+      <c r="D66" s="45"/>
+      <c r="E66" s="45"/>
+      <c r="F66" s="45"/>
+      <c r="G66" s="45"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="21" t="s">
+      <c r="B67" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-      <c r="G67" s="21"/>
+      <c r="C67" s="45"/>
+      <c r="D67" s="45"/>
+      <c r="E67" s="45"/>
+      <c r="F67" s="45"/>
+      <c r="G67" s="45"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="24" t="s">
+      <c r="B69" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="24"/>
-      <c r="D69" s="24"/>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
+      <c r="C69" s="48"/>
+      <c r="D69" s="48"/>
+      <c r="E69" s="48"/>
+      <c r="F69" s="48"/>
+      <c r="G69" s="48"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="25" t="s">
+      <c r="B70" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="25"/>
-      <c r="D70" s="25"/>
-      <c r="E70" s="25"/>
-      <c r="F70" s="25"/>
-      <c r="G70" s="25"/>
+      <c r="C70" s="49"/>
+      <c r="D70" s="49"/>
+      <c r="E70" s="49"/>
+      <c r="F70" s="49"/>
+      <c r="G70" s="49"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="25" t="s">
+      <c r="B71" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="25"/>
-      <c r="D71" s="25"/>
-      <c r="E71" s="25"/>
-      <c r="F71" s="25"/>
-      <c r="G71" s="25"/>
+      <c r="C71" s="49"/>
+      <c r="D71" s="49"/>
+      <c r="E71" s="49"/>
+      <c r="F71" s="49"/>
+      <c r="G71" s="49"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="25" t="s">
+      <c r="B72" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="25"/>
-      <c r="D72" s="25"/>
-      <c r="E72" s="25"/>
-      <c r="F72" s="25"/>
-      <c r="G72" s="25"/>
+      <c r="C72" s="49"/>
+      <c r="D72" s="49"/>
+      <c r="E72" s="49"/>
+      <c r="F72" s="49"/>
+      <c r="G72" s="49"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="25" t="s">
+      <c r="B73" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="25"/>
-      <c r="D73" s="25"/>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
+      <c r="C73" s="49"/>
+      <c r="D73" s="49"/>
+      <c r="E73" s="49"/>
+      <c r="F73" s="49"/>
+      <c r="G73" s="49"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="25" t="s">
+      <c r="B74" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="25"/>
-      <c r="D74" s="25"/>
-      <c r="E74" s="25"/>
-      <c r="F74" s="25"/>
-      <c r="G74" s="25"/>
+      <c r="C74" s="49"/>
+      <c r="D74" s="49"/>
+      <c r="E74" s="49"/>
+      <c r="F74" s="49"/>
+      <c r="G74" s="49"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="25" t="s">
+      <c r="B75" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="25"/>
-      <c r="D75" s="25"/>
-      <c r="E75" s="25"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="25"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="49"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="49"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="25"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="25"/>
-      <c r="E76" s="25"/>
-      <c r="F76" s="25"/>
-      <c r="G76" s="25"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="49"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="71">
@@ -2327,7 +2449,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S69"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:S68"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2351,25 +2474,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
       <c r="S1" s="5"/>
     </row>
     <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.35">
@@ -2428,7 +2551,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>168028</v>
       </c>
@@ -2636,7 +2759,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>161027</v>
       </c>
@@ -2740,7 +2863,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>656008</v>
       </c>
@@ -2792,7 +2915,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>168017</v>
       </c>
@@ -2844,61 +2967,65 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="8">
+    <row r="11" spans="1:19" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="27">
         <v>266049</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="29">
         <v>28864</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="30">
         <f t="shared" ca="1" si="3"/>
         <v>47</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="30">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H11" s="12">
-        <v>4</v>
-      </c>
-      <c r="I11" s="12">
-        <v>1</v>
-      </c>
-      <c r="J11" s="12">
-        <v>3</v>
-      </c>
-      <c r="K11" s="12">
+      <c r="H11" s="24">
+        <v>4</v>
+      </c>
+      <c r="I11" s="24">
+        <v>1</v>
+      </c>
+      <c r="J11" s="24">
+        <v>3</v>
+      </c>
+      <c r="K11" s="24">
         <v>2</v>
       </c>
-      <c r="L11" s="18">
+      <c r="L11" s="31">
         <f t="shared" ca="1" si="1"/>
         <v>1.8</v>
       </c>
-      <c r="M11" s="18" t="str">
+      <c r="M11" s="31" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q11" s="15"/>
-      <c r="S11" s="8" t="s">
+      <c r="N11" s="28" t="s">
+        <v>290</v>
+      </c>
+      <c r="O11" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="P11" s="28" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q11" s="28"/>
+      <c r="S11" s="27" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>166027</v>
       </c>
@@ -2950,219 +3077,227 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="8">
+    <row r="13" spans="1:19" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="27">
         <v>466004</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="30">
         <v>66</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="30">
         <v>5</v>
       </c>
-      <c r="H13" s="12">
-        <v>4</v>
-      </c>
-      <c r="I13" s="12">
+      <c r="H13" s="24">
+        <v>4</v>
+      </c>
+      <c r="I13" s="24">
         <v>5</v>
       </c>
-      <c r="J13" s="12">
-        <v>3</v>
-      </c>
-      <c r="K13" s="12">
-        <v>3</v>
-      </c>
-      <c r="L13" s="18">
+      <c r="J13" s="24">
+        <v>3</v>
+      </c>
+      <c r="K13" s="24">
+        <v>3</v>
+      </c>
+      <c r="L13" s="31">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="M13" s="18" t="str">
+      <c r="M13" s="31" t="str">
         <f t="shared" si="2"/>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q13" s="15"/>
-      <c r="S13" s="8" t="s">
+      <c r="N13" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q13" s="28"/>
+      <c r="S13" s="27" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="7">
+    <row r="14" spans="1:19" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="20">
         <v>159029</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="23">
         <v>52</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="23">
         <v>2</v>
       </c>
-      <c r="H14" s="12">
-        <v>4</v>
-      </c>
-      <c r="I14" s="12">
-        <v>1</v>
-      </c>
-      <c r="J14" s="12">
+      <c r="H14" s="24">
+        <v>4</v>
+      </c>
+      <c r="I14" s="24">
+        <v>1</v>
+      </c>
+      <c r="J14" s="24">
         <v>2</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="24">
         <v>5</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="25">
         <f t="shared" ref="L14" si="4">IF(OR(I14="",J14="",K14="",G14=""),"",ROUND(G14*0.2+I14*0.3+J14*0.3+K14*0.2,2))</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="M14" s="13" t="str">
+      <c r="M14" s="25" t="str">
         <f t="shared" ref="M14" si="5">IF(OR(H14="",L14=""),"",IF(AND(H14&gt;=4,L14&gt;=3.5),"High Impact + High Risk",IF(AND(H14&gt;=4,L14&lt;3.5),"High Impact + Low Risk",IF(AND(H14&lt;4,L14&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q14" s="9"/>
-      <c r="S14" s="7" t="s">
+      <c r="N14" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q14" s="21"/>
+      <c r="S14" s="20" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7">
+    <row r="15" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="32">
         <v>239006</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="34">
         <v>26179</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="35">
         <f t="shared" ca="1" si="3"/>
         <v>55</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="35">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="H15" s="12">
-        <v>4</v>
-      </c>
-      <c r="I15" s="12">
-        <v>3</v>
-      </c>
-      <c r="J15" s="12">
-        <v>4</v>
-      </c>
-      <c r="K15" s="12">
-        <v>3</v>
-      </c>
-      <c r="L15" s="13">
+      <c r="H15" s="36">
+        <v>4</v>
+      </c>
+      <c r="I15" s="36">
+        <v>3</v>
+      </c>
+      <c r="J15" s="36">
+        <v>4</v>
+      </c>
+      <c r="K15" s="36">
+        <v>3</v>
+      </c>
+      <c r="L15" s="37">
         <f t="shared" ca="1" si="1"/>
         <v>3.3</v>
       </c>
-      <c r="M15" s="13" t="str">
+      <c r="M15" s="37" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q15" s="9"/>
-      <c r="S15" s="7" t="s">
+      <c r="N15" s="33"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q15" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="S15" s="32" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="8">
+    <row r="16" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="39">
         <v>246004</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="41">
         <v>28270</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="42">
         <f t="shared" ca="1" si="3"/>
         <v>49</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H16" s="12">
-        <v>4</v>
-      </c>
-      <c r="I16" s="12">
-        <v>1</v>
-      </c>
-      <c r="J16" s="12">
-        <v>3</v>
-      </c>
-      <c r="K16" s="12">
-        <v>4</v>
-      </c>
-      <c r="L16" s="18">
+      <c r="H16" s="36">
+        <v>4</v>
+      </c>
+      <c r="I16" s="36">
+        <v>1</v>
+      </c>
+      <c r="J16" s="36">
+        <v>3</v>
+      </c>
+      <c r="K16" s="36">
+        <v>4</v>
+      </c>
+      <c r="L16" s="43">
         <f t="shared" ca="1" si="1"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="M16" s="18" t="str">
+      <c r="M16" s="43" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q16" s="15"/>
-      <c r="S16" s="8" t="s">
+      <c r="N16" s="40"/>
+      <c r="O16" s="40"/>
+      <c r="P16" s="40" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q16" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="S16" s="39" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>242032</v>
       </c>
@@ -3170,7 +3305,7 @@
         <v>129</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>106</v>
@@ -3209,12 +3344,14 @@
       <c r="N17" s="9"/>
       <c r="O17" s="9"/>
       <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
+      <c r="Q17" s="9" t="s">
+        <v>291</v>
+      </c>
       <c r="S17" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>149024</v>
       </c>
@@ -3261,12 +3398,14 @@
       <c r="N18" s="15"/>
       <c r="O18" s="15"/>
       <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
+      <c r="Q18" s="15" t="s">
+        <v>291</v>
+      </c>
       <c r="S18" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>232027</v>
       </c>
@@ -3313,12 +3452,14 @@
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
       <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
+      <c r="Q19" s="9" t="s">
+        <v>291</v>
+      </c>
       <c r="S19" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>256029</v>
       </c>
@@ -3365,12 +3506,14 @@
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
       <c r="P20" s="15"/>
-      <c r="Q20" s="15"/>
+      <c r="Q20" s="15" t="s">
+        <v>291</v>
+      </c>
       <c r="S20" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>236012</v>
       </c>
@@ -3417,66 +3560,70 @@
       <c r="N21" s="9"/>
       <c r="O21" s="9"/>
       <c r="P21" s="9"/>
-      <c r="Q21" s="9"/>
+      <c r="Q21" s="9" t="s">
+        <v>291</v>
+      </c>
       <c r="S21" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="8">
+    <row r="22" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="39">
         <v>250042</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="41">
         <v>26738</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="42">
         <f t="shared" ca="1" si="3"/>
         <v>53</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H22" s="12">
-        <v>4</v>
-      </c>
-      <c r="I22" s="12">
-        <v>1</v>
-      </c>
-      <c r="J22" s="12">
-        <v>4</v>
-      </c>
-      <c r="K22" s="12">
-        <v>4</v>
-      </c>
-      <c r="L22" s="18">
+      <c r="H22" s="36">
+        <v>4</v>
+      </c>
+      <c r="I22" s="36">
+        <v>1</v>
+      </c>
+      <c r="J22" s="36">
+        <v>4</v>
+      </c>
+      <c r="K22" s="36">
+        <v>4</v>
+      </c>
+      <c r="L22" s="43">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M22" s="18" t="str">
+      <c r="M22" s="43" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q22" s="15"/>
-      <c r="S22" s="8" t="s">
+      <c r="N22" s="40"/>
+      <c r="O22" s="40"/>
+      <c r="P22" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q22" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="S22" s="39" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="23" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>233034</v>
       </c>
@@ -3523,12 +3670,14 @@
       <c r="N23" s="9"/>
       <c r="O23" s="9"/>
       <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
+      <c r="Q23" s="9" t="s">
+        <v>291</v>
+      </c>
       <c r="S23" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>268013</v>
       </c>
@@ -3536,7 +3685,7 @@
         <v>142</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>106</v>
@@ -3575,12 +3724,14 @@
       <c r="N24" s="15"/>
       <c r="O24" s="15"/>
       <c r="P24" s="15"/>
-      <c r="Q24" s="15"/>
+      <c r="Q24" s="15" t="s">
+        <v>291</v>
+      </c>
       <c r="S24" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="25" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>249010</v>
       </c>
@@ -3627,12 +3778,14 @@
       <c r="N25" s="9"/>
       <c r="O25" s="9"/>
       <c r="P25" s="9"/>
-      <c r="Q25" s="9"/>
+      <c r="Q25" s="9" t="s">
+        <v>291</v>
+      </c>
       <c r="S25" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>268012</v>
       </c>
@@ -3679,12 +3832,14 @@
       <c r="N26" s="15"/>
       <c r="O26" s="15"/>
       <c r="P26" s="15"/>
-      <c r="Q26" s="15"/>
+      <c r="Q26" s="15" t="s">
+        <v>291</v>
+      </c>
       <c r="S26" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>238030</v>
       </c>
@@ -3731,390 +3886,406 @@
       <c r="N27" s="9"/>
       <c r="O27" s="9"/>
       <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
+      <c r="Q27" s="9" t="s">
+        <v>291</v>
+      </c>
       <c r="S27" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="28" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="8">
+    <row r="28" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="39">
         <v>256014</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="41">
         <v>32349</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="42">
         <f t="shared" ca="1" si="3"/>
         <v>38</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H28" s="12">
-        <v>4</v>
-      </c>
-      <c r="I28" s="12">
-        <v>1</v>
-      </c>
-      <c r="J28" s="12">
-        <v>4</v>
-      </c>
-      <c r="K28" s="12">
-        <v>4</v>
-      </c>
-      <c r="L28" s="18">
+      <c r="H28" s="36">
+        <v>4</v>
+      </c>
+      <c r="I28" s="36">
+        <v>1</v>
+      </c>
+      <c r="J28" s="36">
+        <v>4</v>
+      </c>
+      <c r="K28" s="36">
+        <v>4</v>
+      </c>
+      <c r="L28" s="43">
         <f t="shared" ca="1" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="M28" s="18" t="str">
+      <c r="M28" s="43" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
-      <c r="P28" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q28" s="15"/>
-      <c r="S28" s="8" t="s">
+      <c r="N28" s="40"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q28" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="S28" s="39" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="29" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="7">
+    <row r="29" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="32">
         <v>443003</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="34">
         <v>28572</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="35">
         <f t="shared" ca="1" si="3"/>
         <v>48</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="35">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H29" s="12">
-        <v>4</v>
-      </c>
-      <c r="I29" s="12">
-        <v>1</v>
-      </c>
-      <c r="J29" s="12">
-        <v>4</v>
-      </c>
-      <c r="K29" s="12">
+      <c r="H29" s="36">
+        <v>4</v>
+      </c>
+      <c r="I29" s="36">
+        <v>1</v>
+      </c>
+      <c r="J29" s="36">
+        <v>4</v>
+      </c>
+      <c r="K29" s="36">
         <v>5</v>
       </c>
-      <c r="L29" s="13">
+      <c r="L29" s="37">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M29" s="13" t="str">
+      <c r="M29" s="37" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q29" s="9"/>
-      <c r="S29" s="7" t="s">
+      <c r="N29" s="33"/>
+      <c r="O29" s="33"/>
+      <c r="P29" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q29" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="S29" s="32" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="30" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="8">
+    <row r="30" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="39">
         <v>254057</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="41">
         <v>32420</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="42">
         <f t="shared" ca="1" si="3"/>
         <v>38</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H30" s="12">
-        <v>4</v>
-      </c>
-      <c r="I30" s="12">
-        <v>1</v>
-      </c>
-      <c r="J30" s="12">
-        <v>4</v>
-      </c>
-      <c r="K30" s="12">
-        <v>4</v>
-      </c>
-      <c r="L30" s="18">
+      <c r="H30" s="36">
+        <v>4</v>
+      </c>
+      <c r="I30" s="36">
+        <v>1</v>
+      </c>
+      <c r="J30" s="36">
+        <v>4</v>
+      </c>
+      <c r="K30" s="36">
+        <v>4</v>
+      </c>
+      <c r="L30" s="43">
         <f t="shared" ca="1" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="M30" s="18" t="str">
+      <c r="M30" s="43" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N30" s="15"/>
-      <c r="O30" s="15"/>
-      <c r="P30" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q30" s="15"/>
-      <c r="S30" s="8" t="s">
+      <c r="N30" s="40"/>
+      <c r="O30" s="40"/>
+      <c r="P30" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q30" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="S30" s="39" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="7">
+    <row r="31" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="32">
         <v>237011</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="34">
         <v>25410</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="35">
         <f t="shared" ca="1" si="3"/>
         <v>57</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="35">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="H31" s="12">
-        <v>4</v>
-      </c>
-      <c r="I31" s="12">
-        <v>1</v>
-      </c>
-      <c r="J31" s="12">
-        <v>4</v>
-      </c>
-      <c r="K31" s="12">
+      <c r="H31" s="36">
+        <v>4</v>
+      </c>
+      <c r="I31" s="36">
+        <v>1</v>
+      </c>
+      <c r="J31" s="36">
+        <v>4</v>
+      </c>
+      <c r="K31" s="36">
         <v>5</v>
       </c>
-      <c r="L31" s="13">
+      <c r="L31" s="37">
         <f t="shared" ca="1" si="1"/>
         <v>3.1</v>
       </c>
-      <c r="M31" s="13" t="str">
+      <c r="M31" s="37" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q31" s="9"/>
-      <c r="S31" s="7" t="s">
+      <c r="N31" s="33"/>
+      <c r="O31" s="33"/>
+      <c r="P31" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q31" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="S31" s="32" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="32" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="8">
+    <row r="32" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="39">
         <v>267096</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="41">
         <v>32140</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="42">
         <f t="shared" ca="1" si="3"/>
         <v>38</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H32" s="12">
-        <v>4</v>
-      </c>
-      <c r="I32" s="12">
-        <v>3</v>
-      </c>
-      <c r="J32" s="12">
-        <v>4</v>
-      </c>
-      <c r="K32" s="12">
-        <v>4</v>
-      </c>
-      <c r="L32" s="18">
+      <c r="H32" s="36">
+        <v>4</v>
+      </c>
+      <c r="I32" s="36">
+        <v>3</v>
+      </c>
+      <c r="J32" s="36">
+        <v>4</v>
+      </c>
+      <c r="K32" s="36">
+        <v>4</v>
+      </c>
+      <c r="L32" s="43">
         <f t="shared" ca="1" si="1"/>
         <v>3.1</v>
       </c>
-      <c r="M32" s="18" t="str">
+      <c r="M32" s="43" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N32" s="15"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q32" s="15"/>
-      <c r="S32" s="8" t="s">
+      <c r="N32" s="40"/>
+      <c r="O32" s="40"/>
+      <c r="P32" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q32" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="S32" s="39" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="33" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="7">
+    <row r="33" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="32">
         <v>249048</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="34">
         <v>29299</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="35">
         <f t="shared" ca="1" si="3"/>
         <v>46</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="35">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H33" s="12">
-        <v>4</v>
-      </c>
-      <c r="I33" s="12">
-        <v>1</v>
-      </c>
-      <c r="J33" s="12">
-        <v>4</v>
-      </c>
-      <c r="K33" s="12">
+      <c r="H33" s="36">
+        <v>4</v>
+      </c>
+      <c r="I33" s="36">
+        <v>1</v>
+      </c>
+      <c r="J33" s="36">
+        <v>4</v>
+      </c>
+      <c r="K33" s="36">
         <v>5</v>
       </c>
-      <c r="L33" s="13">
+      <c r="L33" s="37">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M33" s="13" t="str">
+      <c r="M33" s="37" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
-      <c r="P33" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q33" s="9"/>
-      <c r="S33" s="7" t="s">
+      <c r="N33" s="33"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q33" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="S33" s="32" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="8">
+    <row r="34" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="39">
         <v>269022</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="41">
         <v>30852</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="42">
         <f t="shared" ca="1" si="3"/>
         <v>42</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H34" s="12">
-        <v>4</v>
-      </c>
-      <c r="I34" s="12">
-        <v>3</v>
-      </c>
-      <c r="J34" s="12">
-        <v>4</v>
-      </c>
-      <c r="K34" s="12">
-        <v>4</v>
-      </c>
-      <c r="L34" s="18">
+      <c r="H34" s="36">
+        <v>4</v>
+      </c>
+      <c r="I34" s="36">
+        <v>3</v>
+      </c>
+      <c r="J34" s="36">
+        <v>4</v>
+      </c>
+      <c r="K34" s="36">
+        <v>4</v>
+      </c>
+      <c r="L34" s="43">
         <f t="shared" ca="1" si="1"/>
         <v>3.1</v>
       </c>
-      <c r="M34" s="18" t="str">
+      <c r="M34" s="43" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N34" s="15"/>
-      <c r="O34" s="15"/>
-      <c r="P34" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q34" s="15"/>
-      <c r="S34" s="8" t="s">
+      <c r="N34" s="40"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="40" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q34" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="S34" s="39" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="35" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>253014</v>
       </c>
@@ -4161,12 +4332,14 @@
       <c r="N35" s="9"/>
       <c r="O35" s="9"/>
       <c r="P35" s="9"/>
-      <c r="Q35" s="9"/>
+      <c r="Q35" s="9" t="s">
+        <v>291</v>
+      </c>
       <c r="S35" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="36" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>248031</v>
       </c>
@@ -4213,66 +4386,70 @@
       <c r="N36" s="15"/>
       <c r="O36" s="15"/>
       <c r="P36" s="15"/>
-      <c r="Q36" s="15"/>
+      <c r="Q36" s="15" t="s">
+        <v>291</v>
+      </c>
       <c r="S36" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="7">
+    <row r="37" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="32">
         <v>251007</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="33" t="s">
         <v>165</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="E37" s="10">
+      <c r="E37" s="34">
         <v>30522</v>
       </c>
-      <c r="F37" s="11">
+      <c r="F37" s="35">
         <f t="shared" ca="1" si="3"/>
         <v>43</v>
       </c>
-      <c r="G37" s="11">
+      <c r="G37" s="35">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H37" s="12">
-        <v>4</v>
-      </c>
-      <c r="I37" s="12">
-        <v>1</v>
-      </c>
-      <c r="J37" s="12">
-        <v>3</v>
-      </c>
-      <c r="K37" s="12">
-        <v>4</v>
-      </c>
-      <c r="L37" s="13">
+      <c r="H37" s="36">
+        <v>4</v>
+      </c>
+      <c r="I37" s="36">
+        <v>1</v>
+      </c>
+      <c r="J37" s="36">
+        <v>3</v>
+      </c>
+      <c r="K37" s="36">
+        <v>4</v>
+      </c>
+      <c r="L37" s="37">
         <f t="shared" ca="1" si="1"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="M37" s="13" t="str">
+      <c r="M37" s="37" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q37" s="9"/>
-      <c r="S37" s="7" t="s">
+      <c r="N37" s="33"/>
+      <c r="O37" s="33"/>
+      <c r="P37" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q37" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="S37" s="32" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="8">
         <v>242012</v>
       </c>
@@ -4319,66 +4496,70 @@
       <c r="N38" s="15"/>
       <c r="O38" s="15"/>
       <c r="P38" s="15"/>
-      <c r="Q38" s="15"/>
+      <c r="Q38" s="15" t="s">
+        <v>291</v>
+      </c>
       <c r="S38" s="8" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="39" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="7">
+    <row r="39" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="32">
         <v>257039</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="33" t="s">
         <v>169</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="E39" s="10">
+      <c r="E39" s="34">
         <v>32578</v>
       </c>
-      <c r="F39" s="11">
+      <c r="F39" s="35">
         <f t="shared" ca="1" si="3"/>
         <v>37</v>
       </c>
-      <c r="G39" s="11">
+      <c r="G39" s="35">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H39" s="12">
-        <v>4</v>
-      </c>
-      <c r="I39" s="12">
-        <v>3</v>
-      </c>
-      <c r="J39" s="12">
-        <v>4</v>
-      </c>
-      <c r="K39" s="12">
-        <v>4</v>
-      </c>
-      <c r="L39" s="13">
+      <c r="H39" s="36">
+        <v>4</v>
+      </c>
+      <c r="I39" s="36">
+        <v>3</v>
+      </c>
+      <c r="J39" s="36">
+        <v>4</v>
+      </c>
+      <c r="K39" s="36">
+        <v>4</v>
+      </c>
+      <c r="L39" s="37">
         <f t="shared" ca="1" si="1"/>
         <v>3.1</v>
       </c>
-      <c r="M39" s="13" t="str">
+      <c r="M39" s="37" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q39" s="9"/>
-      <c r="S39" s="7" t="s">
+      <c r="N39" s="33"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q39" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="S39" s="32" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>244023</v>
       </c>
@@ -4430,169 +4611,173 @@
         <v>124</v>
       </c>
     </row>
-    <row r="41" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="7">
+    <row r="41" spans="1:19" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="20">
         <v>241009</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="D41" s="9" t="s">
+      <c r="D41" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="22">
         <v>28315</v>
       </c>
-      <c r="F41" s="11">
+      <c r="F41" s="23">
         <f t="shared" ca="1" si="3"/>
         <v>49</v>
       </c>
-      <c r="G41" s="11">
+      <c r="G41" s="23">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H41" s="12">
-        <v>4</v>
-      </c>
-      <c r="I41" s="12">
-        <v>3</v>
-      </c>
-      <c r="J41" s="12">
-        <v>4</v>
-      </c>
-      <c r="K41" s="12">
+      <c r="H41" s="24">
+        <v>4</v>
+      </c>
+      <c r="I41" s="24">
+        <v>3</v>
+      </c>
+      <c r="J41" s="24">
+        <v>4</v>
+      </c>
+      <c r="K41" s="24">
         <v>5</v>
       </c>
-      <c r="L41" s="13">
+      <c r="L41" s="25">
         <f t="shared" ca="1" si="1"/>
         <v>3.3</v>
       </c>
-      <c r="M41" s="13" t="str">
+      <c r="M41" s="25" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N41" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="O41" s="9" t="s">
+      <c r="N41" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="O41" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="P41" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q41" s="9"/>
-      <c r="S41" s="7" t="s">
+      <c r="P41" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q41" s="21"/>
+      <c r="S41" s="20" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="42" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="8">
+    <row r="42" spans="1:19" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="27">
         <v>368001</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="E42" s="16">
+      <c r="E42" s="29">
         <v>30299</v>
       </c>
-      <c r="F42" s="17">
+      <c r="F42" s="30">
         <f t="shared" ca="1" si="3"/>
         <v>43</v>
       </c>
-      <c r="G42" s="17">
+      <c r="G42" s="30">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H42" s="12">
-        <v>4</v>
-      </c>
-      <c r="I42" s="12">
+      <c r="H42" s="24">
+        <v>4</v>
+      </c>
+      <c r="I42" s="24">
         <v>5</v>
       </c>
-      <c r="J42" s="12">
-        <v>4</v>
-      </c>
-      <c r="K42" s="12">
-        <v>3</v>
-      </c>
-      <c r="L42" s="18">
+      <c r="J42" s="24">
+        <v>4</v>
+      </c>
+      <c r="K42" s="24">
+        <v>3</v>
+      </c>
+      <c r="L42" s="31">
         <f t="shared" ca="1" si="1"/>
         <v>3.5</v>
       </c>
-      <c r="M42" s="18" t="str">
+      <c r="M42" s="31" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N42" s="15"/>
-      <c r="O42" s="15"/>
-      <c r="P42" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q42" s="15"/>
-      <c r="S42" s="8" t="s">
+      <c r="N42" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q42" s="28"/>
+      <c r="S42" s="27" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="43" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="7">
+    <row r="43" spans="1:19" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="20">
         <v>148005</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="D43" s="9" t="s">
+      <c r="D43" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="E43" s="10">
+      <c r="E43" s="22">
         <v>27329</v>
       </c>
-      <c r="F43" s="11">
+      <c r="F43" s="23">
         <f t="shared" ca="1" si="3"/>
         <v>51</v>
       </c>
-      <c r="G43" s="11">
+      <c r="G43" s="23">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H43" s="12">
-        <v>4</v>
-      </c>
-      <c r="I43" s="12">
-        <v>1</v>
-      </c>
-      <c r="J43" s="12">
-        <v>4</v>
-      </c>
-      <c r="K43" s="12">
-        <v>4</v>
-      </c>
-      <c r="L43" s="13">
+      <c r="H43" s="24">
+        <v>4</v>
+      </c>
+      <c r="I43" s="24">
+        <v>1</v>
+      </c>
+      <c r="J43" s="24">
+        <v>4</v>
+      </c>
+      <c r="K43" s="24">
+        <v>4</v>
+      </c>
+      <c r="L43" s="25">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M43" s="13" t="str">
+      <c r="M43" s="25" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9"/>
-      <c r="P43" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q43" s="9"/>
-      <c r="S43" s="7" t="s">
+      <c r="N43" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="O43" s="21"/>
+      <c r="P43" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q43" s="21"/>
+      <c r="S43" s="20" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4640,10 +4825,12 @@
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N44" s="9"/>
+      <c r="N44" s="9" t="s">
+        <v>289</v>
+      </c>
       <c r="O44" s="9"/>
       <c r="P44" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="Q44" s="9"/>
       <c r="S44" s="7" t="s">
@@ -4694,10 +4881,12 @@
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N45" s="15"/>
+      <c r="N45" s="15" t="s">
+        <v>289</v>
+      </c>
       <c r="O45" s="15"/>
       <c r="P45" s="15" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q45" s="15"/>
       <c r="S45" s="8" t="s">
@@ -4748,10 +4937,12 @@
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N46" s="9"/>
+      <c r="N46" s="9" t="s">
+        <v>289</v>
+      </c>
       <c r="O46" s="9"/>
       <c r="P46" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Q46" s="9"/>
       <c r="S46" s="7" t="s">
@@ -4803,13 +4994,13 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N47" s="15" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O47" s="15" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="P47" s="15" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="Q47" s="15"/>
       <c r="S47" s="8" t="s">
@@ -4851,21 +5042,23 @@
         <v>5</v>
       </c>
       <c r="L48" s="13">
-        <f t="shared" ref="L48:L68" si="6">IF(OR(I48="",J48="",K48="",G48=""),"",ROUND(G48*0.2+I48*0.3+J48*0.3+K48*0.2,2))</f>
+        <f t="shared" ref="L48:L67" si="6">IF(OR(I48="",J48="",K48="",G48=""),"",ROUND(G48*0.2+I48*0.3+J48*0.3+K48*0.2,2))</f>
         <v>4.0999999999999996</v>
       </c>
       <c r="M48" s="13" t="str">
-        <f t="shared" ref="M48:M68" si="7">IF(OR(H48="",L48=""),"",IF(AND(H48&gt;=4,L48&gt;=3.5),"High Impact + High Risk",IF(AND(H48&gt;=4,L48&lt;3.5),"High Impact + Low Risk",IF(AND(H48&lt;4,L48&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+        <f t="shared" ref="M48:M67" si="7">IF(OR(H48="",L48=""),"",IF(AND(H48&gt;=4,L48&gt;=3.5),"High Impact + High Risk",IF(AND(H48&gt;=4,L48&lt;3.5),"High Impact + Low Risk",IF(AND(H48&lt;4,L48&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N48" s="9"/>
+      <c r="N48" s="9" t="s">
+        <v>289</v>
+      </c>
       <c r="O48" s="9"/>
       <c r="P48" s="9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="Q48" s="9"/>
       <c r="S48" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -4914,14 +5107,14 @@
         <v>210</v>
       </c>
       <c r="O49" s="15" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="P49" s="15" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="Q49" s="15"/>
       <c r="S49" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="50" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -4966,17 +5159,19 @@
         <f t="shared" si="7"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N50" s="9"/>
+      <c r="N50" s="9" t="s">
+        <v>289</v>
+      </c>
       <c r="O50" s="9"/>
       <c r="P50" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q50" s="9"/>
       <c r="S50" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>161005</v>
       </c>
@@ -5023,10 +5218,10 @@
       <c r="P51" s="15"/>
       <c r="Q51" s="15"/>
       <c r="S51" s="8" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="7">
         <v>163003</v>
       </c>
@@ -5073,10 +5268,10 @@
       <c r="P52" s="9"/>
       <c r="Q52" s="9"/>
       <c r="S52" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <v>166024</v>
       </c>
@@ -5123,10 +5318,10 @@
       <c r="P53" s="15"/>
       <c r="Q53" s="15"/>
       <c r="S53" s="8" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>167001</v>
       </c>
@@ -5173,10 +5368,10 @@
       <c r="P54" s="9"/>
       <c r="Q54" s="9"/>
       <c r="S54" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>167012</v>
       </c>
@@ -5223,7 +5418,7 @@
       <c r="P55" s="15"/>
       <c r="Q55" s="15"/>
       <c r="S55" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="56" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5268,17 +5463,19 @@
         <f t="shared" si="7"/>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N56" s="9"/>
+      <c r="N56" s="9" t="s">
+        <v>289</v>
+      </c>
       <c r="O56" s="9"/>
       <c r="P56" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="Q56" s="9"/>
       <c r="S56" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
         <v>267001</v>
       </c>
@@ -5325,7 +5522,7 @@
       <c r="P57" s="15"/>
       <c r="Q57" s="15"/>
       <c r="S57" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="58" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5370,17 +5567,19 @@
         <f t="shared" si="7"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N58" s="9"/>
+      <c r="N58" s="9" t="s">
+        <v>289</v>
+      </c>
       <c r="O58" s="9"/>
       <c r="P58" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q58" s="9"/>
       <c r="S58" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
         <v>167020</v>
       </c>
@@ -5427,7 +5626,7 @@
       <c r="P59" s="9"/>
       <c r="Q59" s="9"/>
       <c r="S59" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5472,17 +5671,19 @@
         <f t="shared" si="7"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N60" s="15"/>
+      <c r="N60" s="15" t="s">
+        <v>289</v>
+      </c>
       <c r="O60" s="15"/>
       <c r="P60" s="15" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="Q60" s="15"/>
       <c r="S60" s="8" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>167032</v>
       </c>
@@ -5529,7 +5730,7 @@
       <c r="P61" s="9"/>
       <c r="Q61" s="9"/>
       <c r="S61" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="62" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5574,17 +5775,19 @@
         <f t="shared" si="7"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N62" s="15"/>
+      <c r="N62" s="15" t="s">
+        <v>289</v>
+      </c>
       <c r="O62" s="15"/>
       <c r="P62" s="15" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="Q62" s="15"/>
       <c r="S62" s="8" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="8">
         <v>337004</v>
       </c>
@@ -5631,10 +5834,10 @@
       <c r="P63" s="15"/>
       <c r="Q63" s="15"/>
       <c r="S63" s="8" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="8">
         <v>268044</v>
       </c>
@@ -5681,7 +5884,7 @@
       <c r="P64" s="15"/>
       <c r="Q64" s="15"/>
       <c r="S64" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="65" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -5726,138 +5929,151 @@
         <f t="shared" si="7"/>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N65" s="9"/>
+      <c r="N65" s="9" t="s">
+        <v>289</v>
+      </c>
       <c r="O65" s="9"/>
       <c r="P65" s="9" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="S65" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="F66" s="11">
+        <v>55</v>
+      </c>
+      <c r="G66" s="11">
+        <v>3</v>
+      </c>
+      <c r="H66" s="12">
+        <v>4</v>
+      </c>
+      <c r="I66" s="12">
+        <v>4</v>
+      </c>
+      <c r="J66" s="12">
+        <v>4</v>
+      </c>
+      <c r="K66" s="12">
+        <v>4</v>
+      </c>
+      <c r="L66" s="13">
+        <f t="shared" si="6"/>
+        <v>3.8</v>
+      </c>
+      <c r="M66" s="13" t="str">
+        <f t="shared" si="7"/>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N66" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="O66" s="9"/>
+      <c r="P66" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q66" s="9"/>
+      <c r="S66" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="20">
+        <v>168016</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="C67" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E67" s="22" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="66" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="8">
-        <v>269040</v>
-      </c>
-      <c r="B66" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="C66" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="D66" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E66" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="F66" s="17">
-        <v>45</v>
-      </c>
-      <c r="G66" s="17">
-        <v>1</v>
-      </c>
-      <c r="H66" s="12">
-        <v>4</v>
-      </c>
-      <c r="I66" s="12">
-        <v>3</v>
-      </c>
-      <c r="J66" s="12">
-        <v>4</v>
-      </c>
-      <c r="K66" s="12">
-        <v>3</v>
-      </c>
-      <c r="L66" s="18">
+      <c r="F67" s="23">
+        <v>35</v>
+      </c>
+      <c r="G67" s="23">
+        <v>1</v>
+      </c>
+      <c r="H67" s="24">
+        <v>4</v>
+      </c>
+      <c r="I67" s="24">
+        <v>3</v>
+      </c>
+      <c r="J67" s="24">
+        <v>4</v>
+      </c>
+      <c r="K67" s="24">
+        <v>1</v>
+      </c>
+      <c r="L67" s="25">
         <f t="shared" si="6"/>
-        <v>2.9</v>
-      </c>
-      <c r="M66" s="18" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="M67" s="25" t="str">
         <f t="shared" si="7"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N66" s="15"/>
-      <c r="O66" s="15"/>
-      <c r="P66" s="15"/>
-      <c r="Q66" s="15"/>
-      <c r="S66" s="8" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="7" t="s">
+      <c r="N67" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="O67" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="B67" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="D67" s="9" t="s">
+      <c r="P67" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q67" s="21"/>
+      <c r="R67" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="S67" s="20" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="8">
+        <v>258026</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="D68" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="E67" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="F67" s="11">
-        <v>55</v>
-      </c>
-      <c r="G67" s="11">
-        <v>3</v>
-      </c>
-      <c r="H67" s="12">
-        <v>4</v>
-      </c>
-      <c r="I67" s="12">
-        <v>4</v>
-      </c>
-      <c r="J67" s="12">
-        <v>4</v>
-      </c>
-      <c r="K67" s="12">
-        <v>4</v>
-      </c>
-      <c r="L67" s="13">
-        <f t="shared" si="6"/>
-        <v>3.8</v>
-      </c>
-      <c r="M67" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>High Impact + High Risk</v>
-      </c>
-      <c r="N67" s="9"/>
-      <c r="O67" s="9"/>
-      <c r="P67" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q67" s="9"/>
-      <c r="S67" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="7">
-        <v>168016</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="F68" s="11">
-        <v>35</v>
-      </c>
-      <c r="G68" s="11">
+      <c r="E68" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F68" s="17">
+        <v>42</v>
+      </c>
+      <c r="G68" s="17">
         <v>1</v>
       </c>
       <c r="H68" s="12">
@@ -5870,94 +6086,42 @@
         <v>4</v>
       </c>
       <c r="K68" s="12">
-        <v>1</v>
-      </c>
-      <c r="L68" s="13">
-        <f t="shared" si="6"/>
-        <v>2.5</v>
-      </c>
-      <c r="M68" s="13" t="str">
-        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="L68" s="18">
+        <f t="shared" ref="L68" si="8">IF(OR(I68="",J68="",K68="",G68=""),"",ROUND(G68*0.2+I68*0.3+J68*0.3+K68*0.2,2))</f>
+        <v>2.9</v>
+      </c>
+      <c r="M68" s="18" t="str">
+        <f t="shared" ref="M68" si="9">IF(OR(H68="",L68=""),"",IF(AND(H68&gt;=4,L68&gt;=3.5),"High Impact + High Risk",IF(AND(H68&gt;=4,L68&lt;3.5),"High Impact + Low Risk",IF(AND(H68&lt;4,L68&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N68" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="O68" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="P68" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q68" s="9"/>
+      <c r="N68" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="O68" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="P68" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q68" s="15"/>
       <c r="R68" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="S68" s="7" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="8">
-        <v>258026</v>
-      </c>
-      <c r="B69" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="C69" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E69" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="F69" s="17">
-        <v>42</v>
-      </c>
-      <c r="G69" s="17">
-        <v>1</v>
-      </c>
-      <c r="H69" s="12">
-        <v>4</v>
-      </c>
-      <c r="I69" s="12">
-        <v>3</v>
-      </c>
-      <c r="J69" s="12">
-        <v>4</v>
-      </c>
-      <c r="K69" s="12">
-        <v>3</v>
-      </c>
-      <c r="L69" s="18">
-        <f t="shared" ref="L69" si="8">IF(OR(I69="",J69="",K69="",G69=""),"",ROUND(G69*0.2+I69*0.3+J69*0.3+K69*0.2,2))</f>
-        <v>2.9</v>
-      </c>
-      <c r="M69" s="18" t="str">
-        <f t="shared" ref="M69" si="9">IF(OR(H69="",L69=""),"",IF(AND(H69&gt;=4,L69&gt;=3.5),"High Impact + High Risk",IF(AND(H69&gt;=4,L69&lt;3.5),"High Impact + Low Risk",IF(AND(H69&lt;4,L69&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N69" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="O69" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="P69" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q69" s="15"/>
-      <c r="R69" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="S69" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="S68" s="8" t="s">
         <v>93</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S69" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:S68" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="12">
+      <filters>
+        <filter val="High Impact + High Risk"/>
+        <filter val="High Impact + Low Risk"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5D63C34-AFD1-460B-A1AA-ACD88AD9EFC2}"/>
+  <xr:revisionPtr revIDLastSave="160" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A6435A2-154B-4088-9882-52F253894541}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="กรอกข้อมูล" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$S$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$R$68</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="300">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -346,9 +346,6 @@
     <t>Section Manager - Asia Pacific</t>
   </si>
   <si>
-    <t>Key Position (B)</t>
-  </si>
-  <si>
     <t>CCD</t>
   </si>
   <si>
@@ -358,9 +355,6 @@
     <t>Section Manager - Atlantic Ocean</t>
   </si>
   <si>
-    <t>Key Position (A)</t>
-  </si>
-  <si>
     <t>จุฑามาส ศรีโมรา</t>
   </si>
   <si>
@@ -898,15 +892,6 @@
     <t>258026_DeptManager_QualityManagement.docx</t>
   </si>
   <si>
-    <t>266049_Department Manager Human Resources</t>
-  </si>
-  <si>
-    <t>368004_Contract-Procurement</t>
-  </si>
-  <si>
-    <t>149024 A_Acting Procurement Manager</t>
-  </si>
-  <si>
     <t>สรรหาจากภายนอก</t>
   </si>
   <si>
@@ -914,6 +899,45 @@
   </si>
   <si>
     <t xml:space="preserve">รอพี่วุฒิแจ้ง </t>
+  </si>
+  <si>
+    <t>149024 A_Acting Procurement Manager.docx</t>
+  </si>
+  <si>
+    <t>266049_Department Manager Human Resources.docx</t>
+  </si>
+  <si>
+    <t>368004_Contract-Procurement.docx</t>
+  </si>
+  <si>
+    <t>Leadership</t>
+  </si>
+  <si>
+    <t>Change Implementation</t>
+  </si>
+  <si>
+    <t>Initiative &amp; Innovation</t>
+  </si>
+  <si>
+    <t>Quality Orientation</t>
+  </si>
+  <si>
+    <t>Result &amp; Cost Driven</t>
+  </si>
+  <si>
+    <t>Teamwork</t>
+  </si>
+  <si>
+    <t>Communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Orientation </t>
+  </si>
+  <si>
+    <t>Problem Solving &amp; Decision Making</t>
+  </si>
+  <si>
+    <t>ไม่มีผลประเมิน</t>
   </si>
 </sst>
 </file>
@@ -1369,43 +1393,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1416,6 +1416,30 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1695,727 +1719,693 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="51" t="s">
+      <c r="C12" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="51" t="s">
+      <c r="C13" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="52" t="s">
+      <c r="B15" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="48" t="s">
+      <c r="B22" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="52" t="s">
+      <c r="B23" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="53" t="s">
+      <c r="B26" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="54" t="s">
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="54"/>
+      <c r="G26" s="57"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="53" t="s">
+      <c r="B27" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="53"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="53"/>
-      <c r="F27" s="54" t="s">
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="54"/>
+      <c r="G27" s="57"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="53" t="s">
+      <c r="B28" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="54" t="s">
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="54"/>
+      <c r="G28" s="57"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="53" t="s">
+      <c r="B29" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="53"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="54" t="s">
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="54"/>
+      <c r="G29" s="57"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="53" t="s">
+      <c r="B30" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="54" t="s">
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="54"/>
+      <c r="G30" s="57"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="52" t="s">
+      <c r="B32" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="51" t="s">
+      <c r="C33" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="51"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="51"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="51" t="s">
+      <c r="C34" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="51"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="51"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="51" t="s">
+      <c r="C35" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="49"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="52" t="s">
+      <c r="B37" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="52"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="51" t="s">
+      <c r="C38" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="51"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="51"/>
-      <c r="G38" s="51"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="49"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="51" t="s">
+      <c r="C39" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="51"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="49"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="51" t="s">
+      <c r="C40" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="51"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="51"/>
-      <c r="G40" s="51"/>
+      <c r="D40" s="49"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="49"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="51" t="s">
+      <c r="C41" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="51"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
-      <c r="G41" s="51"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="49"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="51" t="s">
+      <c r="C42" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="51"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="49"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="52" t="s">
+      <c r="B44" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="52"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="53"/>
+      <c r="G44" s="53"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="51" t="s">
+      <c r="C45" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="51"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="51" t="s">
+      <c r="C46" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="51"/>
-      <c r="E46" s="51"/>
-      <c r="F46" s="51"/>
-      <c r="G46" s="51"/>
+      <c r="D46" s="49"/>
+      <c r="E46" s="49"/>
+      <c r="F46" s="49"/>
+      <c r="G46" s="49"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="51" t="s">
+      <c r="C47" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="51"/>
-      <c r="E47" s="51"/>
-      <c r="F47" s="51"/>
-      <c r="G47" s="51"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="49"/>
+      <c r="G47" s="49"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="51" t="s">
+      <c r="C48" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="51"/>
-      <c r="E48" s="51"/>
-      <c r="F48" s="51"/>
-      <c r="G48" s="51"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="49"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="51" t="s">
+      <c r="C49" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="51"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="51"/>
-      <c r="G49" s="51"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="49"/>
+      <c r="G49" s="49"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="48" t="s">
+      <c r="B51" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
+      <c r="C51" s="47"/>
+      <c r="D51" s="47"/>
+      <c r="E51" s="47"/>
+      <c r="F51" s="47"/>
+      <c r="G51" s="47"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="55" t="s">
+      <c r="B52" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="55"/>
-      <c r="D52" s="55"/>
-      <c r="E52" s="55"/>
-      <c r="F52" s="55"/>
-      <c r="G52" s="55"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="54"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="56" t="s">
+      <c r="B53" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="56"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
-      <c r="F53" s="56"/>
-      <c r="G53" s="56"/>
+      <c r="C53" s="55"/>
+      <c r="D53" s="55"/>
+      <c r="E53" s="55"/>
+      <c r="F53" s="55"/>
+      <c r="G53" s="55"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="48" t="s">
+      <c r="B55" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="48"/>
-      <c r="D55" s="48"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="48"/>
-      <c r="G55" s="48"/>
+      <c r="C55" s="47"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="47"/>
+      <c r="G55" s="47"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="57" t="s">
+      <c r="B56" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="57"/>
-      <c r="D56" s="57"/>
-      <c r="E56" s="51" t="s">
+      <c r="C56" s="48"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="51"/>
-      <c r="G56" s="51"/>
+      <c r="F56" s="49"/>
+      <c r="G56" s="49"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="58" t="s">
+      <c r="B57" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="58"/>
-      <c r="D57" s="58"/>
-      <c r="E57" s="51" t="s">
+      <c r="C57" s="50"/>
+      <c r="D57" s="50"/>
+      <c r="E57" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="51"/>
-      <c r="G57" s="51"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="49"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="59" t="s">
+      <c r="B58" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="59"/>
-      <c r="D58" s="59"/>
-      <c r="E58" s="51" t="s">
+      <c r="C58" s="51"/>
+      <c r="D58" s="51"/>
+      <c r="E58" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="51"/>
-      <c r="G58" s="51"/>
+      <c r="F58" s="49"/>
+      <c r="G58" s="49"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="60" t="s">
+      <c r="B59" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="60"/>
-      <c r="D59" s="60"/>
-      <c r="E59" s="51" t="s">
+      <c r="C59" s="52"/>
+      <c r="D59" s="52"/>
+      <c r="E59" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="51"/>
-      <c r="G59" s="51"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="49"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="48" t="s">
+      <c r="B62" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="48"/>
-      <c r="D62" s="48"/>
-      <c r="E62" s="48"/>
-      <c r="F62" s="48"/>
-      <c r="G62" s="48"/>
+      <c r="C62" s="47"/>
+      <c r="D62" s="47"/>
+      <c r="E62" s="47"/>
+      <c r="F62" s="47"/>
+      <c r="G62" s="47"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="49" t="s">
+      <c r="B63" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="49"/>
-      <c r="D63" s="49"/>
-      <c r="E63" s="49"/>
-      <c r="F63" s="49"/>
-      <c r="G63" s="49"/>
+      <c r="C63" s="45"/>
+      <c r="D63" s="45"/>
+      <c r="E63" s="45"/>
+      <c r="F63" s="45"/>
+      <c r="G63" s="45"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="45" t="s">
+      <c r="B64" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="45"/>
-      <c r="D64" s="45"/>
-      <c r="E64" s="45"/>
-      <c r="F64" s="45"/>
-      <c r="G64" s="45"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="46"/>
+      <c r="E64" s="46"/>
+      <c r="F64" s="46"/>
+      <c r="G64" s="46"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="45" t="s">
+      <c r="B65" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="45"/>
-      <c r="D65" s="45"/>
-      <c r="E65" s="45"/>
-      <c r="F65" s="45"/>
-      <c r="G65" s="45"/>
+      <c r="C65" s="46"/>
+      <c r="D65" s="46"/>
+      <c r="E65" s="46"/>
+      <c r="F65" s="46"/>
+      <c r="G65" s="46"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="45" t="s">
+      <c r="B66" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="45"/>
-      <c r="D66" s="45"/>
-      <c r="E66" s="45"/>
-      <c r="F66" s="45"/>
-      <c r="G66" s="45"/>
+      <c r="C66" s="46"/>
+      <c r="D66" s="46"/>
+      <c r="E66" s="46"/>
+      <c r="F66" s="46"/>
+      <c r="G66" s="46"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="45" t="s">
+      <c r="B67" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="45"/>
-      <c r="D67" s="45"/>
-      <c r="E67" s="45"/>
-      <c r="F67" s="45"/>
-      <c r="G67" s="45"/>
+      <c r="C67" s="46"/>
+      <c r="D67" s="46"/>
+      <c r="E67" s="46"/>
+      <c r="F67" s="46"/>
+      <c r="G67" s="46"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="48" t="s">
+      <c r="B69" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="48"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="48"/>
+      <c r="C69" s="47"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="47"/>
+      <c r="G69" s="47"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="49" t="s">
+      <c r="B70" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="49"/>
-      <c r="D70" s="49"/>
-      <c r="E70" s="49"/>
-      <c r="F70" s="49"/>
-      <c r="G70" s="49"/>
+      <c r="C70" s="45"/>
+      <c r="D70" s="45"/>
+      <c r="E70" s="45"/>
+      <c r="F70" s="45"/>
+      <c r="G70" s="45"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="49" t="s">
+      <c r="B71" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="49"/>
-      <c r="D71" s="49"/>
-      <c r="E71" s="49"/>
-      <c r="F71" s="49"/>
-      <c r="G71" s="49"/>
+      <c r="C71" s="45"/>
+      <c r="D71" s="45"/>
+      <c r="E71" s="45"/>
+      <c r="F71" s="45"/>
+      <c r="G71" s="45"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="49" t="s">
+      <c r="B72" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="49"/>
-      <c r="D72" s="49"/>
-      <c r="E72" s="49"/>
-      <c r="F72" s="49"/>
-      <c r="G72" s="49"/>
+      <c r="C72" s="45"/>
+      <c r="D72" s="45"/>
+      <c r="E72" s="45"/>
+      <c r="F72" s="45"/>
+      <c r="G72" s="45"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="49" t="s">
+      <c r="B73" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="49"/>
-      <c r="D73" s="49"/>
-      <c r="E73" s="49"/>
-      <c r="F73" s="49"/>
-      <c r="G73" s="49"/>
+      <c r="C73" s="45"/>
+      <c r="D73" s="45"/>
+      <c r="E73" s="45"/>
+      <c r="F73" s="45"/>
+      <c r="G73" s="45"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="49" t="s">
+      <c r="B74" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="49"/>
-      <c r="D74" s="49"/>
-      <c r="E74" s="49"/>
-      <c r="F74" s="49"/>
-      <c r="G74" s="49"/>
+      <c r="C74" s="45"/>
+      <c r="D74" s="45"/>
+      <c r="E74" s="45"/>
+      <c r="F74" s="45"/>
+      <c r="G74" s="45"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="49" t="s">
+      <c r="B75" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="49"/>
-      <c r="D75" s="49"/>
-      <c r="E75" s="49"/>
-      <c r="F75" s="49"/>
-      <c r="G75" s="49"/>
+      <c r="C75" s="45"/>
+      <c r="D75" s="45"/>
+      <c r="E75" s="45"/>
+      <c r="F75" s="45"/>
+      <c r="G75" s="45"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="49"/>
-      <c r="C76" s="49"/>
-      <c r="D76" s="49"/>
-      <c r="E76" s="49"/>
-      <c r="F76" s="49"/>
-      <c r="G76" s="49"/>
+      <c r="B76" s="45"/>
+      <c r="C76" s="45"/>
+      <c r="D76" s="45"/>
+      <c r="E76" s="45"/>
+      <c r="F76" s="45"/>
+      <c r="G76" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B15:G15"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="B17:G17"/>
@@ -2429,18 +2419,52 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2449,8 +2473,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:S68"/>
+  <dimension ref="A1:AA68"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2470,10 +2493,12 @@
     <col min="15" max="15" width="18" customWidth="1"/>
     <col min="16" max="16" width="26" customWidth="1"/>
     <col min="17" max="17" width="28" customWidth="1"/>
-    <col min="19" max="19" width="8.6328125" style="4"/>
+    <col min="18" max="18" width="8.6328125" style="4"/>
+    <col min="19" max="26" width="13.26953125" customWidth="1"/>
+    <col min="27" max="27" width="21.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
@@ -2493,9 +2518,9 @@
       <c r="O1" s="44"/>
       <c r="P1" s="44"/>
       <c r="Q1" s="44"/>
-      <c r="S1" s="5"/>
-    </row>
-    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R1" s="5"/>
+    </row>
+    <row r="2" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2547,11 +2572,38 @@
       <c r="Q2" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="R2" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="S2" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>290</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>168028</v>
       </c>
@@ -2562,7 +2614,7 @@
         <v>101</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E3" s="10">
         <v>31046</v>
@@ -2599,22 +2651,49 @@
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
       <c r="Q3" s="9"/>
-      <c r="S3" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R3" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="S3" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="T3" s="14">
+        <v>3</v>
+      </c>
+      <c r="U3" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="V3" s="14">
+        <v>3</v>
+      </c>
+      <c r="W3" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X3" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y3" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z3" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA3" s="14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>150026</v>
       </c>
       <c r="B4" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>105</v>
-      </c>
       <c r="D4" s="15" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E4" s="16">
         <v>29304</v>
@@ -2651,22 +2730,49 @@
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
-      <c r="S4" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R4" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="S4" s="14">
+        <v>4</v>
+      </c>
+      <c r="T4" s="14">
+        <v>3</v>
+      </c>
+      <c r="U4" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="V4" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="W4" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X4" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y4" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Z4" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA4" s="14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>147022</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E5" s="10">
         <v>29168</v>
@@ -2703,22 +2809,49 @@
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
-      <c r="S5" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R5" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="S5" s="14">
+        <v>4</v>
+      </c>
+      <c r="T5" s="14">
+        <v>3</v>
+      </c>
+      <c r="U5" s="14">
+        <v>3</v>
+      </c>
+      <c r="V5" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="W5" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X5" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y5" s="14">
+        <v>4</v>
+      </c>
+      <c r="Z5" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA5" s="14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>136049</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E6" s="16">
         <v>25766</v>
@@ -2755,22 +2888,49 @@
       <c r="O6" s="15"/>
       <c r="P6" s="15"/>
       <c r="Q6" s="15"/>
-      <c r="S6" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R6" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="S6" s="14">
+        <v>4.5</v>
+      </c>
+      <c r="T6" s="14">
+        <v>3</v>
+      </c>
+      <c r="U6" s="14">
+        <v>4</v>
+      </c>
+      <c r="V6" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="W6" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X6" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y6" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Z6" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA6" s="14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>161027</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E7" s="10">
         <v>31632</v>
@@ -2807,22 +2967,49 @@
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
-      <c r="S7" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R7" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="S7" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="T7" s="14">
+        <v>3</v>
+      </c>
+      <c r="U7" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="V7" s="14">
+        <v>3</v>
+      </c>
+      <c r="W7" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X7" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y7" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Z7" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="AA7" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>656001</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E8" s="10">
         <v>25400</v>
@@ -2859,22 +3046,49 @@
       <c r="O8" s="9"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
-      <c r="S8" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R8" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="S8" s="14">
+        <v>4.5</v>
+      </c>
+      <c r="T8" s="14">
+        <v>3</v>
+      </c>
+      <c r="U8" s="14">
+        <v>4</v>
+      </c>
+      <c r="V8" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="W8" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X8" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y8" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA8" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>656008</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E9" s="16">
         <v>34150</v>
@@ -2911,19 +3125,46 @@
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
       <c r="Q9" s="15"/>
-      <c r="S9" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R9" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="S9" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U9" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V9" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W9" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X9" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y9" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z9" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA9" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>168017</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>90</v>
@@ -2963,19 +3204,46 @@
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
-      <c r="S10" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R10" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="S10" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="T10" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="U10" s="14">
+        <v>3</v>
+      </c>
+      <c r="V10" s="14">
+        <v>3</v>
+      </c>
+      <c r="W10" s="14">
+        <v>3</v>
+      </c>
+      <c r="X10" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y10" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="AA10" s="14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="27">
         <v>266049</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D11" s="28" t="s">
         <v>90</v>
@@ -3012,28 +3280,55 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N11" s="28" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="O11" s="28" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P11" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q11" s="28"/>
-      <c r="S11" s="27" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R11" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="S11" s="14">
+        <v>3</v>
+      </c>
+      <c r="T11" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="U11" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="V11" s="14">
+        <v>3</v>
+      </c>
+      <c r="W11" s="14">
+        <v>3</v>
+      </c>
+      <c r="X11" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y11" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z11" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA11" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>166027</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>90</v>
@@ -3073,25 +3368,52 @@
       <c r="O12" s="9"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
-      <c r="S12" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R12" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="S12" s="14">
+        <v>3</v>
+      </c>
+      <c r="T12" s="14">
+        <v>3</v>
+      </c>
+      <c r="U12" s="14">
+        <v>3</v>
+      </c>
+      <c r="V12" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="W12" s="14">
+        <v>3</v>
+      </c>
+      <c r="X12" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA12" s="14">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="27">
         <v>466004</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D13" s="28" t="s">
         <v>90</v>
       </c>
       <c r="E13" s="29" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F13" s="30">
         <v>66</v>
@@ -3120,32 +3442,59 @@
         <v>High Impact + High Risk</v>
       </c>
       <c r="N13" s="28" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O13" s="28"/>
       <c r="P13" s="28" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Q13" s="28"/>
-      <c r="S13" s="27" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R13" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="S13" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T13" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U13" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V13" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W13" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X13" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y13" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z13" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA13" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="20">
         <v>159029</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>90</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F14" s="23">
         <v>52</v>
@@ -3174,29 +3523,56 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N14" s="21" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O14" s="21"/>
       <c r="P14" s="21" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="Q14" s="21"/>
-      <c r="S14" s="20" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R14" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="S14" s="14">
+        <v>4</v>
+      </c>
+      <c r="T14" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="U14" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="V14" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="W14" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X14" s="14">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Z14" s="14">
+        <v>4</v>
+      </c>
+      <c r="AA14" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="32">
         <v>239006</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E15" s="34">
         <v>26179</v>
@@ -3232,27 +3608,54 @@
       <c r="N15" s="33"/>
       <c r="O15" s="33"/>
       <c r="P15" s="33" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Q15" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="S15" s="32" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R15" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="S15" s="14">
+        <v>4</v>
+      </c>
+      <c r="T15" s="14">
+        <v>4</v>
+      </c>
+      <c r="U15" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="V15" s="14">
+        <v>4</v>
+      </c>
+      <c r="W15" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X15" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y15" s="14">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="14">
+        <v>4</v>
+      </c>
+      <c r="AA15" s="14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="39">
         <v>246004</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E16" s="41">
         <v>28270</v>
@@ -3288,27 +3691,54 @@
       <c r="N16" s="40"/>
       <c r="O16" s="40"/>
       <c r="P16" s="40" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Q16" s="40" t="s">
-        <v>291</v>
-      </c>
-      <c r="S16" s="39" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R16" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="S16" s="14">
+        <v>3</v>
+      </c>
+      <c r="T16" s="14">
+        <v>3</v>
+      </c>
+      <c r="U16" s="14">
+        <v>3</v>
+      </c>
+      <c r="V16" s="14">
+        <v>3</v>
+      </c>
+      <c r="W16" s="14">
+        <v>3</v>
+      </c>
+      <c r="X16" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y16" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z16" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA16" s="14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>242032</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E17" s="10">
         <v>27745</v>
@@ -3345,24 +3775,51 @@
       <c r="O17" s="9"/>
       <c r="P17" s="9"/>
       <c r="Q17" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="S17" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="S17" s="14">
+        <v>4</v>
+      </c>
+      <c r="T17" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="U17" s="14">
+        <v>3</v>
+      </c>
+      <c r="V17" s="14">
+        <v>4</v>
+      </c>
+      <c r="W17" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X17" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z17" s="14">
+        <v>4</v>
+      </c>
+      <c r="AA17" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>149024</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E18" s="16">
         <v>26070</v>
@@ -3399,24 +3856,51 @@
       <c r="O18" s="15"/>
       <c r="P18" s="15"/>
       <c r="Q18" s="15" t="s">
-        <v>291</v>
-      </c>
-      <c r="S18" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="S18" s="14">
+        <v>4</v>
+      </c>
+      <c r="T18" s="14">
+        <v>3</v>
+      </c>
+      <c r="U18" s="14">
+        <v>3</v>
+      </c>
+      <c r="V18" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="W18" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X18" s="14">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="14">
+        <v>4</v>
+      </c>
+      <c r="Z18" s="14">
+        <v>4</v>
+      </c>
+      <c r="AA18" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>232027</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E19" s="10">
         <v>24838</v>
@@ -3453,24 +3937,51 @@
       <c r="O19" s="9"/>
       <c r="P19" s="9"/>
       <c r="Q19" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="S19" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="S19" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T19" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U19" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V19" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W19" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X19" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y19" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z19" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA19" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>256029</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E20" s="16">
         <v>31119</v>
@@ -3507,24 +4018,51 @@
       <c r="O20" s="15"/>
       <c r="P20" s="15"/>
       <c r="Q20" s="15" t="s">
-        <v>291</v>
-      </c>
-      <c r="S20" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="S20" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="T20" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="U20" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="V20" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="W20" s="14">
+        <v>3</v>
+      </c>
+      <c r="X20" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="AA20" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>236012</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E21" s="10">
         <v>26421</v>
@@ -3561,24 +4099,51 @@
       <c r="O21" s="9"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="S21" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="S21" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="T21" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="U21" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="V21" s="14">
+        <v>3</v>
+      </c>
+      <c r="W21" s="14">
+        <v>3</v>
+      </c>
+      <c r="X21" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="Z21" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="39">
         <v>250042</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D22" s="40" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E22" s="41">
         <v>26738</v>
@@ -3614,27 +4179,54 @@
       <c r="N22" s="40"/>
       <c r="O22" s="40"/>
       <c r="P22" s="40" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="Q22" s="40" t="s">
-        <v>291</v>
-      </c>
-      <c r="S22" s="39" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R22" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="S22" s="14">
+        <v>3</v>
+      </c>
+      <c r="T22" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="U22" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="V22" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="W22" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="X22" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z22" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA22" s="14">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>233034</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E23" s="10">
         <v>25245</v>
@@ -3671,24 +4263,51 @@
       <c r="O23" s="9"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="S23" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R23" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="S23" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="T23" s="14">
+        <v>3</v>
+      </c>
+      <c r="U23" s="14">
+        <v>3</v>
+      </c>
+      <c r="V23" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="W23" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X23" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z23" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="AA23" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>268013</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E24" s="16">
         <v>29244</v>
@@ -3725,24 +4344,51 @@
       <c r="O24" s="15"/>
       <c r="P24" s="15"/>
       <c r="Q24" s="15" t="s">
-        <v>291</v>
-      </c>
-      <c r="S24" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="S24" s="14">
+        <v>3</v>
+      </c>
+      <c r="T24" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="U24" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="V24" s="14">
+        <v>3</v>
+      </c>
+      <c r="W24" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X24" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y24" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="Z24" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA24" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>249010</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E25" s="10">
         <v>27467</v>
@@ -3779,24 +4425,51 @@
       <c r="O25" s="9"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="S25" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R25" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="S25" s="14">
+        <v>3</v>
+      </c>
+      <c r="T25" s="14">
+        <v>3</v>
+      </c>
+      <c r="U25" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="V25" s="14">
+        <v>3</v>
+      </c>
+      <c r="W25" s="14">
+        <v>3</v>
+      </c>
+      <c r="X25" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y25" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="Z25" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA25" s="14">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>268012</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E26" s="16">
         <v>31704</v>
@@ -3833,24 +4506,51 @@
       <c r="O26" s="15"/>
       <c r="P26" s="15"/>
       <c r="Q26" s="15" t="s">
-        <v>291</v>
-      </c>
-      <c r="S26" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="S26" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="T26" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="U26" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="V26" s="14">
+        <v>3</v>
+      </c>
+      <c r="W26" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X26" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y26" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA26" s="14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>238030</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E27" s="10">
         <v>27404</v>
@@ -3887,24 +4587,51 @@
       <c r="O27" s="9"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="S27" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R27" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="S27" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="T27" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="U27" s="14">
+        <v>3</v>
+      </c>
+      <c r="V27" s="14">
+        <v>3</v>
+      </c>
+      <c r="W27" s="14">
+        <v>3</v>
+      </c>
+      <c r="X27" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z27" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA27" s="14">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="39">
         <v>256014</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E28" s="41">
         <v>32349</v>
@@ -3940,27 +4667,54 @@
       <c r="N28" s="40"/>
       <c r="O28" s="40"/>
       <c r="P28" s="40" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Q28" s="40" t="s">
-        <v>291</v>
-      </c>
-      <c r="S28" s="39" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R28" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="S28" s="14">
+        <v>3</v>
+      </c>
+      <c r="T28" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="U28" s="14">
+        <v>3</v>
+      </c>
+      <c r="V28" s="14">
+        <v>3</v>
+      </c>
+      <c r="W28" s="14">
+        <v>3</v>
+      </c>
+      <c r="X28" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y28" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Z28" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA28" s="14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="32">
         <v>443003</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E29" s="34">
         <v>28572</v>
@@ -3996,27 +4750,54 @@
       <c r="N29" s="33"/>
       <c r="O29" s="33"/>
       <c r="P29" s="33" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Q29" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="S29" s="32" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R29" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="S29" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T29" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U29" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V29" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W29" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X29" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y29" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z29" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA29" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="39">
         <v>254057</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D30" s="40" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E30" s="41">
         <v>32420</v>
@@ -4052,27 +4833,54 @@
       <c r="N30" s="40"/>
       <c r="O30" s="40"/>
       <c r="P30" s="40" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q30" s="40" t="s">
-        <v>291</v>
-      </c>
-      <c r="S30" s="39" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R30" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="S30" s="14">
+        <v>3</v>
+      </c>
+      <c r="T30" s="14">
+        <v>3</v>
+      </c>
+      <c r="U30" s="14">
+        <v>3</v>
+      </c>
+      <c r="V30" s="14">
+        <v>3</v>
+      </c>
+      <c r="W30" s="14">
+        <v>3</v>
+      </c>
+      <c r="X30" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y30" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z30" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="AA30" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="32">
         <v>237011</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E31" s="34">
         <v>25410</v>
@@ -4108,27 +4916,54 @@
       <c r="N31" s="33"/>
       <c r="O31" s="33"/>
       <c r="P31" s="33" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Q31" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="S31" s="32" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R31" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="S31" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T31" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U31" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V31" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W31" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X31" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y31" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z31" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA31" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="39">
         <v>267096</v>
       </c>
       <c r="B32" s="40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D32" s="40" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E32" s="41">
         <v>32140</v>
@@ -4164,27 +4999,54 @@
       <c r="N32" s="40"/>
       <c r="O32" s="40"/>
       <c r="P32" s="40" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Q32" s="40" t="s">
-        <v>291</v>
-      </c>
-      <c r="S32" s="39" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R32" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="S32" s="14">
+        <v>3</v>
+      </c>
+      <c r="T32" s="14">
+        <v>3</v>
+      </c>
+      <c r="U32" s="14">
+        <v>3</v>
+      </c>
+      <c r="V32" s="14">
+        <v>3</v>
+      </c>
+      <c r="W32" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X32" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="32">
         <v>249048</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E33" s="34">
         <v>29299</v>
@@ -4220,27 +5082,54 @@
       <c r="N33" s="33"/>
       <c r="O33" s="33"/>
       <c r="P33" s="33" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Q33" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="S33" s="32" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R33" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="S33" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T33" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U33" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V33" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W33" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X33" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y33" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z33" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA33" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="39">
         <v>269022</v>
       </c>
       <c r="B34" s="40" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D34" s="40" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E34" s="41">
         <v>30852</v>
@@ -4276,27 +5165,54 @@
       <c r="N34" s="40"/>
       <c r="O34" s="40"/>
       <c r="P34" s="40" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Q34" s="40" t="s">
-        <v>291</v>
-      </c>
-      <c r="S34" s="39" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R34" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="S34" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T34" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U34" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V34" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W34" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X34" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y34" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z34" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA34" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>253014</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E35" s="10">
         <v>30611</v>
@@ -4333,24 +5249,51 @@
       <c r="O35" s="9"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="S35" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R35" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="S35" s="14">
+        <v>1</v>
+      </c>
+      <c r="T35" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="U35" s="14">
+        <v>2</v>
+      </c>
+      <c r="V35" s="14">
+        <v>3</v>
+      </c>
+      <c r="W35" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="X35" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="Z35" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA35" s="14">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>248031</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E36" s="16">
         <v>29617</v>
@@ -4387,24 +5330,51 @@
       <c r="O36" s="15"/>
       <c r="P36" s="15"/>
       <c r="Q36" s="15" t="s">
-        <v>291</v>
-      </c>
-      <c r="S36" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R36" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="S36" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="T36" s="14">
+        <v>3</v>
+      </c>
+      <c r="U36" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="V36" s="14">
+        <v>3</v>
+      </c>
+      <c r="W36" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X36" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y36" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z36" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="AA36" s="14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="32">
         <v>251007</v>
       </c>
       <c r="B37" s="33" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D37" s="33" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E37" s="34">
         <v>30522</v>
@@ -4440,27 +5410,54 @@
       <c r="N37" s="33"/>
       <c r="O37" s="33"/>
       <c r="P37" s="33" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="Q37" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="S37" s="32" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R37" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="S37" s="14">
+        <v>3</v>
+      </c>
+      <c r="T37" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="U37" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="V37" s="14">
+        <v>3</v>
+      </c>
+      <c r="W37" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X37" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y37" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z37" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="AA37" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="8">
         <v>242012</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E38" s="16">
         <v>28064</v>
@@ -4497,24 +5494,51 @@
       <c r="O38" s="15"/>
       <c r="P38" s="15"/>
       <c r="Q38" s="15" t="s">
-        <v>291</v>
-      </c>
-      <c r="S38" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R38" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="S38" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T38" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U38" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V38" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W38" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X38" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y38" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z38" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA38" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="32">
         <v>257039</v>
       </c>
       <c r="B39" s="33" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E39" s="34">
         <v>32578</v>
@@ -4550,27 +5574,54 @@
       <c r="N39" s="33"/>
       <c r="O39" s="33"/>
       <c r="P39" s="33" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Q39" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="S39" s="32" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+      <c r="R39" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="S39" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="T39" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="U39" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="V39" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="W39" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X39" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y39" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Z39" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="AA39" s="14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>244023</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E40" s="16">
         <v>27775</v>
@@ -4607,19 +5658,46 @@
       <c r="O40" s="15"/>
       <c r="P40" s="15"/>
       <c r="Q40" s="15"/>
-      <c r="S40" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R40" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="S40" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="T40" s="14">
+        <v>3</v>
+      </c>
+      <c r="U40" s="14">
+        <v>3</v>
+      </c>
+      <c r="V40" s="14">
+        <v>3</v>
+      </c>
+      <c r="W40" s="14">
+        <v>3</v>
+      </c>
+      <c r="X40" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y40" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z40" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA40" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="20">
         <v>241009</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D41" s="21" t="s">
         <v>90</v>
@@ -4656,28 +5734,55 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N41" s="21" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="O41" s="21" t="s">
         <v>62</v>
       </c>
       <c r="P41" s="21" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="Q41" s="21"/>
-      <c r="S41" s="20" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R41" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="S41" s="14">
+        <v>3</v>
+      </c>
+      <c r="T41" s="14">
+        <v>3</v>
+      </c>
+      <c r="U41" s="14">
+        <v>3</v>
+      </c>
+      <c r="V41" s="14">
+        <v>3</v>
+      </c>
+      <c r="W41" s="14">
+        <v>3</v>
+      </c>
+      <c r="X41" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA41" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="27">
         <v>368001</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C42" s="28" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D42" s="28" t="s">
         <v>90</v>
@@ -4714,26 +5819,53 @@
         <v>High Impact + High Risk</v>
       </c>
       <c r="N42" s="28" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O42" s="28"/>
       <c r="P42" s="28" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Q42" s="28"/>
-      <c r="S42" s="27" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R42" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="S42" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T42" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U42" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V42" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W42" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X42" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y42" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z42" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA42" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="20">
         <v>148005</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D43" s="21" t="s">
         <v>90</v>
@@ -4770,18 +5902,45 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N43" s="21" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O43" s="21"/>
       <c r="P43" s="21" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="Q43" s="21"/>
-      <c r="S43" s="20" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R43" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="S43" s="14">
+        <v>4</v>
+      </c>
+      <c r="T43" s="14">
+        <v>4</v>
+      </c>
+      <c r="U43" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="V43" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="W43" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X43" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y43" s="14">
+        <v>4</v>
+      </c>
+      <c r="Z43" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="AA43" s="14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="7">
         <v>267071</v>
       </c>
@@ -4826,18 +5985,45 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N44" s="9" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O44" s="9"/>
       <c r="P44" s="9" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="Q44" s="9"/>
-      <c r="S44" s="7" t="s">
+      <c r="R44" s="7" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="45" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S44" s="14">
+        <v>3</v>
+      </c>
+      <c r="T44" s="14">
+        <v>3</v>
+      </c>
+      <c r="U44" s="14">
+        <v>3</v>
+      </c>
+      <c r="V44" s="14">
+        <v>3</v>
+      </c>
+      <c r="W44" s="14">
+        <v>3</v>
+      </c>
+      <c r="X44" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y44" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z44" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA44" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="8">
         <v>268051</v>
       </c>
@@ -4882,18 +6068,45 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N45" s="15" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O45" s="15"/>
       <c r="P45" s="15" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="Q45" s="15"/>
-      <c r="S45" s="8" t="s">
+      <c r="R45" s="8" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="46" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S45" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T45" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U45" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V45" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W45" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X45" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y45" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z45" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA45" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="7">
         <v>269032</v>
       </c>
@@ -4938,18 +6151,45 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N46" s="9" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O46" s="9"/>
       <c r="P46" s="9" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="Q46" s="9"/>
-      <c r="S46" s="7" t="s">
+      <c r="R46" s="7" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="47" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S46" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T46" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U46" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V46" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W46" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X46" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y46" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z46" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA46" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8">
         <v>250051</v>
       </c>
@@ -4994,34 +6234,61 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N47" s="15" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O47" s="15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P47" s="15" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="Q47" s="15"/>
-      <c r="S47" s="8" t="s">
+      <c r="R47" s="8" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S47" s="14">
+        <v>3</v>
+      </c>
+      <c r="T47" s="14">
+        <v>3</v>
+      </c>
+      <c r="U47" s="14">
+        <v>3</v>
+      </c>
+      <c r="V47" s="14">
+        <v>3</v>
+      </c>
+      <c r="W47" s="14">
+        <v>3</v>
+      </c>
+      <c r="X47" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y47" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z47" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA47" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="7">
         <v>146037</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F48" s="11">
         <v>60</v>
@@ -5050,32 +6317,59 @@
         <v>High Impact + High Risk</v>
       </c>
       <c r="N48" s="9" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O48" s="9"/>
       <c r="P48" s="9" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Q48" s="9"/>
-      <c r="S48" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R48" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="S48" s="14">
+        <v>3</v>
+      </c>
+      <c r="T48" s="14">
+        <v>3</v>
+      </c>
+      <c r="U48" s="14">
+        <v>3</v>
+      </c>
+      <c r="V48" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="W48" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X48" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y48" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z48" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA48" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="8">
         <v>139013</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D49" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F49" s="17">
         <v>58</v>
@@ -5104,34 +6398,61 @@
         <v>High Impact + High Risk</v>
       </c>
       <c r="N49" s="15" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O49" s="15" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P49" s="15" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="Q49" s="15"/>
-      <c r="S49" s="8" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R49" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="S49" s="14">
+        <v>3</v>
+      </c>
+      <c r="T49" s="14">
+        <v>3</v>
+      </c>
+      <c r="U49" s="14">
+        <v>3</v>
+      </c>
+      <c r="V49" s="14">
+        <v>3</v>
+      </c>
+      <c r="W49" s="14">
+        <v>3</v>
+      </c>
+      <c r="X49" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y49" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z49" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA49" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
         <v>145015</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F50" s="11">
         <v>50</v>
@@ -5160,32 +6481,59 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N50" s="9" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O50" s="9"/>
       <c r="P50" s="9" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Q50" s="9"/>
-      <c r="S50" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R50" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="S50" s="14">
+        <v>3</v>
+      </c>
+      <c r="T50" s="14">
+        <v>3</v>
+      </c>
+      <c r="U50" s="14">
+        <v>3</v>
+      </c>
+      <c r="V50" s="14">
+        <v>3</v>
+      </c>
+      <c r="W50" s="14">
+        <v>3</v>
+      </c>
+      <c r="X50" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y50" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z50" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA50" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>161005</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D51" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F51" s="17">
         <v>45</v>
@@ -5217,25 +6565,52 @@
       <c r="O51" s="15"/>
       <c r="P51" s="15"/>
       <c r="Q51" s="15"/>
-      <c r="S51" s="8" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R51" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="S51" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T51" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U51" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V51" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W51" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X51" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y51" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z51" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA51" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="7">
         <v>163003</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F52" s="11">
         <v>34</v>
@@ -5267,25 +6642,52 @@
       <c r="O52" s="9"/>
       <c r="P52" s="9"/>
       <c r="Q52" s="9"/>
-      <c r="S52" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R52" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="S52" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T52" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U52" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V52" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W52" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X52" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y52" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z52" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA52" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <v>166024</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D53" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F53" s="17">
         <v>27</v>
@@ -5317,25 +6719,52 @@
       <c r="O53" s="15"/>
       <c r="P53" s="15"/>
       <c r="Q53" s="15"/>
-      <c r="S53" s="8" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R53" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="S53" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T53" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U53" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V53" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W53" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X53" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y53" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z53" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA53" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>167001</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F54" s="11">
         <v>37</v>
@@ -5367,25 +6796,52 @@
       <c r="O54" s="9"/>
       <c r="P54" s="9"/>
       <c r="Q54" s="9"/>
-      <c r="S54" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R54" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="S54" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T54" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U54" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V54" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W54" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X54" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y54" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z54" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA54" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>167012</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D55" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F55" s="17">
         <v>31</v>
@@ -5417,25 +6873,52 @@
       <c r="O55" s="15"/>
       <c r="P55" s="15"/>
       <c r="Q55" s="15"/>
-      <c r="S55" s="8" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R55" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="S55" s="14">
+        <v>3</v>
+      </c>
+      <c r="T55" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="U55" s="14">
+        <v>3</v>
+      </c>
+      <c r="V55" s="14">
+        <v>3</v>
+      </c>
+      <c r="W55" s="14">
+        <v>3</v>
+      </c>
+      <c r="X55" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Y55" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="Z55" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA55" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="7">
         <v>260001</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F56" s="11">
         <v>35</v>
@@ -5464,32 +6947,59 @@
         <v>High Impact + High Risk</v>
       </c>
       <c r="N56" s="9" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O56" s="9"/>
       <c r="P56" s="9" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="Q56" s="9"/>
-      <c r="S56" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R56" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="S56" s="14">
+        <v>3</v>
+      </c>
+      <c r="T56" s="14">
+        <v>3</v>
+      </c>
+      <c r="U56" s="14">
+        <v>3</v>
+      </c>
+      <c r="V56" s="14">
+        <v>3</v>
+      </c>
+      <c r="W56" s="14">
+        <v>3</v>
+      </c>
+      <c r="X56" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y56" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z56" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA56" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
         <v>267001</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D57" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F57" s="17">
         <v>31</v>
@@ -5521,25 +7031,52 @@
       <c r="O57" s="15"/>
       <c r="P57" s="15"/>
       <c r="Q57" s="15"/>
-      <c r="S57" s="8" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R57" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="S57" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T57" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U57" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V57" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W57" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X57" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y57" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z57" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA57" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="7">
         <v>160001</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F58" s="11">
         <v>46</v>
@@ -5568,32 +7105,59 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N58" s="9" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O58" s="9"/>
       <c r="P58" s="9" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="Q58" s="9"/>
-      <c r="S58" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R58" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="S58" s="14">
+        <v>3</v>
+      </c>
+      <c r="T58" s="14">
+        <v>3</v>
+      </c>
+      <c r="U58" s="14">
+        <v>3</v>
+      </c>
+      <c r="V58" s="14">
+        <v>3</v>
+      </c>
+      <c r="W58" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X58" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="14">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA58" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
         <v>167020</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F59" s="11">
         <v>51</v>
@@ -5625,25 +7189,52 @@
       <c r="O59" s="9"/>
       <c r="P59" s="9"/>
       <c r="Q59" s="9"/>
-      <c r="S59" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R59" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="S59" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T59" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U59" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V59" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W59" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X59" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y59" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z59" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA59" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="8">
         <v>167029</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D60" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F60" s="17">
         <v>35</v>
@@ -5672,32 +7263,59 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N60" s="15" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O60" s="15"/>
       <c r="P60" s="15" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Q60" s="15"/>
-      <c r="S60" s="8" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R60" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="S60" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="T60" s="14">
+        <v>3</v>
+      </c>
+      <c r="U60" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="V60" s="14">
+        <v>3</v>
+      </c>
+      <c r="W60" s="14">
+        <v>3</v>
+      </c>
+      <c r="X60" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y60" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="Z60" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA60" s="14">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>167032</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F61" s="11">
         <v>29</v>
@@ -5729,25 +7347,52 @@
       <c r="O61" s="9"/>
       <c r="P61" s="9"/>
       <c r="Q61" s="9"/>
-      <c r="S61" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R61" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="S61" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T61" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U61" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V61" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W61" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X61" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y61" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z61" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA61" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="8">
         <v>168024</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D62" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F62" s="17">
         <v>46</v>
@@ -5776,32 +7421,59 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N62" s="15" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O62" s="15"/>
       <c r="P62" s="15" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="Q62" s="15"/>
-      <c r="S62" s="8" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R62" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="S62" s="14">
+        <v>3</v>
+      </c>
+      <c r="T62" s="14">
+        <v>3</v>
+      </c>
+      <c r="U62" s="14">
+        <v>3</v>
+      </c>
+      <c r="V62" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="W62" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="X62" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="Z62" s="14">
+        <v>3</v>
+      </c>
+      <c r="AA62" s="14">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="8">
         <v>337004</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D63" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F63" s="17">
         <v>55</v>
@@ -5833,25 +7505,52 @@
       <c r="O63" s="15"/>
       <c r="P63" s="15"/>
       <c r="Q63" s="15"/>
-      <c r="S63" s="8" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R63" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="S63" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T63" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U63" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V63" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W63" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X63" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y63" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z63" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA63" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="8">
         <v>268044</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D64" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F64" s="17">
         <v>28</v>
@@ -5883,25 +7582,52 @@
       <c r="O64" s="15"/>
       <c r="P64" s="15"/>
       <c r="Q64" s="15"/>
-      <c r="S64" s="8" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R64" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="S64" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T64" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U64" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V64" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W64" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X64" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y64" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z64" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA64" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="7">
         <v>368004</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D65" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F65" s="11">
         <v>59</v>
@@ -5930,32 +7656,59 @@
         <v>High Impact + High Risk</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O65" s="9"/>
       <c r="P65" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q65" s="9"/>
-      <c r="S65" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R65" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="S65" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T65" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U65" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V65" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W65" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X65" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y65" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z65" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA65" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D66" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F66" s="11">
         <v>55</v>
@@ -5984,32 +7737,59 @@
         <v>High Impact + High Risk</v>
       </c>
       <c r="N66" s="9" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O66" s="9"/>
       <c r="P66" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q66" s="9"/>
-      <c r="S66" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R66" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="S66" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="T66" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="U66" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="V66" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="W66" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="X66" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y66" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z66" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA66" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="67" spans="1:27" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="20">
         <v>168016</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D67" s="21" t="s">
         <v>90</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F67" s="23">
         <v>35</v>
@@ -6038,37 +7818,61 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N67" s="21" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O67" s="21" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="P67" s="21" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="Q67" s="21"/>
-      <c r="R67" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="S67" s="20" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R67" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="S67" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="T67" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="U67" s="14">
+        <v>4</v>
+      </c>
+      <c r="V67" s="14">
+        <v>4</v>
+      </c>
+      <c r="W67" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X67" s="14">
+        <v>4</v>
+      </c>
+      <c r="Y67" s="14">
+        <v>4</v>
+      </c>
+      <c r="Z67" s="14">
+        <v>4</v>
+      </c>
+      <c r="AA67" s="14">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="8">
         <v>258026</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D68" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F68" s="17">
         <v>42</v>
@@ -6103,25 +7907,42 @@
         <v>62</v>
       </c>
       <c r="P68" s="15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="Q68" s="15"/>
-      <c r="R68" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="S68" s="8" t="s">
+      <c r="R68" s="8" t="s">
         <v>93</v>
       </c>
+      <c r="S68" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="T68" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="U68" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="V68" s="14">
+        <v>4.5</v>
+      </c>
+      <c r="W68" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="X68" s="14">
+        <v>4</v>
+      </c>
+      <c r="Y68" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="Z68" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="AA68" s="14">
+        <v>3.5</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S68" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="12">
-      <filters>
-        <filter val="High Impact + High Risk"/>
-        <filter val="High Impact + Low Risk"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:R68" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -2473,7 +2473,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA68"/>
+  <dimension ref="A1:R68"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2494,11 +2494,9 @@
     <col min="16" max="16" width="26" customWidth="1"/>
     <col min="17" max="17" width="28" customWidth="1"/>
     <col min="18" max="18" width="8.6328125" style="4"/>
-    <col min="19" max="26" width="13.26953125" customWidth="1"/>
-    <col min="27" max="27" width="21.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
@@ -2520,7 +2518,7 @@
       <c r="Q1" s="44"/>
       <c r="R1" s="5"/>
     </row>
-    <row r="2" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2575,35 +2573,8 @@
       <c r="R2" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="S2" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="T2" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="U2" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="V2" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="X2" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="Y2" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="AA2" s="6" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>168028</v>
       </c>
@@ -2654,35 +2625,8 @@
       <c r="R3" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="S3" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="T3" s="14">
-        <v>3</v>
-      </c>
-      <c r="U3" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="V3" s="14">
-        <v>3</v>
-      </c>
-      <c r="W3" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X3" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y3" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z3" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA3" s="14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>150026</v>
       </c>
@@ -2733,35 +2677,8 @@
       <c r="R4" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="S4" s="14">
-        <v>4</v>
-      </c>
-      <c r="T4" s="14">
-        <v>3</v>
-      </c>
-      <c r="U4" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="V4" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="W4" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X4" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y4" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Z4" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA4" s="14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>147022</v>
       </c>
@@ -2812,35 +2729,8 @@
       <c r="R5" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="S5" s="14">
-        <v>4</v>
-      </c>
-      <c r="T5" s="14">
-        <v>3</v>
-      </c>
-      <c r="U5" s="14">
-        <v>3</v>
-      </c>
-      <c r="V5" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="W5" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X5" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y5" s="14">
-        <v>4</v>
-      </c>
-      <c r="Z5" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA5" s="14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>136049</v>
       </c>
@@ -2891,35 +2781,8 @@
       <c r="R6" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="S6" s="14">
-        <v>4.5</v>
-      </c>
-      <c r="T6" s="14">
-        <v>3</v>
-      </c>
-      <c r="U6" s="14">
-        <v>4</v>
-      </c>
-      <c r="V6" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="W6" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X6" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y6" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Z6" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA6" s="14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>161027</v>
       </c>
@@ -2970,35 +2833,8 @@
       <c r="R7" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="S7" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="T7" s="14">
-        <v>3</v>
-      </c>
-      <c r="U7" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="V7" s="14">
-        <v>3</v>
-      </c>
-      <c r="W7" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X7" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y7" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Z7" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="AA7" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>656001</v>
       </c>
@@ -3049,35 +2885,8 @@
       <c r="R8" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="S8" s="14">
-        <v>4.5</v>
-      </c>
-      <c r="T8" s="14">
-        <v>3</v>
-      </c>
-      <c r="U8" s="14">
-        <v>4</v>
-      </c>
-      <c r="V8" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="W8" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X8" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y8" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA8" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>656008</v>
       </c>
@@ -3128,35 +2937,8 @@
       <c r="R9" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="S9" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T9" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U9" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V9" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W9" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X9" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y9" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z9" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA9" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>168017</v>
       </c>
@@ -3207,35 +2989,8 @@
       <c r="R10" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="S10" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="T10" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="U10" s="14">
-        <v>3</v>
-      </c>
-      <c r="V10" s="14">
-        <v>3</v>
-      </c>
-      <c r="W10" s="14">
-        <v>3</v>
-      </c>
-      <c r="X10" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y10" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z10" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="AA10" s="14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="27">
         <v>266049</v>
       </c>
@@ -3292,35 +3047,8 @@
       <c r="R11" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="S11" s="14">
-        <v>3</v>
-      </c>
-      <c r="T11" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="U11" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="V11" s="14">
-        <v>3</v>
-      </c>
-      <c r="W11" s="14">
-        <v>3</v>
-      </c>
-      <c r="X11" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y11" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z11" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA11" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>166027</v>
       </c>
@@ -3371,35 +3099,8 @@
       <c r="R12" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="S12" s="14">
-        <v>3</v>
-      </c>
-      <c r="T12" s="14">
-        <v>3</v>
-      </c>
-      <c r="U12" s="14">
-        <v>3</v>
-      </c>
-      <c r="V12" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="W12" s="14">
-        <v>3</v>
-      </c>
-      <c r="X12" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y12" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z12" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA12" s="14">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="27">
         <v>466004</v>
       </c>
@@ -3452,35 +3153,8 @@
       <c r="R13" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="S13" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T13" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U13" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V13" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W13" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X13" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y13" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z13" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA13" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="20">
         <v>159029</v>
       </c>
@@ -3533,35 +3207,8 @@
       <c r="R14" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="S14" s="14">
-        <v>4</v>
-      </c>
-      <c r="T14" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="U14" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="V14" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="W14" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X14" s="14">
-        <v>4</v>
-      </c>
-      <c r="Y14" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Z14" s="14">
-        <v>4</v>
-      </c>
-      <c r="AA14" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="32">
         <v>239006</v>
       </c>
@@ -3616,35 +3263,8 @@
       <c r="R15" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="S15" s="14">
-        <v>4</v>
-      </c>
-      <c r="T15" s="14">
-        <v>4</v>
-      </c>
-      <c r="U15" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="V15" s="14">
-        <v>4</v>
-      </c>
-      <c r="W15" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X15" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y15" s="14">
-        <v>4</v>
-      </c>
-      <c r="Z15" s="14">
-        <v>4</v>
-      </c>
-      <c r="AA15" s="14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="39">
         <v>246004</v>
       </c>
@@ -3699,35 +3319,8 @@
       <c r="R16" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="S16" s="14">
-        <v>3</v>
-      </c>
-      <c r="T16" s="14">
-        <v>3</v>
-      </c>
-      <c r="U16" s="14">
-        <v>3</v>
-      </c>
-      <c r="V16" s="14">
-        <v>3</v>
-      </c>
-      <c r="W16" s="14">
-        <v>3</v>
-      </c>
-      <c r="X16" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y16" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z16" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA16" s="14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>242032</v>
       </c>
@@ -3780,35 +3373,8 @@
       <c r="R17" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="S17" s="14">
-        <v>4</v>
-      </c>
-      <c r="T17" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="U17" s="14">
-        <v>3</v>
-      </c>
-      <c r="V17" s="14">
-        <v>4</v>
-      </c>
-      <c r="W17" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X17" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y17" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z17" s="14">
-        <v>4</v>
-      </c>
-      <c r="AA17" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>149024</v>
       </c>
@@ -3861,35 +3427,8 @@
       <c r="R18" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="S18" s="14">
-        <v>4</v>
-      </c>
-      <c r="T18" s="14">
-        <v>3</v>
-      </c>
-      <c r="U18" s="14">
-        <v>3</v>
-      </c>
-      <c r="V18" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="W18" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X18" s="14">
-        <v>4</v>
-      </c>
-      <c r="Y18" s="14">
-        <v>4</v>
-      </c>
-      <c r="Z18" s="14">
-        <v>4</v>
-      </c>
-      <c r="AA18" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>232027</v>
       </c>
@@ -3942,35 +3481,8 @@
       <c r="R19" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="S19" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T19" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U19" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V19" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W19" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X19" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y19" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z19" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA19" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>256029</v>
       </c>
@@ -4023,35 +3535,8 @@
       <c r="R20" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="S20" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="T20" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="U20" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="V20" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="W20" s="14">
-        <v>3</v>
-      </c>
-      <c r="X20" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y20" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z20" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="AA20" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>236012</v>
       </c>
@@ -4104,35 +3589,8 @@
       <c r="R21" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="S21" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="T21" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="U21" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="V21" s="14">
-        <v>3</v>
-      </c>
-      <c r="W21" s="14">
-        <v>3</v>
-      </c>
-      <c r="X21" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="Z21" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA21" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="39">
         <v>250042</v>
       </c>
@@ -4187,35 +3645,8 @@
       <c r="R22" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="S22" s="14">
-        <v>3</v>
-      </c>
-      <c r="T22" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="U22" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="V22" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="W22" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="X22" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y22" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z22" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA22" s="14">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>233034</v>
       </c>
@@ -4268,35 +3699,8 @@
       <c r="R23" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="S23" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="T23" s="14">
-        <v>3</v>
-      </c>
-      <c r="U23" s="14">
-        <v>3</v>
-      </c>
-      <c r="V23" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="W23" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X23" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y23" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z23" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="AA23" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>268013</v>
       </c>
@@ -4349,35 +3753,8 @@
       <c r="R24" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="S24" s="14">
-        <v>3</v>
-      </c>
-      <c r="T24" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="U24" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="V24" s="14">
-        <v>3</v>
-      </c>
-      <c r="W24" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X24" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y24" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="Z24" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA24" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>249010</v>
       </c>
@@ -4430,35 +3807,8 @@
       <c r="R25" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="S25" s="14">
-        <v>3</v>
-      </c>
-      <c r="T25" s="14">
-        <v>3</v>
-      </c>
-      <c r="U25" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="V25" s="14">
-        <v>3</v>
-      </c>
-      <c r="W25" s="14">
-        <v>3</v>
-      </c>
-      <c r="X25" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y25" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="Z25" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA25" s="14">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>268012</v>
       </c>
@@ -4511,35 +3861,8 @@
       <c r="R26" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="S26" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="T26" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="U26" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="V26" s="14">
-        <v>3</v>
-      </c>
-      <c r="W26" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X26" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y26" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z26" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA26" s="14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>238030</v>
       </c>
@@ -4592,35 +3915,8 @@
       <c r="R27" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="S27" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="T27" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="U27" s="14">
-        <v>3</v>
-      </c>
-      <c r="V27" s="14">
-        <v>3</v>
-      </c>
-      <c r="W27" s="14">
-        <v>3</v>
-      </c>
-      <c r="X27" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y27" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z27" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA27" s="14">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="39">
         <v>256014</v>
       </c>
@@ -4675,35 +3971,8 @@
       <c r="R28" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="S28" s="14">
-        <v>3</v>
-      </c>
-      <c r="T28" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="U28" s="14">
-        <v>3</v>
-      </c>
-      <c r="V28" s="14">
-        <v>3</v>
-      </c>
-      <c r="W28" s="14">
-        <v>3</v>
-      </c>
-      <c r="X28" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y28" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Z28" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA28" s="14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="32">
         <v>443003</v>
       </c>
@@ -4758,35 +4027,8 @@
       <c r="R29" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="S29" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T29" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U29" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V29" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W29" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X29" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y29" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z29" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA29" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="39">
         <v>254057</v>
       </c>
@@ -4841,35 +4083,8 @@
       <c r="R30" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="S30" s="14">
-        <v>3</v>
-      </c>
-      <c r="T30" s="14">
-        <v>3</v>
-      </c>
-      <c r="U30" s="14">
-        <v>3</v>
-      </c>
-      <c r="V30" s="14">
-        <v>3</v>
-      </c>
-      <c r="W30" s="14">
-        <v>3</v>
-      </c>
-      <c r="X30" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y30" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z30" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="AA30" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="32">
         <v>237011</v>
       </c>
@@ -4924,35 +4139,8 @@
       <c r="R31" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="S31" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T31" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U31" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V31" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W31" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X31" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y31" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z31" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA31" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="39">
         <v>267096</v>
       </c>
@@ -5007,35 +4195,8 @@
       <c r="R32" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="S32" s="14">
-        <v>3</v>
-      </c>
-      <c r="T32" s="14">
-        <v>3</v>
-      </c>
-      <c r="U32" s="14">
-        <v>3</v>
-      </c>
-      <c r="V32" s="14">
-        <v>3</v>
-      </c>
-      <c r="W32" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X32" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y32" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z32" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA32" s="14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="32">
         <v>249048</v>
       </c>
@@ -5090,35 +4251,8 @@
       <c r="R33" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="S33" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T33" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U33" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V33" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W33" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X33" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y33" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z33" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA33" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="39">
         <v>269022</v>
       </c>
@@ -5173,35 +4307,8 @@
       <c r="R34" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="S34" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T34" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U34" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V34" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W34" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X34" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y34" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z34" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA34" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>253014</v>
       </c>
@@ -5254,35 +4361,8 @@
       <c r="R35" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="S35" s="14">
-        <v>1</v>
-      </c>
-      <c r="T35" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="U35" s="14">
-        <v>2</v>
-      </c>
-      <c r="V35" s="14">
-        <v>3</v>
-      </c>
-      <c r="W35" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="X35" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y35" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="Z35" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA35" s="14">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>248031</v>
       </c>
@@ -5335,35 +4415,8 @@
       <c r="R36" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="S36" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="T36" s="14">
-        <v>3</v>
-      </c>
-      <c r="U36" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="V36" s="14">
-        <v>3</v>
-      </c>
-      <c r="W36" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X36" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y36" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z36" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="AA36" s="14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="32">
         <v>251007</v>
       </c>
@@ -5418,35 +4471,8 @@
       <c r="R37" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="S37" s="14">
-        <v>3</v>
-      </c>
-      <c r="T37" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="U37" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="V37" s="14">
-        <v>3</v>
-      </c>
-      <c r="W37" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X37" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y37" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z37" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="AA37" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="8">
         <v>242012</v>
       </c>
@@ -5499,35 +4525,8 @@
       <c r="R38" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="S38" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T38" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U38" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V38" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W38" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X38" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y38" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z38" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA38" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="32">
         <v>257039</v>
       </c>
@@ -5582,35 +4581,8 @@
       <c r="R39" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="S39" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="T39" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="U39" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="V39" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="W39" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X39" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y39" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Z39" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="AA39" s="14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>244023</v>
       </c>
@@ -5661,35 +4633,8 @@
       <c r="R40" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="S40" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="T40" s="14">
-        <v>3</v>
-      </c>
-      <c r="U40" s="14">
-        <v>3</v>
-      </c>
-      <c r="V40" s="14">
-        <v>3</v>
-      </c>
-      <c r="W40" s="14">
-        <v>3</v>
-      </c>
-      <c r="X40" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y40" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z40" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA40" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="20">
         <v>241009</v>
       </c>
@@ -5746,35 +4691,8 @@
       <c r="R41" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="S41" s="14">
-        <v>3</v>
-      </c>
-      <c r="T41" s="14">
-        <v>3</v>
-      </c>
-      <c r="U41" s="14">
-        <v>3</v>
-      </c>
-      <c r="V41" s="14">
-        <v>3</v>
-      </c>
-      <c r="W41" s="14">
-        <v>3</v>
-      </c>
-      <c r="X41" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y41" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z41" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA41" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="27">
         <v>368001</v>
       </c>
@@ -5829,35 +4747,8 @@
       <c r="R42" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="S42" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T42" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U42" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V42" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W42" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X42" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y42" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z42" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA42" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="43" spans="1:27" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="20">
         <v>148005</v>
       </c>
@@ -5912,35 +4803,8 @@
       <c r="R43" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="S43" s="14">
-        <v>4</v>
-      </c>
-      <c r="T43" s="14">
-        <v>4</v>
-      </c>
-      <c r="U43" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="V43" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="W43" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X43" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y43" s="14">
-        <v>4</v>
-      </c>
-      <c r="Z43" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="AA43" s="14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="7">
         <v>267071</v>
       </c>
@@ -5995,35 +4859,8 @@
       <c r="R44" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="S44" s="14">
-        <v>3</v>
-      </c>
-      <c r="T44" s="14">
-        <v>3</v>
-      </c>
-      <c r="U44" s="14">
-        <v>3</v>
-      </c>
-      <c r="V44" s="14">
-        <v>3</v>
-      </c>
-      <c r="W44" s="14">
-        <v>3</v>
-      </c>
-      <c r="X44" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y44" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z44" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA44" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="8">
         <v>268051</v>
       </c>
@@ -6078,35 +4915,8 @@
       <c r="R45" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="S45" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T45" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U45" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V45" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W45" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X45" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y45" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z45" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA45" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="46" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="7">
         <v>269032</v>
       </c>
@@ -6161,35 +4971,8 @@
       <c r="R46" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="S46" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T46" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U46" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V46" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W46" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X46" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y46" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z46" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA46" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="47" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8">
         <v>250051</v>
       </c>
@@ -6246,35 +5029,8 @@
       <c r="R47" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="S47" s="14">
-        <v>3</v>
-      </c>
-      <c r="T47" s="14">
-        <v>3</v>
-      </c>
-      <c r="U47" s="14">
-        <v>3</v>
-      </c>
-      <c r="V47" s="14">
-        <v>3</v>
-      </c>
-      <c r="W47" s="14">
-        <v>3</v>
-      </c>
-      <c r="X47" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y47" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z47" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA47" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="7">
         <v>146037</v>
       </c>
@@ -6327,35 +5083,8 @@
       <c r="R48" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="S48" s="14">
-        <v>3</v>
-      </c>
-      <c r="T48" s="14">
-        <v>3</v>
-      </c>
-      <c r="U48" s="14">
-        <v>3</v>
-      </c>
-      <c r="V48" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="W48" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X48" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y48" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z48" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA48" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="8">
         <v>139013</v>
       </c>
@@ -6410,35 +5139,8 @@
       <c r="R49" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="S49" s="14">
-        <v>3</v>
-      </c>
-      <c r="T49" s="14">
-        <v>3</v>
-      </c>
-      <c r="U49" s="14">
-        <v>3</v>
-      </c>
-      <c r="V49" s="14">
-        <v>3</v>
-      </c>
-      <c r="W49" s="14">
-        <v>3</v>
-      </c>
-      <c r="X49" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y49" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z49" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA49" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
         <v>145015</v>
       </c>
@@ -6491,35 +5193,8 @@
       <c r="R50" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="S50" s="14">
-        <v>3</v>
-      </c>
-      <c r="T50" s="14">
-        <v>3</v>
-      </c>
-      <c r="U50" s="14">
-        <v>3</v>
-      </c>
-      <c r="V50" s="14">
-        <v>3</v>
-      </c>
-      <c r="W50" s="14">
-        <v>3</v>
-      </c>
-      <c r="X50" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y50" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z50" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA50" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>161005</v>
       </c>
@@ -6568,35 +5243,8 @@
       <c r="R51" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="S51" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T51" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U51" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V51" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W51" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X51" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y51" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z51" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA51" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="52" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="7">
         <v>163003</v>
       </c>
@@ -6645,35 +5293,8 @@
       <c r="R52" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="S52" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T52" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U52" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V52" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W52" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X52" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y52" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z52" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA52" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="53" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <v>166024</v>
       </c>
@@ -6722,35 +5343,8 @@
       <c r="R53" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="S53" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T53" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U53" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V53" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W53" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X53" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y53" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z53" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA53" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="54" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>167001</v>
       </c>
@@ -6799,35 +5393,8 @@
       <c r="R54" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="S54" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T54" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U54" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V54" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W54" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X54" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y54" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z54" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA54" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="55" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>167012</v>
       </c>
@@ -6876,35 +5443,8 @@
       <c r="R55" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="S55" s="14">
-        <v>3</v>
-      </c>
-      <c r="T55" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="U55" s="14">
-        <v>3</v>
-      </c>
-      <c r="V55" s="14">
-        <v>3</v>
-      </c>
-      <c r="W55" s="14">
-        <v>3</v>
-      </c>
-      <c r="X55" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Y55" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="Z55" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA55" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="7">
         <v>260001</v>
       </c>
@@ -6957,35 +5497,8 @@
       <c r="R56" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="S56" s="14">
-        <v>3</v>
-      </c>
-      <c r="T56" s="14">
-        <v>3</v>
-      </c>
-      <c r="U56" s="14">
-        <v>3</v>
-      </c>
-      <c r="V56" s="14">
-        <v>3</v>
-      </c>
-      <c r="W56" s="14">
-        <v>3</v>
-      </c>
-      <c r="X56" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y56" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z56" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA56" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="57" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
         <v>267001</v>
       </c>
@@ -7034,35 +5547,8 @@
       <c r="R57" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="S57" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T57" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U57" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V57" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W57" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X57" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y57" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z57" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA57" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="58" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="7">
         <v>160001</v>
       </c>
@@ -7115,35 +5601,8 @@
       <c r="R58" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="S58" s="14">
-        <v>3</v>
-      </c>
-      <c r="T58" s="14">
-        <v>3</v>
-      </c>
-      <c r="U58" s="14">
-        <v>3</v>
-      </c>
-      <c r="V58" s="14">
-        <v>3</v>
-      </c>
-      <c r="W58" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X58" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y58" s="14">
-        <v>3</v>
-      </c>
-      <c r="Z58" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA58" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
         <v>167020</v>
       </c>
@@ -7192,35 +5651,8 @@
       <c r="R59" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="S59" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T59" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U59" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V59" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W59" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X59" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y59" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z59" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA59" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="60" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="8">
         <v>167029</v>
       </c>
@@ -7273,35 +5705,8 @@
       <c r="R60" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="S60" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="T60" s="14">
-        <v>3</v>
-      </c>
-      <c r="U60" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="V60" s="14">
-        <v>3</v>
-      </c>
-      <c r="W60" s="14">
-        <v>3</v>
-      </c>
-      <c r="X60" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y60" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="Z60" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA60" s="14">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>167032</v>
       </c>
@@ -7350,35 +5755,8 @@
       <c r="R61" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="S61" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T61" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U61" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V61" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W61" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X61" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y61" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z61" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA61" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="62" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="62" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="8">
         <v>168024</v>
       </c>
@@ -7431,35 +5809,8 @@
       <c r="R62" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="S62" s="14">
-        <v>3</v>
-      </c>
-      <c r="T62" s="14">
-        <v>3</v>
-      </c>
-      <c r="U62" s="14">
-        <v>3</v>
-      </c>
-      <c r="V62" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="W62" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="X62" s="14">
-        <v>3</v>
-      </c>
-      <c r="Y62" s="14">
-        <v>2.5</v>
-      </c>
-      <c r="Z62" s="14">
-        <v>3</v>
-      </c>
-      <c r="AA62" s="14">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="8">
         <v>337004</v>
       </c>
@@ -7508,35 +5859,8 @@
       <c r="R63" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="S63" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T63" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U63" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V63" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W63" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X63" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y63" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z63" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA63" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="64" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="8">
         <v>268044</v>
       </c>
@@ -7585,35 +5909,8 @@
       <c r="R64" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="S64" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T64" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U64" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V64" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W64" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X64" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y64" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z64" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA64" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="65" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="65" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="7">
         <v>368004</v>
       </c>
@@ -7666,35 +5963,8 @@
       <c r="R65" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="S65" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T65" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U65" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V65" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W65" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X65" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y65" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z65" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA65" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="66" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>238</v>
       </c>
@@ -7747,35 +6017,8 @@
       <c r="R66" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="S66" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T66" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="U66" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="V66" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="W66" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="X66" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y66" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z66" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA66" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="67" spans="1:27" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="67" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="20">
         <v>168016</v>
       </c>
@@ -7830,35 +6073,8 @@
       <c r="R67" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="S67" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="T67" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="U67" s="14">
-        <v>4</v>
-      </c>
-      <c r="V67" s="14">
-        <v>4</v>
-      </c>
-      <c r="W67" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X67" s="14">
-        <v>4</v>
-      </c>
-      <c r="Y67" s="14">
-        <v>4</v>
-      </c>
-      <c r="Z67" s="14">
-        <v>4</v>
-      </c>
-      <c r="AA67" s="14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:27" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="68" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="8">
         <v>258026</v>
       </c>
@@ -7912,33 +6128,6 @@
       <c r="Q68" s="15"/>
       <c r="R68" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="S68" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="T68" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="U68" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="V68" s="14">
-        <v>4.5</v>
-      </c>
-      <c r="W68" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="X68" s="14">
-        <v>4</v>
-      </c>
-      <c r="Y68" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="Z68" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="AA68" s="14">
-        <v>3.5</v>
       </c>
     </row>
   </sheetData>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="160" documentId="8_{403FDADD-8B2B-43ED-91C4-EFCFAA5913E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A6435A2-154B-4088-9882-52F253894541}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{89C05139-767C-4D44-95FE-72D2855E25B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4DE5FDA-ACA3-4036-931A-3B6E609C1F95}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="คำอธิบาย" sheetId="2" r:id="rId1"/>
     <sheet name="กรอกข้อมูล" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$R$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$R$69</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="293">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -898,9 +898,6 @@
     <t>พุฒิพงศ์ สีธิสุข</t>
   </si>
   <si>
-    <t xml:space="preserve">รอพี่วุฒิแจ้ง </t>
-  </si>
-  <si>
     <t>149024 A_Acting Procurement Manager.docx</t>
   </si>
   <si>
@@ -910,34 +907,17 @@
     <t>368004_Contract-Procurement.docx</t>
   </si>
   <si>
-    <t>Leadership</t>
-  </si>
-  <si>
-    <t>Change Implementation</t>
-  </si>
-  <si>
-    <t>Initiative &amp; Innovation</t>
-  </si>
-  <si>
-    <t>Quality Orientation</t>
-  </si>
-  <si>
-    <t>Result &amp; Cost Driven</t>
-  </si>
-  <si>
-    <t>Teamwork</t>
-  </si>
-  <si>
-    <t>Communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Orientation </t>
-  </si>
-  <si>
-    <t>Problem Solving &amp; Decision Making</t>
-  </si>
-  <si>
-    <t>ไม่มีผลประเมิน</t>
+    <t>วัชระ สะติรัน</t>
+  </si>
+  <si>
+    <t>Department Manager - Batch and Furnace</t>
+  </si>
+  <si>
+    <t>วงษ์ศักดิ์ ศรีสวัสดิ์ หรือ
+ภานุวัฒน์ ธนสานสกุลวงศ์</t>
+  </si>
+  <si>
+    <t>ภราดร นิเทศพัตรพงศ์</t>
   </si>
 </sst>
 </file>
@@ -1265,7 +1245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1389,6 +1369,9 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1524,10 +1507,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1719,678 +1698,678 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="60" t="s">
+      <c r="C8" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="49" t="s">
+      <c r="C9" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="53" t="s">
+      <c r="B23" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="54" t="s">
+      <c r="B25" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="54"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="54"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="55"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="57" t="s">
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="57"/>
+      <c r="G26" s="58"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="56" t="s">
+      <c r="B27" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="57" t="s">
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="57"/>
+      <c r="G27" s="58"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="56" t="s">
+      <c r="B28" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="57" t="s">
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="57"/>
+      <c r="G28" s="58"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="56" t="s">
+      <c r="B29" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="56"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="57" t="s">
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="57"/>
+      <c r="G29" s="58"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="56" t="s">
+      <c r="B30" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="57" t="s">
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="57"/>
+      <c r="G30" s="58"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="53" t="s">
+      <c r="B32" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="53"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="49" t="s">
+      <c r="C33" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="49"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="49"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="49" t="s">
+      <c r="C34" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="49" t="s">
+      <c r="C35" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="49"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="49"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="53" t="s">
+      <c r="B37" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="53"/>
-      <c r="D37" s="53"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="49" t="s">
+      <c r="C38" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="49"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="49"/>
-      <c r="G38" s="49"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="49" t="s">
+      <c r="C39" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="49"/>
-      <c r="E39" s="49"/>
-      <c r="F39" s="49"/>
-      <c r="G39" s="49"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="49" t="s">
+      <c r="C40" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="49"/>
-      <c r="E40" s="49"/>
-      <c r="F40" s="49"/>
-      <c r="G40" s="49"/>
+      <c r="D40" s="50"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="50"/>
+      <c r="G40" s="50"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="49" t="s">
+      <c r="C41" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="49"/>
-      <c r="E41" s="49"/>
-      <c r="F41" s="49"/>
-      <c r="G41" s="49"/>
+      <c r="D41" s="50"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="50"/>
+      <c r="G41" s="50"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="49" t="s">
+      <c r="C42" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="49"/>
-      <c r="E42" s="49"/>
-      <c r="F42" s="49"/>
-      <c r="G42" s="49"/>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="50"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="53" t="s">
+      <c r="B44" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="53"/>
-      <c r="D44" s="53"/>
-      <c r="E44" s="53"/>
-      <c r="F44" s="53"/>
-      <c r="G44" s="53"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="54"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="49" t="s">
+      <c r="C45" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="50"/>
+      <c r="G45" s="50"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="49" t="s">
+      <c r="C46" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="49"/>
-      <c r="E46" s="49"/>
-      <c r="F46" s="49"/>
-      <c r="G46" s="49"/>
+      <c r="D46" s="50"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="50"/>
+      <c r="G46" s="50"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="49" t="s">
+      <c r="C47" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="49"/>
-      <c r="E47" s="49"/>
-      <c r="F47" s="49"/>
-      <c r="G47" s="49"/>
+      <c r="D47" s="50"/>
+      <c r="E47" s="50"/>
+      <c r="F47" s="50"/>
+      <c r="G47" s="50"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="49" t="s">
+      <c r="C48" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49"/>
-      <c r="G48" s="49"/>
+      <c r="D48" s="50"/>
+      <c r="E48" s="50"/>
+      <c r="F48" s="50"/>
+      <c r="G48" s="50"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="49" t="s">
+      <c r="C49" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="49"/>
-      <c r="E49" s="49"/>
-      <c r="F49" s="49"/>
-      <c r="G49" s="49"/>
+      <c r="D49" s="50"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="50"/>
+      <c r="G49" s="50"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="47" t="s">
+      <c r="B51" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="47"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="47"/>
-      <c r="G51" s="47"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="54" t="s">
+      <c r="B52" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="54"/>
-      <c r="D52" s="54"/>
-      <c r="E52" s="54"/>
-      <c r="F52" s="54"/>
-      <c r="G52" s="54"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="55"/>
+      <c r="G52" s="55"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="55" t="s">
+      <c r="B53" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="55"/>
-      <c r="D53" s="55"/>
-      <c r="E53" s="55"/>
-      <c r="F53" s="55"/>
-      <c r="G53" s="55"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="56"/>
+      <c r="G53" s="56"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="47" t="s">
+      <c r="B55" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="47"/>
-      <c r="D55" s="47"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="47"/>
-      <c r="G55" s="47"/>
+      <c r="C55" s="48"/>
+      <c r="D55" s="48"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="48"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="48" t="s">
+      <c r="B56" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="48"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="49" t="s">
+      <c r="C56" s="49"/>
+      <c r="D56" s="49"/>
+      <c r="E56" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="49"/>
-      <c r="G56" s="49"/>
+      <c r="F56" s="50"/>
+      <c r="G56" s="50"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="50" t="s">
+      <c r="B57" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="50"/>
-      <c r="D57" s="50"/>
-      <c r="E57" s="49" t="s">
+      <c r="C57" s="51"/>
+      <c r="D57" s="51"/>
+      <c r="E57" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="49"/>
-      <c r="G57" s="49"/>
+      <c r="F57" s="50"/>
+      <c r="G57" s="50"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="51" t="s">
+      <c r="B58" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="51"/>
-      <c r="D58" s="51"/>
-      <c r="E58" s="49" t="s">
+      <c r="C58" s="52"/>
+      <c r="D58" s="52"/>
+      <c r="E58" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="49"/>
-      <c r="G58" s="49"/>
+      <c r="F58" s="50"/>
+      <c r="G58" s="50"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="52" t="s">
+      <c r="B59" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="52"/>
-      <c r="D59" s="52"/>
-      <c r="E59" s="49" t="s">
+      <c r="C59" s="53"/>
+      <c r="D59" s="53"/>
+      <c r="E59" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="49"/>
-      <c r="G59" s="49"/>
+      <c r="F59" s="50"/>
+      <c r="G59" s="50"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="47" t="s">
+      <c r="B62" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="47"/>
-      <c r="D62" s="47"/>
-      <c r="E62" s="47"/>
-      <c r="F62" s="47"/>
-      <c r="G62" s="47"/>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="45" t="s">
+      <c r="B63" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
-      <c r="E63" s="45"/>
-      <c r="F63" s="45"/>
-      <c r="G63" s="45"/>
+      <c r="C63" s="46"/>
+      <c r="D63" s="46"/>
+      <c r="E63" s="46"/>
+      <c r="F63" s="46"/>
+      <c r="G63" s="46"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="46" t="s">
+      <c r="B64" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="46"/>
-      <c r="D64" s="46"/>
-      <c r="E64" s="46"/>
-      <c r="F64" s="46"/>
-      <c r="G64" s="46"/>
+      <c r="C64" s="47"/>
+      <c r="D64" s="47"/>
+      <c r="E64" s="47"/>
+      <c r="F64" s="47"/>
+      <c r="G64" s="47"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="46" t="s">
+      <c r="B65" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="46"/>
-      <c r="D65" s="46"/>
-      <c r="E65" s="46"/>
-      <c r="F65" s="46"/>
-      <c r="G65" s="46"/>
+      <c r="C65" s="47"/>
+      <c r="D65" s="47"/>
+      <c r="E65" s="47"/>
+      <c r="F65" s="47"/>
+      <c r="G65" s="47"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="46" t="s">
+      <c r="B66" s="47" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="46"/>
-      <c r="D66" s="46"/>
-      <c r="E66" s="46"/>
-      <c r="F66" s="46"/>
-      <c r="G66" s="46"/>
+      <c r="C66" s="47"/>
+      <c r="D66" s="47"/>
+      <c r="E66" s="47"/>
+      <c r="F66" s="47"/>
+      <c r="G66" s="47"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="46" t="s">
+      <c r="B67" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="46"/>
-      <c r="D67" s="46"/>
-      <c r="E67" s="46"/>
-      <c r="F67" s="46"/>
-      <c r="G67" s="46"/>
+      <c r="C67" s="47"/>
+      <c r="D67" s="47"/>
+      <c r="E67" s="47"/>
+      <c r="F67" s="47"/>
+      <c r="G67" s="47"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="47" t="s">
+      <c r="B69" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="47"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="47"/>
-      <c r="F69" s="47"/>
-      <c r="G69" s="47"/>
+      <c r="C69" s="48"/>
+      <c r="D69" s="48"/>
+      <c r="E69" s="48"/>
+      <c r="F69" s="48"/>
+      <c r="G69" s="48"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="45" t="s">
+      <c r="B70" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="45"/>
-      <c r="D70" s="45"/>
-      <c r="E70" s="45"/>
-      <c r="F70" s="45"/>
-      <c r="G70" s="45"/>
+      <c r="C70" s="46"/>
+      <c r="D70" s="46"/>
+      <c r="E70" s="46"/>
+      <c r="F70" s="46"/>
+      <c r="G70" s="46"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="45" t="s">
+      <c r="B71" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="45"/>
-      <c r="D71" s="45"/>
-      <c r="E71" s="45"/>
-      <c r="F71" s="45"/>
-      <c r="G71" s="45"/>
+      <c r="C71" s="46"/>
+      <c r="D71" s="46"/>
+      <c r="E71" s="46"/>
+      <c r="F71" s="46"/>
+      <c r="G71" s="46"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="45" t="s">
+      <c r="B72" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="45"/>
-      <c r="D72" s="45"/>
-      <c r="E72" s="45"/>
-      <c r="F72" s="45"/>
-      <c r="G72" s="45"/>
+      <c r="C72" s="46"/>
+      <c r="D72" s="46"/>
+      <c r="E72" s="46"/>
+      <c r="F72" s="46"/>
+      <c r="G72" s="46"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="45" t="s">
+      <c r="B73" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="45"/>
-      <c r="D73" s="45"/>
-      <c r="E73" s="45"/>
-      <c r="F73" s="45"/>
-      <c r="G73" s="45"/>
+      <c r="C73" s="46"/>
+      <c r="D73" s="46"/>
+      <c r="E73" s="46"/>
+      <c r="F73" s="46"/>
+      <c r="G73" s="46"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="45" t="s">
+      <c r="B74" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="45"/>
-      <c r="D74" s="45"/>
-      <c r="E74" s="45"/>
-      <c r="F74" s="45"/>
-      <c r="G74" s="45"/>
+      <c r="C74" s="46"/>
+      <c r="D74" s="46"/>
+      <c r="E74" s="46"/>
+      <c r="F74" s="46"/>
+      <c r="G74" s="46"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="45" t="s">
+      <c r="B75" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="45"/>
-      <c r="D75" s="45"/>
-      <c r="E75" s="45"/>
-      <c r="F75" s="45"/>
-      <c r="G75" s="45"/>
+      <c r="C75" s="46"/>
+      <c r="D75" s="46"/>
+      <c r="E75" s="46"/>
+      <c r="F75" s="46"/>
+      <c r="G75" s="46"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="45"/>
-      <c r="C76" s="45"/>
-      <c r="D76" s="45"/>
-      <c r="E76" s="45"/>
-      <c r="F76" s="45"/>
-      <c r="G76" s="45"/>
+      <c r="B76" s="46"/>
+      <c r="C76" s="46"/>
+      <c r="D76" s="46"/>
+      <c r="E76" s="46"/>
+      <c r="F76" s="46"/>
+      <c r="G76" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="71">
@@ -2473,7 +2452,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R68"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:R69"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2497,25 +2477,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="5"/>
     </row>
     <row r="2" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.35">
@@ -2574,7 +2554,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>168028</v>
       </c>
@@ -2626,7 +2606,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>150026</v>
       </c>
@@ -2678,7 +2658,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>147022</v>
       </c>
@@ -2730,7 +2710,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>136049</v>
       </c>
@@ -2782,7 +2762,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>161027</v>
       </c>
@@ -2834,7 +2814,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>656001</v>
       </c>
@@ -2886,7 +2866,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>656008</v>
       </c>
@@ -2938,7 +2918,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>168017</v>
       </c>
@@ -3041,14 +3021,14 @@
         <v>252</v>
       </c>
       <c r="P11" s="28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q11" s="28"/>
       <c r="R11" s="27" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>166027</v>
       </c>
@@ -3100,7 +3080,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" s="26" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="27">
         <v>466004</v>
       </c>
@@ -3154,7 +3134,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" s="26" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="20">
         <v>159029</v>
       </c>
@@ -3252,14 +3232,16 @@
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
+      <c r="N15" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="O15" s="33" t="s">
+        <v>252</v>
+      </c>
       <c r="P15" s="33" t="s">
         <v>258</v>
       </c>
-      <c r="Q15" s="33" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q15" s="33"/>
       <c r="R15" s="32" t="s">
         <v>122</v>
       </c>
@@ -3308,19 +3290,21 @@
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
+      <c r="N16" s="44" t="s">
+        <v>291</v>
+      </c>
+      <c r="O16" s="40" t="s">
+        <v>252</v>
+      </c>
       <c r="P16" s="40" t="s">
         <v>259</v>
       </c>
-      <c r="Q16" s="40" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q16" s="40"/>
       <c r="R16" s="39" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>242032</v>
       </c>
@@ -3365,11 +3349,11 @@
         <v>Low Impact + Low Risk</v>
       </c>
       <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
+      <c r="O17" s="9" t="s">
+        <v>252</v>
+      </c>
       <c r="P17" s="9"/>
-      <c r="Q17" s="9" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q17" s="9"/>
       <c r="R17" s="7" t="s">
         <v>122</v>
       </c>
@@ -3418,17 +3402,19 @@
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
+      <c r="N18" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="O18" s="15" t="s">
+        <v>252</v>
+      </c>
       <c r="P18" s="15"/>
-      <c r="Q18" s="15" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q18" s="15"/>
       <c r="R18" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>232027</v>
       </c>
@@ -3473,16 +3459,16 @@
         <v>Low Impact + Low Risk</v>
       </c>
       <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
+      <c r="O19" s="9" t="s">
+        <v>252</v>
+      </c>
       <c r="P19" s="9"/>
-      <c r="Q19" s="9" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q19" s="9"/>
       <c r="R19" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>256029</v>
       </c>
@@ -3527,16 +3513,16 @@
         <v>Low Impact + Low Risk</v>
       </c>
       <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
+      <c r="O20" s="15" t="s">
+        <v>252</v>
+      </c>
       <c r="P20" s="15"/>
-      <c r="Q20" s="15" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q20" s="15"/>
       <c r="R20" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>236012</v>
       </c>
@@ -3581,11 +3567,11 @@
         <v>Low Impact + Low Risk</v>
       </c>
       <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
+      <c r="O21" s="9" t="s">
+        <v>252</v>
+      </c>
       <c r="P21" s="9"/>
-      <c r="Q21" s="9" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q21" s="9"/>
       <c r="R21" s="7" t="s">
         <v>122</v>
       </c>
@@ -3634,19 +3620,21 @@
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N22" s="40"/>
-      <c r="O22" s="40"/>
+      <c r="N22" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="O22" s="40" t="s">
+        <v>252</v>
+      </c>
       <c r="P22" s="40" t="s">
         <v>260</v>
       </c>
-      <c r="Q22" s="40" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q22" s="40"/>
       <c r="R22" s="39" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>233034</v>
       </c>
@@ -3693,14 +3681,12 @@
       <c r="N23" s="9"/>
       <c r="O23" s="9"/>
       <c r="P23" s="9"/>
-      <c r="Q23" s="9" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q23" s="9"/>
       <c r="R23" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>268013</v>
       </c>
@@ -3747,14 +3733,12 @@
       <c r="N24" s="15"/>
       <c r="O24" s="15"/>
       <c r="P24" s="15"/>
-      <c r="Q24" s="15" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q24" s="15"/>
       <c r="R24" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>249010</v>
       </c>
@@ -3801,14 +3785,12 @@
       <c r="N25" s="9"/>
       <c r="O25" s="9"/>
       <c r="P25" s="9"/>
-      <c r="Q25" s="9" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q25" s="9"/>
       <c r="R25" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>268012</v>
       </c>
@@ -3855,14 +3837,12 @@
       <c r="N26" s="15"/>
       <c r="O26" s="15"/>
       <c r="P26" s="15"/>
-      <c r="Q26" s="15" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q26" s="15"/>
       <c r="R26" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>238030</v>
       </c>
@@ -3909,14 +3889,12 @@
       <c r="N27" s="9"/>
       <c r="O27" s="9"/>
       <c r="P27" s="9"/>
-      <c r="Q27" s="9" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q27" s="9"/>
       <c r="R27" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="39">
         <v>256014</v>
       </c>
@@ -3965,14 +3943,12 @@
       <c r="P28" s="40" t="s">
         <v>261</v>
       </c>
-      <c r="Q28" s="40" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q28" s="40"/>
       <c r="R28" s="39" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="32">
         <v>443003</v>
       </c>
@@ -4021,14 +3997,12 @@
       <c r="P29" s="33" t="s">
         <v>262</v>
       </c>
-      <c r="Q29" s="33" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q29" s="33"/>
       <c r="R29" s="32" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="39">
         <v>254057</v>
       </c>
@@ -4077,14 +4051,12 @@
       <c r="P30" s="40" t="s">
         <v>263</v>
       </c>
-      <c r="Q30" s="40" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q30" s="40"/>
       <c r="R30" s="39" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="32">
         <v>237011</v>
       </c>
@@ -4133,14 +4105,12 @@
       <c r="P31" s="33" t="s">
         <v>262</v>
       </c>
-      <c r="Q31" s="33" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q31" s="33"/>
       <c r="R31" s="32" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="39">
         <v>267096</v>
       </c>
@@ -4189,14 +4159,12 @@
       <c r="P32" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="Q32" s="40" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q32" s="40"/>
       <c r="R32" s="39" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="32">
         <v>249048</v>
       </c>
@@ -4245,14 +4213,12 @@
       <c r="P33" s="33" t="s">
         <v>262</v>
       </c>
-      <c r="Q33" s="33" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q33" s="33"/>
       <c r="R33" s="32" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="39">
         <v>269022</v>
       </c>
@@ -4301,14 +4267,12 @@
       <c r="P34" s="40" t="s">
         <v>265</v>
       </c>
-      <c r="Q34" s="40" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q34" s="40"/>
       <c r="R34" s="39" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>253014</v>
       </c>
@@ -4355,14 +4319,12 @@
       <c r="N35" s="9"/>
       <c r="O35" s="9"/>
       <c r="P35" s="9"/>
-      <c r="Q35" s="9" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q35" s="9"/>
       <c r="R35" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>248031</v>
       </c>
@@ -4409,14 +4371,12 @@
       <c r="N36" s="15"/>
       <c r="O36" s="15"/>
       <c r="P36" s="15"/>
-      <c r="Q36" s="15" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q36" s="15"/>
       <c r="R36" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="32">
         <v>251007</v>
       </c>
@@ -4465,14 +4425,12 @@
       <c r="P37" s="33" t="s">
         <v>266</v>
       </c>
-      <c r="Q37" s="33" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q37" s="33"/>
       <c r="R37" s="32" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="8">
         <v>242012</v>
       </c>
@@ -4519,14 +4477,12 @@
       <c r="N38" s="15"/>
       <c r="O38" s="15"/>
       <c r="P38" s="15"/>
-      <c r="Q38" s="15" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q38" s="15"/>
       <c r="R38" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="32">
         <v>257039</v>
       </c>
@@ -4575,14 +4531,12 @@
       <c r="P39" s="33" t="s">
         <v>267</v>
       </c>
-      <c r="Q39" s="33" t="s">
-        <v>286</v>
-      </c>
+      <c r="Q39" s="33"/>
       <c r="R39" s="32" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>244023</v>
       </c>
@@ -4692,7 +4646,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" s="26" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="27">
         <v>368001</v>
       </c>
@@ -4748,7 +4702,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" s="26" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="20">
         <v>148005</v>
       </c>
@@ -4766,7 +4720,7 @@
       </c>
       <c r="F43" s="23">
         <f t="shared" ca="1" si="3"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G43" s="23">
         <f t="shared" ca="1" si="0"/>
@@ -4804,7 +4758,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="7">
         <v>267071</v>
       </c>
@@ -4860,7 +4814,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="8">
         <v>268051</v>
       </c>
@@ -4916,7 +4870,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="7">
         <v>269032</v>
       </c>
@@ -5030,7 +4984,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="7">
         <v>146037</v>
       </c>
@@ -5140,7 +5094,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
         <v>145015</v>
       </c>
@@ -5194,7 +5148,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>161005</v>
       </c>
@@ -5244,7 +5198,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="7">
         <v>163003</v>
       </c>
@@ -5294,7 +5248,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <v>166024</v>
       </c>
@@ -5344,7 +5298,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>167001</v>
       </c>
@@ -5394,7 +5348,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>167012</v>
       </c>
@@ -5444,7 +5398,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="7">
         <v>260001</v>
       </c>
@@ -5498,7 +5452,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
         <v>267001</v>
       </c>
@@ -5548,7 +5502,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="7">
         <v>160001</v>
       </c>
@@ -5602,7 +5556,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
         <v>167020</v>
       </c>
@@ -5652,7 +5606,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="8">
         <v>167029</v>
       </c>
@@ -5706,7 +5660,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>167032</v>
       </c>
@@ -5756,7 +5710,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="8">
         <v>168024</v>
       </c>
@@ -5810,7 +5764,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="8">
         <v>337004</v>
       </c>
@@ -5860,7 +5814,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="8">
         <v>268044</v>
       </c>
@@ -5910,7 +5864,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="65" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="7">
         <v>368004</v>
       </c>
@@ -5957,14 +5911,14 @@
       </c>
       <c r="O65" s="9"/>
       <c r="P65" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="7" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="66" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>238</v>
       </c>
@@ -6011,14 +5965,14 @@
       </c>
       <c r="O66" s="9"/>
       <c r="P66" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q66" s="9"/>
       <c r="R66" s="7" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="67" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" s="26" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="20">
         <v>168016</v>
       </c>
@@ -6130,8 +6084,75 @@
         <v>93</v>
       </c>
     </row>
+    <row r="69" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="7">
+        <v>264090</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E69" s="16">
+        <v>31762</v>
+      </c>
+      <c r="F69" s="17">
+        <f t="shared" ref="F69" ca="1" si="10">DATEDIF(E69,TODAY(),"Y")</f>
+        <v>39</v>
+      </c>
+      <c r="G69" s="17">
+        <f t="shared" ref="G69" ca="1" si="11">IF(F69="","",IF(F69&lt;50,1,IF(F69&lt;55,2,IF(F69&lt;58,3,IF(F69&lt;60,4,5)))))</f>
+        <v>1</v>
+      </c>
+      <c r="H69" s="12">
+        <v>4</v>
+      </c>
+      <c r="I69" s="12">
+        <v>5</v>
+      </c>
+      <c r="J69" s="12">
+        <v>4</v>
+      </c>
+      <c r="K69" s="12">
+        <v>5</v>
+      </c>
+      <c r="L69" s="13">
+        <v>3.9</v>
+      </c>
+      <c r="M69" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="N69" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="O69" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="P69" s="9"/>
+      <c r="Q69" s="9"/>
+      <c r="R69" s="7"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R68" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:R69" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="13">
+      <filters>
+        <filter val="ชรัณ แสงจันทร์"/>
+        <filter val="ทิฆัมพร จันทร์สอน"/>
+        <filter val="ธัญญรัตน์ เจริญผล"/>
+        <filter val="ปองพล สิงห์สนั่น"/>
+        <filter val="พุฒิพงศ์ สีธิสุข"/>
+        <filter val="ภราดร นิเทศพัตรพงศ์"/>
+        <filter val="ภาณุพงศ์ ธีระบุตร"/>
+        <filter val="วงษ์ศักดิ์ ศรีสวัสดิ์ หรือ_x000a_ภานุวัฒน์ ธนสานสกุลวงศ์"/>
+        <filter val="วินัย แสงโชติ"/>
+        <filter val="ศรัณย์ กิจเจริญวิศาล"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{89C05139-767C-4D44-95FE-72D2855E25B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4DE5FDA-ACA3-4036-931A-3B6E609C1F95}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{89C05139-767C-4D44-95FE-72D2855E25B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9571274A-88E4-46B1-AEC0-7303A890D29B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="295">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -905,12 +905,6 @@
   </si>
   <si>
     <t>368004_Contract-Procurement.docx</t>
-  </si>
-  <si>
-    <t>วัชระ สะติรัน</t>
-  </si>
-  <si>
-    <t>Department Manager - Batch and Furnace</t>
   </si>
   <si>
     <t>วงษ์ศักดิ์ ศรีสวัสดิ์ หรือ
@@ -918,13 +912,28 @@
   </si>
   <si>
     <t>ภราดร นิเทศพัตรพงศ์</t>
+  </si>
+  <si>
+    <t>268029 B</t>
+  </si>
+  <si>
+    <t>Acting Department Manager - Batch and Furnace</t>
+  </si>
+  <si>
+    <t>02/04/1974</t>
+  </si>
+  <si>
+    <t>รักษาการ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="28" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
+  </numFmts>
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1109,8 +1118,20 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1189,6 +1210,17 @@
         <bgColor rgb="FFF0F0F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1245,7 +1277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1376,19 +1408,43 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1400,35 +1456,44 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1507,6 +1572,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1698,693 +1767,727 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="C12" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="47" t="s">
+      <c r="B20" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="48" t="s">
+      <c r="B22" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="54" t="s">
+      <c r="B23" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="57" t="s">
+      <c r="B26" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="58" t="s">
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="58"/>
+      <c r="G26" s="55"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="58" t="s">
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="58"/>
+      <c r="G27" s="55"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="58" t="s">
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="58"/>
+      <c r="G28" s="55"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="57" t="s">
+      <c r="B29" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="58" t="s">
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="58"/>
+      <c r="G29" s="55"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="57" t="s">
+      <c r="B30" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="57"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="58" t="s">
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="58"/>
+      <c r="G30" s="55"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="54" t="s">
+      <c r="B32" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="54"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="50" t="s">
+      <c r="C33" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="50" t="s">
+      <c r="C35" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="54" t="s">
+      <c r="B37" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="54"/>
-      <c r="D37" s="54"/>
-      <c r="E37" s="54"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="54"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="50" t="s">
+      <c r="C38" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="50" t="s">
+      <c r="C39" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="50" t="s">
+      <c r="C40" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="50"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="50" t="s">
+      <c r="C41" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="50"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="52"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="50" t="s">
+      <c r="C42" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="50"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="54" t="s">
+      <c r="B44" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="54"/>
-      <c r="D44" s="54"/>
-      <c r="E44" s="54"/>
-      <c r="F44" s="54"/>
-      <c r="G44" s="54"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="53"/>
+      <c r="G44" s="53"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="50" t="s">
+      <c r="C45" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="50"/>
-      <c r="E45" s="50"/>
-      <c r="F45" s="50"/>
-      <c r="G45" s="50"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="52"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="50" t="s">
+      <c r="C46" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="50"/>
-      <c r="E46" s="50"/>
-      <c r="F46" s="50"/>
-      <c r="G46" s="50"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="50" t="s">
+      <c r="C47" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="50"/>
-      <c r="E47" s="50"/>
-      <c r="F47" s="50"/>
-      <c r="G47" s="50"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="52"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="50" t="s">
+      <c r="C48" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="50"/>
-      <c r="E48" s="50"/>
-      <c r="F48" s="50"/>
-      <c r="G48" s="50"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="52"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="50" t="s">
+      <c r="C49" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="50"/>
-      <c r="E49" s="50"/>
-      <c r="F49" s="50"/>
-      <c r="G49" s="50"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="52"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="48" t="s">
+      <c r="B51" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="49"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
+      <c r="G51" s="49"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="55" t="s">
+      <c r="B52" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="55"/>
-      <c r="D52" s="55"/>
-      <c r="E52" s="55"/>
-      <c r="F52" s="55"/>
-      <c r="G52" s="55"/>
+      <c r="C52" s="56"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="56"/>
+      <c r="F52" s="56"/>
+      <c r="G52" s="56"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="56" t="s">
+      <c r="B53" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="56"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
-      <c r="F53" s="56"/>
-      <c r="G53" s="56"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="48" t="s">
+      <c r="B55" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="48"/>
-      <c r="D55" s="48"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="48"/>
-      <c r="G55" s="48"/>
+      <c r="C55" s="49"/>
+      <c r="D55" s="49"/>
+      <c r="E55" s="49"/>
+      <c r="F55" s="49"/>
+      <c r="G55" s="49"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="49" t="s">
+      <c r="B56" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="49"/>
-      <c r="D56" s="49"/>
-      <c r="E56" s="50" t="s">
+      <c r="C56" s="58"/>
+      <c r="D56" s="58"/>
+      <c r="E56" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="50"/>
-      <c r="G56" s="50"/>
+      <c r="F56" s="52"/>
+      <c r="G56" s="52"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="51" t="s">
+      <c r="B57" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="51"/>
-      <c r="D57" s="51"/>
-      <c r="E57" s="50" t="s">
+      <c r="C57" s="59"/>
+      <c r="D57" s="59"/>
+      <c r="E57" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="50"/>
-      <c r="G57" s="50"/>
+      <c r="F57" s="52"/>
+      <c r="G57" s="52"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="52" t="s">
+      <c r="B58" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="52"/>
-      <c r="D58" s="52"/>
-      <c r="E58" s="50" t="s">
+      <c r="C58" s="60"/>
+      <c r="D58" s="60"/>
+      <c r="E58" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="50"/>
-      <c r="G58" s="50"/>
+      <c r="F58" s="52"/>
+      <c r="G58" s="52"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="53" t="s">
+      <c r="B59" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="53"/>
-      <c r="D59" s="53"/>
-      <c r="E59" s="50" t="s">
+      <c r="C59" s="61"/>
+      <c r="D59" s="61"/>
+      <c r="E59" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="50"/>
-      <c r="G59" s="50"/>
+      <c r="F59" s="52"/>
+      <c r="G59" s="52"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="48" t="s">
+      <c r="B62" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="48"/>
-      <c r="D62" s="48"/>
-      <c r="E62" s="48"/>
-      <c r="F62" s="48"/>
-      <c r="G62" s="48"/>
+      <c r="C62" s="49"/>
+      <c r="D62" s="49"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="49"/>
+      <c r="G62" s="49"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="46" t="s">
+      <c r="B63" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="46"/>
-      <c r="D63" s="46"/>
-      <c r="E63" s="46"/>
-      <c r="F63" s="46"/>
-      <c r="G63" s="46"/>
+      <c r="C63" s="50"/>
+      <c r="D63" s="50"/>
+      <c r="E63" s="50"/>
+      <c r="F63" s="50"/>
+      <c r="G63" s="50"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="47" t="s">
+      <c r="B64" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="47"/>
-      <c r="D64" s="47"/>
-      <c r="E64" s="47"/>
-      <c r="F64" s="47"/>
-      <c r="G64" s="47"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="46"/>
+      <c r="E64" s="46"/>
+      <c r="F64" s="46"/>
+      <c r="G64" s="46"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="47" t="s">
+      <c r="B65" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="47"/>
-      <c r="D65" s="47"/>
-      <c r="E65" s="47"/>
-      <c r="F65" s="47"/>
-      <c r="G65" s="47"/>
+      <c r="C65" s="46"/>
+      <c r="D65" s="46"/>
+      <c r="E65" s="46"/>
+      <c r="F65" s="46"/>
+      <c r="G65" s="46"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="47" t="s">
+      <c r="B66" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="47"/>
-      <c r="D66" s="47"/>
-      <c r="E66" s="47"/>
-      <c r="F66" s="47"/>
-      <c r="G66" s="47"/>
+      <c r="C66" s="46"/>
+      <c r="D66" s="46"/>
+      <c r="E66" s="46"/>
+      <c r="F66" s="46"/>
+      <c r="G66" s="46"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="47" t="s">
+      <c r="B67" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="47"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="47"/>
-      <c r="G67" s="47"/>
+      <c r="C67" s="46"/>
+      <c r="D67" s="46"/>
+      <c r="E67" s="46"/>
+      <c r="F67" s="46"/>
+      <c r="G67" s="46"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="48" t="s">
+      <c r="B69" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="48"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="48"/>
+      <c r="C69" s="49"/>
+      <c r="D69" s="49"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="49"/>
+      <c r="G69" s="49"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="46" t="s">
+      <c r="B70" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="46"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="46"/>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
+      <c r="C70" s="50"/>
+      <c r="D70" s="50"/>
+      <c r="E70" s="50"/>
+      <c r="F70" s="50"/>
+      <c r="G70" s="50"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="46" t="s">
+      <c r="B71" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="46"/>
-      <c r="D71" s="46"/>
-      <c r="E71" s="46"/>
-      <c r="F71" s="46"/>
-      <c r="G71" s="46"/>
+      <c r="C71" s="50"/>
+      <c r="D71" s="50"/>
+      <c r="E71" s="50"/>
+      <c r="F71" s="50"/>
+      <c r="G71" s="50"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="46" t="s">
+      <c r="B72" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="46"/>
-      <c r="D72" s="46"/>
-      <c r="E72" s="46"/>
-      <c r="F72" s="46"/>
-      <c r="G72" s="46"/>
+      <c r="C72" s="50"/>
+      <c r="D72" s="50"/>
+      <c r="E72" s="50"/>
+      <c r="F72" s="50"/>
+      <c r="G72" s="50"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="46" t="s">
+      <c r="B73" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="46"/>
-      <c r="D73" s="46"/>
-      <c r="E73" s="46"/>
-      <c r="F73" s="46"/>
-      <c r="G73" s="46"/>
+      <c r="C73" s="50"/>
+      <c r="D73" s="50"/>
+      <c r="E73" s="50"/>
+      <c r="F73" s="50"/>
+      <c r="G73" s="50"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="46" t="s">
+      <c r="B74" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="46"/>
-      <c r="D74" s="46"/>
-      <c r="E74" s="46"/>
-      <c r="F74" s="46"/>
-      <c r="G74" s="46"/>
+      <c r="C74" s="50"/>
+      <c r="D74" s="50"/>
+      <c r="E74" s="50"/>
+      <c r="F74" s="50"/>
+      <c r="G74" s="50"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="46" t="s">
+      <c r="B75" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="46"/>
-      <c r="D75" s="46"/>
-      <c r="E75" s="46"/>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
+      <c r="C75" s="50"/>
+      <c r="D75" s="50"/>
+      <c r="E75" s="50"/>
+      <c r="F75" s="50"/>
+      <c r="G75" s="50"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="46"/>
-      <c r="C76" s="46"/>
-      <c r="D76" s="46"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
+      <c r="B76" s="50"/>
+      <c r="C76" s="50"/>
+      <c r="D76" s="50"/>
+      <c r="E76" s="50"/>
+      <c r="F76" s="50"/>
+      <c r="G76" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="B17:G17"/>
@@ -2398,52 +2501,18 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B15:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2452,7 +2521,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:R69"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2554,7 +2622,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>168028</v>
       </c>
@@ -2606,7 +2674,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>150026</v>
       </c>
@@ -2658,7 +2726,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>147022</v>
       </c>
@@ -2710,7 +2778,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>136049</v>
       </c>
@@ -2762,7 +2830,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>161027</v>
       </c>
@@ -2814,7 +2882,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>656001</v>
       </c>
@@ -2866,7 +2934,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>656008</v>
       </c>
@@ -2918,7 +2986,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>168017</v>
       </c>
@@ -3028,7 +3096,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>166027</v>
       </c>
@@ -3080,7 +3148,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="26" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="27">
         <v>466004</v>
       </c>
@@ -3134,7 +3202,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="26" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="20">
         <v>159029</v>
       </c>
@@ -3291,7 +3359,7 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N16" s="44" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="O16" s="40" t="s">
         <v>252</v>
@@ -3304,7 +3372,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>242032</v>
       </c>
@@ -3414,7 +3482,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>232027</v>
       </c>
@@ -3468,7 +3536,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>256029</v>
       </c>
@@ -3522,7 +3590,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>236012</v>
       </c>
@@ -3621,7 +3689,7 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N22" s="40" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="O22" s="40" t="s">
         <v>252</v>
@@ -3634,7 +3702,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>233034</v>
       </c>
@@ -3686,7 +3754,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>268013</v>
       </c>
@@ -3738,7 +3806,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>249010</v>
       </c>
@@ -3790,7 +3858,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>268012</v>
       </c>
@@ -3842,7 +3910,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>238030</v>
       </c>
@@ -3894,7 +3962,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="39">
         <v>256014</v>
       </c>
@@ -3948,7 +4016,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="32">
         <v>443003</v>
       </c>
@@ -4002,7 +4070,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="39">
         <v>254057</v>
       </c>
@@ -4056,7 +4124,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="32">
         <v>237011</v>
       </c>
@@ -4110,7 +4178,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="39">
         <v>267096</v>
       </c>
@@ -4164,7 +4232,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="32">
         <v>249048</v>
       </c>
@@ -4218,7 +4286,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="39">
         <v>269022</v>
       </c>
@@ -4272,7 +4340,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>253014</v>
       </c>
@@ -4324,7 +4392,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>248031</v>
       </c>
@@ -4376,7 +4444,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="32">
         <v>251007</v>
       </c>
@@ -4430,7 +4498,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="8">
         <v>242012</v>
       </c>
@@ -4482,7 +4550,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="38" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="32">
         <v>257039</v>
       </c>
@@ -4536,7 +4604,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>244023</v>
       </c>
@@ -4646,7 +4714,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="26" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="27">
         <v>368001</v>
       </c>
@@ -4702,7 +4770,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="26" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="20">
         <v>148005</v>
       </c>
@@ -4758,7 +4826,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="7">
         <v>267071</v>
       </c>
@@ -4814,7 +4882,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="8">
         <v>268051</v>
       </c>
@@ -4870,7 +4938,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="7">
         <v>269032</v>
       </c>
@@ -4984,7 +5052,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="7">
         <v>146037</v>
       </c>
@@ -5094,7 +5162,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
         <v>145015</v>
       </c>
@@ -5148,7 +5216,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>161005</v>
       </c>
@@ -5198,7 +5266,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="7">
         <v>163003</v>
       </c>
@@ -5248,7 +5316,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <v>166024</v>
       </c>
@@ -5298,7 +5366,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>167001</v>
       </c>
@@ -5348,7 +5416,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>167012</v>
       </c>
@@ -5398,7 +5466,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="7">
         <v>260001</v>
       </c>
@@ -5452,7 +5520,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
         <v>267001</v>
       </c>
@@ -5502,7 +5570,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="7">
         <v>160001</v>
       </c>
@@ -5556,7 +5624,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
         <v>167020</v>
       </c>
@@ -5606,7 +5674,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="8">
         <v>167029</v>
       </c>
@@ -5660,7 +5728,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>167032</v>
       </c>
@@ -5710,7 +5778,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="8">
         <v>168024</v>
       </c>
@@ -5764,7 +5832,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="8">
         <v>337004</v>
       </c>
@@ -5814,7 +5882,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="8">
         <v>268044</v>
       </c>
@@ -5864,7 +5932,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="65" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="7">
         <v>368004</v>
       </c>
@@ -5918,7 +5986,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="66" spans="1:18" s="14" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>238</v>
       </c>
@@ -5972,7 +6040,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="67" spans="1:18" s="26" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="20">
         <v>168016</v>
       </c>
@@ -6084,29 +6152,29 @@
         <v>93</v>
       </c>
     </row>
-    <row r="69" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="7">
-        <v>264090</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>290</v>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A69" s="62" t="s">
+        <v>291</v>
+      </c>
+      <c r="B69" s="63" t="s">
+        <v>294</v>
+      </c>
+      <c r="C69" s="64" t="s">
+        <v>292</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E69" s="16">
-        <v>31762</v>
+      <c r="E69" s="65" t="s">
+        <v>293</v>
       </c>
       <c r="F69" s="17">
         <f t="shared" ref="F69" ca="1" si="10">DATEDIF(E69,TODAY(),"Y")</f>
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G69" s="17">
         <f t="shared" ref="G69" ca="1" si="11">IF(F69="","",IF(F69&lt;50,1,IF(F69&lt;55,2,IF(F69&lt;58,3,IF(F69&lt;60,4,5)))))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69" s="12">
         <v>4</v>
@@ -6134,28 +6202,19 @@
       </c>
       <c r="P69" s="9"/>
       <c r="Q69" s="9"/>
-      <c r="R69" s="7"/>
+      <c r="R69" s="7" t="s">
+        <v>122</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:R69" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="13">
-      <filters>
-        <filter val="ชรัณ แสงจันทร์"/>
-        <filter val="ทิฆัมพร จันทร์สอน"/>
-        <filter val="ธัญญรัตน์ เจริญผล"/>
-        <filter val="ปองพล สิงห์สนั่น"/>
-        <filter val="พุฒิพงศ์ สีธิสุข"/>
-        <filter val="ภราดร นิเทศพัตรพงศ์"/>
-        <filter val="ภาณุพงศ์ ธีระบุตร"/>
-        <filter val="วงษ์ศักดิ์ ศรีสวัสดิ์ หรือ_x000a_ภานุวัฒน์ ธนสานสกุลวงศ์"/>
-        <filter val="วินัย แสงโชติ"/>
-        <filter val="ศรัณย์ กิจเจริญวิศาล"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:R69" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
+  <conditionalFormatting sqref="A69">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="J3:K48 H3:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"1,2,3,4,5"</formula1>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{89C05139-767C-4D44-95FE-72D2855E25B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9571274A-88E4-46B1-AEC0-7303A890D29B}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{89C05139-767C-4D44-95FE-72D2855E25B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{915993F0-8F33-4790-88A3-88B85F5FCDBA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="กรอกข้อมูล" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$R$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">กรอกข้อมูล!$A$2:$R$70</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="294">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -905,10 +905,6 @@
   </si>
   <si>
     <t>368004_Contract-Procurement.docx</t>
-  </si>
-  <si>
-    <t>วงษ์ศักดิ์ ศรีสวัสดิ์ หรือ
-ภานุวัฒน์ ธนสานสกุลวงศ์</t>
   </si>
   <si>
     <t>ภราดร นิเทศพัตรพงศ์</t>
@@ -1405,46 +1401,34 @@
     <xf numFmtId="0" fontId="24" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1456,16 +1440,28 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1572,10 +1568,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1767,34 +1759,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="49" t="s">
+      <c r="B6" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="50" t="s">
@@ -1810,507 +1802,507 @@
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="C8" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="49" t="s">
+      <c r="B22" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="53" t="s">
+      <c r="B23" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="56" t="s">
+      <c r="B25" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="56"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="55" t="s">
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="55"/>
+      <c r="G26" s="62"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="54" t="s">
+      <c r="B27" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="54"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="55" t="s">
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="55"/>
+      <c r="G27" s="62"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="54" t="s">
+      <c r="B28" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="55" t="s">
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="61"/>
+      <c r="F28" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="55"/>
+      <c r="G28" s="62"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="54" t="s">
+      <c r="B29" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="54"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="55" t="s">
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="61"/>
+      <c r="F29" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="55"/>
+      <c r="G29" s="62"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="54" t="s">
+      <c r="B30" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="54"/>
-      <c r="D30" s="54"/>
-      <c r="E30" s="54"/>
-      <c r="F30" s="55" t="s">
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="55"/>
+      <c r="G30" s="62"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="53" t="s">
+      <c r="B32" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="53"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="58"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="52" t="s">
+      <c r="C33" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="52" t="s">
+      <c r="C34" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="52" t="s">
+      <c r="C35" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="53" t="s">
+      <c r="B37" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="53"/>
-      <c r="D37" s="53"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
+      <c r="C37" s="58"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="52" t="s">
+      <c r="C38" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="52" t="s">
+      <c r="C39" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
-      <c r="G39" s="52"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="52" t="s">
+      <c r="C40" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="54"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="52" t="s">
+      <c r="C41" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="52"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="52"/>
-      <c r="G41" s="52"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="52" t="s">
+      <c r="C42" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="53" t="s">
+      <c r="B44" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="53"/>
-      <c r="D44" s="53"/>
-      <c r="E44" s="53"/>
-      <c r="F44" s="53"/>
-      <c r="G44" s="53"/>
+      <c r="C44" s="58"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="58"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="52" t="s">
+      <c r="C45" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="52"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="52" t="s">
+      <c r="C46" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="52"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="52" t="s">
+      <c r="C47" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="52"/>
-      <c r="G47" s="52"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="52" t="s">
+      <c r="C48" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="52"/>
-      <c r="G48" s="52"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="52" t="s">
+      <c r="C49" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="52"/>
-      <c r="G49" s="52"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="49" t="s">
+      <c r="B51" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="49"/>
-      <c r="D51" s="49"/>
-      <c r="E51" s="49"/>
-      <c r="F51" s="49"/>
-      <c r="G51" s="49"/>
+      <c r="C51" s="52"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="52"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="56" t="s">
+      <c r="B52" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="56"/>
-      <c r="D52" s="56"/>
-      <c r="E52" s="56"/>
-      <c r="F52" s="56"/>
-      <c r="G52" s="56"/>
+      <c r="C52" s="59"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="59"/>
+      <c r="G52" s="59"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="57" t="s">
+      <c r="B53" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="57"/>
-      <c r="D53" s="57"/>
-      <c r="E53" s="57"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
+      <c r="C53" s="60"/>
+      <c r="D53" s="60"/>
+      <c r="E53" s="60"/>
+      <c r="F53" s="60"/>
+      <c r="G53" s="60"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="49" t="s">
+      <c r="B55" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="49"/>
-      <c r="D55" s="49"/>
-      <c r="E55" s="49"/>
-      <c r="F55" s="49"/>
-      <c r="G55" s="49"/>
+      <c r="C55" s="52"/>
+      <c r="D55" s="52"/>
+      <c r="E55" s="52"/>
+      <c r="F55" s="52"/>
+      <c r="G55" s="52"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="58" t="s">
+      <c r="B56" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="58"/>
-      <c r="D56" s="58"/>
-      <c r="E56" s="52" t="s">
+      <c r="C56" s="53"/>
+      <c r="D56" s="53"/>
+      <c r="E56" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="52"/>
-      <c r="G56" s="52"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="59" t="s">
+      <c r="B57" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="59"/>
-      <c r="D57" s="59"/>
-      <c r="E57" s="52" t="s">
+      <c r="C57" s="55"/>
+      <c r="D57" s="55"/>
+      <c r="E57" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="52"/>
-      <c r="G57" s="52"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="54"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="60" t="s">
+      <c r="B58" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="60"/>
-      <c r="D58" s="60"/>
-      <c r="E58" s="52" t="s">
+      <c r="C58" s="56"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="52"/>
-      <c r="G58" s="52"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="54"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="61" t="s">
+      <c r="B59" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="61"/>
-      <c r="D59" s="61"/>
-      <c r="E59" s="52" t="s">
+      <c r="C59" s="57"/>
+      <c r="D59" s="57"/>
+      <c r="E59" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="52"/>
-      <c r="G59" s="52"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="54"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="49" t="s">
+      <c r="B62" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="49"/>
-      <c r="D62" s="49"/>
-      <c r="E62" s="49"/>
-      <c r="F62" s="49"/>
-      <c r="G62" s="49"/>
+      <c r="C62" s="52"/>
+      <c r="D62" s="52"/>
+      <c r="E62" s="52"/>
+      <c r="F62" s="52"/>
+      <c r="G62" s="52"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B63" s="50" t="s">
@@ -2323,54 +2315,54 @@
       <c r="G63" s="50"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="46" t="s">
+      <c r="B64" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="46"/>
-      <c r="D64" s="46"/>
-      <c r="E64" s="46"/>
-      <c r="F64" s="46"/>
-      <c r="G64" s="46"/>
+      <c r="C64" s="51"/>
+      <c r="D64" s="51"/>
+      <c r="E64" s="51"/>
+      <c r="F64" s="51"/>
+      <c r="G64" s="51"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="46" t="s">
+      <c r="B65" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="46"/>
-      <c r="D65" s="46"/>
-      <c r="E65" s="46"/>
-      <c r="F65" s="46"/>
-      <c r="G65" s="46"/>
+      <c r="C65" s="51"/>
+      <c r="D65" s="51"/>
+      <c r="E65" s="51"/>
+      <c r="F65" s="51"/>
+      <c r="G65" s="51"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="46" t="s">
+      <c r="B66" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="46"/>
-      <c r="D66" s="46"/>
-      <c r="E66" s="46"/>
-      <c r="F66" s="46"/>
-      <c r="G66" s="46"/>
+      <c r="C66" s="51"/>
+      <c r="D66" s="51"/>
+      <c r="E66" s="51"/>
+      <c r="F66" s="51"/>
+      <c r="G66" s="51"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="46" t="s">
+      <c r="B67" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="46"/>
-      <c r="D67" s="46"/>
-      <c r="E67" s="46"/>
-      <c r="F67" s="46"/>
-      <c r="G67" s="46"/>
+      <c r="C67" s="51"/>
+      <c r="D67" s="51"/>
+      <c r="E67" s="51"/>
+      <c r="F67" s="51"/>
+      <c r="G67" s="51"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="49" t="s">
+      <c r="B69" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="49"/>
-      <c r="D69" s="49"/>
-      <c r="E69" s="49"/>
-      <c r="F69" s="49"/>
-      <c r="G69" s="49"/>
+      <c r="C69" s="52"/>
+      <c r="D69" s="52"/>
+      <c r="E69" s="52"/>
+      <c r="F69" s="52"/>
+      <c r="G69" s="52"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="50" t="s">
@@ -2442,52 +2434,18 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B15:G15"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="B17:G17"/>
@@ -2501,18 +2459,52 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2521,7 +2513,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R69"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2545,25 +2537,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="5"/>
     </row>
     <row r="2" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.35">
@@ -2643,7 +2635,7 @@
         <v>41</v>
       </c>
       <c r="G3" s="11">
-        <f t="shared" ref="G3:G47" ca="1" si="0">IF(F3="","",IF(F3&lt;50,1,IF(F3&lt;55,2,IF(F3&lt;58,3,IF(F3&lt;60,4,5)))))</f>
+        <f t="shared" ref="G3:G48" ca="1" si="0">IF(F3="","",IF(F3&lt;50,1,IF(F3&lt;55,2,IF(F3&lt;58,3,IF(F3&lt;60,4,5)))))</f>
         <v>1</v>
       </c>
       <c r="H3" s="12">
@@ -2659,11 +2651,11 @@
         <v>3</v>
       </c>
       <c r="L3" s="13">
-        <f t="shared" ref="L3:L47" ca="1" si="1">IF(OR(I3="",J3="",K3="",G3=""),"",ROUND(G3*0.2+I3*0.3+J3*0.3+K3*0.2,2))</f>
+        <f t="shared" ref="L3:L48" ca="1" si="1">IF(OR(I3="",J3="",K3="",G3=""),"",ROUND(G3*0.2+I3*0.3+J3*0.3+K3*0.2,2))</f>
         <v>2.2999999999999998</v>
       </c>
       <c r="M3" s="13" t="str">
-        <f t="shared" ref="M3:M47" ca="1" si="2">IF(OR(H3="",L3=""),"",IF(AND(H3&gt;=4,L3&gt;=3.5),"High Impact + High Risk",IF(AND(H3&gt;=4,L3&lt;3.5),"High Impact + Low Risk",IF(AND(H3&lt;4,L3&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+        <f t="shared" ref="M3:M48" ca="1" si="2">IF(OR(H3="",L3=""),"",IF(AND(H3&gt;=4,L3&gt;=3.5),"High Impact + High Risk",IF(AND(H3&gt;=4,L3&lt;3.5),"High Impact + Low Risk",IF(AND(H3&lt;4,L3&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
         <v>Low Impact + Low Risk</v>
       </c>
       <c r="N3" s="9"/>
@@ -2691,7 +2683,7 @@
         <v>29304</v>
       </c>
       <c r="F4" s="17">
-        <f t="shared" ref="F4:F47" ca="1" si="3">DATEDIF(E4,TODAY(),"Y")</f>
+        <f t="shared" ref="F4:F48" ca="1" si="3">DATEDIF(E4,TODAY(),"Y")</f>
         <v>46</v>
       </c>
       <c r="G4" s="17">
@@ -3359,7 +3351,7 @@
         <v>High Impact + Low Risk</v>
       </c>
       <c r="N16" s="44" t="s">
-        <v>289</v>
+        <v>151</v>
       </c>
       <c r="O16" s="40" t="s">
         <v>252</v>
@@ -3372,1761 +3364,1765 @@
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7">
+    <row r="17" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="39">
+        <v>246004</v>
+      </c>
+      <c r="B17" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="41">
+        <v>28270</v>
+      </c>
+      <c r="F17" s="42">
+        <f t="shared" ref="F17" ca="1" si="6">DATEDIF(E17,TODAY(),"Y")</f>
+        <v>49</v>
+      </c>
+      <c r="G17" s="42">
+        <f t="shared" ref="G17" ca="1" si="7">IF(F17="","",IF(F17&lt;50,1,IF(F17&lt;55,2,IF(F17&lt;58,3,IF(F17&lt;60,4,5)))))</f>
+        <v>1</v>
+      </c>
+      <c r="H17" s="36">
+        <v>4</v>
+      </c>
+      <c r="I17" s="36">
+        <v>1</v>
+      </c>
+      <c r="J17" s="36">
+        <v>3</v>
+      </c>
+      <c r="K17" s="36">
+        <v>4</v>
+      </c>
+      <c r="L17" s="43">
+        <f t="shared" ref="L17" ca="1" si="8">IF(OR(I17="",J17="",K17="",G17=""),"",ROUND(G17*0.2+I17*0.3+J17*0.3+K17*0.2,2))</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M17" s="43" t="str">
+        <f t="shared" ref="M17" ca="1" si="9">IF(OR(H17="",L17=""),"",IF(AND(H17&gt;=4,L17&gt;=3.5),"High Impact + High Risk",IF(AND(H17&gt;=4,L17&lt;3.5),"High Impact + Low Risk",IF(AND(H17&lt;4,L17&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N17" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="O17" s="40" t="s">
+        <v>252</v>
+      </c>
+      <c r="P17" s="40" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="39" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="7">
         <v>242032</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B18" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C18" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" s="10">
+      <c r="D18" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="10">
         <v>27745</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F18" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>50</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G18" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H17" s="12">
-        <v>3</v>
-      </c>
-      <c r="I17" s="12">
-        <v>1</v>
-      </c>
-      <c r="J17" s="12">
-        <v>4</v>
-      </c>
-      <c r="K17" s="12">
-        <v>4</v>
-      </c>
-      <c r="L17" s="13">
+      <c r="H18" s="12">
+        <v>3</v>
+      </c>
+      <c r="I18" s="12">
+        <v>1</v>
+      </c>
+      <c r="J18" s="12">
+        <v>4</v>
+      </c>
+      <c r="K18" s="12">
+        <v>4</v>
+      </c>
+      <c r="L18" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M17" s="13" t="str">
+      <c r="M18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9" t="s">
+      <c r="N18" s="9"/>
+      <c r="O18" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="7" t="s">
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="8">
+    <row r="19" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
         <v>149024</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B19" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C19" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="16">
+      <c r="D19" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="16">
         <v>26070</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F19" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>55</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G19" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="H18" s="12">
-        <v>3</v>
-      </c>
-      <c r="I18" s="12">
-        <v>1</v>
-      </c>
-      <c r="J18" s="12">
-        <v>3</v>
-      </c>
-      <c r="K18" s="12">
-        <v>3</v>
-      </c>
-      <c r="L18" s="18">
+      <c r="H19" s="12">
+        <v>3</v>
+      </c>
+      <c r="I19" s="12">
+        <v>1</v>
+      </c>
+      <c r="J19" s="12">
+        <v>3</v>
+      </c>
+      <c r="K19" s="12">
+        <v>3</v>
+      </c>
+      <c r="L19" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2.4</v>
       </c>
-      <c r="M18" s="18" t="str">
+      <c r="M19" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N18" s="15" t="s">
+      <c r="N19" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="O18" s="15" t="s">
+      <c r="O19" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="8" t="s">
+      <c r="P19" s="15"/>
+      <c r="Q19" s="15"/>
+      <c r="R19" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="7">
+    <row r="20" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="7">
         <v>232027</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B20" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C20" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E19" s="10">
+      <c r="D20" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" s="10">
         <v>24838</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F20" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>58</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G20" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>4</v>
       </c>
-      <c r="H19" s="12">
-        <v>3</v>
-      </c>
-      <c r="I19" s="12">
-        <v>1</v>
-      </c>
-      <c r="J19" s="12">
-        <v>4</v>
-      </c>
-      <c r="K19" s="12">
-        <v>4</v>
-      </c>
-      <c r="L19" s="13">
+      <c r="H20" s="12">
+        <v>3</v>
+      </c>
+      <c r="I20" s="12">
+        <v>1</v>
+      </c>
+      <c r="J20" s="12">
+        <v>4</v>
+      </c>
+      <c r="K20" s="12">
+        <v>4</v>
+      </c>
+      <c r="L20" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>3.1</v>
       </c>
-      <c r="M19" s="13" t="str">
+      <c r="M20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9" t="s">
+      <c r="N20" s="9"/>
+      <c r="O20" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="7" t="s">
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="8">
+    <row r="21" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="8">
         <v>256029</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B21" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C21" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="D20" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="16">
+      <c r="D21" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="16">
         <v>31119</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F21" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>41</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G21" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H20" s="12">
-        <v>3</v>
-      </c>
-      <c r="I20" s="12">
-        <v>1</v>
-      </c>
-      <c r="J20" s="12">
-        <v>3</v>
-      </c>
-      <c r="K20" s="12">
-        <v>3</v>
-      </c>
-      <c r="L20" s="18">
+      <c r="H21" s="12">
+        <v>3</v>
+      </c>
+      <c r="I21" s="12">
+        <v>1</v>
+      </c>
+      <c r="J21" s="12">
+        <v>3</v>
+      </c>
+      <c r="K21" s="12">
+        <v>3</v>
+      </c>
+      <c r="L21" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
-      <c r="M20" s="18" t="str">
+      <c r="M21" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15" t="s">
+      <c r="N21" s="15"/>
+      <c r="O21" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="8" t="s">
+      <c r="P21" s="15"/>
+      <c r="Q21" s="15"/>
+      <c r="R21" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="7">
+    <row r="22" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="7">
         <v>236012</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B22" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C22" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" s="10">
+      <c r="D22" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="10">
         <v>26421</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F22" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>54</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G22" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H21" s="12">
-        <v>3</v>
-      </c>
-      <c r="I21" s="12">
-        <v>1</v>
-      </c>
-      <c r="J21" s="12">
-        <v>3</v>
-      </c>
-      <c r="K21" s="12">
-        <v>3</v>
-      </c>
-      <c r="L21" s="13">
+      <c r="H22" s="12">
+        <v>3</v>
+      </c>
+      <c r="I22" s="12">
+        <v>1</v>
+      </c>
+      <c r="J22" s="12">
+        <v>3</v>
+      </c>
+      <c r="K22" s="12">
+        <v>3</v>
+      </c>
+      <c r="L22" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="M21" s="13" t="str">
+      <c r="M22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9" t="s">
+      <c r="N22" s="9"/>
+      <c r="O22" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="7" t="s">
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="39">
+    <row r="23" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="39">
         <v>250042</v>
       </c>
-      <c r="B22" s="40" t="s">
+      <c r="B23" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C23" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="D22" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="41">
+      <c r="D23" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="41">
         <v>26738</v>
       </c>
-      <c r="F22" s="42">
+      <c r="F23" s="42">
         <f t="shared" ca="1" si="3"/>
         <v>53</v>
       </c>
-      <c r="G22" s="42">
+      <c r="G23" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H22" s="36">
-        <v>4</v>
-      </c>
-      <c r="I22" s="36">
-        <v>1</v>
-      </c>
-      <c r="J22" s="36">
-        <v>4</v>
-      </c>
-      <c r="K22" s="36">
-        <v>4</v>
-      </c>
-      <c r="L22" s="43">
+      <c r="H23" s="36">
+        <v>4</v>
+      </c>
+      <c r="I23" s="36">
+        <v>1</v>
+      </c>
+      <c r="J23" s="36">
+        <v>4</v>
+      </c>
+      <c r="K23" s="36">
+        <v>4</v>
+      </c>
+      <c r="L23" s="43">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M22" s="43" t="str">
+      <c r="M23" s="43" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N22" s="40" t="s">
-        <v>290</v>
-      </c>
-      <c r="O22" s="40" t="s">
+      <c r="N23" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="O23" s="40" t="s">
         <v>252</v>
       </c>
-      <c r="P22" s="40" t="s">
+      <c r="P23" s="40" t="s">
         <v>260</v>
       </c>
-      <c r="Q22" s="40"/>
-      <c r="R22" s="39" t="s">
+      <c r="Q23" s="40"/>
+      <c r="R23" s="39" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="7">
+    <row r="24" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="7">
         <v>233034</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B24" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C24" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" s="10">
+      <c r="D24" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" s="10">
         <v>25245</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F24" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>57</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G24" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="H23" s="12">
-        <v>3</v>
-      </c>
-      <c r="I23" s="12">
-        <v>1</v>
-      </c>
-      <c r="J23" s="12">
-        <v>3</v>
-      </c>
-      <c r="K23" s="12">
-        <v>4</v>
-      </c>
-      <c r="L23" s="13">
+      <c r="H24" s="12">
+        <v>3</v>
+      </c>
+      <c r="I24" s="12">
+        <v>1</v>
+      </c>
+      <c r="J24" s="12">
+        <v>3</v>
+      </c>
+      <c r="K24" s="12">
+        <v>4</v>
+      </c>
+      <c r="L24" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.6</v>
       </c>
-      <c r="M23" s="13" t="str">
+      <c r="M24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="7" t="s">
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="8">
+    <row r="25" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="8">
         <v>268013</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B25" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C25" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="D24" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E24" s="16">
+      <c r="D25" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="16">
         <v>29244</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F25" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>46</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G25" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H24" s="12">
-        <v>3</v>
-      </c>
-      <c r="I24" s="12">
-        <v>3</v>
-      </c>
-      <c r="J24" s="12">
-        <v>3</v>
-      </c>
-      <c r="K24" s="12">
-        <v>4</v>
-      </c>
-      <c r="L24" s="18">
+      <c r="H25" s="12">
+        <v>3</v>
+      </c>
+      <c r="I25" s="12">
+        <v>3</v>
+      </c>
+      <c r="J25" s="12">
+        <v>3</v>
+      </c>
+      <c r="K25" s="12">
+        <v>4</v>
+      </c>
+      <c r="L25" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2.8</v>
       </c>
-      <c r="M24" s="18" t="str">
+      <c r="M25" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N24" s="15"/>
-      <c r="O24" s="15"/>
-      <c r="P24" s="15"/>
-      <c r="Q24" s="15"/>
-      <c r="R24" s="8" t="s">
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="15"/>
+      <c r="R25" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="7">
+    <row r="26" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="7">
         <v>249010</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B26" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C26" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E25" s="10">
+      <c r="D26" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="10">
         <v>27467</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F26" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>51</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G26" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H25" s="12">
-        <v>3</v>
-      </c>
-      <c r="I25" s="12">
-        <v>1</v>
-      </c>
-      <c r="J25" s="12">
-        <v>4</v>
-      </c>
-      <c r="K25" s="12">
-        <v>4</v>
-      </c>
-      <c r="L25" s="13">
+      <c r="H26" s="12">
+        <v>3</v>
+      </c>
+      <c r="I26" s="12">
+        <v>1</v>
+      </c>
+      <c r="J26" s="12">
+        <v>4</v>
+      </c>
+      <c r="K26" s="12">
+        <v>4</v>
+      </c>
+      <c r="L26" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M25" s="13" t="str">
+      <c r="M26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="7" t="s">
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="8">
+    <row r="27" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
         <v>268012</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B27" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C27" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="D26" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E26" s="16">
+      <c r="D27" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="16">
         <v>31704</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F27" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>40</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G27" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H26" s="12">
-        <v>3</v>
-      </c>
-      <c r="I26" s="12">
+      <c r="H27" s="12">
+        <v>3</v>
+      </c>
+      <c r="I27" s="12">
         <v>5</v>
       </c>
-      <c r="J26" s="12">
-        <v>4</v>
-      </c>
-      <c r="K26" s="12">
-        <v>4</v>
-      </c>
-      <c r="L26" s="18">
+      <c r="J27" s="12">
+        <v>4</v>
+      </c>
+      <c r="K27" s="12">
+        <v>4</v>
+      </c>
+      <c r="L27" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>3.7</v>
       </c>
-      <c r="M26" s="18" t="str">
+      <c r="M27" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + High Risk</v>
       </c>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="8" t="s">
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="7">
+    <row r="28" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="7">
         <v>238030</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B28" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C28" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E27" s="10">
+      <c r="D28" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="10">
         <v>27404</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F28" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>51</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G28" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H27" s="12">
-        <v>3</v>
-      </c>
-      <c r="I27" s="12">
-        <v>1</v>
-      </c>
-      <c r="J27" s="12">
-        <v>3</v>
-      </c>
-      <c r="K27" s="12">
-        <v>4</v>
-      </c>
-      <c r="L27" s="13">
+      <c r="H28" s="12">
+        <v>3</v>
+      </c>
+      <c r="I28" s="12">
+        <v>1</v>
+      </c>
+      <c r="J28" s="12">
+        <v>3</v>
+      </c>
+      <c r="K28" s="12">
+        <v>4</v>
+      </c>
+      <c r="L28" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.4</v>
       </c>
-      <c r="M27" s="13" t="str">
+      <c r="M28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="7" t="s">
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="39">
+    <row r="29" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="39">
         <v>256014</v>
       </c>
-      <c r="B28" s="40" t="s">
+      <c r="B29" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="C28" s="40" t="s">
+      <c r="C29" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="D28" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" s="41">
+      <c r="D29" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29" s="41">
         <v>32349</v>
       </c>
-      <c r="F28" s="42">
+      <c r="F29" s="42">
         <f t="shared" ca="1" si="3"/>
         <v>38</v>
       </c>
-      <c r="G28" s="42">
+      <c r="G29" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H28" s="36">
-        <v>4</v>
-      </c>
-      <c r="I28" s="36">
-        <v>1</v>
-      </c>
-      <c r="J28" s="36">
-        <v>4</v>
-      </c>
-      <c r="K28" s="36">
-        <v>4</v>
-      </c>
-      <c r="L28" s="43">
+      <c r="H29" s="36">
+        <v>4</v>
+      </c>
+      <c r="I29" s="36">
+        <v>1</v>
+      </c>
+      <c r="J29" s="36">
+        <v>4</v>
+      </c>
+      <c r="K29" s="36">
+        <v>4</v>
+      </c>
+      <c r="L29" s="43">
         <f t="shared" ca="1" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="M28" s="43" t="str">
+      <c r="M29" s="43" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N28" s="40"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="40" t="s">
+      <c r="N29" s="40"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="40" t="s">
         <v>261</v>
       </c>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="39" t="s">
+      <c r="Q29" s="40"/>
+      <c r="R29" s="39" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="32">
+    <row r="30" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="32">
         <v>443003</v>
       </c>
-      <c r="B29" s="33" t="s">
+      <c r="B30" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C30" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="D29" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" s="34">
+      <c r="D30" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" s="34">
         <v>28572</v>
       </c>
-      <c r="F29" s="35">
+      <c r="F30" s="35">
         <f t="shared" ca="1" si="3"/>
         <v>48</v>
       </c>
-      <c r="G29" s="35">
+      <c r="G30" s="35">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H29" s="36">
-        <v>4</v>
-      </c>
-      <c r="I29" s="36">
-        <v>1</v>
-      </c>
-      <c r="J29" s="36">
-        <v>4</v>
-      </c>
-      <c r="K29" s="36">
+      <c r="H30" s="36">
+        <v>4</v>
+      </c>
+      <c r="I30" s="36">
+        <v>1</v>
+      </c>
+      <c r="J30" s="36">
+        <v>4</v>
+      </c>
+      <c r="K30" s="36">
         <v>5</v>
       </c>
-      <c r="L29" s="37">
+      <c r="L30" s="37">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M29" s="37" t="str">
+      <c r="M30" s="37" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N29" s="33"/>
-      <c r="O29" s="33"/>
-      <c r="P29" s="33" t="s">
+      <c r="N30" s="33"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="33" t="s">
         <v>262</v>
       </c>
-      <c r="Q29" s="33"/>
-      <c r="R29" s="32" t="s">
+      <c r="Q30" s="33"/>
+      <c r="R30" s="32" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="39">
+    <row r="31" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="39">
         <v>254057</v>
       </c>
-      <c r="B30" s="40" t="s">
+      <c r="B31" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C31" s="40" t="s">
         <v>152</v>
       </c>
-      <c r="D30" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="E30" s="41">
+      <c r="D31" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" s="41">
         <v>32420</v>
       </c>
-      <c r="F30" s="42">
+      <c r="F31" s="42">
         <f t="shared" ca="1" si="3"/>
         <v>38</v>
       </c>
-      <c r="G30" s="42">
+      <c r="G31" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H30" s="36">
-        <v>4</v>
-      </c>
-      <c r="I30" s="36">
-        <v>1</v>
-      </c>
-      <c r="J30" s="36">
-        <v>4</v>
-      </c>
-      <c r="K30" s="36">
-        <v>4</v>
-      </c>
-      <c r="L30" s="43">
+      <c r="H31" s="36">
+        <v>4</v>
+      </c>
+      <c r="I31" s="36">
+        <v>1</v>
+      </c>
+      <c r="J31" s="36">
+        <v>4</v>
+      </c>
+      <c r="K31" s="36">
+        <v>4</v>
+      </c>
+      <c r="L31" s="43">
         <f t="shared" ca="1" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="M30" s="43" t="str">
+      <c r="M31" s="43" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N30" s="40"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="40" t="s">
+      <c r="N31" s="40"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="40" t="s">
         <v>263</v>
       </c>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="39" t="s">
+      <c r="Q31" s="40"/>
+      <c r="R31" s="39" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="32">
+    <row r="32" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="32">
         <v>237011</v>
       </c>
-      <c r="B31" s="33" t="s">
+      <c r="B32" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="C31" s="33" t="s">
+      <c r="C32" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="D31" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="E31" s="34">
+      <c r="D32" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="E32" s="34">
         <v>25410</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F32" s="35">
         <f t="shared" ca="1" si="3"/>
         <v>57</v>
       </c>
-      <c r="G31" s="35">
+      <c r="G32" s="35">
         <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
-      <c r="H31" s="36">
-        <v>4</v>
-      </c>
-      <c r="I31" s="36">
-        <v>1</v>
-      </c>
-      <c r="J31" s="36">
-        <v>4</v>
-      </c>
-      <c r="K31" s="36">
+      <c r="H32" s="36">
+        <v>4</v>
+      </c>
+      <c r="I32" s="36">
+        <v>1</v>
+      </c>
+      <c r="J32" s="36">
+        <v>4</v>
+      </c>
+      <c r="K32" s="36">
         <v>5</v>
       </c>
-      <c r="L31" s="37">
+      <c r="L32" s="37">
         <f t="shared" ca="1" si="1"/>
         <v>3.1</v>
       </c>
-      <c r="M31" s="37" t="str">
+      <c r="M32" s="37" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N31" s="33"/>
-      <c r="O31" s="33"/>
-      <c r="P31" s="33" t="s">
+      <c r="N32" s="33"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="33" t="s">
         <v>262</v>
       </c>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="32" t="s">
+      <c r="Q32" s="33"/>
+      <c r="R32" s="32" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="39">
+    <row r="33" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="39">
         <v>267096</v>
       </c>
-      <c r="B32" s="40" t="s">
+      <c r="B33" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="C32" s="40" t="s">
+      <c r="C33" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="D32" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" s="41">
+      <c r="D33" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="41">
         <v>32140</v>
       </c>
-      <c r="F32" s="42">
+      <c r="F33" s="42">
         <f t="shared" ca="1" si="3"/>
         <v>38</v>
       </c>
-      <c r="G32" s="42">
+      <c r="G33" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H32" s="36">
-        <v>4</v>
-      </c>
-      <c r="I32" s="36">
-        <v>3</v>
-      </c>
-      <c r="J32" s="36">
-        <v>4</v>
-      </c>
-      <c r="K32" s="36">
-        <v>4</v>
-      </c>
-      <c r="L32" s="43">
+      <c r="H33" s="36">
+        <v>4</v>
+      </c>
+      <c r="I33" s="36">
+        <v>3</v>
+      </c>
+      <c r="J33" s="36">
+        <v>4</v>
+      </c>
+      <c r="K33" s="36">
+        <v>4</v>
+      </c>
+      <c r="L33" s="43">
         <f t="shared" ca="1" si="1"/>
         <v>3.1</v>
       </c>
-      <c r="M32" s="43" t="str">
+      <c r="M33" s="43" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N32" s="40"/>
-      <c r="O32" s="40"/>
-      <c r="P32" s="40" t="s">
+      <c r="N33" s="40"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="39" t="s">
+      <c r="Q33" s="40"/>
+      <c r="R33" s="39" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="32">
+    <row r="34" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="32">
         <v>249048</v>
       </c>
-      <c r="B33" s="33" t="s">
+      <c r="B34" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C34" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="D33" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="E33" s="34">
+      <c r="D34" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="E34" s="34">
         <v>29299</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F34" s="35">
         <f t="shared" ca="1" si="3"/>
         <v>46</v>
       </c>
-      <c r="G33" s="35">
+      <c r="G34" s="35">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H33" s="36">
-        <v>4</v>
-      </c>
-      <c r="I33" s="36">
-        <v>1</v>
-      </c>
-      <c r="J33" s="36">
-        <v>4</v>
-      </c>
-      <c r="K33" s="36">
+      <c r="H34" s="36">
+        <v>4</v>
+      </c>
+      <c r="I34" s="36">
+        <v>1</v>
+      </c>
+      <c r="J34" s="36">
+        <v>4</v>
+      </c>
+      <c r="K34" s="36">
         <v>5</v>
       </c>
-      <c r="L33" s="37">
+      <c r="L34" s="37">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M33" s="37" t="str">
+      <c r="M34" s="37" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33"/>
-      <c r="P33" s="33" t="s">
+      <c r="N34" s="33"/>
+      <c r="O34" s="33"/>
+      <c r="P34" s="33" t="s">
         <v>262</v>
       </c>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="32" t="s">
+      <c r="Q34" s="33"/>
+      <c r="R34" s="32" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="39">
+    <row r="35" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="39">
         <v>269022</v>
       </c>
-      <c r="B34" s="40" t="s">
+      <c r="B35" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="C34" s="40" t="s">
+      <c r="C35" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="D34" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="E34" s="41">
+      <c r="D35" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="E35" s="41">
         <v>30852</v>
       </c>
-      <c r="F34" s="42">
+      <c r="F35" s="42">
         <f t="shared" ca="1" si="3"/>
         <v>42</v>
       </c>
-      <c r="G34" s="42">
+      <c r="G35" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H34" s="36">
-        <v>4</v>
-      </c>
-      <c r="I34" s="36">
-        <v>3</v>
-      </c>
-      <c r="J34" s="36">
-        <v>4</v>
-      </c>
-      <c r="K34" s="36">
-        <v>4</v>
-      </c>
-      <c r="L34" s="43">
+      <c r="H35" s="36">
+        <v>4</v>
+      </c>
+      <c r="I35" s="36">
+        <v>3</v>
+      </c>
+      <c r="J35" s="36">
+        <v>4</v>
+      </c>
+      <c r="K35" s="36">
+        <v>4</v>
+      </c>
+      <c r="L35" s="43">
         <f t="shared" ca="1" si="1"/>
         <v>3.1</v>
       </c>
-      <c r="M34" s="43" t="str">
+      <c r="M35" s="43" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N34" s="40"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="40" t="s">
+      <c r="N35" s="40"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="40" t="s">
         <v>265</v>
       </c>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="39" t="s">
+      <c r="Q35" s="40"/>
+      <c r="R35" s="39" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="7">
+    <row r="36" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="7">
         <v>253014</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B36" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C36" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="D35" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E35" s="10">
+      <c r="D36" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E36" s="10">
         <v>30611</v>
       </c>
-      <c r="F35" s="11">
+      <c r="F36" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>43</v>
       </c>
-      <c r="G35" s="11">
+      <c r="G36" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H35" s="12">
-        <v>3</v>
-      </c>
-      <c r="I35" s="12">
-        <v>1</v>
-      </c>
-      <c r="J35" s="12">
-        <v>3</v>
-      </c>
-      <c r="K35" s="12">
-        <v>4</v>
-      </c>
-      <c r="L35" s="13">
+      <c r="H36" s="12">
+        <v>3</v>
+      </c>
+      <c r="I36" s="12">
+        <v>1</v>
+      </c>
+      <c r="J36" s="12">
+        <v>3</v>
+      </c>
+      <c r="K36" s="12">
+        <v>4</v>
+      </c>
+      <c r="L36" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="M35" s="13" t="str">
+      <c r="M36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="7" t="s">
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="8">
+    <row r="37" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="8">
         <v>248031</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B37" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C37" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="D36" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E36" s="16">
+      <c r="D37" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E37" s="16">
         <v>29617</v>
       </c>
-      <c r="F36" s="17">
+      <c r="F37" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>45</v>
       </c>
-      <c r="G36" s="17">
+      <c r="G37" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H36" s="12">
-        <v>3</v>
-      </c>
-      <c r="I36" s="12">
-        <v>1</v>
-      </c>
-      <c r="J36" s="12">
-        <v>4</v>
-      </c>
-      <c r="K36" s="12">
-        <v>4</v>
-      </c>
-      <c r="L36" s="18">
+      <c r="H37" s="12">
+        <v>3</v>
+      </c>
+      <c r="I37" s="12">
+        <v>1</v>
+      </c>
+      <c r="J37" s="12">
+        <v>4</v>
+      </c>
+      <c r="K37" s="12">
+        <v>4</v>
+      </c>
+      <c r="L37" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="M36" s="18" t="str">
+      <c r="M37" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N36" s="15"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="15"/>
-      <c r="R36" s="8" t="s">
+      <c r="N37" s="15"/>
+      <c r="O37" s="15"/>
+      <c r="P37" s="15"/>
+      <c r="Q37" s="15"/>
+      <c r="R37" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="32">
+    <row r="38" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="32">
         <v>251007</v>
       </c>
-      <c r="B37" s="33" t="s">
+      <c r="B38" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="C37" s="33" t="s">
+      <c r="C38" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="D37" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="E37" s="34">
+      <c r="D38" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="E38" s="34">
         <v>30522</v>
       </c>
-      <c r="F37" s="35">
+      <c r="F38" s="35">
         <f t="shared" ca="1" si="3"/>
         <v>43</v>
       </c>
-      <c r="G37" s="35">
+      <c r="G38" s="35">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H37" s="36">
-        <v>4</v>
-      </c>
-      <c r="I37" s="36">
-        <v>1</v>
-      </c>
-      <c r="J37" s="36">
-        <v>3</v>
-      </c>
-      <c r="K37" s="36">
-        <v>4</v>
-      </c>
-      <c r="L37" s="37">
+      <c r="H38" s="36">
+        <v>4</v>
+      </c>
+      <c r="I38" s="36">
+        <v>1</v>
+      </c>
+      <c r="J38" s="36">
+        <v>3</v>
+      </c>
+      <c r="K38" s="36">
+        <v>4</v>
+      </c>
+      <c r="L38" s="37">
         <f t="shared" ca="1" si="1"/>
         <v>2.2000000000000002</v>
       </c>
-      <c r="M37" s="37" t="str">
+      <c r="M38" s="37" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N37" s="33"/>
-      <c r="O37" s="33"/>
-      <c r="P37" s="33" t="s">
+      <c r="N38" s="33"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="33" t="s">
         <v>266</v>
       </c>
-      <c r="Q37" s="33"/>
-      <c r="R37" s="32" t="s">
+      <c r="Q38" s="33"/>
+      <c r="R38" s="32" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="8">
+    <row r="39" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="8">
         <v>242012</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B39" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C39" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="D38" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E38" s="16">
+      <c r="D39" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E39" s="16">
         <v>28064</v>
       </c>
-      <c r="F38" s="17">
+      <c r="F39" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>49</v>
       </c>
-      <c r="G38" s="17">
+      <c r="G39" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H38" s="12">
-        <v>3</v>
-      </c>
-      <c r="I38" s="12">
-        <v>1</v>
-      </c>
-      <c r="J38" s="12">
-        <v>4</v>
-      </c>
-      <c r="K38" s="12">
+      <c r="H39" s="12">
+        <v>3</v>
+      </c>
+      <c r="I39" s="12">
+        <v>1</v>
+      </c>
+      <c r="J39" s="12">
+        <v>4</v>
+      </c>
+      <c r="K39" s="12">
         <v>5</v>
       </c>
-      <c r="L38" s="18">
+      <c r="L39" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M38" s="18" t="str">
+      <c r="M39" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="15"/>
-      <c r="R38" s="8" t="s">
+      <c r="N39" s="15"/>
+      <c r="O39" s="15"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="15"/>
+      <c r="R39" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="32">
+    <row r="40" spans="1:18" s="38" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="32">
         <v>257039</v>
       </c>
-      <c r="B39" s="33" t="s">
+      <c r="B40" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="C39" s="33" t="s">
+      <c r="C40" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="D39" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="E39" s="34">
+      <c r="D40" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="E40" s="34">
         <v>32578</v>
       </c>
-      <c r="F39" s="35">
+      <c r="F40" s="35">
         <f t="shared" ca="1" si="3"/>
         <v>37</v>
       </c>
-      <c r="G39" s="35">
+      <c r="G40" s="35">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H39" s="36">
-        <v>4</v>
-      </c>
-      <c r="I39" s="36">
-        <v>3</v>
-      </c>
-      <c r="J39" s="36">
-        <v>4</v>
-      </c>
-      <c r="K39" s="36">
-        <v>4</v>
-      </c>
-      <c r="L39" s="37">
+      <c r="H40" s="36">
+        <v>4</v>
+      </c>
+      <c r="I40" s="36">
+        <v>3</v>
+      </c>
+      <c r="J40" s="36">
+        <v>4</v>
+      </c>
+      <c r="K40" s="36">
+        <v>4</v>
+      </c>
+      <c r="L40" s="37">
         <f t="shared" ca="1" si="1"/>
         <v>3.1</v>
       </c>
-      <c r="M39" s="37" t="str">
+      <c r="M40" s="37" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N39" s="33"/>
-      <c r="O39" s="33"/>
-      <c r="P39" s="33" t="s">
+      <c r="N40" s="33"/>
+      <c r="O40" s="33"/>
+      <c r="P40" s="33" t="s">
         <v>267</v>
       </c>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="32" t="s">
+      <c r="Q40" s="33"/>
+      <c r="R40" s="32" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="8">
+    <row r="41" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="8">
         <v>244023</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B41" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C41" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="D40" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E40" s="16">
+      <c r="D41" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E41" s="16">
         <v>27775</v>
       </c>
-      <c r="F40" s="17">
+      <c r="F41" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>50</v>
       </c>
-      <c r="G40" s="17">
+      <c r="G41" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H40" s="12">
-        <v>3</v>
-      </c>
-      <c r="I40" s="12">
-        <v>1</v>
-      </c>
-      <c r="J40" s="12">
-        <v>3</v>
-      </c>
-      <c r="K40" s="12">
-        <v>4</v>
-      </c>
-      <c r="L40" s="18">
+      <c r="H41" s="12">
+        <v>3</v>
+      </c>
+      <c r="I41" s="12">
+        <v>1</v>
+      </c>
+      <c r="J41" s="12">
+        <v>3</v>
+      </c>
+      <c r="K41" s="12">
+        <v>4</v>
+      </c>
+      <c r="L41" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2.4</v>
       </c>
-      <c r="M40" s="18" t="str">
+      <c r="M41" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N40" s="15"/>
-      <c r="O40" s="15"/>
-      <c r="P40" s="15"/>
-      <c r="Q40" s="15"/>
-      <c r="R40" s="8" t="s">
+      <c r="N41" s="15"/>
+      <c r="O41" s="15"/>
+      <c r="P41" s="15"/>
+      <c r="Q41" s="15"/>
+      <c r="R41" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="20">
+    <row r="42" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="20">
         <v>241009</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B42" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C42" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="D41" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E41" s="22">
+      <c r="D42" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" s="22">
         <v>28315</v>
       </c>
-      <c r="F41" s="23">
+      <c r="F42" s="23">
         <f t="shared" ca="1" si="3"/>
         <v>49</v>
       </c>
-      <c r="G41" s="23">
+      <c r="G42" s="23">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H41" s="24">
-        <v>4</v>
-      </c>
-      <c r="I41" s="24">
-        <v>3</v>
-      </c>
-      <c r="J41" s="24">
-        <v>4</v>
-      </c>
-      <c r="K41" s="24">
+      <c r="H42" s="24">
+        <v>4</v>
+      </c>
+      <c r="I42" s="24">
+        <v>3</v>
+      </c>
+      <c r="J42" s="24">
+        <v>4</v>
+      </c>
+      <c r="K42" s="24">
         <v>5</v>
       </c>
-      <c r="L41" s="25">
+      <c r="L42" s="25">
         <f t="shared" ca="1" si="1"/>
         <v>3.3</v>
       </c>
-      <c r="M41" s="25" t="str">
+      <c r="M42" s="25" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N41" s="21" t="s">
+      <c r="N42" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="O41" s="21" t="s">
+      <c r="O42" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="P41" s="21" t="s">
+      <c r="P42" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="Q41" s="21"/>
-      <c r="R41" s="20" t="s">
+      <c r="Q42" s="21"/>
+      <c r="R42" s="20" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="27">
+    <row r="43" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="27">
         <v>368001</v>
       </c>
-      <c r="B42" s="28" t="s">
+      <c r="B43" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="C42" s="28" t="s">
+      <c r="C43" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="D42" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="E42" s="29">
+      <c r="D43" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="29">
         <v>30299</v>
       </c>
-      <c r="F42" s="30">
+      <c r="F43" s="30">
         <f t="shared" ca="1" si="3"/>
         <v>43</v>
       </c>
-      <c r="G42" s="30">
+      <c r="G43" s="30">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H42" s="24">
-        <v>4</v>
-      </c>
-      <c r="I42" s="24">
+      <c r="H43" s="24">
+        <v>4</v>
+      </c>
+      <c r="I43" s="24">
         <v>5</v>
       </c>
-      <c r="J42" s="24">
-        <v>4</v>
-      </c>
-      <c r="K42" s="24">
-        <v>3</v>
-      </c>
-      <c r="L42" s="31">
+      <c r="J43" s="24">
+        <v>4</v>
+      </c>
+      <c r="K43" s="24">
+        <v>3</v>
+      </c>
+      <c r="L43" s="31">
         <f t="shared" ca="1" si="1"/>
         <v>3.5</v>
       </c>
-      <c r="M42" s="31" t="str">
+      <c r="M43" s="31" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N42" s="28" t="s">
+      <c r="N43" s="28" t="s">
         <v>284</v>
       </c>
-      <c r="O42" s="28"/>
-      <c r="P42" s="28" t="s">
+      <c r="O43" s="28"/>
+      <c r="P43" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="Q42" s="28"/>
-      <c r="R42" s="27" t="s">
+      <c r="Q43" s="28"/>
+      <c r="R43" s="27" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="20">
+    <row r="44" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="20">
         <v>148005</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="B44" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="C43" s="21" t="s">
+      <c r="C44" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="D43" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E43" s="22">
+      <c r="D44" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" s="22">
         <v>27329</v>
       </c>
-      <c r="F43" s="23">
+      <c r="F44" s="23">
         <f t="shared" ca="1" si="3"/>
         <v>52</v>
       </c>
-      <c r="G43" s="23">
+      <c r="G44" s="23">
         <f t="shared" ca="1" si="0"/>
         <v>2</v>
       </c>
-      <c r="H43" s="24">
-        <v>4</v>
-      </c>
-      <c r="I43" s="24">
-        <v>1</v>
-      </c>
-      <c r="J43" s="24">
-        <v>4</v>
-      </c>
-      <c r="K43" s="24">
-        <v>4</v>
-      </c>
-      <c r="L43" s="25">
+      <c r="H44" s="24">
+        <v>4</v>
+      </c>
+      <c r="I44" s="24">
+        <v>1</v>
+      </c>
+      <c r="J44" s="24">
+        <v>4</v>
+      </c>
+      <c r="K44" s="24">
+        <v>4</v>
+      </c>
+      <c r="L44" s="25">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M43" s="25" t="str">
+      <c r="M44" s="25" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N43" s="21" t="s">
+      <c r="N44" s="21" t="s">
         <v>284</v>
       </c>
-      <c r="O43" s="21"/>
-      <c r="P43" s="21" t="s">
+      <c r="O44" s="21"/>
+      <c r="P44" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="Q43" s="21"/>
-      <c r="R43" s="20" t="s">
+      <c r="Q44" s="21"/>
+      <c r="R44" s="20" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="7">
+    <row r="45" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="7">
         <v>267071</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B45" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C45" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="D44" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E44" s="10">
+      <c r="D45" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E45" s="10">
         <v>28726</v>
       </c>
-      <c r="F44" s="11">
+      <c r="F45" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>48</v>
       </c>
-      <c r="G44" s="11">
+      <c r="G45" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H44" s="12">
-        <v>4</v>
-      </c>
-      <c r="I44" s="12">
-        <v>1</v>
-      </c>
-      <c r="J44" s="12">
+      <c r="H45" s="12">
+        <v>4</v>
+      </c>
+      <c r="I45" s="12">
+        <v>1</v>
+      </c>
+      <c r="J45" s="12">
         <v>2</v>
       </c>
-      <c r="K44" s="12">
+      <c r="K45" s="12">
         <v>2</v>
       </c>
-      <c r="L44" s="13">
+      <c r="L45" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="M44" s="13" t="str">
+      <c r="M45" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N44" s="9" t="s">
+      <c r="N45" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="O44" s="9"/>
-      <c r="P44" s="9" t="s">
+      <c r="O45" s="9"/>
+      <c r="P45" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="Q44" s="9"/>
-      <c r="R44" s="7" t="s">
+      <c r="Q45" s="9"/>
+      <c r="R45" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="8">
+    <row r="46" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="8">
         <v>268051</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B46" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C46" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="D45" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E45" s="16">
+      <c r="D46" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E46" s="16">
         <v>37469</v>
       </c>
-      <c r="F45" s="17">
+      <c r="F46" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>24</v>
       </c>
-      <c r="G45" s="17">
+      <c r="G46" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H45" s="12">
-        <v>4</v>
-      </c>
-      <c r="I45" s="12">
+      <c r="H46" s="12">
+        <v>4</v>
+      </c>
+      <c r="I46" s="12">
         <v>5</v>
       </c>
-      <c r="J45" s="12">
+      <c r="J46" s="12">
         <v>2</v>
       </c>
-      <c r="K45" s="12">
+      <c r="K46" s="12">
         <v>2</v>
       </c>
-      <c r="L45" s="18">
+      <c r="L46" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="M45" s="18" t="str">
+      <c r="M46" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N45" s="15" t="s">
+      <c r="N46" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="O45" s="15"/>
-      <c r="P45" s="15" t="s">
+      <c r="O46" s="15"/>
+      <c r="P46" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="Q45" s="15"/>
-      <c r="R45" s="8" t="s">
+      <c r="Q46" s="15"/>
+      <c r="R46" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="7">
+    <row r="47" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="7">
         <v>269032</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B47" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C47" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D46" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E46" s="10">
+      <c r="D47" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" s="10">
         <v>30484</v>
       </c>
-      <c r="F46" s="11">
+      <c r="F47" s="11">
         <f t="shared" ca="1" si="3"/>
         <v>43</v>
       </c>
-      <c r="G46" s="11">
+      <c r="G47" s="11">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H46" s="12">
-        <v>4</v>
-      </c>
-      <c r="I46" s="12">
-        <v>3</v>
-      </c>
-      <c r="J46" s="12">
+      <c r="H47" s="12">
+        <v>4</v>
+      </c>
+      <c r="I47" s="12">
+        <v>3</v>
+      </c>
+      <c r="J47" s="12">
         <v>2</v>
       </c>
-      <c r="K46" s="12">
+      <c r="K47" s="12">
         <v>2</v>
       </c>
-      <c r="L46" s="13">
+      <c r="L47" s="13">
         <f t="shared" ca="1" si="1"/>
         <v>2.1</v>
       </c>
-      <c r="M46" s="13" t="str">
+      <c r="M47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N46" s="9" t="s">
+      <c r="N47" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="O46" s="9"/>
-      <c r="P46" s="9" t="s">
+      <c r="O47" s="9"/>
+      <c r="P47" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="Q46" s="9"/>
-      <c r="R46" s="7" t="s">
+      <c r="Q47" s="9"/>
+      <c r="R47" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="8">
+    <row r="48" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="8">
         <v>250051</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B48" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C48" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="D47" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E47" s="16">
+      <c r="D48" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E48" s="16">
         <v>29866</v>
       </c>
-      <c r="F47" s="17">
+      <c r="F48" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>45</v>
       </c>
-      <c r="G47" s="17">
+      <c r="G48" s="17">
         <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
-      <c r="H47" s="12">
-        <v>4</v>
-      </c>
-      <c r="I47" s="12">
-        <v>1</v>
-      </c>
-      <c r="J47" s="12">
+      <c r="H48" s="12">
+        <v>4</v>
+      </c>
+      <c r="I48" s="12">
+        <v>1</v>
+      </c>
+      <c r="J48" s="12">
         <v>2</v>
       </c>
-      <c r="K47" s="12">
+      <c r="K48" s="12">
         <v>2</v>
       </c>
-      <c r="L47" s="18">
+      <c r="L48" s="18">
         <f t="shared" ca="1" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="M47" s="18" t="str">
+      <c r="M48" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N47" s="15" t="s">
+      <c r="N48" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="O47" s="15" t="s">
+      <c r="O48" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="P47" s="15" t="s">
+      <c r="P48" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="Q47" s="15"/>
-      <c r="R47" s="8" t="s">
+      <c r="Q48" s="15"/>
+      <c r="R48" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="7">
+    <row r="49" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="7">
         <v>146037</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B49" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C49" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="D48" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E48" s="10" t="s">
+      <c r="D49" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E49" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="F48" s="11">
+      <c r="F49" s="11">
         <v>60</v>
       </c>
-      <c r="G48" s="11">
+      <c r="G49" s="11">
         <v>5</v>
-      </c>
-      <c r="H48" s="12">
-        <v>5</v>
-      </c>
-      <c r="I48" s="12">
-        <v>3</v>
-      </c>
-      <c r="J48" s="12">
-        <v>4</v>
-      </c>
-      <c r="K48" s="12">
-        <v>5</v>
-      </c>
-      <c r="L48" s="13">
-        <f t="shared" ref="L48:L67" si="6">IF(OR(I48="",J48="",K48="",G48=""),"",ROUND(G48*0.2+I48*0.3+J48*0.3+K48*0.2,2))</f>
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="M48" s="13" t="str">
-        <f t="shared" ref="M48:M67" si="7">IF(OR(H48="",L48=""),"",IF(AND(H48&gt;=4,L48&gt;=3.5),"High Impact + High Risk",IF(AND(H48&gt;=4,L48&lt;3.5),"High Impact + Low Risk",IF(AND(H48&lt;4,L48&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
-        <v>High Impact + High Risk</v>
-      </c>
-      <c r="N48" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="O48" s="9"/>
-      <c r="P48" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q48" s="9"/>
-      <c r="R48" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="8">
-        <v>139013</v>
-      </c>
-      <c r="B49" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="C49" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="D49" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="F49" s="17">
-        <v>58</v>
-      </c>
-      <c r="G49" s="17">
-        <v>4</v>
       </c>
       <c r="H49" s="12">
         <v>5</v>
@@ -5140,206 +5136,210 @@
       <c r="K49" s="12">
         <v>5</v>
       </c>
-      <c r="L49" s="18">
-        <f t="shared" si="6"/>
+      <c r="L49" s="13">
+        <f t="shared" ref="L49:L68" si="10">IF(OR(I49="",J49="",K49="",G49=""),"",ROUND(G49*0.2+I49*0.3+J49*0.3+K49*0.2,2))</f>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="M49" s="13" t="str">
+        <f t="shared" ref="M49:M68" si="11">IF(OR(H49="",L49=""),"",IF(AND(H49&gt;=4,L49&gt;=3.5),"High Impact + High Risk",IF(AND(H49&gt;=4,L49&lt;3.5),"High Impact + Low Risk",IF(AND(H49&lt;4,L49&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N49" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="O49" s="9"/>
+      <c r="P49" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q49" s="9"/>
+      <c r="R49" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="8">
+        <v>139013</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F50" s="17">
+        <v>58</v>
+      </c>
+      <c r="G50" s="17">
+        <v>4</v>
+      </c>
+      <c r="H50" s="12">
+        <v>5</v>
+      </c>
+      <c r="I50" s="12">
+        <v>3</v>
+      </c>
+      <c r="J50" s="12">
+        <v>4</v>
+      </c>
+      <c r="K50" s="12">
+        <v>5</v>
+      </c>
+      <c r="L50" s="18">
+        <f t="shared" si="10"/>
         <v>3.9</v>
       </c>
-      <c r="M49" s="18" t="str">
-        <f t="shared" si="7"/>
+      <c r="M50" s="18" t="str">
+        <f t="shared" si="11"/>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N49" s="15" t="s">
+      <c r="N50" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="O49" s="15" t="s">
+      <c r="O50" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="P49" s="15" t="s">
+      <c r="P50" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="Q49" s="15"/>
-      <c r="R49" s="8" t="s">
+      <c r="Q50" s="15"/>
+      <c r="R50" s="8" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="7">
+    <row r="51" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="7">
         <v>145015</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B51" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C51" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="D50" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E50" s="10" t="s">
+      <c r="D51" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E51" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="F50" s="11">
+      <c r="F51" s="11">
         <v>50</v>
       </c>
-      <c r="G50" s="11">
+      <c r="G51" s="11">
         <v>2</v>
       </c>
-      <c r="H50" s="12">
-        <v>4</v>
-      </c>
-      <c r="I50" s="12">
-        <v>3</v>
-      </c>
-      <c r="J50" s="12">
-        <v>4</v>
-      </c>
-      <c r="K50" s="12">
-        <v>4</v>
-      </c>
-      <c r="L50" s="13">
-        <f t="shared" si="6"/>
+      <c r="H51" s="12">
+        <v>4</v>
+      </c>
+      <c r="I51" s="12">
+        <v>3</v>
+      </c>
+      <c r="J51" s="12">
+        <v>4</v>
+      </c>
+      <c r="K51" s="12">
+        <v>4</v>
+      </c>
+      <c r="L51" s="13">
+        <f t="shared" si="10"/>
         <v>3.3</v>
       </c>
-      <c r="M50" s="13" t="str">
-        <f t="shared" si="7"/>
+      <c r="M51" s="13" t="str">
+        <f t="shared" si="11"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N50" s="9" t="s">
+      <c r="N51" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="O50" s="9"/>
-      <c r="P50" s="9" t="s">
+      <c r="O51" s="9"/>
+      <c r="P51" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="Q50" s="9"/>
-      <c r="R50" s="7" t="s">
+      <c r="Q51" s="9"/>
+      <c r="R51" s="7" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="8">
+    <row r="52" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="8">
         <v>161005</v>
       </c>
-      <c r="B51" s="15" t="s">
+      <c r="B52" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C52" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="D51" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E51" s="16" t="s">
+      <c r="D52" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="F51" s="17">
+      <c r="F52" s="17">
         <v>45</v>
       </c>
-      <c r="G51" s="17">
-        <v>1</v>
-      </c>
-      <c r="H51" s="12">
+      <c r="G52" s="17">
+        <v>1</v>
+      </c>
+      <c r="H52" s="12">
         <v>2</v>
       </c>
-      <c r="I51" s="12">
-        <v>1</v>
-      </c>
-      <c r="J51" s="12">
-        <v>3</v>
-      </c>
-      <c r="K51" s="12">
-        <v>3</v>
-      </c>
-      <c r="L51" s="18">
-        <f t="shared" si="6"/>
+      <c r="I52" s="12">
+        <v>1</v>
+      </c>
+      <c r="J52" s="12">
+        <v>3</v>
+      </c>
+      <c r="K52" s="12">
+        <v>3</v>
+      </c>
+      <c r="L52" s="18">
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="M51" s="18" t="str">
-        <f t="shared" si="7"/>
+      <c r="M52" s="18" t="str">
+        <f t="shared" si="11"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N51" s="15"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="15"/>
-      <c r="R51" s="8" t="s">
+      <c r="N52" s="15"/>
+      <c r="O52" s="15"/>
+      <c r="P52" s="15"/>
+      <c r="Q52" s="15"/>
+      <c r="R52" s="8" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="7">
+    <row r="53" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="7">
         <v>163003</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B53" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C53" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="D52" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E52" s="10" t="s">
+      <c r="D53" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E53" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="F52" s="11">
+      <c r="F53" s="11">
         <v>34</v>
       </c>
-      <c r="G52" s="11">
-        <v>1</v>
-      </c>
-      <c r="H52" s="12">
-        <v>3</v>
-      </c>
-      <c r="I52" s="12">
-        <v>3</v>
-      </c>
-      <c r="J52" s="12">
-        <v>2</v>
-      </c>
-      <c r="K52" s="12">
-        <v>3</v>
-      </c>
-      <c r="L52" s="13">
-        <f t="shared" si="6"/>
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="M52" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N52" s="9"/>
-      <c r="O52" s="9"/>
-      <c r="P52" s="9"/>
-      <c r="Q52" s="9"/>
-      <c r="R52" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="8">
-        <v>166024</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E53" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="F53" s="17">
-        <v>27</v>
-      </c>
-      <c r="G53" s="17">
+      <c r="G53" s="11">
         <v>1</v>
       </c>
       <c r="H53" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I53" s="12">
         <v>3</v>
@@ -5350,533 +5350,533 @@
       <c r="K53" s="12">
         <v>3</v>
       </c>
-      <c r="L53" s="18">
-        <f t="shared" si="6"/>
+      <c r="L53" s="13">
+        <f t="shared" si="10"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="M53" s="18" t="str">
-        <f t="shared" si="7"/>
+      <c r="M53" s="13" t="str">
+        <f t="shared" si="11"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N53" s="15"/>
-      <c r="O53" s="15"/>
-      <c r="P53" s="15"/>
-      <c r="Q53" s="15"/>
-      <c r="R53" s="8" t="s">
+      <c r="N53" s="9"/>
+      <c r="O53" s="9"/>
+      <c r="P53" s="9"/>
+      <c r="Q53" s="9"/>
+      <c r="R53" s="7" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="54" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="7">
+      <c r="A54" s="8">
+        <v>166024</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E54" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="F54" s="17">
+        <v>27</v>
+      </c>
+      <c r="G54" s="17">
+        <v>1</v>
+      </c>
+      <c r="H54" s="12">
+        <v>2</v>
+      </c>
+      <c r="I54" s="12">
+        <v>3</v>
+      </c>
+      <c r="J54" s="12">
+        <v>2</v>
+      </c>
+      <c r="K54" s="12">
+        <v>3</v>
+      </c>
+      <c r="L54" s="18">
+        <f t="shared" si="10"/>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M54" s="18" t="str">
+        <f t="shared" si="11"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N54" s="15"/>
+      <c r="O54" s="15"/>
+      <c r="P54" s="15"/>
+      <c r="Q54" s="15"/>
+      <c r="R54" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="7">
         <v>167001</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B55" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="C55" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="D54" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E54" s="10" t="s">
+      <c r="D55" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E55" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F54" s="11">
+      <c r="F55" s="11">
         <v>37</v>
       </c>
-      <c r="G54" s="11">
-        <v>1</v>
-      </c>
-      <c r="H54" s="12">
-        <v>3</v>
-      </c>
-      <c r="I54" s="12">
+      <c r="G55" s="11">
+        <v>1</v>
+      </c>
+      <c r="H55" s="12">
+        <v>3</v>
+      </c>
+      <c r="I55" s="12">
         <v>5</v>
       </c>
-      <c r="J54" s="12">
-        <v>3</v>
-      </c>
-      <c r="K54" s="12">
-        <v>3</v>
-      </c>
-      <c r="L54" s="13">
-        <f t="shared" si="6"/>
+      <c r="J55" s="12">
+        <v>3</v>
+      </c>
+      <c r="K55" s="12">
+        <v>3</v>
+      </c>
+      <c r="L55" s="13">
+        <f t="shared" si="10"/>
         <v>3.2</v>
       </c>
-      <c r="M54" s="13" t="str">
-        <f t="shared" si="7"/>
+      <c r="M55" s="13" t="str">
+        <f t="shared" si="11"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N54" s="9"/>
-      <c r="O54" s="9"/>
-      <c r="P54" s="9"/>
-      <c r="Q54" s="9"/>
-      <c r="R54" s="7" t="s">
+      <c r="N55" s="9"/>
+      <c r="O55" s="9"/>
+      <c r="P55" s="9"/>
+      <c r="Q55" s="9"/>
+      <c r="R55" s="7" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="8">
+    <row r="56" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="8">
         <v>167012</v>
       </c>
-      <c r="B55" s="15" t="s">
+      <c r="B56" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="C56" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="D55" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E55" s="16" t="s">
+      <c r="D56" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E56" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="F55" s="17">
+      <c r="F56" s="17">
         <v>31</v>
       </c>
-      <c r="G55" s="17">
-        <v>1</v>
-      </c>
-      <c r="H55" s="12">
+      <c r="G56" s="17">
+        <v>1</v>
+      </c>
+      <c r="H56" s="12">
         <v>2</v>
       </c>
-      <c r="I55" s="12">
-        <v>3</v>
-      </c>
-      <c r="J55" s="12">
-        <v>3</v>
-      </c>
-      <c r="K55" s="12">
-        <v>3</v>
-      </c>
-      <c r="L55" s="18">
-        <f t="shared" si="6"/>
+      <c r="I56" s="12">
+        <v>3</v>
+      </c>
+      <c r="J56" s="12">
+        <v>3</v>
+      </c>
+      <c r="K56" s="12">
+        <v>3</v>
+      </c>
+      <c r="L56" s="18">
+        <f t="shared" si="10"/>
         <v>2.6</v>
       </c>
-      <c r="M55" s="18" t="str">
-        <f t="shared" si="7"/>
+      <c r="M56" s="18" t="str">
+        <f t="shared" si="11"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N55" s="15"/>
-      <c r="O55" s="15"/>
-      <c r="P55" s="15"/>
-      <c r="Q55" s="15"/>
-      <c r="R55" s="8" t="s">
+      <c r="N56" s="15"/>
+      <c r="O56" s="15"/>
+      <c r="P56" s="15"/>
+      <c r="Q56" s="15"/>
+      <c r="R56" s="8" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="7">
+    <row r="57" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="7">
         <v>260001</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B57" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="C56" s="9" t="s">
+      <c r="C57" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="D56" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E56" s="10" t="s">
+      <c r="D57" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E57" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="F56" s="11">
+      <c r="F57" s="11">
         <v>35</v>
       </c>
-      <c r="G56" s="11">
-        <v>1</v>
-      </c>
-      <c r="H56" s="12">
+      <c r="G57" s="11">
+        <v>1</v>
+      </c>
+      <c r="H57" s="12">
         <v>5</v>
       </c>
-      <c r="I56" s="12">
-        <v>4</v>
-      </c>
-      <c r="J56" s="12">
-        <v>4</v>
-      </c>
-      <c r="K56" s="12">
+      <c r="I57" s="12">
+        <v>4</v>
+      </c>
+      <c r="J57" s="12">
+        <v>4</v>
+      </c>
+      <c r="K57" s="12">
         <v>5</v>
       </c>
-      <c r="L56" s="13">
-        <f t="shared" si="6"/>
+      <c r="L57" s="13">
+        <f t="shared" si="10"/>
         <v>3.6</v>
       </c>
-      <c r="M56" s="13" t="str">
-        <f t="shared" si="7"/>
+      <c r="M57" s="13" t="str">
+        <f t="shared" si="11"/>
         <v>High Impact + High Risk</v>
       </c>
-      <c r="N56" s="9" t="s">
+      <c r="N57" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="O56" s="9"/>
-      <c r="P56" s="9" t="s">
+      <c r="O57" s="9"/>
+      <c r="P57" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="Q56" s="9"/>
-      <c r="R56" s="7" t="s">
+      <c r="Q57" s="9"/>
+      <c r="R57" s="7" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="8">
+    <row r="58" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="8">
         <v>267001</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B58" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C58" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="D57" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E57" s="16" t="s">
+      <c r="D58" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E58" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="F57" s="17">
+      <c r="F58" s="17">
         <v>31</v>
       </c>
-      <c r="G57" s="17">
-        <v>1</v>
-      </c>
-      <c r="H57" s="12">
-        <v>3</v>
-      </c>
-      <c r="I57" s="12">
-        <v>4</v>
-      </c>
-      <c r="J57" s="12">
-        <v>3</v>
-      </c>
-      <c r="K57" s="12">
-        <v>3</v>
-      </c>
-      <c r="L57" s="18">
-        <f t="shared" si="6"/>
+      <c r="G58" s="17">
+        <v>1</v>
+      </c>
+      <c r="H58" s="12">
+        <v>3</v>
+      </c>
+      <c r="I58" s="12">
+        <v>4</v>
+      </c>
+      <c r="J58" s="12">
+        <v>3</v>
+      </c>
+      <c r="K58" s="12">
+        <v>3</v>
+      </c>
+      <c r="L58" s="18">
+        <f t="shared" si="10"/>
         <v>2.9</v>
       </c>
-      <c r="M57" s="18" t="str">
-        <f t="shared" si="7"/>
+      <c r="M58" s="18" t="str">
+        <f t="shared" si="11"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N57" s="15"/>
-      <c r="O57" s="15"/>
-      <c r="P57" s="15"/>
-      <c r="Q57" s="15"/>
-      <c r="R57" s="8" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="7">
-        <v>160001</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F58" s="11">
-        <v>46</v>
-      </c>
-      <c r="G58" s="11">
-        <v>1</v>
-      </c>
-      <c r="H58" s="12">
-        <v>4</v>
-      </c>
-      <c r="I58" s="12">
-        <v>3</v>
-      </c>
-      <c r="J58" s="12">
-        <v>4</v>
-      </c>
-      <c r="K58" s="12">
-        <v>4</v>
-      </c>
-      <c r="L58" s="13">
-        <f t="shared" si="6"/>
-        <v>3.1</v>
-      </c>
-      <c r="M58" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N58" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="O58" s="9"/>
-      <c r="P58" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q58" s="9"/>
-      <c r="R58" s="7" t="s">
+      <c r="N58" s="15"/>
+      <c r="O58" s="15"/>
+      <c r="P58" s="15"/>
+      <c r="Q58" s="15"/>
+      <c r="R58" s="8" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="59" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
-        <v>167020</v>
+        <v>160001</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>90</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F59" s="11">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G59" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I59" s="12">
         <v>3</v>
       </c>
       <c r="J59" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K59" s="12">
         <v>4</v>
       </c>
       <c r="L59" s="13">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" si="10"/>
+        <v>3.1</v>
       </c>
       <c r="M59" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N59" s="9"/>
+        <f t="shared" si="11"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N59" s="9" t="s">
+        <v>284</v>
+      </c>
       <c r="O59" s="9"/>
-      <c r="P59" s="9"/>
+      <c r="P59" s="9" t="s">
+        <v>279</v>
+      </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="7" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="60" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="8">
+      <c r="A60" s="7">
+        <v>167020</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="F60" s="11">
+        <v>51</v>
+      </c>
+      <c r="G60" s="11">
+        <v>2</v>
+      </c>
+      <c r="H60" s="12">
+        <v>3</v>
+      </c>
+      <c r="I60" s="12">
+        <v>3</v>
+      </c>
+      <c r="J60" s="12">
+        <v>3</v>
+      </c>
+      <c r="K60" s="12">
+        <v>4</v>
+      </c>
+      <c r="L60" s="13">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="M60" s="13" t="str">
+        <f t="shared" si="11"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N60" s="9"/>
+      <c r="O60" s="9"/>
+      <c r="P60" s="9"/>
+      <c r="Q60" s="9"/>
+      <c r="R60" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="8">
         <v>167029</v>
       </c>
-      <c r="B60" s="15" t="s">
+      <c r="B61" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C61" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="D60" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E60" s="16" t="s">
+      <c r="D61" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E61" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="F60" s="17">
+      <c r="F61" s="17">
         <v>35</v>
       </c>
-      <c r="G60" s="17">
-        <v>1</v>
-      </c>
-      <c r="H60" s="12">
+      <c r="G61" s="17">
+        <v>1</v>
+      </c>
+      <c r="H61" s="12">
         <v>5</v>
       </c>
-      <c r="I60" s="12">
-        <v>3</v>
-      </c>
-      <c r="J60" s="12">
-        <v>4</v>
-      </c>
-      <c r="K60" s="12">
+      <c r="I61" s="12">
+        <v>3</v>
+      </c>
+      <c r="J61" s="12">
+        <v>4</v>
+      </c>
+      <c r="K61" s="12">
         <v>5</v>
       </c>
-      <c r="L60" s="18">
-        <f t="shared" si="6"/>
+      <c r="L61" s="18">
+        <f t="shared" si="10"/>
         <v>3.3</v>
       </c>
-      <c r="M60" s="18" t="str">
-        <f t="shared" si="7"/>
+      <c r="M61" s="18" t="str">
+        <f t="shared" si="11"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N60" s="15" t="s">
+      <c r="N61" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="O60" s="15"/>
-      <c r="P60" s="15" t="s">
+      <c r="O61" s="15"/>
+      <c r="P61" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="Q60" s="15"/>
-      <c r="R60" s="8" t="s">
+      <c r="Q61" s="15"/>
+      <c r="R61" s="8" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="7">
+    <row r="62" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="7">
         <v>167032</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B62" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C62" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="D61" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E61" s="10" t="s">
+      <c r="D62" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E62" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="F61" s="11">
+      <c r="F62" s="11">
         <v>29</v>
       </c>
-      <c r="G61" s="11">
-        <v>1</v>
-      </c>
-      <c r="H61" s="12">
-        <v>3</v>
-      </c>
-      <c r="I61" s="12">
+      <c r="G62" s="11">
+        <v>1</v>
+      </c>
+      <c r="H62" s="12">
+        <v>3</v>
+      </c>
+      <c r="I62" s="12">
         <v>5</v>
       </c>
-      <c r="J61" s="12">
-        <v>3</v>
-      </c>
-      <c r="K61" s="12">
-        <v>3</v>
-      </c>
-      <c r="L61" s="13">
-        <f t="shared" si="6"/>
+      <c r="J62" s="12">
+        <v>3</v>
+      </c>
+      <c r="K62" s="12">
+        <v>3</v>
+      </c>
+      <c r="L62" s="13">
+        <f t="shared" si="10"/>
         <v>3.2</v>
       </c>
-      <c r="M61" s="13" t="str">
-        <f t="shared" si="7"/>
+      <c r="M62" s="13" t="str">
+        <f t="shared" si="11"/>
         <v>Low Impact + Low Risk</v>
       </c>
-      <c r="N61" s="9"/>
-      <c r="O61" s="9"/>
-      <c r="P61" s="9"/>
-      <c r="Q61" s="9"/>
-      <c r="R61" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="8">
-        <v>168024</v>
-      </c>
-      <c r="B62" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="C62" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="D62" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E62" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="F62" s="17">
-        <v>46</v>
-      </c>
-      <c r="G62" s="17">
-        <v>1</v>
-      </c>
-      <c r="H62" s="12">
-        <v>5</v>
-      </c>
-      <c r="I62" s="12">
-        <v>3</v>
-      </c>
-      <c r="J62" s="12">
-        <v>4</v>
-      </c>
-      <c r="K62" s="12">
-        <v>5</v>
-      </c>
-      <c r="L62" s="18">
-        <f t="shared" si="6"/>
-        <v>3.3</v>
-      </c>
-      <c r="M62" s="18" t="str">
-        <f t="shared" si="7"/>
-        <v>High Impact + Low Risk</v>
-      </c>
-      <c r="N62" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="O62" s="15"/>
-      <c r="P62" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q62" s="15"/>
-      <c r="R62" s="8" t="s">
+      <c r="N62" s="9"/>
+      <c r="O62" s="9"/>
+      <c r="P62" s="9"/>
+      <c r="Q62" s="9"/>
+      <c r="R62" s="7" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="63" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="8">
-        <v>337004</v>
+        <v>168024</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D63" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F63" s="17">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="G63" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H63" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I63" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J63" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K63" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L63" s="18">
-        <f t="shared" si="6"/>
-        <v>2.6</v>
+        <f t="shared" si="10"/>
+        <v>3.3</v>
       </c>
       <c r="M63" s="18" t="str">
-        <f t="shared" si="7"/>
-        <v>Low Impact + Low Risk</v>
-      </c>
-      <c r="N63" s="15"/>
+        <f t="shared" si="11"/>
+        <v>High Impact + Low Risk</v>
+      </c>
+      <c r="N63" s="15" t="s">
+        <v>284</v>
+      </c>
       <c r="O63" s="15"/>
-      <c r="P63" s="15"/>
+      <c r="P63" s="15" t="s">
+        <v>281</v>
+      </c>
       <c r="Q63" s="15"/>
       <c r="R63" s="8" t="s">
         <v>242</v>
@@ -5884,44 +5884,44 @@
     </row>
     <row r="64" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="8">
-        <v>268044</v>
+        <v>337004</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D64" s="15" t="s">
         <v>90</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F64" s="17">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="G64" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H64" s="12">
         <v>3</v>
       </c>
       <c r="I64" s="12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J64" s="12">
         <v>3</v>
       </c>
       <c r="K64" s="12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L64" s="18">
-        <f t="shared" si="6"/>
-        <v>2.9</v>
+        <f t="shared" si="10"/>
+        <v>2.6</v>
       </c>
       <c r="M64" s="18" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>Low Impact + Low Risk</v>
       </c>
       <c r="N64" s="15"/>
@@ -5933,99 +5933,95 @@
       </c>
     </row>
     <row r="65" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="7">
+      <c r="A65" s="8">
+        <v>268044</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="F65" s="17">
+        <v>28</v>
+      </c>
+      <c r="G65" s="17">
+        <v>1</v>
+      </c>
+      <c r="H65" s="12">
+        <v>3</v>
+      </c>
+      <c r="I65" s="12">
+        <v>4</v>
+      </c>
+      <c r="J65" s="12">
+        <v>3</v>
+      </c>
+      <c r="K65" s="12">
+        <v>3</v>
+      </c>
+      <c r="L65" s="18">
+        <f t="shared" si="10"/>
+        <v>2.9</v>
+      </c>
+      <c r="M65" s="18" t="str">
+        <f t="shared" si="11"/>
+        <v>Low Impact + Low Risk</v>
+      </c>
+      <c r="N65" s="15"/>
+      <c r="O65" s="15"/>
+      <c r="P65" s="15"/>
+      <c r="Q65" s="15"/>
+      <c r="R65" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="7">
         <v>368004</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B66" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="C65" s="9" t="s">
+      <c r="C66" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="D65" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E65" s="10" t="s">
+      <c r="D66" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E66" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="F65" s="11">
+      <c r="F66" s="11">
         <v>59</v>
       </c>
-      <c r="G65" s="11">
-        <v>4</v>
-      </c>
-      <c r="H65" s="12">
-        <v>4</v>
-      </c>
-      <c r="I65" s="12">
-        <v>3</v>
-      </c>
-      <c r="J65" s="12">
-        <v>4</v>
-      </c>
-      <c r="K65" s="12">
-        <v>4</v>
-      </c>
-      <c r="L65" s="13">
-        <f t="shared" si="6"/>
+      <c r="G66" s="11">
+        <v>4</v>
+      </c>
+      <c r="H66" s="12">
+        <v>4</v>
+      </c>
+      <c r="I66" s="12">
+        <v>3</v>
+      </c>
+      <c r="J66" s="12">
+        <v>4</v>
+      </c>
+      <c r="K66" s="12">
+        <v>4</v>
+      </c>
+      <c r="L66" s="13">
+        <f t="shared" si="10"/>
         <v>3.7</v>
       </c>
-      <c r="M65" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>High Impact + High Risk</v>
-      </c>
-      <c r="N65" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="O65" s="9"/>
-      <c r="P65" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q65" s="9"/>
-      <c r="R65" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="F66" s="11">
-        <v>55</v>
-      </c>
-      <c r="G66" s="11">
-        <v>3</v>
-      </c>
-      <c r="H66" s="12">
-        <v>4</v>
-      </c>
-      <c r="I66" s="12">
-        <v>4</v>
-      </c>
-      <c r="J66" s="12">
-        <v>4</v>
-      </c>
-      <c r="K66" s="12">
-        <v>4</v>
-      </c>
-      <c r="L66" s="13">
-        <f t="shared" si="6"/>
-        <v>3.8</v>
-      </c>
       <c r="M66" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>High Impact + High Risk</v>
       </c>
       <c r="N66" s="9" t="s">
@@ -6033,198 +6029,252 @@
       </c>
       <c r="O66" s="9"/>
       <c r="P66" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q66" s="9"/>
       <c r="R66" s="7" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="67" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="20">
+    <row r="67" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="F67" s="11">
+        <v>55</v>
+      </c>
+      <c r="G67" s="11">
+        <v>3</v>
+      </c>
+      <c r="H67" s="12">
+        <v>4</v>
+      </c>
+      <c r="I67" s="12">
+        <v>4</v>
+      </c>
+      <c r="J67" s="12">
+        <v>4</v>
+      </c>
+      <c r="K67" s="12">
+        <v>4</v>
+      </c>
+      <c r="L67" s="13">
+        <f t="shared" si="10"/>
+        <v>3.8</v>
+      </c>
+      <c r="M67" s="13" t="str">
+        <f t="shared" si="11"/>
+        <v>High Impact + High Risk</v>
+      </c>
+      <c r="N67" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="O67" s="9"/>
+      <c r="P67" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q67" s="9"/>
+      <c r="R67" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="20">
         <v>168016</v>
       </c>
-      <c r="B67" s="21" t="s">
+      <c r="B68" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="C67" s="21" t="s">
+      <c r="C68" s="21" t="s">
         <v>244</v>
       </c>
-      <c r="D67" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E67" s="22" t="s">
+      <c r="D68" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E68" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="F67" s="23">
+      <c r="F68" s="23">
         <v>35</v>
       </c>
-      <c r="G67" s="23">
-        <v>1</v>
-      </c>
-      <c r="H67" s="24">
-        <v>4</v>
-      </c>
-      <c r="I67" s="24">
-        <v>3</v>
-      </c>
-      <c r="J67" s="24">
-        <v>4</v>
-      </c>
-      <c r="K67" s="24">
-        <v>1</v>
-      </c>
-      <c r="L67" s="25">
-        <f t="shared" si="6"/>
+      <c r="G68" s="23">
+        <v>1</v>
+      </c>
+      <c r="H68" s="24">
+        <v>4</v>
+      </c>
+      <c r="I68" s="24">
+        <v>3</v>
+      </c>
+      <c r="J68" s="24">
+        <v>4</v>
+      </c>
+      <c r="K68" s="24">
+        <v>1</v>
+      </c>
+      <c r="L68" s="25">
+        <f t="shared" si="10"/>
         <v>2.5</v>
       </c>
-      <c r="M67" s="25" t="str">
-        <f t="shared" si="7"/>
+      <c r="M68" s="25" t="str">
+        <f t="shared" si="11"/>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N67" s="21" t="s">
+      <c r="N68" s="21" t="s">
         <v>284</v>
       </c>
-      <c r="O67" s="21" t="s">
+      <c r="O68" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="P67" s="21" t="s">
+      <c r="P68" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="Q67" s="21"/>
-      <c r="R67" s="20" t="s">
+      <c r="Q68" s="21"/>
+      <c r="R68" s="20" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="68" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="8">
+    <row r="69" spans="1:18" s="14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="8">
         <v>258026</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B69" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="C68" s="15" t="s">
+      <c r="C69" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="D68" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E68" s="16" t="s">
+      <c r="D69" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E69" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="F68" s="17">
+      <c r="F69" s="17">
         <v>42</v>
       </c>
-      <c r="G68" s="17">
-        <v>1</v>
-      </c>
-      <c r="H68" s="12">
-        <v>4</v>
-      </c>
-      <c r="I68" s="12">
-        <v>3</v>
-      </c>
-      <c r="J68" s="12">
-        <v>4</v>
-      </c>
-      <c r="K68" s="12">
-        <v>3</v>
-      </c>
-      <c r="L68" s="18">
-        <f t="shared" ref="L68" si="8">IF(OR(I68="",J68="",K68="",G68=""),"",ROUND(G68*0.2+I68*0.3+J68*0.3+K68*0.2,2))</f>
+      <c r="G69" s="17">
+        <v>1</v>
+      </c>
+      <c r="H69" s="12">
+        <v>4</v>
+      </c>
+      <c r="I69" s="12">
+        <v>3</v>
+      </c>
+      <c r="J69" s="12">
+        <v>4</v>
+      </c>
+      <c r="K69" s="12">
+        <v>3</v>
+      </c>
+      <c r="L69" s="18">
+        <f t="shared" ref="L69" si="12">IF(OR(I69="",J69="",K69="",G69=""),"",ROUND(G69*0.2+I69*0.3+J69*0.3+K69*0.2,2))</f>
         <v>2.9</v>
       </c>
-      <c r="M68" s="18" t="str">
-        <f t="shared" ref="M68" si="9">IF(OR(H68="",L68=""),"",IF(AND(H68&gt;=4,L68&gt;=3.5),"High Impact + High Risk",IF(AND(H68&gt;=4,L68&lt;3.5),"High Impact + Low Risk",IF(AND(H68&lt;4,L68&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
+      <c r="M69" s="18" t="str">
+        <f t="shared" ref="M69" si="13">IF(OR(H69="",L69=""),"",IF(AND(H69&gt;=4,L69&gt;=3.5),"High Impact + High Risk",IF(AND(H69&gt;=4,L69&lt;3.5),"High Impact + Low Risk",IF(AND(H69&lt;4,L69&gt;=3.5),"Low Impact + High Risk","Low Impact + Low Risk"))))</f>
         <v>High Impact + Low Risk</v>
       </c>
-      <c r="N68" s="15" t="s">
+      <c r="N69" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="O68" s="15" t="s">
+      <c r="O69" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="P68" s="15" t="s">
+      <c r="P69" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="Q68" s="15"/>
-      <c r="R68" s="8" t="s">
+      <c r="Q69" s="15"/>
+      <c r="R69" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A69" s="62" t="s">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A70" s="45" t="s">
+        <v>290</v>
+      </c>
+      <c r="B70" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="C70" s="47" t="s">
         <v>291</v>
       </c>
-      <c r="B69" s="63" t="s">
-        <v>294</v>
-      </c>
-      <c r="C69" s="64" t="s">
+      <c r="D70" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E70" s="48" t="s">
         <v>292</v>
       </c>
-      <c r="D69" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E69" s="65" t="s">
-        <v>293</v>
-      </c>
-      <c r="F69" s="17">
-        <f t="shared" ref="F69" ca="1" si="10">DATEDIF(E69,TODAY(),"Y")</f>
+      <c r="F70" s="17">
+        <f t="shared" ref="F70" ca="1" si="14">DATEDIF(E70,TODAY(),"Y")</f>
         <v>52</v>
       </c>
-      <c r="G69" s="17">
-        <f t="shared" ref="G69" ca="1" si="11">IF(F69="","",IF(F69&lt;50,1,IF(F69&lt;55,2,IF(F69&lt;58,3,IF(F69&lt;60,4,5)))))</f>
+      <c r="G70" s="17">
+        <f t="shared" ref="G70" ca="1" si="15">IF(F70="","",IF(F70&lt;50,1,IF(F70&lt;55,2,IF(F70&lt;58,3,IF(F70&lt;60,4,5)))))</f>
         <v>2</v>
       </c>
-      <c r="H69" s="12">
-        <v>4</v>
-      </c>
-      <c r="I69" s="12">
+      <c r="H70" s="12">
+        <v>4</v>
+      </c>
+      <c r="I70" s="12">
         <v>5</v>
       </c>
-      <c r="J69" s="12">
-        <v>4</v>
-      </c>
-      <c r="K69" s="12">
+      <c r="J70" s="12">
+        <v>4</v>
+      </c>
+      <c r="K70" s="12">
         <v>5</v>
       </c>
-      <c r="L69" s="13">
+      <c r="L70" s="13">
         <v>3.9</v>
       </c>
-      <c r="M69" s="13" t="s">
+      <c r="M70" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="N69" s="9" t="s">
+      <c r="N70" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="O69" s="9" t="s">
+      <c r="O70" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="P69" s="9"/>
-      <c r="Q69" s="9"/>
-      <c r="R69" s="7" t="s">
+      <c r="P70" s="9"/>
+      <c r="Q70" s="9"/>
+      <c r="R70" s="7" t="s">
         <v>122</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:R69" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:R70" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A69">
+  <conditionalFormatting sqref="A70">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="J3:K48 H3:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H3:H49 J3:K49" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"1,2,3,4,5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I3:I48" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I3:I49" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1,3,5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="O3:O47" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="O3:O48" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Ready Now,Ready in 1 Year,Ready in 3 Years,No Successor"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{89C05139-767C-4D44-95FE-72D2855E25B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{915993F0-8F33-4790-88A3-88B85F5FCDBA}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{89C05139-767C-4D44-95FE-72D2855E25B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{205631E2-A73D-4853-93AD-8EA954E0468A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="295">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -920,6 +920,9 @@
   </si>
   <si>
     <t>รักษาการ</t>
+  </si>
+  <si>
+    <t>268029 B_Department Manager_Batch &amp; Furnace.docx</t>
   </si>
 </sst>
 </file>
@@ -1416,19 +1419,43 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1439,30 +1466,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1759,693 +1762,727 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="64" t="s">
+      <c r="B4" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="65" t="s">
+      <c r="C8" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="65"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="54" t="s">
+      <c r="C11" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="54" t="s">
+      <c r="C13" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="52" t="s">
+      <c r="B22" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="52"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="58" t="s">
+      <c r="B23" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="59" t="s">
+      <c r="B25" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="60"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="60"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="61"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="62" t="s">
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="62"/>
+      <c r="G26" s="59"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="61" t="s">
+      <c r="B27" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="61"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="61"/>
-      <c r="F27" s="62" t="s">
+      <c r="C27" s="58"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="62"/>
+      <c r="G27" s="59"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="61" t="s">
+      <c r="B28" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="61"/>
-      <c r="D28" s="61"/>
-      <c r="E28" s="61"/>
-      <c r="F28" s="62" t="s">
+      <c r="C28" s="58"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="62"/>
+      <c r="G28" s="59"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
-      <c r="E29" s="61"/>
-      <c r="F29" s="62" t="s">
+      <c r="C29" s="58"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="62"/>
+      <c r="G29" s="59"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="62" t="s">
+      <c r="C30" s="58"/>
+      <c r="D30" s="58"/>
+      <c r="E30" s="58"/>
+      <c r="F30" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="62"/>
+      <c r="G30" s="59"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="58" t="s">
+      <c r="B32" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="58"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="58"/>
+      <c r="C32" s="57"/>
+      <c r="D32" s="57"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="57"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="54" t="s">
+      <c r="C33" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="54" t="s">
+      <c r="C34" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="54"/>
-      <c r="E34" s="54"/>
-      <c r="F34" s="54"/>
-      <c r="G34" s="54"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="56"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="54" t="s">
+      <c r="C35" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="54"/>
-      <c r="E35" s="54"/>
-      <c r="F35" s="54"/>
-      <c r="G35" s="54"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="58" t="s">
+      <c r="B37" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="58"/>
-      <c r="D37" s="58"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="58"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="54" t="s">
+      <c r="C38" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="54"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="54"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="54" t="s">
+      <c r="C39" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="54"/>
-      <c r="E39" s="54"/>
-      <c r="F39" s="54"/>
-      <c r="G39" s="54"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="54" t="s">
+      <c r="C40" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="54"/>
-      <c r="E40" s="54"/>
-      <c r="F40" s="54"/>
-      <c r="G40" s="54"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="56"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="54" t="s">
+      <c r="C41" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="54"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="54"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="56"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="54" t="s">
+      <c r="C42" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="54"/>
-      <c r="E42" s="54"/>
-      <c r="F42" s="54"/>
-      <c r="G42" s="54"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="56"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="58" t="s">
+      <c r="B44" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="58"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="54" t="s">
+      <c r="C45" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="54"/>
-      <c r="E45" s="54"/>
-      <c r="F45" s="54"/>
-      <c r="G45" s="54"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="56"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="56"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="54" t="s">
+      <c r="C46" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="54"/>
-      <c r="E46" s="54"/>
-      <c r="F46" s="54"/>
-      <c r="G46" s="54"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="56"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="54" t="s">
+      <c r="C47" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="54"/>
-      <c r="E47" s="54"/>
-      <c r="F47" s="54"/>
-      <c r="G47" s="54"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56"/>
+      <c r="F47" s="56"/>
+      <c r="G47" s="56"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="54" t="s">
+      <c r="C48" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="54"/>
-      <c r="E48" s="54"/>
-      <c r="F48" s="54"/>
-      <c r="G48" s="54"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="56"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="56"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="54" t="s">
+      <c r="C49" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="54"/>
-      <c r="E49" s="54"/>
-      <c r="F49" s="54"/>
-      <c r="G49" s="54"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="56"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="52" t="s">
+      <c r="B51" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="52"/>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="52"/>
-      <c r="G51" s="52"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="59" t="s">
+      <c r="B52" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="59"/>
-      <c r="D52" s="59"/>
-      <c r="E52" s="59"/>
-      <c r="F52" s="59"/>
-      <c r="G52" s="59"/>
+      <c r="C52" s="60"/>
+      <c r="D52" s="60"/>
+      <c r="E52" s="60"/>
+      <c r="F52" s="60"/>
+      <c r="G52" s="60"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="60" t="s">
+      <c r="B53" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="60"/>
-      <c r="D53" s="60"/>
-      <c r="E53" s="60"/>
-      <c r="F53" s="60"/>
-      <c r="G53" s="60"/>
+      <c r="C53" s="61"/>
+      <c r="D53" s="61"/>
+      <c r="E53" s="61"/>
+      <c r="F53" s="61"/>
+      <c r="G53" s="61"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="52" t="s">
+      <c r="B55" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="52"/>
-      <c r="D55" s="52"/>
-      <c r="E55" s="52"/>
-      <c r="F55" s="52"/>
-      <c r="G55" s="52"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="53"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="53"/>
+      <c r="G55" s="53"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="53" t="s">
+      <c r="B56" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="53"/>
-      <c r="D56" s="53"/>
-      <c r="E56" s="54" t="s">
+      <c r="C56" s="62"/>
+      <c r="D56" s="62"/>
+      <c r="E56" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="54"/>
-      <c r="G56" s="54"/>
+      <c r="F56" s="56"/>
+      <c r="G56" s="56"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="55" t="s">
+      <c r="B57" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="55"/>
-      <c r="D57" s="55"/>
-      <c r="E57" s="54" t="s">
+      <c r="C57" s="63"/>
+      <c r="D57" s="63"/>
+      <c r="E57" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="54"/>
-      <c r="G57" s="54"/>
+      <c r="F57" s="56"/>
+      <c r="G57" s="56"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="56" t="s">
+      <c r="B58" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="56"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="54" t="s">
+      <c r="C58" s="64"/>
+      <c r="D58" s="64"/>
+      <c r="E58" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="54"/>
-      <c r="G58" s="54"/>
+      <c r="F58" s="56"/>
+      <c r="G58" s="56"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="57" t="s">
+      <c r="B59" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="57"/>
-      <c r="D59" s="57"/>
-      <c r="E59" s="54" t="s">
+      <c r="C59" s="65"/>
+      <c r="D59" s="65"/>
+      <c r="E59" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="54"/>
-      <c r="G59" s="54"/>
+      <c r="F59" s="56"/>
+      <c r="G59" s="56"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="52" t="s">
+      <c r="B62" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="52"/>
-      <c r="D62" s="52"/>
-      <c r="E62" s="52"/>
-      <c r="F62" s="52"/>
-      <c r="G62" s="52"/>
+      <c r="C62" s="53"/>
+      <c r="D62" s="53"/>
+      <c r="E62" s="53"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="53"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="50" t="s">
+      <c r="B63" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="50"/>
-      <c r="D63" s="50"/>
-      <c r="E63" s="50"/>
-      <c r="F63" s="50"/>
-      <c r="G63" s="50"/>
+      <c r="C63" s="54"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="54"/>
+      <c r="G63" s="54"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="51" t="s">
+      <c r="B64" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="51"/>
-      <c r="D64" s="51"/>
-      <c r="E64" s="51"/>
-      <c r="F64" s="51"/>
-      <c r="G64" s="51"/>
+      <c r="C64" s="50"/>
+      <c r="D64" s="50"/>
+      <c r="E64" s="50"/>
+      <c r="F64" s="50"/>
+      <c r="G64" s="50"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="51" t="s">
+      <c r="B65" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="51"/>
-      <c r="D65" s="51"/>
-      <c r="E65" s="51"/>
-      <c r="F65" s="51"/>
-      <c r="G65" s="51"/>
+      <c r="C65" s="50"/>
+      <c r="D65" s="50"/>
+      <c r="E65" s="50"/>
+      <c r="F65" s="50"/>
+      <c r="G65" s="50"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="51" t="s">
+      <c r="B66" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="51"/>
-      <c r="D66" s="51"/>
-      <c r="E66" s="51"/>
-      <c r="F66" s="51"/>
-      <c r="G66" s="51"/>
+      <c r="C66" s="50"/>
+      <c r="D66" s="50"/>
+      <c r="E66" s="50"/>
+      <c r="F66" s="50"/>
+      <c r="G66" s="50"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="51" t="s">
+      <c r="B67" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="51"/>
-      <c r="D67" s="51"/>
-      <c r="E67" s="51"/>
-      <c r="F67" s="51"/>
-      <c r="G67" s="51"/>
+      <c r="C67" s="50"/>
+      <c r="D67" s="50"/>
+      <c r="E67" s="50"/>
+      <c r="F67" s="50"/>
+      <c r="G67" s="50"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="52" t="s">
+      <c r="B69" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="52"/>
-      <c r="D69" s="52"/>
-      <c r="E69" s="52"/>
-      <c r="F69" s="52"/>
-      <c r="G69" s="52"/>
+      <c r="C69" s="53"/>
+      <c r="D69" s="53"/>
+      <c r="E69" s="53"/>
+      <c r="F69" s="53"/>
+      <c r="G69" s="53"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="50" t="s">
+      <c r="B70" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="50"/>
-      <c r="D70" s="50"/>
-      <c r="E70" s="50"/>
-      <c r="F70" s="50"/>
-      <c r="G70" s="50"/>
+      <c r="C70" s="54"/>
+      <c r="D70" s="54"/>
+      <c r="E70" s="54"/>
+      <c r="F70" s="54"/>
+      <c r="G70" s="54"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="50" t="s">
+      <c r="B71" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="50"/>
-      <c r="D71" s="50"/>
-      <c r="E71" s="50"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="50"/>
+      <c r="C71" s="54"/>
+      <c r="D71" s="54"/>
+      <c r="E71" s="54"/>
+      <c r="F71" s="54"/>
+      <c r="G71" s="54"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="50" t="s">
+      <c r="B72" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="50"/>
-      <c r="D72" s="50"/>
-      <c r="E72" s="50"/>
-      <c r="F72" s="50"/>
-      <c r="G72" s="50"/>
+      <c r="C72" s="54"/>
+      <c r="D72" s="54"/>
+      <c r="E72" s="54"/>
+      <c r="F72" s="54"/>
+      <c r="G72" s="54"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="50" t="s">
+      <c r="B73" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="50"/>
-      <c r="D73" s="50"/>
-      <c r="E73" s="50"/>
-      <c r="F73" s="50"/>
-      <c r="G73" s="50"/>
+      <c r="C73" s="54"/>
+      <c r="D73" s="54"/>
+      <c r="E73" s="54"/>
+      <c r="F73" s="54"/>
+      <c r="G73" s="54"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="50" t="s">
+      <c r="B74" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="50"/>
-      <c r="D74" s="50"/>
-      <c r="E74" s="50"/>
-      <c r="F74" s="50"/>
-      <c r="G74" s="50"/>
+      <c r="C74" s="54"/>
+      <c r="D74" s="54"/>
+      <c r="E74" s="54"/>
+      <c r="F74" s="54"/>
+      <c r="G74" s="54"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="50" t="s">
+      <c r="B75" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="50"/>
-      <c r="D75" s="50"/>
-      <c r="E75" s="50"/>
-      <c r="F75" s="50"/>
-      <c r="G75" s="50"/>
+      <c r="C75" s="54"/>
+      <c r="D75" s="54"/>
+      <c r="E75" s="54"/>
+      <c r="F75" s="54"/>
+      <c r="G75" s="54"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="50"/>
-      <c r="C76" s="50"/>
-      <c r="D76" s="50"/>
-      <c r="E76" s="50"/>
-      <c r="F76" s="50"/>
-      <c r="G76" s="50"/>
+      <c r="B76" s="54"/>
+      <c r="C76" s="54"/>
+      <c r="D76" s="54"/>
+      <c r="E76" s="54"/>
+      <c r="F76" s="54"/>
+      <c r="G76" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="B17:G17"/>
@@ -2459,52 +2496,18 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B15:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6250,7 +6253,9 @@
       <c r="O70" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="P70" s="9"/>
+      <c r="P70" s="9" t="s">
+        <v>294</v>
+      </c>
       <c r="Q70" s="9"/>
       <c r="R70" s="7" t="s">
         <v>122</v>

--- a/succession.xlsx
+++ b/succession.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oceanglass-my.sharepoint.com/personal/pongkrit_oceanglass_com/Documents/Desktop/Dynamic Org/oceanglass-orgchart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{89C05139-767C-4D44-95FE-72D2855E25B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{205631E2-A73D-4853-93AD-8EA954E0468A}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{89C05139-767C-4D44-95FE-72D2855E25B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{051A3486-607C-4F53-A01D-1D27ACB4B436}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="295">
   <si>
     <t>OCEAN GLASS  |  Succession Planning — Risk Assessment</t>
   </si>
@@ -1419,43 +1419,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1466,6 +1442,30 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1762,727 +1762,693 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
     </row>
     <row r="6" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="55" t="s">
+      <c r="C8" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>3</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>5</v>
       </c>
-      <c r="C13" s="56" t="s">
+      <c r="C13" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="57" t="s">
+      <c r="B15" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
     </row>
     <row r="17" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
     </row>
     <row r="18" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
     </row>
     <row r="19" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="50" t="s">
+      <c r="B19" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
     </row>
     <row r="20" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="50" t="s">
+      <c r="B20" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
     </row>
     <row r="22" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="53" t="s">
+      <c r="B22" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="57" t="s">
+      <c r="B23" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="60" t="s">
+      <c r="B25" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="60"/>
-      <c r="D25" s="60"/>
-      <c r="E25" s="60"/>
-      <c r="F25" s="60"/>
-      <c r="G25" s="60"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="58" t="s">
+      <c r="B26" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="59" t="s">
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="59"/>
+      <c r="G26" s="62"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="58" t="s">
+      <c r="B27" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="59" t="s">
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="59"/>
+      <c r="G27" s="62"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="58" t="s">
+      <c r="B28" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="59" t="s">
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="61"/>
+      <c r="F28" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="59"/>
+      <c r="G28" s="62"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="58" t="s">
+      <c r="B29" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="59" t="s">
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="61"/>
+      <c r="F29" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="G29" s="59"/>
+      <c r="G29" s="62"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="58" t="s">
+      <c r="B30" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="58"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="59" t="s">
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="59"/>
+      <c r="G30" s="62"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="57" t="s">
+      <c r="B32" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="57"/>
-      <c r="D32" s="57"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="57"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="58"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>1</v>
       </c>
-      <c r="C33" s="56" t="s">
+      <c r="C33" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="56"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="56" t="s">
+      <c r="C34" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-      <c r="G34" s="56"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>5</v>
       </c>
-      <c r="C35" s="56" t="s">
+      <c r="C35" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
     </row>
     <row r="37" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="57" t="s">
+      <c r="B37" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="57"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
+      <c r="C37" s="58"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="56" t="s">
+      <c r="C38" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>2</v>
       </c>
-      <c r="C39" s="56" t="s">
+      <c r="C39" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="56"/>
-      <c r="E39" s="56"/>
-      <c r="F39" s="56"/>
-      <c r="G39" s="56"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>3</v>
       </c>
-      <c r="C40" s="56" t="s">
+      <c r="C40" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="54"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>4</v>
       </c>
-      <c r="C41" s="56" t="s">
+      <c r="C41" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="56"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="56"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>5</v>
       </c>
-      <c r="C42" s="56" t="s">
+      <c r="C42" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
     </row>
     <row r="44" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="57" t="s">
+      <c r="B44" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
+      <c r="C44" s="58"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="58"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>1</v>
       </c>
-      <c r="C45" s="56" t="s">
+      <c r="C45" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="56"/>
-      <c r="E45" s="56"/>
-      <c r="F45" s="56"/>
-      <c r="G45" s="56"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>2</v>
       </c>
-      <c r="C46" s="56" t="s">
+      <c r="C46" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="56"/>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="56"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>3</v>
       </c>
-      <c r="C47" s="56" t="s">
+      <c r="C47" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="56"/>
-      <c r="E47" s="56"/>
-      <c r="F47" s="56"/>
-      <c r="G47" s="56"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C48" s="56" t="s">
+      <c r="C48" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="56"/>
-      <c r="E48" s="56"/>
-      <c r="F48" s="56"/>
-      <c r="G48" s="56"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="2">
         <v>5</v>
       </c>
-      <c r="C49" s="56" t="s">
+      <c r="C49" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="56"/>
-      <c r="E49" s="56"/>
-      <c r="F49" s="56"/>
-      <c r="G49" s="56"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
     </row>
     <row r="51" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="53" t="s">
+      <c r="B51" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="53"/>
-      <c r="D51" s="53"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="53"/>
-      <c r="G51" s="53"/>
+      <c r="C51" s="52"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="52"/>
     </row>
     <row r="52" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="60" t="s">
+      <c r="B52" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="60"/>
-      <c r="D52" s="60"/>
-      <c r="E52" s="60"/>
-      <c r="F52" s="60"/>
-      <c r="G52" s="60"/>
+      <c r="C52" s="59"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="59"/>
+      <c r="G52" s="59"/>
     </row>
     <row r="53" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="61" t="s">
+      <c r="B53" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="61"/>
-      <c r="D53" s="61"/>
-      <c r="E53" s="61"/>
-      <c r="F53" s="61"/>
-      <c r="G53" s="61"/>
+      <c r="C53" s="60"/>
+      <c r="D53" s="60"/>
+      <c r="E53" s="60"/>
+      <c r="F53" s="60"/>
+      <c r="G53" s="60"/>
     </row>
     <row r="55" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="53" t="s">
+      <c r="B55" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="53"/>
-      <c r="D55" s="53"/>
-      <c r="E55" s="53"/>
-      <c r="F55" s="53"/>
-      <c r="G55" s="53"/>
+      <c r="C55" s="52"/>
+      <c r="D55" s="52"/>
+      <c r="E55" s="52"/>
+      <c r="F55" s="52"/>
+      <c r="G55" s="52"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="62" t="s">
+      <c r="B56" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="62"/>
-      <c r="D56" s="62"/>
-      <c r="E56" s="56" t="s">
+      <c r="C56" s="53"/>
+      <c r="D56" s="53"/>
+      <c r="E56" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="56"/>
-      <c r="G56" s="56"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B57" s="63" t="s">
+      <c r="B57" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="63"/>
-      <c r="D57" s="63"/>
-      <c r="E57" s="56" t="s">
+      <c r="C57" s="55"/>
+      <c r="D57" s="55"/>
+      <c r="E57" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="56"/>
-      <c r="G57" s="56"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="54"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="64" t="s">
+      <c r="B58" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="64"/>
-      <c r="D58" s="64"/>
-      <c r="E58" s="56" t="s">
+      <c r="C58" s="56"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="F58" s="56"/>
-      <c r="G58" s="56"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="54"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="65" t="s">
+      <c r="B59" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C59" s="65"/>
-      <c r="D59" s="65"/>
-      <c r="E59" s="56" t="s">
+      <c r="C59" s="57"/>
+      <c r="D59" s="57"/>
+      <c r="E59" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="56"/>
-      <c r="G59" s="56"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="54"/>
     </row>
     <row r="62" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="53" t="s">
+      <c r="B62" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="53"/>
-      <c r="D62" s="53"/>
-      <c r="E62" s="53"/>
-      <c r="F62" s="53"/>
-      <c r="G62" s="53"/>
+      <c r="C62" s="52"/>
+      <c r="D62" s="52"/>
+      <c r="E62" s="52"/>
+      <c r="F62" s="52"/>
+      <c r="G62" s="52"/>
     </row>
     <row r="63" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="54" t="s">
+      <c r="B63" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="54"/>
-      <c r="D63" s="54"/>
-      <c r="E63" s="54"/>
-      <c r="F63" s="54"/>
-      <c r="G63" s="54"/>
+      <c r="C63" s="50"/>
+      <c r="D63" s="50"/>
+      <c r="E63" s="50"/>
+      <c r="F63" s="50"/>
+      <c r="G63" s="50"/>
     </row>
     <row r="64" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="50" t="s">
+      <c r="B64" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="50"/>
-      <c r="D64" s="50"/>
-      <c r="E64" s="50"/>
-      <c r="F64" s="50"/>
-      <c r="G64" s="50"/>
+      <c r="C64" s="51"/>
+      <c r="D64" s="51"/>
+      <c r="E64" s="51"/>
+      <c r="F64" s="51"/>
+      <c r="G64" s="51"/>
     </row>
     <row r="65" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="50" t="s">
+      <c r="B65" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="50"/>
-      <c r="D65" s="50"/>
-      <c r="E65" s="50"/>
-      <c r="F65" s="50"/>
-      <c r="G65" s="50"/>
+      <c r="C65" s="51"/>
+      <c r="D65" s="51"/>
+      <c r="E65" s="51"/>
+      <c r="F65" s="51"/>
+      <c r="G65" s="51"/>
     </row>
     <row r="66" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="50" t="s">
+      <c r="B66" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="50"/>
-      <c r="D66" s="50"/>
-      <c r="E66" s="50"/>
-      <c r="F66" s="50"/>
-      <c r="G66" s="50"/>
+      <c r="C66" s="51"/>
+      <c r="D66" s="51"/>
+      <c r="E66" s="51"/>
+      <c r="F66" s="51"/>
+      <c r="G66" s="51"/>
     </row>
     <row r="67" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="50" t="s">
+      <c r="B67" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="50"/>
-      <c r="D67" s="50"/>
-      <c r="E67" s="50"/>
-      <c r="F67" s="50"/>
-      <c r="G67" s="50"/>
+      <c r="C67" s="51"/>
+      <c r="D67" s="51"/>
+      <c r="E67" s="51"/>
+      <c r="F67" s="51"/>
+      <c r="G67" s="51"/>
     </row>
     <row r="69" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="53" t="s">
+      <c r="B69" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="53"/>
-      <c r="D69" s="53"/>
-      <c r="E69" s="53"/>
-      <c r="F69" s="53"/>
-      <c r="G69" s="53"/>
+      <c r="C69" s="52"/>
+      <c r="D69" s="52"/>
+      <c r="E69" s="52"/>
+      <c r="F69" s="52"/>
+      <c r="G69" s="52"/>
     </row>
     <row r="70" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="54" t="s">
+      <c r="B70" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="54"/>
-      <c r="D70" s="54"/>
-      <c r="E70" s="54"/>
-      <c r="F70" s="54"/>
-      <c r="G70" s="54"/>
+      <c r="C70" s="50"/>
+      <c r="D70" s="50"/>
+      <c r="E70" s="50"/>
+      <c r="F70" s="50"/>
+      <c r="G70" s="50"/>
     </row>
     <row r="71" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="54" t="s">
+      <c r="B71" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="54"/>
-      <c r="D71" s="54"/>
-      <c r="E71" s="54"/>
-      <c r="F71" s="54"/>
-      <c r="G71" s="54"/>
+      <c r="C71" s="50"/>
+      <c r="D71" s="50"/>
+      <c r="E71" s="50"/>
+      <c r="F71" s="50"/>
+      <c r="G71" s="50"/>
     </row>
     <row r="72" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="54" t="s">
+      <c r="B72" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="C72" s="54"/>
-      <c r="D72" s="54"/>
-      <c r="E72" s="54"/>
-      <c r="F72" s="54"/>
-      <c r="G72" s="54"/>
+      <c r="C72" s="50"/>
+      <c r="D72" s="50"/>
+      <c r="E72" s="50"/>
+      <c r="F72" s="50"/>
+      <c r="G72" s="50"/>
     </row>
     <row r="73" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="54" t="s">
+      <c r="B73" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="C73" s="54"/>
-      <c r="D73" s="54"/>
-      <c r="E73" s="54"/>
-      <c r="F73" s="54"/>
-      <c r="G73" s="54"/>
+      <c r="C73" s="50"/>
+      <c r="D73" s="50"/>
+      <c r="E73" s="50"/>
+      <c r="F73" s="50"/>
+      <c r="G73" s="50"/>
     </row>
     <row r="74" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="54" t="s">
+      <c r="B74" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="C74" s="54"/>
-      <c r="D74" s="54"/>
-      <c r="E74" s="54"/>
-      <c r="F74" s="54"/>
-      <c r="G74" s="54"/>
+      <c r="C74" s="50"/>
+      <c r="D74" s="50"/>
+      <c r="E74" s="50"/>
+      <c r="F74" s="50"/>
+      <c r="G74" s="50"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="54" t="s">
+      <c r="B75" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="54"/>
-      <c r="D75" s="54"/>
-      <c r="E75" s="54"/>
-      <c r="F75" s="54"/>
-      <c r="G75" s="54"/>
+      <c r="C75" s="50"/>
+      <c r="D75" s="50"/>
+      <c r="E75" s="50"/>
+      <c r="F75" s="50"/>
+      <c r="G75" s="50"/>
     </row>
     <row r="76" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="54"/>
-      <c r="C76" s="54"/>
-      <c r="D76" s="54"/>
-      <c r="E76" s="54"/>
-      <c r="F76" s="54"/>
-      <c r="G76" s="54"/>
+      <c r="B76" s="50"/>
+      <c r="C76" s="50"/>
+      <c r="D76" s="50"/>
+      <c r="E76" s="50"/>
+      <c r="F76" s="50"/>
+      <c r="G76" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="B73:G73"/>
-    <mergeCell ref="B74:G74"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="B76:G76"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G67"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="B71:G71"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="E59:G59"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B15:G15"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="B17:G17"/>
@@ -2496,18 +2462,52 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B73:G73"/>
+    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B76:G76"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="B67:G67"/>
+    <mergeCell ref="B69:G69"/>
+    <mergeCell ref="B70:G70"/>
+    <mergeCell ref="B71:G71"/>
+    <mergeCell ref="B72:G72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3470,9 +3470,7 @@
         <v>Low Impact + Low Risk</v>
       </c>
       <c r="N18" s="9"/>
-      <c r="O18" s="9" t="s">
-        <v>252</v>
-      </c>
+      <c r="O18" s="9"/>
       <c r="P18" s="9"/>
       <c r="Q18" s="9"/>
       <c r="R18" s="7" t="s">
@@ -3580,9 +3578,7 @@
         <v>Low Impact + Low Risk</v>
       </c>
       <c r="N20" s="9"/>
-      <c r="O20" s="9" t="s">
-        <v>252</v>
-      </c>
+      <c r="O20" s="9"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="7" t="s">
@@ -3634,9 +3630,7 @@
         <v>Low Impact + Low Risk</v>
       </c>
       <c r="N21" s="15"/>
-      <c r="O21" s="15" t="s">
-        <v>252</v>
-      </c>
+      <c r="O21" s="15"/>
       <c r="P21" s="15"/>
       <c r="Q21" s="15"/>
       <c r="R21" s="8" t="s">
@@ -3688,9 +3682,7 @@
         <v>Low Impact + Low Risk</v>
       </c>
       <c r="N22" s="9"/>
-      <c r="O22" s="9" t="s">
-        <v>252</v>
-      </c>
+      <c r="O22" s="9"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="7" t="s">
